--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T47"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3738,6 +3738,636 @@
         <v>8152.734606749675</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Cursor CLI</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Composer 2.5 Fast</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>cursor</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.3830075380367747</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.15929203539823</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.6779026217228465</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.3118279569892475</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.5573437730061347</v>
+      </c>
+      <c r="J48" t="n">
+        <v>472.3722024539875</v>
+      </c>
+      <c r="K48" t="n">
+        <v>116.8680981595092</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4259887.413087938</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2153033.982617587</v>
+      </c>
+      <c r="N48" t="n">
+        <v>20146.14621676892</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.9355410155352529</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.6872016098268293</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>8.991024900330346e-05</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.04864903599920222</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1.455177033493845</v>
+      </c>
+      <c r="T48" t="n">
+        <v>9018.073864121761</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Opus 5 (xhigh)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6814975428587521</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.6047197640118001</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.891385767790262</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.5483870967741939</v>
+      </c>
+      <c r="I49" t="n">
+        <v>8.170783921523503</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1421.879982617586</v>
+      </c>
+      <c r="K49" t="n">
+        <v>152.0771983640082</v>
+      </c>
+      <c r="L49" t="n">
+        <v>21565879.13803684</v>
+      </c>
+      <c r="M49" t="n">
+        <v>10747525.6196319</v>
+      </c>
+      <c r="N49" t="n">
+        <v>73273.02862985685</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.9740249879523308</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.08340662896047824</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.160073088125399e-05</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.0287575977377849</v>
+      </c>
+      <c r="S49" t="n">
+        <v>11.98945470477945</v>
+      </c>
+      <c r="T49" t="n">
+        <v>15167.15855183185</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Grok Build</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>xai</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.6408998279698193</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.59882005899705</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.842696629213483</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.481182795698925</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.438982443762777</v>
+      </c>
+      <c r="J50" t="n">
+        <v>929.185109406954</v>
+      </c>
+      <c r="K50" t="n">
+        <v>60.74437627811862</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3598867.582822087</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1837535.160531697</v>
+      </c>
+      <c r="N50" t="n">
+        <v>25699.40797546012</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.9238990226060745</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.2627734486604427</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.0001780837480736792</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.04138463831252327</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.805559523223389</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3873.143840110653</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Kimi Code CLI</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kimi K3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Moonshot AI</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>moonshotai</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6263880112748017</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.63716814159292</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.8764044943820229</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.365591397849462</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3.081635541610432</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1447.373053169734</v>
+      </c>
+      <c r="K51" t="n">
+        <v>122.9498977505112</v>
+      </c>
+      <c r="L51" t="n">
+        <v>10383196.73788345</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5296768.575664621</v>
+      </c>
+      <c r="N51" t="n">
+        <v>54498.01533742331</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.9500000000000018</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.2032647932621707</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>6.032708683920082e-05</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.02596654718296782</v>
+      </c>
+      <c r="S51" t="n">
+        <v>4.919691127770471</v>
+      </c>
+      <c r="T51" t="n">
+        <v>7173.822060003357</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Opencode</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Gemini 3.7 Flash (high)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SST</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5962784529614886</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.572271386430678</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.910112359550562</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.306451612903226</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.26793256886503</v>
+      </c>
+      <c r="J52" t="n">
+        <v>527.0915644171779</v>
+      </c>
+      <c r="K52" t="n">
+        <v>83.44887525562373</v>
+      </c>
+      <c r="L52" t="n">
+        <v>18493123.37423313</v>
+      </c>
+      <c r="M52" t="n">
+        <v>9497213.109406954</v>
+      </c>
+      <c r="N52" t="n">
+        <v>49098.7944785276</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.8634331167917663</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.4702761547447575</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.224325285107308e-05</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.06787569673449199</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.126410173917388</v>
+      </c>
+      <c r="T52" t="n">
+        <v>35085.21976571864</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Fable 5 (max) (with fallback)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6717276042685724</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.660766961651917</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.865168539325843</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.489247311827957</v>
+      </c>
+      <c r="I53" t="n">
+        <v>11.68740762091003</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1407.30630163599</v>
+      </c>
+      <c r="K53" t="n">
+        <v>137.007744236847</v>
+      </c>
+      <c r="L53" t="n">
+        <v>13868659.99897749</v>
+      </c>
+      <c r="M53" t="n">
+        <v>6901095.023517382</v>
+      </c>
+      <c r="N53" t="n">
+        <v>74265.48875255625</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.9619283373252908</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.05747447390016408</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4.843493202069251e-05</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.02863886576025522</v>
+      </c>
+      <c r="S53" t="n">
+        <v>17.39902833624972</v>
+      </c>
+      <c r="T53" t="n">
+        <v>9854.75584302807</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GLM-5.2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>novita</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.4331015719360217</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.286135693215339</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.722846441947565</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.290322580645161</v>
+      </c>
+      <c r="I54" t="n">
+        <v>6.657531358159519</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1507.044470347651</v>
+      </c>
+      <c r="K54" t="n">
+        <v>127.4036879531512</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6619529.539877302</v>
+      </c>
+      <c r="M54" t="n">
+        <v>5529735.922290388</v>
+      </c>
+      <c r="N54" t="n">
+        <v>28567.83231083845</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.3295602231414034</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.06505437956446262</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>6.542784790473939e-05</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.01724308394838987</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15.37175524069208</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4392.391644786887</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Flash (max)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.497576003161905</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.427728613569321</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.677902621722846</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.387096774193548</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.05949917044417183</v>
+      </c>
+      <c r="J55" t="n">
+        <v>868.3750143149272</v>
+      </c>
+      <c r="K55" t="n">
+        <v>105.9314928425358</v>
+      </c>
+      <c r="L55" t="n">
+        <v>20844227.99386501</v>
+      </c>
+      <c r="M55" t="n">
+        <v>10443571.69734151</v>
+      </c>
+      <c r="N55" t="n">
+        <v>58411.25766871166</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.9807621661364226</v>
+      </c>
+      <c r="P55" t="n">
+        <v>8.362738496140571</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2.38711648763559e-05</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.03437980100483081</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.1195780545405674</v>
+      </c>
+      <c r="T55" t="n">
+        <v>24003.71688527831</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Sol (max)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.6505240024334411</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.687315634218289</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.831460674157303</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.432795698924731</v>
+      </c>
+      <c r="I56" t="n">
+        <v>6.420249160020451</v>
+      </c>
+      <c r="J56" t="n">
+        <v>613.70177198364</v>
+      </c>
+      <c r="K56" t="n">
+        <v>112.2689161554192</v>
+      </c>
+      <c r="L56" t="n">
+        <v>13169248.79601226</v>
+      </c>
+      <c r="M56" t="n">
+        <v>6786107.398261759</v>
+      </c>
+      <c r="N56" t="n">
+        <v>35184.01329243354</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.902597320865973</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.1013237938621324</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4.939719892226686e-05</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.06360001213593849</v>
+      </c>
+      <c r="S56" t="n">
+        <v>9.869350148501775</v>
+      </c>
+      <c r="T56" t="n">
+        <v>21458.71072434076</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,10 +509,15 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>score_per_sec</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>cost_per_score</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>token_efficiency</t>
         </is>
@@ -521,857 +526,893 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Opus 4.8 (xhigh)</t>
+          <t>GPT-5.6 Sol (medium)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.590718121759733</v>
+        <v>0.616195748748264</v>
       </c>
       <c r="F2" t="n">
-        <v>0.513274336283186</v>
+        <v>0.640117994100295</v>
       </c>
       <c r="G2" t="n">
-        <v>0.831460674157303</v>
+        <v>0.805243445692884</v>
       </c>
       <c r="H2" t="n">
-        <v>0.42741935483871</v>
+        <v>0.403225806451613</v>
       </c>
       <c r="I2" t="n">
-        <v>5.665366469580767</v>
+        <v>2.813450298568507</v>
       </c>
       <c r="J2" t="n">
-        <v>1065.615385480574</v>
+        <v>297.9599253578734</v>
       </c>
       <c r="K2" t="n">
-        <v>136.1303390500093</v>
+        <v>71.35378323108384</v>
       </c>
       <c r="L2" t="n">
-        <v>13628306.24233129</v>
+        <v>5765545.476482615</v>
       </c>
       <c r="M2" t="n">
-        <v>6783846.309815951</v>
+        <v>2974758.351738241</v>
       </c>
       <c r="N2" t="n">
-        <v>62541.86503067485</v>
+        <v>14440.59713701431</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9687226730983397</v>
+        <v>0.8970664465490255</v>
       </c>
       <c r="P2" t="n">
-        <v>0.104268298428971</v>
+        <v>0.21901781917448</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.3344940395079e-05</v>
+        <v>0.00010687553350532</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03326067527600474</v>
+        <v>0.1240829446459615</v>
       </c>
       <c r="S2" t="n">
-        <v>9.590642746330172</v>
+        <v>0.002068049077432692</v>
       </c>
       <c r="T2" t="n">
-        <v>12789.14177481134</v>
+        <v>4.565838541216378</v>
+      </c>
+      <c r="U2" t="n">
+        <v>19350.07021349512</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qwen3.7 Plus (thinking)</t>
+          <t>Muse Spark 1.1 (xhigh)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3812184526692477</v>
+        <v>0.5492139250715367</v>
       </c>
       <c r="F3" t="n">
-        <v>0.191740412979351</v>
+        <v>0.542772861356932</v>
       </c>
       <c r="G3" t="n">
-        <v>0.715355805243446</v>
+        <v>0.771535580524345</v>
       </c>
       <c r="H3" t="n">
-        <v>0.236559139784946</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>6.300658805725988</v>
+        <v>1.435218435173823</v>
       </c>
       <c r="J3" t="n">
-        <v>643.9465817995908</v>
+        <v>761.3780071574635</v>
       </c>
       <c r="K3" t="n">
-        <v>145.9662576687116</v>
+        <v>55.51329243353784</v>
       </c>
       <c r="L3" t="n">
-        <v>8784635.035787327</v>
+        <v>12289527.21472391</v>
       </c>
       <c r="M3" t="n">
-        <v>4715248.469325154</v>
+        <v>6284599.100204499</v>
       </c>
       <c r="N3" t="n">
-        <v>32611.0408997955</v>
+        <v>34558.96932515338</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8105104948122446</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06050453840204764</v>
+        <v>0.3826692241484622</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.339604902380339e-05</v>
+        <v>4.468958939392973e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03552019345491834</v>
+        <v>0.04328051926180355</v>
       </c>
       <c r="S3" t="n">
-        <v>16.52768579697415</v>
+        <v>0.0007213419876967259</v>
       </c>
       <c r="T3" t="n">
-        <v>13641.86919237547</v>
+        <v>2.613222953126837</v>
+      </c>
+      <c r="U3" t="n">
+        <v>16141.16391489395</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (high)</t>
+          <t>Sonnet 4.6 (medium)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5464647209828707</v>
+        <v>0.3864931360777617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6047197640117991</v>
+        <v>0.289085545722714</v>
       </c>
       <c r="G4" t="n">
-        <v>0.722846441947566</v>
+        <v>0.6741573033707861</v>
       </c>
       <c r="H4" t="n">
-        <v>0.311827956989247</v>
+        <v>0.196236559139785</v>
       </c>
       <c r="I4" t="n">
-        <v>1.561839053374232</v>
+        <v>2.041513021472394</v>
       </c>
       <c r="J4" t="n">
-        <v>358.7396482617588</v>
+        <v>827.6555807770975</v>
       </c>
       <c r="K4" t="n">
-        <v>67.06952965235175</v>
+        <v>67.41768916155419</v>
       </c>
       <c r="L4" t="n">
-        <v>5600275.774028629</v>
+        <v>8444053.035787314</v>
       </c>
       <c r="M4" t="n">
-        <v>2877096.291411043</v>
+        <v>4205086.787321064</v>
       </c>
       <c r="N4" t="n">
-        <v>20902.66564417178</v>
+        <v>40070.1308793456</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9049339862289004</v>
+        <v>0.9487221679807681</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3498854250073181</v>
+        <v>0.1893170075393457</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.757818061694565e-05</v>
+        <v>4.577104554409345e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.09139743381542303</v>
+        <v>0.02801840367329206</v>
       </c>
       <c r="S4" t="n">
-        <v>2.85807846948493</v>
+        <v>0.0004669733945548676</v>
       </c>
       <c r="T4" t="n">
-        <v>15610.97526065008</v>
+        <v>5.282145608561714</v>
+      </c>
+      <c r="U4" t="n">
+        <v>10202.37551936649</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (none)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.1909870904304247</v>
+        <v>0.4708693600598457</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0648967551622419</v>
+        <v>0.371681415929204</v>
       </c>
       <c r="G5" t="n">
-        <v>0.333333333333333</v>
+        <v>0.764044943820225</v>
       </c>
       <c r="H5" t="n">
-        <v>0.174731182795699</v>
+        <v>0.276881720430108</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3280835570961148</v>
+        <v>1.998031234219498</v>
       </c>
       <c r="J5" t="n">
-        <v>131.816209611452</v>
+        <v>386.6294212678936</v>
       </c>
       <c r="K5" t="n">
-        <v>54.28629856850716</v>
+        <v>77.78698023176551</v>
       </c>
       <c r="L5" t="n">
-        <v>3549957.210633946</v>
+        <v>3955817.742194954</v>
       </c>
       <c r="M5" t="n">
-        <v>1835572.532719836</v>
+        <v>2043912.618541241</v>
       </c>
       <c r="N5" t="n">
-        <v>7934.628834355828</v>
+        <v>11032.14533060668</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8748960056789888</v>
+        <v>0.8915632417465629</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5821294188616513</v>
+        <v>0.2356666662639956</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.379982887070306e-05</v>
+        <v>0.0001190321169343297</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08693335561387526</v>
+        <v>0.07307297388528267</v>
       </c>
       <c r="S5" t="n">
-        <v>1.71783106573705</v>
+        <v>0.001217882898088044</v>
       </c>
       <c r="T5" t="n">
-        <v>26931.11280545826</v>
+        <v>4.243281478254512</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10231.5486732035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gemini CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro (high)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3293046837328304</v>
+        <v>0.5531133827505798</v>
       </c>
       <c r="F6" t="n">
-        <v>0.141592920353982</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G6" t="n">
-        <v>0.760299625468165</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08602150537634411</v>
+        <v>0.306451612903226</v>
       </c>
       <c r="I6" t="n">
-        <v>1.040041561860939</v>
+        <v>2.65253587423313</v>
       </c>
       <c r="J6" t="n">
-        <v>663.8363599182014</v>
+        <v>386.3044764826171</v>
       </c>
       <c r="K6" t="n">
-        <v>30.96883483789777</v>
+        <v>78.53885480572598</v>
       </c>
       <c r="L6" t="n">
-        <v>4727804.222392637</v>
+        <v>6885560.579754606</v>
       </c>
       <c r="M6" t="n">
-        <v>2465901.789877301</v>
+        <v>3492715.358895706</v>
       </c>
       <c r="N6" t="n">
-        <v>12977.50562372188</v>
+        <v>13239.49488752556</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8650361016121304</v>
+        <v>0.9409891933709401</v>
       </c>
       <c r="P6" t="n">
-        <v>0.316626465526635</v>
+        <v>0.2085224890353234</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.965277499713736e-05</v>
+        <v>8.032946284386509e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02976378248760652</v>
+        <v>0.08590840900216211</v>
       </c>
       <c r="S6" t="n">
-        <v>3.158295685538259</v>
+        <v>0.001431806816702702</v>
       </c>
       <c r="T6" t="n">
-        <v>7121.942255430543</v>
+        <v>4.795645806005133</v>
+      </c>
+      <c r="U6" t="n">
+        <v>17824.18014528092</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Composer 2.5</t>
+          <t>Opus 5 (low)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.3830075380367747</v>
+        <v>0.5940064571013326</v>
       </c>
       <c r="F7" t="n">
-        <v>0.15929203539823</v>
+        <v>0.569321533923304</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6779026217228465</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3118279569892475</v>
+        <v>0.39247311827957</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08505141359918203</v>
+        <v>2.295157744887527</v>
       </c>
       <c r="J7" t="n">
-        <v>625.1976421267894</v>
+        <v>598.7677147239262</v>
       </c>
       <c r="K7" t="n">
-        <v>116.8680981595092</v>
+        <v>64.39263803680981</v>
       </c>
       <c r="L7" t="n">
-        <v>3705076.4698364</v>
+        <v>5258606.375255628</v>
       </c>
       <c r="M7" t="n">
-        <v>1872461.576687117</v>
+        <v>2618171.039877301</v>
       </c>
       <c r="N7" t="n">
-        <v>18453.85787321063</v>
+        <v>22632.92229038855</v>
       </c>
       <c r="O7" t="n">
-        <v>1.052833075750478</v>
+        <v>0.9637890151908798</v>
       </c>
       <c r="P7" t="n">
-        <v>4.503247175194019</v>
+        <v>0.2588085539760761</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001033737201255894</v>
+        <v>0.0001129589124404576</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03675710004924502</v>
+        <v>0.05952289435396941</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2220619835190183</v>
+        <v>0.0009920482392328236</v>
       </c>
       <c r="T7" t="n">
-        <v>5926.248309626565</v>
+        <v>3.863859925172484</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8782.381290681667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opus 5 (high)</t>
+          <t>GPT-5.6 Terra (low)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.6561729860226817</v>
+        <v>0.3864628427996264</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6076696165191739</v>
+        <v>0.297935103244838</v>
       </c>
       <c r="G8" t="n">
-        <v>0.868913857677903</v>
+        <v>0.632958801498127</v>
       </c>
       <c r="H8" t="n">
-        <v>0.491935483870968</v>
+        <v>0.228494623655914</v>
       </c>
       <c r="I8" t="n">
-        <v>3.918602446063396</v>
+        <v>0.4909580805725972</v>
       </c>
       <c r="J8" t="n">
-        <v>842.8052382413097</v>
+        <v>154.8149498977502</v>
       </c>
       <c r="K8" t="n">
-        <v>94.85071574642126</v>
+        <v>37.80981595092025</v>
       </c>
       <c r="L8" t="n">
-        <v>9911366.349693259</v>
+        <v>1657646.844580775</v>
       </c>
       <c r="M8" t="n">
-        <v>4937399.112474437</v>
+        <v>861642.4202453988</v>
       </c>
       <c r="N8" t="n">
-        <v>37331.49386503067</v>
+        <v>6854.071574642127</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9702723303233403</v>
+        <v>0.8771903855272027</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1674507672197952</v>
+        <v>0.787160570509198</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.620408961504982e-05</v>
+        <v>0.0002331394313952103</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04671349604271027</v>
+        <v>0.1497773347037368</v>
       </c>
       <c r="S8" t="n">
-        <v>5.971904557997063</v>
+        <v>0.002496288911728947</v>
       </c>
       <c r="T8" t="n">
-        <v>11759.97241115327</v>
+        <v>1.270388834838514</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10707.27888796005</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Opus 4.8 (high)</t>
+          <t>GPT-5.6 Terra (none)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5757636668124306</v>
+        <v>0.230919689668531</v>
       </c>
       <c r="F9" t="n">
-        <v>0.51622418879056</v>
+        <v>0.132743362831858</v>
       </c>
       <c r="G9" t="n">
-        <v>0.823970037453184</v>
+        <v>0.374531835205993</v>
       </c>
       <c r="H9" t="n">
-        <v>0.387096774193548</v>
+        <v>0.185483870967742</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7823013803681</v>
+        <v>0.3616287844580779</v>
       </c>
       <c r="J9" t="n">
-        <v>761.0308312883442</v>
+        <v>88.85438650306737</v>
       </c>
       <c r="K9" t="n">
-        <v>104.7627811860941</v>
+        <v>33.82924335378323</v>
       </c>
       <c r="L9" t="n">
-        <v>9188690.866053157</v>
+        <v>1105801.555214723</v>
       </c>
       <c r="M9" t="n">
-        <v>4574601.889570553</v>
+        <v>582183.7985685072</v>
       </c>
       <c r="N9" t="n">
-        <v>40682.70756646217</v>
+        <v>5133.394683026585</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9682475638703767</v>
+        <v>0.8482758058887612</v>
       </c>
       <c r="P9" t="n">
-        <v>0.152225750650361</v>
+        <v>0.6385545055949509</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.266003233818007e-05</v>
+        <v>0.0002088256148488518</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04539345659657893</v>
+        <v>0.1559313155533808</v>
       </c>
       <c r="S9" t="n">
-        <v>6.569190795431485</v>
+        <v>0.002598855259223013</v>
       </c>
       <c r="T9" t="n">
-        <v>12074.00605636132</v>
+        <v>1.566037027752682</v>
+      </c>
+      <c r="U9" t="n">
+        <v>12445.098083892</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>GPT-5.6 Luna (xhigh)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.466554082589455</v>
+        <v>0.529584326329171</v>
       </c>
       <c r="F10" t="n">
-        <v>0.315634218289085</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G10" t="n">
-        <v>0.745318352059925</v>
+        <v>0.707865168539326</v>
       </c>
       <c r="H10" t="n">
-        <v>0.338709677419355</v>
+        <v>0.314516129032258</v>
       </c>
       <c r="I10" t="n">
-        <v>2.72490571101738</v>
+        <v>1.209317104846625</v>
       </c>
       <c r="J10" t="n">
-        <v>826.6777535787322</v>
+        <v>413.8987709611449</v>
       </c>
       <c r="K10" t="n">
-        <v>86.42229038854805</v>
+        <v>96.1922290388548</v>
       </c>
       <c r="L10" t="n">
-        <v>5728865.180470356</v>
+        <v>12806609.00511247</v>
       </c>
       <c r="M10" t="n">
-        <v>2855520.426380368</v>
+        <v>6575104.906952964</v>
       </c>
       <c r="N10" t="n">
-        <v>17872.17893660532</v>
+        <v>30840.24642126789</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9538631453697449</v>
+        <v>0.910023539336985</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1712184317802544</v>
+        <v>0.4379201486580617</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.14391799932617e-05</v>
+        <v>4.135242405837159e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.03386234216922258</v>
+        <v>0.07677012305681181</v>
       </c>
       <c r="S10" t="n">
-        <v>5.840492694638288</v>
+        <v>0.001279502050946864</v>
       </c>
       <c r="T10" t="n">
-        <v>6929.985905233076</v>
+        <v>2.283521329320756</v>
+      </c>
+      <c r="U10" t="n">
+        <v>30941.40380115963</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (high)</t>
+          <t>GPT-5.6 Luna (high)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.3282816619106221</v>
+        <v>0.516945881593198</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08554572271386431</v>
+        <v>0.533923303834808</v>
       </c>
       <c r="G11" t="n">
-        <v>0.700374531835206</v>
+        <v>0.726591760299625</v>
       </c>
       <c r="H11" t="n">
-        <v>0.198924731182796</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2547256318476481</v>
+        <v>0.9174253706543963</v>
       </c>
       <c r="J11" t="n">
-        <v>1072.531835378324</v>
+        <v>342.6686574642128</v>
       </c>
       <c r="K11" t="n">
-        <v>128.1457055214724</v>
+        <v>83.81901840490798</v>
       </c>
       <c r="L11" t="n">
-        <v>9942165.528629858</v>
+        <v>9641370.493865021</v>
       </c>
       <c r="M11" t="n">
-        <v>5181244.880368099</v>
+        <v>4959371.744376278</v>
       </c>
       <c r="N11" t="n">
-        <v>41975.79754601227</v>
+        <v>22230.90593047035</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8541357545221669</v>
+        <v>0.9032288062243126</v>
       </c>
       <c r="P11" t="n">
-        <v>1.288765718351297</v>
+        <v>0.5634745867388236</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.301913058732417e-05</v>
+        <v>5.361746879472582e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01836486252894252</v>
+        <v>0.09051528997463437</v>
       </c>
       <c r="S11" t="n">
-        <v>0.77593622002864</v>
+        <v>0.001508588166243906</v>
       </c>
       <c r="T11" t="n">
-        <v>9269.809250112252</v>
+        <v>1.774702929882995</v>
+      </c>
+      <c r="U11" t="n">
+        <v>28136.13175249894</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gemini 3.6 Flash (high)</t>
+          <t>Qwen3.7 Plus (thinking)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.4724127134829677</v>
+        <v>0.3812184526692477</v>
       </c>
       <c r="F12" t="n">
-        <v>0.412979351032448</v>
+        <v>0.191740412979351</v>
       </c>
       <c r="G12" t="n">
-        <v>0.786516853932584</v>
+        <v>0.715355805243446</v>
       </c>
       <c r="H12" t="n">
-        <v>0.217741935483871</v>
+        <v>0.236559139784946</v>
       </c>
       <c r="I12" t="n">
-        <v>2.083890154754598</v>
+        <v>6.300658805725953</v>
       </c>
       <c r="J12" t="n">
-        <v>626.0057290388545</v>
+        <v>643.9465817995912</v>
       </c>
       <c r="K12" t="n">
-        <v>65.01533742331287</v>
+        <v>145.9662576687116</v>
       </c>
       <c r="L12" t="n">
-        <v>13020159.54294479</v>
+        <v>8784635.035787327</v>
       </c>
       <c r="M12" t="n">
-        <v>6765842.061349694</v>
+        <v>4715248.469325154</v>
       </c>
       <c r="N12" t="n">
-        <v>42763.3517382413</v>
+        <v>32611.0408997955</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8377770485520734</v>
+        <v>0.8105104948122452</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2266975120570113</v>
+        <v>0.06050453840204798</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.628317394458913e-05</v>
+        <v>4.339604902380339e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0452787594332364</v>
+        <v>0.03552019345491832</v>
       </c>
       <c r="S12" t="n">
-        <v>4.411164423138944</v>
+        <v>0.0005920032242486387</v>
       </c>
       <c r="T12" t="n">
-        <v>20798.78655892726</v>
+        <v>16.52768579697406</v>
+      </c>
+      <c r="U12" t="n">
+        <v>13641.86919237546</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Muse Spark 1.2 (xhigh)</t>
+          <t>GPT-5.6 Luna (none)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5888788742875287</v>
+        <v>0.1909870904304247</v>
       </c>
       <c r="F13" t="n">
-        <v>0.528023598820059</v>
+        <v>0.0648967551622419</v>
       </c>
       <c r="G13" t="n">
-        <v>0.797752808988764</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="H13" t="n">
-        <v>0.440860215053763</v>
+        <v>0.174731182795699</v>
       </c>
       <c r="I13" t="n">
-        <v>1.914379785695295</v>
+        <v>0.3280835570961145</v>
       </c>
       <c r="J13" t="n">
-        <v>1064.740692229038</v>
+        <v>131.816209611452</v>
       </c>
       <c r="K13" t="n">
-        <v>65.87116564417177</v>
+        <v>54.28629856850716</v>
       </c>
       <c r="L13" t="n">
-        <v>16350688.07453988</v>
+        <v>3549957.210633946</v>
       </c>
       <c r="M13" t="n">
-        <v>8360784.971370144</v>
+        <v>1835572.532719836</v>
       </c>
       <c r="N13" t="n">
-        <v>47157.38036809816</v>
+        <v>7934.628834355828</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.8748960056789888</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3076081761245981</v>
+        <v>0.5821294188616518</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.601554085081526e-05</v>
+        <v>5.379982887070306e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>0.03318435438330296</v>
+        <v>0.08693335561387526</v>
       </c>
       <c r="S13" t="n">
-        <v>3.250888882728999</v>
+        <v>0.001448889260231254</v>
       </c>
       <c r="T13" t="n">
-        <v>15356.49777816762</v>
+        <v>1.717831065737049</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26931.11280545826</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>Opus 4.8 (high)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1380,472 +1421,493 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5127556084440553</v>
+        <v>0.5757636668124306</v>
       </c>
       <c r="F14" t="n">
-        <v>0.395280235988201</v>
+        <v>0.516224188790561</v>
       </c>
       <c r="G14" t="n">
-        <v>0.782771535580524</v>
+        <v>0.823970037453183</v>
       </c>
       <c r="H14" t="n">
-        <v>0.360215053763441</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="I14" t="n">
-        <v>2.942840985557261</v>
+        <v>3.7823013803681</v>
       </c>
       <c r="J14" t="n">
-        <v>752.2755521472382</v>
+        <v>761.0308312883442</v>
       </c>
       <c r="K14" t="n">
-        <v>54.41308793456033</v>
+        <v>104.7627811860941</v>
       </c>
       <c r="L14" t="n">
-        <v>7582747.093047047</v>
+        <v>9188690.866053157</v>
       </c>
       <c r="M14" t="n">
-        <v>3744700.533231084</v>
+        <v>4574601.889570553</v>
       </c>
       <c r="N14" t="n">
-        <v>25943.59151329243</v>
+        <v>40682.70756646217</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9584168731547833</v>
+        <v>0.9682475638703767</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1742382993034736</v>
+        <v>0.152225750650361</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.762135175446157e-05</v>
+        <v>6.266003233818007e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.04089636625679125</v>
+        <v>0.04539345659657893</v>
       </c>
       <c r="S14" t="n">
-        <v>5.739266303663147</v>
+        <v>0.0007565576099429822</v>
       </c>
       <c r="T14" t="n">
-        <v>10079.74680474918</v>
+        <v>6.569190795431485</v>
+      </c>
+      <c r="U14" t="n">
+        <v>12074.00605636132</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opus 4.8 (low)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.4904379267565557</v>
+        <v>0.466554082589455</v>
       </c>
       <c r="F15" t="n">
-        <v>0.410029498525074</v>
+        <v>0.315634218289085</v>
       </c>
       <c r="G15" t="n">
-        <v>0.779026217228464</v>
+        <v>0.745318352059925</v>
       </c>
       <c r="H15" t="n">
-        <v>0.282258064516129</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="I15" t="n">
-        <v>2.182594679703477</v>
+        <v>2.72490571101738</v>
       </c>
       <c r="J15" t="n">
-        <v>516.6536431492844</v>
+        <v>826.6777535787322</v>
       </c>
       <c r="K15" t="n">
-        <v>68.16359918200409</v>
+        <v>86.42229038854805</v>
       </c>
       <c r="L15" t="n">
-        <v>5214050.029652352</v>
+        <v>5728865.180470356</v>
       </c>
       <c r="M15" t="n">
-        <v>2595804.632924335</v>
+        <v>2855520.426380368</v>
       </c>
       <c r="N15" t="n">
-        <v>23270.04396728017</v>
+        <v>17872.17893660532</v>
       </c>
       <c r="O15" t="n">
-        <v>0.966158217610491</v>
+        <v>0.9538631453697446</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2247040787358583</v>
+        <v>0.1712184317802544</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.406084022351733e-05</v>
+        <v>8.14391799932617e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.05695551748367478</v>
+        <v>0.03386234216922258</v>
       </c>
       <c r="S15" t="n">
-        <v>4.450297500720978</v>
+        <v>0.0005643723694870431</v>
       </c>
       <c r="T15" t="n">
-        <v>10091.9641210113</v>
+        <v>5.840492694638288</v>
+      </c>
+      <c r="U15" t="n">
+        <v>6929.985905233076</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (max)</t>
+          <t>Gemini 3.6 Flash (high)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.6042010361726687</v>
+        <v>0.4724127134829677</v>
       </c>
       <c r="F16" t="n">
-        <v>0.669616519174041</v>
+        <v>0.412979351032448</v>
       </c>
       <c r="G16" t="n">
-        <v>0.782771535580524</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H16" t="n">
-        <v>0.360215053763441</v>
+        <v>0.217741935483871</v>
       </c>
       <c r="I16" t="n">
-        <v>2.695350269529651</v>
+        <v>2.083890154754598</v>
       </c>
       <c r="J16" t="n">
-        <v>491.0206543967283</v>
+        <v>626.0057290388545</v>
       </c>
       <c r="K16" t="n">
-        <v>95.80674846625767</v>
+        <v>65.01533742331287</v>
       </c>
       <c r="L16" t="n">
-        <v>9630511.582822077</v>
+        <v>13020159.54294479</v>
       </c>
       <c r="M16" t="n">
-        <v>4933733.868098159</v>
+        <v>6765842.061349694</v>
       </c>
       <c r="N16" t="n">
-        <v>37445.42126789366</v>
+        <v>42763.3517382413</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9184675548550253</v>
+        <v>0.8377770485520734</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2241641997342721</v>
+        <v>0.2266975120570113</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.273820772412349e-05</v>
+        <v>3.628317394458913e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>0.07383001477789093</v>
+        <v>0.0452787594332364</v>
       </c>
       <c r="S16" t="n">
-        <v>4.461015635794728</v>
+        <v>0.0007546459905539399</v>
       </c>
       <c r="T16" t="n">
-        <v>19613.25149275889</v>
+        <v>4.411164423138944</v>
+      </c>
+      <c r="U16" t="n">
+        <v>20798.78655892726</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (none)</t>
+          <t>Muse Spark 1.2 (xhigh)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4336881923573268</v>
+        <v>0.5888788742875287</v>
       </c>
       <c r="F17" t="n">
-        <v>0.353982300884956</v>
+        <v>0.528023598820059</v>
       </c>
       <c r="G17" t="n">
-        <v>0.602996254681648</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="H17" t="n">
-        <v>0.344086021505376</v>
+        <v>0.440860215053763</v>
       </c>
       <c r="I17" t="n">
-        <v>1.39701781850716</v>
+        <v>1.914379785695295</v>
       </c>
       <c r="J17" t="n">
-        <v>197.8853650306747</v>
+        <v>1064.740692229038</v>
       </c>
       <c r="K17" t="n">
-        <v>55.10736196319019</v>
+        <v>65.87116564417177</v>
       </c>
       <c r="L17" t="n">
-        <v>3404912.347648262</v>
+        <v>16350688.07453988</v>
       </c>
       <c r="M17" t="n">
-        <v>1731981.235173824</v>
+        <v>8360784.971370144</v>
       </c>
       <c r="N17" t="n">
-        <v>7689.902862985686</v>
+        <v>47157.38036809816</v>
       </c>
       <c r="O17" t="n">
-        <v>0.891939654668184</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P17" t="n">
-        <v>0.31043855462113</v>
+        <v>0.3076081761245981</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0001273713235692751</v>
+        <v>3.601554085081526e-05</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1314967963265297</v>
+        <v>0.03318435438330296</v>
       </c>
       <c r="S17" t="n">
-        <v>3.221249374841456</v>
+        <v>0.0005530725730550494</v>
       </c>
       <c r="T17" t="n">
-        <v>17206.48895445329</v>
+        <v>3.250888882728999</v>
+      </c>
+      <c r="U17" t="n">
+        <v>15356.49777816762</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5716614223656344</v>
+        <v>0.5127556084440553</v>
       </c>
       <c r="F18" t="n">
-        <v>0.634218289085546</v>
+        <v>0.395280235988201</v>
       </c>
       <c r="G18" t="n">
-        <v>0.752808988764045</v>
+        <v>0.782771535580524</v>
       </c>
       <c r="H18" t="n">
-        <v>0.327956989247312</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I18" t="n">
-        <v>1.508396035337423</v>
+        <v>2.942840985557261</v>
       </c>
       <c r="J18" t="n">
-        <v>482.0907147239265</v>
+        <v>752.2755521472382</v>
       </c>
       <c r="K18" t="n">
-        <v>114.6288343558282</v>
+        <v>54.41308793456033</v>
       </c>
       <c r="L18" t="n">
-        <v>15963259.28016359</v>
+        <v>7582747.093047047</v>
       </c>
       <c r="M18" t="n">
-        <v>8170928.992842535</v>
+        <v>3744700.533231084</v>
       </c>
       <c r="N18" t="n">
-        <v>41094.49386503067</v>
+        <v>25943.59151329243</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9181831202060821</v>
+        <v>0.9584168731547833</v>
       </c>
       <c r="P18" t="n">
-        <v>0.378986293369404</v>
+        <v>0.1742382993034736</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.58110716823348e-05</v>
+        <v>6.762135175446157e-05</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0711477825528751</v>
+        <v>0.04089636625679125</v>
       </c>
       <c r="S18" t="n">
-        <v>2.638617853720858</v>
+        <v>0.0006816061042798542</v>
       </c>
       <c r="T18" t="n">
-        <v>33112.56324300934</v>
+        <v>5.739266303663147</v>
+      </c>
+      <c r="U18" t="n">
+        <v>10079.74680474918</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (xhigh)</t>
+          <t>Opus 4.8 (low)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.633388342362512</v>
+        <v>0.490437926756556</v>
       </c>
       <c r="F19" t="n">
-        <v>0.669616519174041</v>
+        <v>0.410029498525074</v>
       </c>
       <c r="G19" t="n">
-        <v>0.797752808988764</v>
+        <v>0.779026217228465</v>
       </c>
       <c r="H19" t="n">
-        <v>0.432795698924731</v>
+        <v>0.282258064516129</v>
       </c>
       <c r="I19" t="n">
-        <v>4.799269930470346</v>
+        <v>2.182594679703477</v>
       </c>
       <c r="J19" t="n">
-        <v>440.5130695296522</v>
+        <v>516.6536431492842</v>
       </c>
       <c r="K19" t="n">
-        <v>93.87525562372188</v>
+        <v>68.16359918200409</v>
       </c>
       <c r="L19" t="n">
-        <v>9886595.803681007</v>
+        <v>5214050.029652352</v>
       </c>
       <c r="M19" t="n">
-        <v>5095034.968302658</v>
+        <v>2595804.632924335</v>
       </c>
       <c r="N19" t="n">
-        <v>25684.60429447853</v>
+        <v>23270.04396728017</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9080963249335339</v>
+        <v>0.966158217610491</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1319759779172157</v>
+        <v>0.2247040787358585</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.406536232893095e-05</v>
+        <v>9.406084022351739e-05</v>
       </c>
       <c r="R19" t="n">
-        <v>0.08627054035497261</v>
+        <v>0.05695551748367484</v>
       </c>
       <c r="S19" t="n">
-        <v>7.577136504548331</v>
+        <v>0.0009492586247279141</v>
       </c>
       <c r="T19" t="n">
-        <v>22443.36544710738</v>
+        <v>4.450297500720974</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10091.9641210113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>GPT-5.6 Sol (none)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.6131027159527611</v>
+        <v>0.4336881923573268</v>
       </c>
       <c r="F20" t="n">
-        <v>0.519174041297935</v>
+        <v>0.353982300884956</v>
       </c>
       <c r="G20" t="n">
-        <v>0.838951310861423</v>
+        <v>0.602996254681648</v>
       </c>
       <c r="H20" t="n">
-        <v>0.481182795698925</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I20" t="n">
-        <v>3.230610966002044</v>
+        <v>1.397017818507157</v>
       </c>
       <c r="J20" t="n">
-        <v>1792.147180981595</v>
+        <v>197.8853650306747</v>
       </c>
       <c r="K20" t="n">
-        <v>159.5848670756646</v>
+        <v>55.10736196319019</v>
       </c>
       <c r="L20" t="n">
-        <v>12503741.56441715</v>
+        <v>3404912.347648262</v>
       </c>
       <c r="M20" t="n">
-        <v>6469207.32413088</v>
+        <v>1731981.235173824</v>
       </c>
       <c r="N20" t="n">
-        <v>63117.84253578731</v>
+        <v>7689.902862985686</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8998815214008221</v>
+        <v>0.8919396546681836</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1897791849296822</v>
+        <v>0.3104385546211307</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.903354030424894e-05</v>
+        <v>0.0001273713235692751</v>
       </c>
       <c r="R20" t="n">
-        <v>0.02052630684998603</v>
+        <v>0.1314967963265297</v>
       </c>
       <c r="S20" t="n">
-        <v>5.26928177276409</v>
+        <v>0.002191613272108827</v>
       </c>
       <c r="T20" t="n">
-        <v>6976.961321652501</v>
+        <v>3.221249374841448</v>
+      </c>
+      <c r="U20" t="n">
+        <v>17206.48895445329</v>
       </c>
     </row>
     <row r="21">
@@ -1856,7 +1918,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GPT-5.5 (xhigh)</t>
+          <t>GPT-5.6 Sol (xhigh)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1870,122 +1932,128 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.6103327520587847</v>
+        <v>0.633388342362512</v>
       </c>
       <c r="F21" t="n">
-        <v>0.64306784660767</v>
+        <v>0.669616519174041</v>
       </c>
       <c r="G21" t="n">
-        <v>0.827715355805243</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="H21" t="n">
-        <v>0.360215053763441</v>
+        <v>0.432795698924731</v>
       </c>
       <c r="I21" t="n">
-        <v>4.75237007157464</v>
+        <v>4.799269930470346</v>
       </c>
       <c r="J21" t="n">
-        <v>614.9898987730061</v>
+        <v>440.5130695296522</v>
       </c>
       <c r="K21" t="n">
-        <v>107.1319018404908</v>
+        <v>93.87525562372188</v>
       </c>
       <c r="L21" t="n">
-        <v>12150851.17995912</v>
+        <v>9886595.803681007</v>
       </c>
       <c r="M21" t="n">
-        <v>6164087.486707566</v>
+        <v>5095034.968302658</v>
       </c>
       <c r="N21" t="n">
-        <v>25286.0654396728</v>
+        <v>25684.60429447853</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9341674523911524</v>
+        <v>0.9080963249335335</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1284270254350285</v>
+        <v>0.1319759779172157</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.022962943249859e-05</v>
+        <v>6.406536232893095e-05</v>
       </c>
       <c r="R21" t="n">
-        <v>0.05954563676019593</v>
+        <v>0.08627054035497261</v>
       </c>
       <c r="S21" t="n">
-        <v>7.786523098332615</v>
+        <v>0.001437842339249544</v>
       </c>
       <c r="T21" t="n">
-        <v>19757.80611063991</v>
+        <v>7.577136504548331</v>
+      </c>
+      <c r="U21" t="n">
+        <v>22443.36544710738</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (low)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.250636604330228</v>
+        <v>0.6131027159527611</v>
       </c>
       <c r="F22" t="n">
-        <v>0.103244837758112</v>
+        <v>0.519174041297935</v>
       </c>
       <c r="G22" t="n">
-        <v>0.49812734082397</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H22" t="n">
-        <v>0.150537634408602</v>
+        <v>0.481182795698925</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1920449385685069</v>
+        <v>3.230610966002048</v>
       </c>
       <c r="J22" t="n">
-        <v>100.0260337423312</v>
+        <v>1792.147180981595</v>
       </c>
       <c r="K22" t="n">
-        <v>34.30674846625767</v>
+        <v>159.5848670756646</v>
       </c>
       <c r="L22" t="n">
-        <v>1435665.844580776</v>
+        <v>12503741.56441715</v>
       </c>
       <c r="M22" t="n">
-        <v>762148.6063394684</v>
+        <v>6469207.32413088</v>
       </c>
       <c r="N22" t="n">
-        <v>5609.407975460122</v>
+        <v>63117.84253578731</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8430087375482049</v>
+        <v>0.8998815214008221</v>
       </c>
       <c r="P22" t="n">
-        <v>1.305093517165619</v>
+        <v>0.189779184929682</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.0001745786495348544</v>
+        <v>4.903354030424894e-05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1503428227350525</v>
+        <v>0.02052630684998603</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7662286164533125</v>
+        <v>0.0003421051141664338</v>
       </c>
       <c r="T22" t="n">
-        <v>14352.92184311812</v>
+        <v>5.269281772764097</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6976.961321652501</v>
       </c>
     </row>
     <row r="23">
@@ -1996,7 +2064,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (medium)</t>
+          <t>GPT-5.6 Luna (low)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2010,52 +2078,55 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.4804969202427884</v>
+        <v>0.250636604330228</v>
       </c>
       <c r="F23" t="n">
-        <v>0.457227138643068</v>
+        <v>0.103244837758112</v>
       </c>
       <c r="G23" t="n">
-        <v>0.696629213483146</v>
+        <v>0.49812734082397</v>
       </c>
       <c r="H23" t="n">
-        <v>0.287634408602151</v>
+        <v>0.150537634408602</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8847820614519432</v>
+        <v>0.1920449385685069</v>
       </c>
       <c r="J23" t="n">
-        <v>240.094656441718</v>
+        <v>100.0260337423312</v>
       </c>
       <c r="K23" t="n">
-        <v>50.95501022494887</v>
+        <v>34.30674846625767</v>
       </c>
       <c r="L23" t="n">
-        <v>3164606.548057258</v>
+        <v>1435665.844580776</v>
       </c>
       <c r="M23" t="n">
-        <v>1632285.212678937</v>
+        <v>762148.6063394684</v>
       </c>
       <c r="N23" t="n">
-        <v>11855.54703476483</v>
+        <v>5609.407975460122</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8944384528371319</v>
+        <v>0.8430087375482054</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5430681081556789</v>
+        <v>1.305093517165619</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0001518346476713713</v>
+        <v>0.0001745786495348544</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1200768715215685</v>
+        <v>0.1503428227350525</v>
       </c>
       <c r="S23" t="n">
-        <v>1.841389661779466</v>
+        <v>0.002505713712250875</v>
       </c>
       <c r="T23" t="n">
-        <v>13180.66213949852</v>
+        <v>0.7662286164533125</v>
+      </c>
+      <c r="U23" t="n">
+        <v>14352.92184311812</v>
       </c>
     </row>
     <row r="24">
@@ -2066,7 +2137,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (xhigh)</t>
+          <t>GPT-5.6 Terra (medium)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2080,52 +2151,55 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5602917313962744</v>
+        <v>0.4804969202427884</v>
       </c>
       <c r="F24" t="n">
-        <v>0.584070796460177</v>
+        <v>0.457227138643068</v>
       </c>
       <c r="G24" t="n">
-        <v>0.771535580524345</v>
+        <v>0.696629213483146</v>
       </c>
       <c r="H24" t="n">
-        <v>0.325268817204301</v>
+        <v>0.287634408602151</v>
       </c>
       <c r="I24" t="n">
-        <v>1.879152746625766</v>
+        <v>0.8847820614519432</v>
       </c>
       <c r="J24" t="n">
-        <v>403.2234447852761</v>
+        <v>240.094656441718</v>
       </c>
       <c r="K24" t="n">
-        <v>74.95092024539876</v>
+        <v>50.95501022494887</v>
       </c>
       <c r="L24" t="n">
-        <v>6631652.20858896</v>
+        <v>3164606.548057258</v>
       </c>
       <c r="M24" t="n">
-        <v>3404439.702453988</v>
+        <v>1632285.212678937</v>
       </c>
       <c r="N24" t="n">
-        <v>26011.59611451943</v>
+        <v>11855.54703476483</v>
       </c>
       <c r="O24" t="n">
-        <v>0.910418152728672</v>
+        <v>0.8944384528371322</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2981618883309738</v>
+        <v>0.5430681081556789</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.448750232568207e-05</v>
+        <v>0.0001518346476713713</v>
       </c>
       <c r="R24" t="n">
-        <v>0.08337189793534551</v>
+        <v>0.1200768715215685</v>
       </c>
       <c r="S24" t="n">
-        <v>3.353882703110441</v>
+        <v>0.002001281192026142</v>
       </c>
       <c r="T24" t="n">
-        <v>16446.59380389064</v>
+        <v>1.841389661779466</v>
+      </c>
+      <c r="U24" t="n">
+        <v>13180.66213949852</v>
       </c>
     </row>
     <row r="25">
@@ -2136,7 +2210,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (high)</t>
+          <t>GPT-5.6 Terra (xhigh)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2150,52 +2224,55 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.6411644486641199</v>
+        <v>0.5602917313962741</v>
       </c>
       <c r="F25" t="n">
-        <v>0.648967551622419</v>
+        <v>0.584070796460177</v>
       </c>
       <c r="G25" t="n">
-        <v>0.820224719101124</v>
+        <v>0.771535580524344</v>
       </c>
       <c r="H25" t="n">
-        <v>0.454301075268817</v>
+        <v>0.325268817204301</v>
       </c>
       <c r="I25" t="n">
-        <v>3.85057263394683</v>
+        <v>1.879152746625766</v>
       </c>
       <c r="J25" t="n">
-        <v>369.9402760736197</v>
+        <v>403.2234447852764</v>
       </c>
       <c r="K25" t="n">
-        <v>84.6717791411043</v>
+        <v>74.95092024539876</v>
       </c>
       <c r="L25" t="n">
-        <v>8030278.504089993</v>
+        <v>6631652.208588957</v>
       </c>
       <c r="M25" t="n">
-        <v>4136516.062372188</v>
+        <v>3404439.702453988</v>
       </c>
       <c r="N25" t="n">
-        <v>19997.77709611452</v>
+        <v>26011.59611451943</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9060190184699437</v>
+        <v>0.9104181527286717</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1665114541695913</v>
+        <v>0.2981618883309736</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.984336388053802e-05</v>
+        <v>8.448750232568207e-05</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1039893988514825</v>
+        <v>0.0833718979353454</v>
       </c>
       <c r="S25" t="n">
-        <v>6.005592858383808</v>
+        <v>0.001389531632255757</v>
       </c>
       <c r="T25" t="n">
-        <v>21706.95926737086</v>
+        <v>3.353882703110444</v>
+      </c>
+      <c r="U25" t="n">
+        <v>16446.59380389062</v>
       </c>
     </row>
     <row r="26">
@@ -2206,7 +2283,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (medium)</t>
+          <t>GPT-5.6 Sol (high)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2220,52 +2297,55 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.616195748748264</v>
+        <v>0.6411644486641199</v>
       </c>
       <c r="F26" t="n">
-        <v>0.640117994100295</v>
+        <v>0.648967551622419</v>
       </c>
       <c r="G26" t="n">
-        <v>0.805243445692884</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H26" t="n">
-        <v>0.403225806451613</v>
+        <v>0.454301075268817</v>
       </c>
       <c r="I26" t="n">
-        <v>2.813450298568507</v>
+        <v>3.85057263394683</v>
       </c>
       <c r="J26" t="n">
-        <v>297.9599253578734</v>
+        <v>369.9402760736197</v>
       </c>
       <c r="K26" t="n">
-        <v>71.35378323108384</v>
+        <v>84.6717791411043</v>
       </c>
       <c r="L26" t="n">
-        <v>5765545.476482615</v>
+        <v>8030278.504089991</v>
       </c>
       <c r="M26" t="n">
-        <v>2974758.351738241</v>
+        <v>4136516.062372188</v>
       </c>
       <c r="N26" t="n">
-        <v>14440.59713701431</v>
+        <v>19997.77709611452</v>
       </c>
       <c r="O26" t="n">
-        <v>0.8970664465490255</v>
+        <v>0.906019018469944</v>
       </c>
       <c r="P26" t="n">
-        <v>0.21901781917448</v>
+        <v>0.1665114541695913</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.00010687553350532</v>
+        <v>7.984336388053805e-05</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1240829446459615</v>
+        <v>0.1039893988514825</v>
       </c>
       <c r="S26" t="n">
-        <v>4.565838541216378</v>
+        <v>0.001733156647524709</v>
       </c>
       <c r="T26" t="n">
-        <v>19350.07021349512</v>
+        <v>6.005592858383808</v>
+      </c>
+      <c r="U26" t="n">
+        <v>21706.95926737085</v>
       </c>
     </row>
     <row r="27">
@@ -2302,10 +2382,10 @@
         <v>0.467741935483871</v>
       </c>
       <c r="I27" t="n">
-        <v>7.724725797009217</v>
+        <v>7.724725797009212</v>
       </c>
       <c r="J27" t="n">
-        <v>1386.687798057258</v>
+        <v>1386.687798057262</v>
       </c>
       <c r="K27" t="n">
         <v>165.0175845341703</v>
@@ -2320,22 +2400,25 @@
         <v>89374.98517382414</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9657541826994761</v>
+        <v>0.9657541826994763</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0804436480649737</v>
+        <v>0.08044364806497376</v>
       </c>
       <c r="Q27" t="n">
         <v>3.467550398761645e-05</v>
       </c>
       <c r="R27" t="n">
-        <v>0.02688731195083498</v>
+        <v>0.02688731195083492</v>
       </c>
       <c r="S27" t="n">
-        <v>12.43106229086364</v>
+        <v>0.0004481218658472487</v>
       </c>
       <c r="T27" t="n">
-        <v>12923.29784182189</v>
+        <v>12.43106229086363</v>
+      </c>
+      <c r="U27" t="n">
+        <v>12923.29784182185</v>
       </c>
     </row>
     <row r="28">
@@ -2375,7 +2458,7 @@
         <v>3.303841633946831</v>
       </c>
       <c r="J28" t="n">
-        <v>722.9228824130873</v>
+        <v>722.922882413088</v>
       </c>
       <c r="K28" t="n">
         <v>92.91239658858525</v>
@@ -2399,83 +2482,89 @@
         <v>7.12486434410271e-05</v>
       </c>
       <c r="R28" t="n">
-        <v>0.04628613043791073</v>
+        <v>0.04628613043791069</v>
       </c>
       <c r="S28" t="n">
+        <v>0.0007714355072985115</v>
+      </c>
+      <c r="T28" t="n">
         <v>5.924171543245923</v>
       </c>
-      <c r="T28" t="n">
-        <v>10827.37116162827</v>
+      <c r="U28" t="n">
+        <v>10827.37116162826</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Muse Spark 1.1 (xhigh)</t>
+          <t>GPT-5.6 Sol (low)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.5492139250715363</v>
+        <v>0.5523451808562164</v>
       </c>
       <c r="F29" t="n">
-        <v>0.542772861356932</v>
+        <v>0.533923303834808</v>
       </c>
       <c r="G29" t="n">
-        <v>0.771535580524344</v>
+        <v>0.779026217228465</v>
       </c>
       <c r="H29" t="n">
-        <v>0.333333333333333</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I29" t="n">
-        <v>1.435218435173823</v>
+        <v>1.660386587423313</v>
       </c>
       <c r="J29" t="n">
-        <v>761.3780071574632</v>
+        <v>212.899582822086</v>
       </c>
       <c r="K29" t="n">
-        <v>55.51329243353784</v>
+        <v>53.92126789366053</v>
       </c>
       <c r="L29" t="n">
-        <v>12289527.21472391</v>
+        <v>3200236.065439673</v>
       </c>
       <c r="M29" t="n">
-        <v>6284599.100204499</v>
+        <v>1658130.417177914</v>
       </c>
       <c r="N29" t="n">
-        <v>34558.96932515338</v>
+        <v>8962.606339468302</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.8829664546361218</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3826692241484619</v>
+        <v>0.3326605894313919</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.46895893939297e-05</v>
+        <v>0.0001725951365966907</v>
       </c>
       <c r="R29" t="n">
-        <v>0.04328051926180354</v>
+        <v>0.1556635781624227</v>
       </c>
       <c r="S29" t="n">
-        <v>2.613222953126839</v>
+        <v>0.002594392969373712</v>
       </c>
       <c r="T29" t="n">
-        <v>16141.16391489395</v>
+        <v>3.006066939607346</v>
+      </c>
+      <c r="U29" t="n">
+        <v>15031.6690292156</v>
       </c>
     </row>
     <row r="30">
@@ -2486,7 +2575,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sonnet 4.6 (medium)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2500,192 +2589,201 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.3864931360777617</v>
+        <v>0.423892771774363</v>
       </c>
       <c r="F30" t="n">
-        <v>0.289085545722714</v>
+        <v>0.274336283185841</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6741573033707861</v>
+        <v>0.771535580524345</v>
       </c>
       <c r="H30" t="n">
-        <v>0.196236559139785</v>
+        <v>0.225806451612903</v>
       </c>
       <c r="I30" t="n">
-        <v>2.041513021472394</v>
+        <v>1.800661744734152</v>
       </c>
       <c r="J30" t="n">
-        <v>827.6555807770975</v>
+        <v>399.3926789366056</v>
       </c>
       <c r="K30" t="n">
-        <v>67.41768916155419</v>
+        <v>42.04907975460122</v>
       </c>
       <c r="L30" t="n">
-        <v>8444053.035787314</v>
+        <v>4636274.728016362</v>
       </c>
       <c r="M30" t="n">
-        <v>4205086.787321064</v>
+        <v>2310268.645194274</v>
       </c>
       <c r="N30" t="n">
-        <v>40070.1308793456</v>
+        <v>17168.18507157464</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9487221679807681</v>
+        <v>0.9576237577125696</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1893170075393457</v>
+        <v>0.23540943934306</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.577104554409345e-05</v>
+        <v>9.142960601813308e-05</v>
       </c>
       <c r="R30" t="n">
-        <v>0.02801840367329206</v>
+        <v>0.06368060219375923</v>
       </c>
       <c r="S30" t="n">
-        <v>5.282145608561714</v>
+        <v>0.001061343369895987</v>
       </c>
       <c r="T30" t="n">
-        <v>10202.37551936649</v>
+        <v>4.247918022279086</v>
+      </c>
+      <c r="U30" t="n">
+        <v>11608.31175063242</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (low)</t>
+          <t>GLM-5.1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>friendliai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5523451808562161</v>
+        <v>0.3691032797641257</v>
       </c>
       <c r="F31" t="n">
-        <v>0.533923303834808</v>
+        <v>0.185840707964602</v>
       </c>
       <c r="G31" t="n">
-        <v>0.779026217228464</v>
+        <v>0.6741573033707861</v>
       </c>
       <c r="H31" t="n">
-        <v>0.344086021505376</v>
+        <v>0.247311827956989</v>
       </c>
       <c r="I31" t="n">
-        <v>1.660386587423309</v>
+        <v>4.282000252842536</v>
       </c>
       <c r="J31" t="n">
-        <v>212.899582822086</v>
+        <v>1140.250613496931</v>
       </c>
       <c r="K31" t="n">
-        <v>53.92126789366053</v>
+        <v>174.2367075664622</v>
       </c>
       <c r="L31" t="n">
-        <v>3200236.065439673</v>
+        <v>25761884.92944783</v>
       </c>
       <c r="M31" t="n">
-        <v>1658130.417177914</v>
+        <v>13139446.7402863</v>
       </c>
       <c r="N31" t="n">
-        <v>8962.606339468302</v>
+        <v>49883.45705521473</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8829664546361218</v>
+        <v>0.8889225409991813</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3326605894313923</v>
+        <v>0.08619879915212579</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0001725951365966906</v>
+        <v>1.432749508721747e-05</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1556635781624227</v>
+        <v>0.01942221869798375</v>
       </c>
       <c r="S31" t="n">
-        <v>3.006066939607342</v>
+        <v>0.0003237036449663959</v>
       </c>
       <c r="T31" t="n">
-        <v>15031.6690292156</v>
+        <v>11.60108968844421</v>
+      </c>
+      <c r="U31" t="n">
+        <v>22593.17787204784</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.423892771774363</v>
+        <v>0.5657152973570364</v>
       </c>
       <c r="F32" t="n">
-        <v>0.274336283185841</v>
+        <v>0.56047197640118</v>
       </c>
       <c r="G32" t="n">
-        <v>0.771535580524345</v>
+        <v>0.865168539325843</v>
       </c>
       <c r="H32" t="n">
-        <v>0.225806451612903</v>
+        <v>0.271505376344086</v>
       </c>
       <c r="I32" t="n">
-        <v>1.800661744734152</v>
+        <v>1.396316917192255</v>
       </c>
       <c r="J32" t="n">
-        <v>399.3926789366056</v>
+        <v>384.9621257668713</v>
       </c>
       <c r="K32" t="n">
-        <v>42.04907975460122</v>
+        <v>110.7985685071575</v>
       </c>
       <c r="L32" t="n">
-        <v>4636274.728016358</v>
+        <v>15113684.86595342</v>
       </c>
       <c r="M32" t="n">
-        <v>2310268.645194274</v>
+        <v>7938344.274012004</v>
       </c>
       <c r="N32" t="n">
-        <v>17168.18507157464</v>
+        <v>64430.0844098625</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9576237577125707</v>
+        <v>0.8677594149804605</v>
       </c>
       <c r="P32" t="n">
-        <v>0.23540943934306</v>
+        <v>0.4051482083985556</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.142960601813316e-05</v>
+        <v>3.743066647045306e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.06368060219375923</v>
+        <v>0.08817209686227062</v>
       </c>
       <c r="S32" t="n">
-        <v>4.247918022279086</v>
+        <v>0.00146953494770451</v>
       </c>
       <c r="T32" t="n">
-        <v>11608.31175063241</v>
+        <v>2.468232560999683</v>
+      </c>
+      <c r="U32" t="n">
+        <v>39260.1865335347</v>
       </c>
     </row>
     <row r="33">
@@ -2696,7 +2794,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GLM-5.1</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2706,336 +2804,351 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>friendliai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.3691032797641257</v>
+        <v>0.6702814566291138</v>
       </c>
       <c r="F33" t="n">
-        <v>0.185840707964602</v>
+        <v>0.631268436578171</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6741573033707861</v>
+        <v>0.887640449438202</v>
       </c>
       <c r="H33" t="n">
-        <v>0.247311827956989</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I33" t="n">
-        <v>4.282000252842536</v>
+        <v>8.943547018021487</v>
       </c>
       <c r="J33" t="n">
-        <v>1140.250613496931</v>
+        <v>1451.329194274025</v>
       </c>
       <c r="K33" t="n">
-        <v>174.2367075664622</v>
+        <v>165.7202546941811</v>
       </c>
       <c r="L33" t="n">
-        <v>25761884.92944787</v>
+        <v>23699428.05214722</v>
       </c>
       <c r="M33" t="n">
-        <v>13139446.7402863</v>
+        <v>11810977.87014315</v>
       </c>
       <c r="N33" t="n">
-        <v>49883.45705521473</v>
+        <v>81385.06339468302</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8889225409991813</v>
+        <v>0.974703359327879</v>
       </c>
       <c r="P33" t="n">
-        <v>0.08619879915212579</v>
+        <v>0.07494581906691815</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.432749508721745e-05</v>
+        <v>2.828260054015881e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01942221869798375</v>
+        <v>0.02771038270050364</v>
       </c>
       <c r="S33" t="n">
-        <v>11.60108968844421</v>
+        <v>0.0004618397116750606</v>
       </c>
       <c r="T33" t="n">
-        <v>22593.17787204787</v>
+        <v>13.34297246264148</v>
+      </c>
+      <c r="U33" t="n">
+        <v>16329.46415303249</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>GPT-5.6 Luna (medium)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.4708693600598457</v>
+        <v>0.4196699779001627</v>
       </c>
       <c r="F34" t="n">
-        <v>0.371681415929204</v>
+        <v>0.365781710914454</v>
       </c>
       <c r="G34" t="n">
-        <v>0.764044943820225</v>
+        <v>0.621722846441948</v>
       </c>
       <c r="H34" t="n">
-        <v>0.276881720430108</v>
+        <v>0.271505376344086</v>
       </c>
       <c r="I34" t="n">
-        <v>1.998031234219494</v>
+        <v>0.4430536771983641</v>
       </c>
       <c r="J34" t="n">
-        <v>386.6294212678939</v>
+        <v>191.3819171779141</v>
       </c>
       <c r="K34" t="n">
-        <v>77.78698023176551</v>
+        <v>57.08588957055215</v>
       </c>
       <c r="L34" t="n">
-        <v>3955817.742194958</v>
+        <v>4287327.734151328</v>
       </c>
       <c r="M34" t="n">
-        <v>2043912.618541241</v>
+        <v>2221162.702453987</v>
       </c>
       <c r="N34" t="n">
-        <v>11032.14533060668</v>
+        <v>11663.1390593047</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8915632417465629</v>
+        <v>0.8832984632099323</v>
       </c>
       <c r="P34" t="n">
-        <v>0.235666666263996</v>
+        <v>0.9472215207735832</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0001190321169343296</v>
+        <v>9.788614351947506e-05</v>
       </c>
       <c r="R34" t="n">
-        <v>0.07307297388528261</v>
+        <v>0.1315704171288112</v>
       </c>
       <c r="S34" t="n">
-        <v>4.243281478254504</v>
+        <v>0.002192840285480187</v>
       </c>
       <c r="T34" t="n">
-        <v>10231.5486732035</v>
+        <v>1.05571925686751</v>
+      </c>
+      <c r="U34" t="n">
+        <v>22401.94788186653</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.8</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>Opus 4.8 (xhigh)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.5657152973570364</v>
+        <v>0.590718121759733</v>
       </c>
       <c r="F35" t="n">
-        <v>0.56047197640118</v>
+        <v>0.513274336283186</v>
       </c>
       <c r="G35" t="n">
-        <v>0.865168539325843</v>
+        <v>0.831460674157303</v>
       </c>
       <c r="H35" t="n">
-        <v>0.271505376344086</v>
+        <v>0.42741935483871</v>
       </c>
       <c r="I35" t="n">
-        <v>1.396316917192255</v>
+        <v>5.665366469580767</v>
       </c>
       <c r="J35" t="n">
-        <v>384.9621257668713</v>
+        <v>1065.615385480571</v>
       </c>
       <c r="K35" t="n">
-        <v>110.7985685071575</v>
+        <v>136.1303390500093</v>
       </c>
       <c r="L35" t="n">
-        <v>15113684.86595342</v>
+        <v>13628306.24233129</v>
       </c>
       <c r="M35" t="n">
-        <v>7938344.274012004</v>
+        <v>6783846.309815951</v>
       </c>
       <c r="N35" t="n">
-        <v>64430.0844098625</v>
+        <v>62541.86503067485</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8677594149804605</v>
+        <v>0.9687226730983403</v>
       </c>
       <c r="P35" t="n">
-        <v>0.4051482083985556</v>
+        <v>0.104268298428971</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.743066647045306e-05</v>
+        <v>4.3344940395079e-05</v>
       </c>
       <c r="R35" t="n">
-        <v>0.08817209686227062</v>
+        <v>0.03326067527600483</v>
       </c>
       <c r="S35" t="n">
-        <v>2.468232560999683</v>
+        <v>0.0005543445879334139</v>
       </c>
       <c r="T35" t="n">
-        <v>39260.1865335347</v>
+        <v>9.590642746330172</v>
+      </c>
+      <c r="U35" t="n">
+        <v>12789.14177481137</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>Kimi K2.6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.5531133827505798</v>
+        <v>0.3388925953605663</v>
       </c>
       <c r="F36" t="n">
-        <v>0.566371681415929</v>
+        <v>0.165191740412979</v>
       </c>
       <c r="G36" t="n">
-        <v>0.786516853932584</v>
+        <v>0.6928838951310859</v>
       </c>
       <c r="H36" t="n">
-        <v>0.306451612903226</v>
+        <v>0.158602150537634</v>
       </c>
       <c r="I36" t="n">
-        <v>2.65253587423313</v>
+        <v>1.21710007411043</v>
       </c>
       <c r="J36" t="n">
-        <v>386.3044764826176</v>
+        <v>2443.385067484662</v>
       </c>
       <c r="K36" t="n">
-        <v>78.53885480572598</v>
+        <v>133.7675410760877</v>
       </c>
       <c r="L36" t="n">
-        <v>6885560.579754606</v>
+        <v>11660527.81595092</v>
       </c>
       <c r="M36" t="n">
-        <v>3492715.358895706</v>
+        <v>5891966.377300614</v>
       </c>
       <c r="N36" t="n">
-        <v>13239.49488752556</v>
+        <v>36930.17791411043</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9409891933709401</v>
+        <v>0.9554328157869921</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2085224890353234</v>
+        <v>0.2784426708775452</v>
       </c>
       <c r="Q36" t="n">
-        <v>8.032946284386509e-05</v>
+        <v>2.906322944463811e-05</v>
       </c>
       <c r="R36" t="n">
-        <v>0.085908409002162</v>
+        <v>0.008321879343629747</v>
       </c>
       <c r="S36" t="n">
-        <v>4.795645806005133</v>
+        <v>0.0001386979890604958</v>
       </c>
       <c r="T36" t="n">
-        <v>17824.1801452809</v>
+        <v>3.591403561991346</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4772.284144289555</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Opus 5 (low)</t>
+          <t>GPT-5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.5940064571013324</v>
+        <v>0.6103327520587847</v>
       </c>
       <c r="F37" t="n">
-        <v>0.569321533923304</v>
+        <v>0.64306784660767</v>
       </c>
       <c r="G37" t="n">
-        <v>0.820224719101123</v>
+        <v>0.827715355805243</v>
       </c>
       <c r="H37" t="n">
-        <v>0.39247311827957</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I37" t="n">
-        <v>2.295157744887527</v>
+        <v>4.75237007157464</v>
       </c>
       <c r="J37" t="n">
-        <v>598.7677147239262</v>
+        <v>614.9898987730064</v>
       </c>
       <c r="K37" t="n">
-        <v>64.39263803680981</v>
+        <v>107.1319018404908</v>
       </c>
       <c r="L37" t="n">
-        <v>5258606.375255628</v>
+        <v>12150851.17995912</v>
       </c>
       <c r="M37" t="n">
-        <v>2618171.039877301</v>
+        <v>6164087.486707566</v>
       </c>
       <c r="N37" t="n">
-        <v>22632.92229038855</v>
+        <v>25286.0654396728</v>
       </c>
       <c r="O37" t="n">
-        <v>0.9637890151908798</v>
+        <v>0.9341674523911524</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2588085539760759</v>
+        <v>0.1284270254350285</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.0001129589124404576</v>
+        <v>5.022962943249859e-05</v>
       </c>
       <c r="R37" t="n">
-        <v>0.05952289435396939</v>
+        <v>0.0595456367601959</v>
       </c>
       <c r="S37" t="n">
-        <v>3.863859925172485</v>
+        <v>0.0009924272793365983</v>
       </c>
       <c r="T37" t="n">
-        <v>8782.381290681667</v>
+        <v>7.786523098332615</v>
+      </c>
+      <c r="U37" t="n">
+        <v>19757.8061106399</v>
       </c>
     </row>
     <row r="38">
@@ -3046,7 +3159,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (low)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3060,542 +3173,566 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.3864628427996264</v>
+        <v>0.5716614223656344</v>
       </c>
       <c r="F38" t="n">
-        <v>0.297935103244838</v>
+        <v>0.634218289085546</v>
       </c>
       <c r="G38" t="n">
-        <v>0.632958801498127</v>
+        <v>0.752808988764045</v>
       </c>
       <c r="H38" t="n">
-        <v>0.228494623655914</v>
+        <v>0.327956989247312</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4909580805725969</v>
+        <v>1.508396035337423</v>
       </c>
       <c r="J38" t="n">
-        <v>154.8149498977502</v>
+        <v>482.0907147239265</v>
       </c>
       <c r="K38" t="n">
-        <v>37.80981595092025</v>
+        <v>114.6288343558282</v>
       </c>
       <c r="L38" t="n">
-        <v>1657646.844580775</v>
+        <v>15963259.28016359</v>
       </c>
       <c r="M38" t="n">
-        <v>861642.4202453988</v>
+        <v>8170928.992842535</v>
       </c>
       <c r="N38" t="n">
-        <v>6854.071574642127</v>
+        <v>41094.49386503067</v>
       </c>
       <c r="O38" t="n">
-        <v>0.8771903855272029</v>
+        <v>0.9181831202060821</v>
       </c>
       <c r="P38" t="n">
-        <v>0.7871605705091984</v>
+        <v>0.378986293369404</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0002331394313952103</v>
+        <v>3.58110716823348e-05</v>
       </c>
       <c r="R38" t="n">
-        <v>0.1497773347037368</v>
+        <v>0.0711477825528751</v>
       </c>
       <c r="S38" t="n">
-        <v>1.270388834838513</v>
+        <v>0.001185796375881252</v>
       </c>
       <c r="T38" t="n">
-        <v>10707.27888796005</v>
+        <v>2.638617853720858</v>
+      </c>
+      <c r="U38" t="n">
+        <v>33112.56324300934</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-5.6 Terra (max)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.6702814566291138</v>
+        <v>0.6042010361726687</v>
       </c>
       <c r="F39" t="n">
-        <v>0.631268436578171</v>
+        <v>0.669616519174041</v>
       </c>
       <c r="G39" t="n">
-        <v>0.887640449438202</v>
+        <v>0.782771535580524</v>
       </c>
       <c r="H39" t="n">
-        <v>0.491935483870968</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I39" t="n">
-        <v>8.943547018021487</v>
+        <v>2.695350269529651</v>
       </c>
       <c r="J39" t="n">
-        <v>1451.329194274025</v>
+        <v>491.0206543967279</v>
       </c>
       <c r="K39" t="n">
-        <v>165.7202546941811</v>
+        <v>95.80674846625767</v>
       </c>
       <c r="L39" t="n">
-        <v>23699428.05214722</v>
+        <v>9630511.582822077</v>
       </c>
       <c r="M39" t="n">
-        <v>11810977.87014315</v>
+        <v>4933733.868098159</v>
       </c>
       <c r="N39" t="n">
-        <v>81385.06339468302</v>
+        <v>37445.42126789366</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9747033593278787</v>
+        <v>0.9184675548550253</v>
       </c>
       <c r="P39" t="n">
-        <v>0.07494581906691815</v>
+        <v>0.2241641997342721</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.82826005401588e-05</v>
+        <v>6.273820772412349e-05</v>
       </c>
       <c r="R39" t="n">
-        <v>0.02771038270050364</v>
+        <v>0.07383001477789099</v>
       </c>
       <c r="S39" t="n">
-        <v>13.34297246264148</v>
+        <v>0.001230500246298183</v>
       </c>
       <c r="T39" t="n">
-        <v>16329.4641530325</v>
+        <v>4.461015635794727</v>
+      </c>
+      <c r="U39" t="n">
+        <v>19613.2514927589</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (none)</t>
+          <t>DeepSeek V4 Pro (high)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.2309196896685307</v>
+        <v>0.3282816619106221</v>
       </c>
       <c r="F40" t="n">
-        <v>0.132743362831858</v>
+        <v>0.08554572271386431</v>
       </c>
       <c r="G40" t="n">
-        <v>0.374531835205992</v>
+        <v>0.700374531835206</v>
       </c>
       <c r="H40" t="n">
-        <v>0.185483870967742</v>
+        <v>0.198924731182796</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3616287844580776</v>
+        <v>0.2547256318476481</v>
       </c>
       <c r="J40" t="n">
-        <v>88.85438650306735</v>
+        <v>1072.531835378324</v>
       </c>
       <c r="K40" t="n">
-        <v>33.82924335378323</v>
+        <v>128.1457055214724</v>
       </c>
       <c r="L40" t="n">
-        <v>1105801.555214723</v>
+        <v>9942165.528629862</v>
       </c>
       <c r="M40" t="n">
-        <v>582183.7985685072</v>
+        <v>5181244.880368099</v>
       </c>
       <c r="N40" t="n">
-        <v>5133.394683026585</v>
+        <v>41975.79754601227</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8482758058887612</v>
+        <v>0.8541357545221669</v>
       </c>
       <c r="P40" t="n">
-        <v>0.6385545055949505</v>
+        <v>1.288765718351297</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0002088256148488515</v>
+        <v>3.301913058732416e-05</v>
       </c>
       <c r="R40" t="n">
-        <v>0.1559313155533806</v>
+        <v>0.01836486252894252</v>
       </c>
       <c r="S40" t="n">
-        <v>1.566037027752682</v>
+        <v>0.000306081042149042</v>
       </c>
       <c r="T40" t="n">
-        <v>12445.098083892</v>
+        <v>0.77593622002864</v>
+      </c>
+      <c r="U40" t="n">
+        <v>9269.809250112256</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (high)</t>
+          <t>Opus 5 (high)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.516945881593198</v>
+        <v>0.6561729860226817</v>
       </c>
       <c r="F41" t="n">
-        <v>0.533923303834808</v>
+        <v>0.6076696165191739</v>
       </c>
       <c r="G41" t="n">
-        <v>0.726591760299625</v>
+        <v>0.868913857677903</v>
       </c>
       <c r="H41" t="n">
-        <v>0.290322580645161</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I41" t="n">
-        <v>0.9174253706543963</v>
+        <v>3.918602446063396</v>
       </c>
       <c r="J41" t="n">
-        <v>342.6686574642128</v>
+        <v>842.8052382413097</v>
       </c>
       <c r="K41" t="n">
-        <v>83.81901840490798</v>
+        <v>94.85071574642126</v>
       </c>
       <c r="L41" t="n">
-        <v>9641370.493865021</v>
+        <v>9911366.349693259</v>
       </c>
       <c r="M41" t="n">
-        <v>4959371.744376278</v>
+        <v>4937399.112474437</v>
       </c>
       <c r="N41" t="n">
-        <v>22230.90593047035</v>
+        <v>37331.49386503067</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9032288062243126</v>
+        <v>0.9702723303233399</v>
       </c>
       <c r="P41" t="n">
-        <v>0.5634745867388236</v>
+        <v>0.1674507672197952</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.361746879472582e-05</v>
+        <v>6.620408961504982e-05</v>
       </c>
       <c r="R41" t="n">
-        <v>0.09051528997463437</v>
+        <v>0.04671349604271027</v>
       </c>
       <c r="S41" t="n">
-        <v>1.774702929882995</v>
+        <v>0.0007785582673785045</v>
       </c>
       <c r="T41" t="n">
-        <v>28136.13175249894</v>
+        <v>5.971904557997063</v>
+      </c>
+      <c r="U41" t="n">
+        <v>11759.97241115327</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (medium)</t>
+          <t>Composer 2.5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.4196699779001624</v>
+        <v>0.3830075380367747</v>
       </c>
       <c r="F42" t="n">
-        <v>0.365781710914454</v>
+        <v>0.15929203539823</v>
       </c>
       <c r="G42" t="n">
-        <v>0.621722846441947</v>
+        <v>0.6779026217228465</v>
       </c>
       <c r="H42" t="n">
-        <v>0.271505376344086</v>
+        <v>0.3118279569892475</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4430536771983641</v>
+        <v>0.08505141359918199</v>
       </c>
       <c r="J42" t="n">
-        <v>191.3819171779141</v>
+        <v>625.1976421267898</v>
       </c>
       <c r="K42" t="n">
-        <v>57.08588957055215</v>
+        <v>116.8680981595092</v>
       </c>
       <c r="L42" t="n">
-        <v>4287327.734151328</v>
+        <v>3705076.4698364</v>
       </c>
       <c r="M42" t="n">
-        <v>2221162.702453987</v>
+        <v>1872461.576687117</v>
       </c>
       <c r="N42" t="n">
-        <v>11663.1390593047</v>
+        <v>18453.85787321063</v>
       </c>
       <c r="O42" t="n">
-        <v>0.8832984632099323</v>
+        <v>1.052833075750478</v>
       </c>
       <c r="P42" t="n">
-        <v>0.9472215207735825</v>
+        <v>4.503247175194022</v>
       </c>
       <c r="Q42" t="n">
-        <v>9.788614351947498e-05</v>
+        <v>0.0001033737201255894</v>
       </c>
       <c r="R42" t="n">
-        <v>0.1315704171288111</v>
+        <v>0.03675710004924499</v>
       </c>
       <c r="S42" t="n">
-        <v>1.055719256867511</v>
+        <v>0.0006126183341540833</v>
       </c>
       <c r="T42" t="n">
-        <v>22401.94788186653</v>
+        <v>0.2220619835190182</v>
+      </c>
+      <c r="U42" t="n">
+        <v>5926.248309626562</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Gemini CLI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kimi K2.6</t>
+          <t>Gemini 3.1 Pro (high)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.3388925953605663</v>
+        <v>0.3293046837328304</v>
       </c>
       <c r="F43" t="n">
-        <v>0.165191740412979</v>
+        <v>0.141592920353982</v>
       </c>
       <c r="G43" t="n">
-        <v>0.6928838951310859</v>
+        <v>0.760299625468165</v>
       </c>
       <c r="H43" t="n">
-        <v>0.158602150537634</v>
+        <v>0.08602150537634411</v>
       </c>
       <c r="I43" t="n">
-        <v>1.21710007411043</v>
+        <v>1.040041561860939</v>
       </c>
       <c r="J43" t="n">
-        <v>2443.385067484662</v>
+        <v>663.8363599182014</v>
       </c>
       <c r="K43" t="n">
-        <v>133.7675410760877</v>
+        <v>30.96883483789777</v>
       </c>
       <c r="L43" t="n">
-        <v>11660527.81595092</v>
+        <v>4727804.222392637</v>
       </c>
       <c r="M43" t="n">
-        <v>5891966.377300614</v>
+        <v>2465901.789877301</v>
       </c>
       <c r="N43" t="n">
-        <v>36930.17791411043</v>
+        <v>12977.50562372188</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9554328157869918</v>
+        <v>0.8650361016121304</v>
       </c>
       <c r="P43" t="n">
-        <v>0.2784426708775452</v>
+        <v>0.316626465526635</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.906322944463811e-05</v>
+        <v>6.965277499713736e-05</v>
       </c>
       <c r="R43" t="n">
-        <v>0.008321879343629747</v>
+        <v>0.02976378248760652</v>
       </c>
       <c r="S43" t="n">
-        <v>3.591403561991347</v>
+        <v>0.0004960630414601087</v>
       </c>
       <c r="T43" t="n">
-        <v>4772.284144289555</v>
+        <v>3.158295685538259</v>
+      </c>
+      <c r="U43" t="n">
+        <v>7121.942255430543</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Opus 4.7 (max)</t>
+          <t>GPT-5.6 Terra (high)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.5158095272716129</v>
+        <v>0.5464647209828707</v>
       </c>
       <c r="F44" t="n">
-        <v>0.40117994100295</v>
+        <v>0.6047197640117991</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7752808988764049</v>
+        <v>0.722846441947566</v>
       </c>
       <c r="H44" t="n">
-        <v>0.370967741935484</v>
+        <v>0.311827956989247</v>
       </c>
       <c r="I44" t="n">
-        <v>5.915424259100206</v>
+        <v>1.561839053374232</v>
       </c>
       <c r="J44" t="n">
-        <v>950.3123588957067</v>
+        <v>358.7396482617585</v>
       </c>
       <c r="K44" t="n">
-        <v>107.999326082915</v>
+        <v>67.06952965235175</v>
       </c>
       <c r="L44" t="n">
-        <v>16129723.11451944</v>
+        <v>5600275.774028629</v>
       </c>
       <c r="M44" t="n">
-        <v>8042457.98977505</v>
+        <v>2877096.291411043</v>
       </c>
       <c r="N44" t="n">
-        <v>47224.16462167689</v>
+        <v>20902.66564417178</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9665216325317725</v>
+        <v>0.9049339862289001</v>
       </c>
       <c r="P44" t="n">
-        <v>0.08719738512044993</v>
+        <v>0.3498854250073181</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.197882093879829e-05</v>
+        <v>9.757818061694565e-05</v>
       </c>
       <c r="R44" t="n">
-        <v>0.03256673592276544</v>
+        <v>0.09139743381542312</v>
       </c>
       <c r="S44" t="n">
-        <v>11.46823380791353</v>
+        <v>0.001523290563590385</v>
       </c>
       <c r="T44" t="n">
-        <v>16973.07518263015</v>
+        <v>2.85807846948493</v>
+      </c>
+      <c r="U44" t="n">
+        <v>15610.9752606501</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (xhigh)</t>
+          <t>Opus 4.7 (max)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.529584326329171</v>
+        <v>0.5158095272716129</v>
       </c>
       <c r="F45" t="n">
-        <v>0.566371681415929</v>
+        <v>0.40117994100295</v>
       </c>
       <c r="G45" t="n">
-        <v>0.707865168539326</v>
+        <v>0.7752808988764049</v>
       </c>
       <c r="H45" t="n">
-        <v>0.314516129032258</v>
+        <v>0.370967741935484</v>
       </c>
       <c r="I45" t="n">
-        <v>1.209317104846625</v>
+        <v>5.915424259100206</v>
       </c>
       <c r="J45" t="n">
-        <v>413.8987709611452</v>
+        <v>950.3123588957063</v>
       </c>
       <c r="K45" t="n">
-        <v>96.1922290388548</v>
+        <v>107.999326082915</v>
       </c>
       <c r="L45" t="n">
-        <v>12806609.00511247</v>
+        <v>16129723.11451944</v>
       </c>
       <c r="M45" t="n">
-        <v>6575104.906952964</v>
+        <v>8042457.98977505</v>
       </c>
       <c r="N45" t="n">
-        <v>30840.24642126789</v>
+        <v>47224.16462167689</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9100235393369858</v>
+        <v>0.9665216325317725</v>
       </c>
       <c r="P45" t="n">
-        <v>0.4379201486580617</v>
+        <v>0.08719738512044993</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.135242405837159e-05</v>
+        <v>3.197882093879828e-05</v>
       </c>
       <c r="R45" t="n">
-        <v>0.07677012305681175</v>
+        <v>0.03256673592276545</v>
       </c>
       <c r="S45" t="n">
-        <v>2.283521329320756</v>
+        <v>0.0005427789320460909</v>
       </c>
       <c r="T45" t="n">
-        <v>30941.40380115961</v>
+        <v>11.46823380791353</v>
+      </c>
+      <c r="U45" t="n">
+        <v>16973.07518263016</v>
       </c>
     </row>
     <row r="46">
@@ -3620,10 +3757,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.6406847456950576</v>
+        <v>0.640684745695058</v>
       </c>
       <c r="F46" t="n">
-        <v>0.628318584070796</v>
+        <v>0.628318584070797</v>
       </c>
       <c r="G46" t="n">
         <v>0.850187265917603</v>
@@ -3650,21 +3787,24 @@
         <v>30206.12781186094</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9695331242878965</v>
+        <v>0.9695331242878962</v>
       </c>
       <c r="P46" t="n">
-        <v>0.2019897766252883</v>
+        <v>0.2019897766252884</v>
       </c>
       <c r="Q46" t="n">
-        <v>8.009201951135682e-05</v>
+        <v>8.009201951135686e-05</v>
       </c>
       <c r="R46" t="n">
-        <v>0.05259242308809695</v>
+        <v>0.05259242308809697</v>
       </c>
       <c r="S46" t="n">
-        <v>4.950745610532073</v>
+        <v>0.0008765403848016162</v>
       </c>
       <c r="T46" t="n">
+        <v>4.950745610532072</v>
+      </c>
+      <c r="U46" t="n">
         <v>10944.16634952406</v>
       </c>
     </row>
@@ -3702,10 +3842,10 @@
         <v>0.451612903225806</v>
       </c>
       <c r="I47" t="n">
-        <v>2.072823051942741</v>
+        <v>2.072823051942737</v>
       </c>
       <c r="J47" t="n">
-        <v>2448.643313905929</v>
+        <v>2448.643313905933</v>
       </c>
       <c r="K47" t="n">
         <v>151.4345603271984</v>
@@ -3720,92 +3860,98 @@
         <v>58305.98057259714</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9538301727874866</v>
+        <v>0.9538301727874863</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2973743539749664</v>
+        <v>0.2973743539749669</v>
       </c>
       <c r="Q47" t="n">
         <v>3.087712875993296e-05</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01510398217189026</v>
+        <v>0.01510398217189024</v>
       </c>
       <c r="S47" t="n">
-        <v>3.362764766474052</v>
+        <v>0.0002517330361981707</v>
       </c>
       <c r="T47" t="n">
-        <v>8152.734606749675</v>
+        <v>3.362764766474046</v>
+      </c>
+      <c r="U47" t="n">
+        <v>8152.734606749663</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Composer 2.5 Fast</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.3830075380367747</v>
+        <v>0.5962784529614886</v>
       </c>
       <c r="F48" t="n">
-        <v>0.15929203539823</v>
+        <v>0.572271386430678</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6779026217228465</v>
+        <v>0.910112359550562</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3118279569892475</v>
+        <v>0.306451612903226</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5573437730061347</v>
+        <v>1.26793256886503</v>
       </c>
       <c r="J48" t="n">
-        <v>472.3722024539875</v>
+        <v>527.0915644171779</v>
       </c>
       <c r="K48" t="n">
-        <v>116.8680981595092</v>
+        <v>83.44887525562373</v>
       </c>
       <c r="L48" t="n">
-        <v>4259887.413087938</v>
+        <v>18493123.37423313</v>
       </c>
       <c r="M48" t="n">
-        <v>2153033.982617587</v>
+        <v>9497213.109406954</v>
       </c>
       <c r="N48" t="n">
-        <v>20146.14621676892</v>
+        <v>49098.7944785276</v>
       </c>
       <c r="O48" t="n">
-        <v>0.9355410155352529</v>
+        <v>0.8634331167917663</v>
       </c>
       <c r="P48" t="n">
-        <v>0.6872016098268293</v>
+        <v>0.4702761547447575</v>
       </c>
       <c r="Q48" t="n">
-        <v>8.991024900330346e-05</v>
+        <v>3.224325285107308e-05</v>
       </c>
       <c r="R48" t="n">
-        <v>0.04864903599920222</v>
+        <v>0.06787569673449199</v>
       </c>
       <c r="S48" t="n">
-        <v>1.455177033493845</v>
+        <v>0.001131261612241533</v>
       </c>
       <c r="T48" t="n">
-        <v>9018.073864121761</v>
+        <v>2.126410173917388</v>
+      </c>
+      <c r="U48" t="n">
+        <v>35085.21976571865</v>
       </c>
     </row>
     <row r="49">
@@ -3816,7 +3962,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Opus 5 (xhigh)</t>
+          <t>GLM-5.2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3826,266 +3972,278 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>novita</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6814975428587521</v>
+        <v>0.433101571936022</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6047197640118001</v>
+        <v>0.286135693215339</v>
       </c>
       <c r="G49" t="n">
-        <v>0.891385767790262</v>
+        <v>0.722846441947566</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5483870967741939</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="I49" t="n">
-        <v>8.170783921523503</v>
+        <v>6.657531358159516</v>
       </c>
       <c r="J49" t="n">
-        <v>1421.879982617586</v>
+        <v>1507.044470347651</v>
       </c>
       <c r="K49" t="n">
-        <v>152.0771983640082</v>
+        <v>127.4036879531512</v>
       </c>
       <c r="L49" t="n">
-        <v>21565879.13803684</v>
+        <v>6619529.539877302</v>
       </c>
       <c r="M49" t="n">
-        <v>10747525.6196319</v>
+        <v>5529735.922290388</v>
       </c>
       <c r="N49" t="n">
-        <v>73273.02862985685</v>
+        <v>28567.83231083845</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9740249879523308</v>
+        <v>0.3295602231414034</v>
       </c>
       <c r="P49" t="n">
-        <v>0.08340662896047824</v>
+        <v>0.06505437956446269</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.160073088125399e-05</v>
+        <v>6.542784790473944e-05</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0287575977377849</v>
+        <v>0.01724308394838989</v>
       </c>
       <c r="S49" t="n">
-        <v>11.98945470477945</v>
+        <v>0.0002873847324731648</v>
       </c>
       <c r="T49" t="n">
-        <v>15167.15855183185</v>
+        <v>15.37175524069206</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4392.391644786887</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Grok 4.5 (high)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.6408998279698193</v>
+        <v>0.4975760031619054</v>
       </c>
       <c r="F50" t="n">
-        <v>0.59882005899705</v>
+        <v>0.427728613569322</v>
       </c>
       <c r="G50" t="n">
-        <v>0.842696629213483</v>
+        <v>0.677902621722846</v>
       </c>
       <c r="H50" t="n">
-        <v>0.481182795698925</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="I50" t="n">
-        <v>2.438982443762777</v>
+        <v>0.05949917044417178</v>
       </c>
       <c r="J50" t="n">
-        <v>929.185109406954</v>
+        <v>868.3750143149272</v>
       </c>
       <c r="K50" t="n">
-        <v>60.74437627811862</v>
+        <v>105.9314928425358</v>
       </c>
       <c r="L50" t="n">
-        <v>3598867.582822087</v>
+        <v>20844227.99386505</v>
       </c>
       <c r="M50" t="n">
-        <v>1837535.160531697</v>
+        <v>10443571.69734151</v>
       </c>
       <c r="N50" t="n">
-        <v>25699.40797546012</v>
+        <v>58411.25766871166</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9238990226060745</v>
+        <v>0.9807621661364233</v>
       </c>
       <c r="P50" t="n">
-        <v>0.2627734486604427</v>
+        <v>8.362738496140583</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.0001780837480736792</v>
+        <v>2.387116487635588e-05</v>
       </c>
       <c r="R50" t="n">
-        <v>0.04138463831252327</v>
+        <v>0.03437980100483083</v>
       </c>
       <c r="S50" t="n">
-        <v>3.805559523223389</v>
+        <v>0.0005729966834138472</v>
       </c>
       <c r="T50" t="n">
-        <v>3873.143840110653</v>
+        <v>0.1195780545405672</v>
+      </c>
+      <c r="U50" t="n">
+        <v>24003.71688527835</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Opus 5 (xhigh)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.6263880112748017</v>
+        <v>0.6814975428587517</v>
       </c>
       <c r="F51" t="n">
-        <v>0.63716814159292</v>
+        <v>0.6047197640117991</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8764044943820229</v>
+        <v>0.891385767790262</v>
       </c>
       <c r="H51" t="n">
-        <v>0.365591397849462</v>
+        <v>0.5483870967741939</v>
       </c>
       <c r="I51" t="n">
-        <v>3.081635541610432</v>
+        <v>8.170783921523503</v>
       </c>
       <c r="J51" t="n">
-        <v>1447.373053169734</v>
+        <v>1421.879982617589</v>
       </c>
       <c r="K51" t="n">
-        <v>122.9498977505112</v>
+        <v>152.0771983640082</v>
       </c>
       <c r="L51" t="n">
-        <v>10383196.73788345</v>
+        <v>21565879.13803684</v>
       </c>
       <c r="M51" t="n">
-        <v>5296768.575664621</v>
+        <v>10747525.6196319</v>
       </c>
       <c r="N51" t="n">
-        <v>54498.01533742331</v>
+        <v>73273.02862985685</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.9740249879523308</v>
       </c>
       <c r="P51" t="n">
-        <v>0.2032647932621707</v>
+        <v>0.08340662896047819</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.032708683920082e-05</v>
+        <v>3.160073088125398e-05</v>
       </c>
       <c r="R51" t="n">
-        <v>0.02596654718296782</v>
+        <v>0.02875759773778482</v>
       </c>
       <c r="S51" t="n">
-        <v>4.919691127770471</v>
+        <v>0.000479293295629747</v>
       </c>
       <c r="T51" t="n">
-        <v>7173.822060003357</v>
+        <v>11.98945470477946</v>
+      </c>
+      <c r="U51" t="n">
+        <v>15167.15855183182</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>Grok 4.5 (high)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.5962784529614886</v>
+        <v>0.6408998279698193</v>
       </c>
       <c r="F52" t="n">
-        <v>0.572271386430678</v>
+        <v>0.59882005899705</v>
       </c>
       <c r="G52" t="n">
-        <v>0.910112359550562</v>
+        <v>0.842696629213483</v>
       </c>
       <c r="H52" t="n">
-        <v>0.306451612903226</v>
+        <v>0.481182795698925</v>
       </c>
       <c r="I52" t="n">
-        <v>1.26793256886503</v>
+        <v>2.438982443762777</v>
       </c>
       <c r="J52" t="n">
-        <v>527.0915644171779</v>
+        <v>929.185109406954</v>
       </c>
       <c r="K52" t="n">
-        <v>83.44887525562373</v>
+        <v>60.74437627811862</v>
       </c>
       <c r="L52" t="n">
-        <v>18493123.37423313</v>
+        <v>3598867.582822087</v>
       </c>
       <c r="M52" t="n">
-        <v>9497213.109406954</v>
+        <v>1837535.160531697</v>
       </c>
       <c r="N52" t="n">
-        <v>49098.7944785276</v>
+        <v>25699.40797546012</v>
       </c>
       <c r="O52" t="n">
-        <v>0.8634331167917663</v>
+        <v>0.9238990226060743</v>
       </c>
       <c r="P52" t="n">
-        <v>0.4702761547447575</v>
+        <v>0.2627734486604427</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.224325285107308e-05</v>
+        <v>0.0001780837480736792</v>
       </c>
       <c r="R52" t="n">
-        <v>0.06787569673449199</v>
+        <v>0.04138463831252327</v>
       </c>
       <c r="S52" t="n">
-        <v>2.126410173917388</v>
+        <v>0.0006897439718753878</v>
       </c>
       <c r="T52" t="n">
-        <v>35085.21976571864</v>
+        <v>3.805559523223389</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3873.143840110653</v>
       </c>
     </row>
     <row r="53">
@@ -4152,220 +4310,232 @@
         <v>0.02863886576025522</v>
       </c>
       <c r="S53" t="n">
+        <v>0.0004773144293375869</v>
+      </c>
+      <c r="T53" t="n">
         <v>17.39902833624972</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>9854.75584302807</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GLM-5.2</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>novita</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.4331015719360217</v>
+        <v>0.6505240024334411</v>
       </c>
       <c r="F54" t="n">
-        <v>0.286135693215339</v>
+        <v>0.687315634218289</v>
       </c>
       <c r="G54" t="n">
-        <v>0.722846441947565</v>
+        <v>0.831460674157303</v>
       </c>
       <c r="H54" t="n">
-        <v>0.290322580645161</v>
+        <v>0.432795698924731</v>
       </c>
       <c r="I54" t="n">
-        <v>6.657531358159519</v>
+        <v>6.420249160020451</v>
       </c>
       <c r="J54" t="n">
-        <v>1507.044470347651</v>
+        <v>613.70177198364</v>
       </c>
       <c r="K54" t="n">
-        <v>127.4036879531512</v>
+        <v>112.2689161554192</v>
       </c>
       <c r="L54" t="n">
-        <v>6619529.539877302</v>
+        <v>13169248.79601226</v>
       </c>
       <c r="M54" t="n">
-        <v>5529735.922290388</v>
+        <v>6786107.398261759</v>
       </c>
       <c r="N54" t="n">
-        <v>28567.83231083845</v>
+        <v>35184.01329243354</v>
       </c>
       <c r="O54" t="n">
-        <v>0.3295602231414034</v>
+        <v>0.9025973208659727</v>
       </c>
       <c r="P54" t="n">
-        <v>0.06505437956446262</v>
+        <v>0.1013237938621324</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.542784790473939e-05</v>
+        <v>4.939719892226686e-05</v>
       </c>
       <c r="R54" t="n">
-        <v>0.01724308394838987</v>
+        <v>0.06360001213593849</v>
       </c>
       <c r="S54" t="n">
-        <v>15.37175524069208</v>
+        <v>0.001060000202265642</v>
       </c>
       <c r="T54" t="n">
-        <v>4392.391644786887</v>
+        <v>9.869350148501775</v>
+      </c>
+      <c r="U54" t="n">
+        <v>21458.71072434076</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash (max)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.497576003161905</v>
+        <v>0.6263880112748017</v>
       </c>
       <c r="F55" t="n">
-        <v>0.427728613569321</v>
+        <v>0.63716814159292</v>
       </c>
       <c r="G55" t="n">
-        <v>0.677902621722846</v>
+        <v>0.8764044943820229</v>
       </c>
       <c r="H55" t="n">
-        <v>0.387096774193548</v>
+        <v>0.365591397849462</v>
       </c>
       <c r="I55" t="n">
-        <v>0.05949917044417183</v>
+        <v>3.081635541610432</v>
       </c>
       <c r="J55" t="n">
-        <v>868.3750143149272</v>
+        <v>1447.373053169734</v>
       </c>
       <c r="K55" t="n">
-        <v>105.9314928425358</v>
+        <v>122.9498977505112</v>
       </c>
       <c r="L55" t="n">
-        <v>20844227.99386501</v>
+        <v>10383196.73788345</v>
       </c>
       <c r="M55" t="n">
-        <v>10443571.69734151</v>
+        <v>5296768.575664621</v>
       </c>
       <c r="N55" t="n">
-        <v>58411.25766871166</v>
+        <v>54498.01533742331</v>
       </c>
       <c r="O55" t="n">
-        <v>0.9807621661364226</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P55" t="n">
-        <v>8.362738496140571</v>
+        <v>0.2032647932621707</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.38711648763559e-05</v>
+        <v>6.032708683920082e-05</v>
       </c>
       <c r="R55" t="n">
-        <v>0.03437980100483081</v>
+        <v>0.02596654718296782</v>
       </c>
       <c r="S55" t="n">
-        <v>0.1195780545405674</v>
+        <v>0.0004327757863827971</v>
       </c>
       <c r="T55" t="n">
-        <v>24003.71688527831</v>
+        <v>4.919691127770471</v>
+      </c>
+      <c r="U55" t="n">
+        <v>7173.822060003357</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Composer 2.5 Fast</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.6505240024334411</v>
+        <v>0.3830075380367747</v>
       </c>
       <c r="F56" t="n">
-        <v>0.687315634218289</v>
+        <v>0.15929203539823</v>
       </c>
       <c r="G56" t="n">
-        <v>0.831460674157303</v>
+        <v>0.6779026217228465</v>
       </c>
       <c r="H56" t="n">
-        <v>0.432795698924731</v>
+        <v>0.3118279569892475</v>
       </c>
       <c r="I56" t="n">
-        <v>6.420249160020451</v>
+        <v>0.5573437730061347</v>
       </c>
       <c r="J56" t="n">
-        <v>613.70177198364</v>
+        <v>472.3722024539878</v>
       </c>
       <c r="K56" t="n">
-        <v>112.2689161554192</v>
+        <v>116.8680981595092</v>
       </c>
       <c r="L56" t="n">
-        <v>13169248.79601226</v>
+        <v>4259887.413087931</v>
       </c>
       <c r="M56" t="n">
-        <v>6786107.398261759</v>
+        <v>2153033.982617587</v>
       </c>
       <c r="N56" t="n">
-        <v>35184.01329243354</v>
+        <v>20146.14621676892</v>
       </c>
       <c r="O56" t="n">
-        <v>0.902597320865973</v>
+        <v>0.9355410155352526</v>
       </c>
       <c r="P56" t="n">
-        <v>0.1013237938621324</v>
+        <v>0.6872016098268293</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.939719892226686e-05</v>
+        <v>8.991024900330358e-05</v>
       </c>
       <c r="R56" t="n">
-        <v>0.06360001213593849</v>
+        <v>0.0486490359992022</v>
       </c>
       <c r="S56" t="n">
-        <v>9.869350148501775</v>
+        <v>0.00081081726665337</v>
       </c>
       <c r="T56" t="n">
-        <v>21458.71072434076</v>
+        <v>1.455177033493845</v>
+      </c>
+      <c r="U56" t="n">
+        <v>9018.073864121743</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -526,956 +526,956 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (medium)</t>
+          <t>Opus 4.7 (max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.616195748748264</v>
+        <v>0.5158095272716127</v>
       </c>
       <c r="F2" t="n">
-        <v>0.640117994100295</v>
+        <v>0.40117994100295</v>
       </c>
       <c r="G2" t="n">
-        <v>0.805243445692884</v>
+        <v>0.7752808988764039</v>
       </c>
       <c r="H2" t="n">
-        <v>0.403225806451613</v>
+        <v>0.370967741935484</v>
       </c>
       <c r="I2" t="n">
-        <v>2.813450298568507</v>
+        <v>5.915424259100202</v>
       </c>
       <c r="J2" t="n">
-        <v>297.9599253578734</v>
+        <v>950.3123588957067</v>
       </c>
       <c r="K2" t="n">
-        <v>71.35378323108384</v>
+        <v>107.999326082915</v>
       </c>
       <c r="L2" t="n">
-        <v>5765545.476482615</v>
+        <v>16129723.11451944</v>
       </c>
       <c r="M2" t="n">
-        <v>2974758.351738241</v>
+        <v>8042457.98977505</v>
       </c>
       <c r="N2" t="n">
-        <v>14440.59713701431</v>
+        <v>47224.16462167689</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8970664465490255</v>
+        <v>0.9665216325317721</v>
       </c>
       <c r="P2" t="n">
-        <v>0.21901781917448</v>
+        <v>0.08719738512044996</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00010687553350532</v>
+        <v>3.197882093879827e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1240829446459615</v>
+        <v>0.03256673592276543</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002068049077432692</v>
+        <v>0.0005427789320460904</v>
       </c>
       <c r="T2" t="n">
-        <v>4.565838541216378</v>
+        <v>11.46823380791353</v>
       </c>
       <c r="U2" t="n">
-        <v>19350.07021349512</v>
+        <v>16973.07518263015</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Muse Spark 1.1 (xhigh)</t>
+          <t>Qwen3.7 Plus (thinking)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.5492139250715367</v>
+        <v>0.3812184526692477</v>
       </c>
       <c r="F3" t="n">
-        <v>0.542772861356932</v>
+        <v>0.191740412979351</v>
       </c>
       <c r="G3" t="n">
-        <v>0.771535580524345</v>
+        <v>0.715355805243446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.333333333333333</v>
+        <v>0.236559139784946</v>
       </c>
       <c r="I3" t="n">
-        <v>1.435218435173823</v>
+        <v>6.300658805725988</v>
       </c>
       <c r="J3" t="n">
-        <v>761.3780071574635</v>
+        <v>643.9465817995912</v>
       </c>
       <c r="K3" t="n">
-        <v>55.51329243353784</v>
+        <v>145.9662576687116</v>
       </c>
       <c r="L3" t="n">
-        <v>12289527.21472391</v>
+        <v>8784635.035787323</v>
       </c>
       <c r="M3" t="n">
-        <v>6284599.100204499</v>
+        <v>4715248.469325154</v>
       </c>
       <c r="N3" t="n">
-        <v>34558.96932515338</v>
+        <v>32611.0408997955</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.8105104948122446</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3826692241484622</v>
+        <v>0.06050453840204764</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.468958939392973e-05</v>
+        <v>4.339604902380341e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04328051926180355</v>
+        <v>0.03552019345491832</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007213419876967259</v>
+        <v>0.0005920032242486387</v>
       </c>
       <c r="T3" t="n">
-        <v>2.613222953126837</v>
+        <v>16.52768579697415</v>
       </c>
       <c r="U3" t="n">
-        <v>16141.16391489395</v>
+        <v>13641.86919237545</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sonnet 4.6 (medium)</t>
+          <t>GPT-5.6 Terra (high)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.3864931360777617</v>
+        <v>0.5464647209828707</v>
       </c>
       <c r="F4" t="n">
-        <v>0.289085545722714</v>
+        <v>0.6047197640117991</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6741573033707861</v>
+        <v>0.722846441947566</v>
       </c>
       <c r="H4" t="n">
-        <v>0.196236559139785</v>
+        <v>0.311827956989247</v>
       </c>
       <c r="I4" t="n">
-        <v>2.041513021472394</v>
+        <v>1.561839053374232</v>
       </c>
       <c r="J4" t="n">
-        <v>827.6555807770975</v>
+        <v>358.7396482617588</v>
       </c>
       <c r="K4" t="n">
-        <v>67.41768916155419</v>
+        <v>67.06952965235175</v>
       </c>
       <c r="L4" t="n">
-        <v>8444053.035787314</v>
+        <v>5600275.774028629</v>
       </c>
       <c r="M4" t="n">
-        <v>4205086.787321064</v>
+        <v>2877096.291411043</v>
       </c>
       <c r="N4" t="n">
-        <v>40070.1308793456</v>
+        <v>20902.66564417178</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9487221679807681</v>
+        <v>0.9049339862289001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1893170075393457</v>
+        <v>0.3498854250073181</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.577104554409345e-05</v>
+        <v>9.757818061694565e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02801840367329206</v>
+        <v>0.09139743381542303</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004669733945548676</v>
+        <v>0.001523290563590384</v>
       </c>
       <c r="T4" t="n">
-        <v>5.282145608561714</v>
+        <v>2.85807846948493</v>
       </c>
       <c r="U4" t="n">
-        <v>10202.37551936649</v>
+        <v>15610.97526065008</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Gemini CLI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>Gemini 3.1 Pro (high)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4708693600598457</v>
+        <v>0.3293046837328304</v>
       </c>
       <c r="F5" t="n">
-        <v>0.371681415929204</v>
+        <v>0.141592920353982</v>
       </c>
       <c r="G5" t="n">
-        <v>0.764044943820225</v>
+        <v>0.760299625468165</v>
       </c>
       <c r="H5" t="n">
-        <v>0.276881720430108</v>
+        <v>0.08602150537634411</v>
       </c>
       <c r="I5" t="n">
-        <v>1.998031234219498</v>
+        <v>1.040041561860939</v>
       </c>
       <c r="J5" t="n">
-        <v>386.6294212678936</v>
+        <v>663.8363599182018</v>
       </c>
       <c r="K5" t="n">
-        <v>77.78698023176551</v>
+        <v>30.96883483789777</v>
       </c>
       <c r="L5" t="n">
-        <v>3955817.742194954</v>
+        <v>4727804.222392637</v>
       </c>
       <c r="M5" t="n">
-        <v>2043912.618541241</v>
+        <v>2465901.789877301</v>
       </c>
       <c r="N5" t="n">
-        <v>11032.14533060668</v>
+        <v>12977.50562372188</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8915632417465629</v>
+        <v>0.8650361016121304</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2356666662639956</v>
+        <v>0.316626465526635</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0001190321169343297</v>
+        <v>6.965277499713736e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.07307297388528267</v>
+        <v>0.02976378248760651</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001217882898088044</v>
+        <v>0.0004960630414601085</v>
       </c>
       <c r="T5" t="n">
-        <v>4.243281478254512</v>
+        <v>3.158295685538259</v>
       </c>
       <c r="U5" t="n">
-        <v>10231.5486732035</v>
+        <v>7121.942255430539</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>Composer 2.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5531133827505798</v>
+        <v>0.3830075380367747</v>
       </c>
       <c r="F6" t="n">
-        <v>0.566371681415929</v>
+        <v>0.15929203539823</v>
       </c>
       <c r="G6" t="n">
-        <v>0.786516853932584</v>
+        <v>0.6779026217228465</v>
       </c>
       <c r="H6" t="n">
-        <v>0.306451612903226</v>
+        <v>0.3118279569892475</v>
       </c>
       <c r="I6" t="n">
-        <v>2.65253587423313</v>
+        <v>0.08505141359918204</v>
       </c>
       <c r="J6" t="n">
-        <v>386.3044764826171</v>
+        <v>625.1976421267894</v>
       </c>
       <c r="K6" t="n">
-        <v>78.53885480572598</v>
+        <v>116.8680981595092</v>
       </c>
       <c r="L6" t="n">
-        <v>6885560.579754606</v>
+        <v>3705076.4698364</v>
       </c>
       <c r="M6" t="n">
-        <v>3492715.358895706</v>
+        <v>1872461.576687117</v>
       </c>
       <c r="N6" t="n">
-        <v>13239.49488752556</v>
+        <v>18453.85787321063</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9409891933709401</v>
+        <v>1.052833075750478</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2085224890353234</v>
+        <v>4.503247175194018</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.032946284386509e-05</v>
+        <v>0.0001033737201255894</v>
       </c>
       <c r="R6" t="n">
-        <v>0.08590840900216211</v>
+        <v>0.03675710004924502</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001431806816702702</v>
+        <v>0.0006126183341540836</v>
       </c>
       <c r="T6" t="n">
-        <v>4.795645806005133</v>
+        <v>0.2220619835190183</v>
       </c>
       <c r="U6" t="n">
-        <v>17824.18014528092</v>
+        <v>5926.248309626565</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Opus 5 (low)</t>
+          <t>GPT-5.6 Luna (none)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5940064571013326</v>
+        <v>0.1909870904304247</v>
       </c>
       <c r="F7" t="n">
-        <v>0.569321533923304</v>
+        <v>0.0648967551622419</v>
       </c>
       <c r="G7" t="n">
-        <v>0.820224719101124</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>0.39247311827957</v>
+        <v>0.174731182795699</v>
       </c>
       <c r="I7" t="n">
-        <v>2.295157744887527</v>
+        <v>0.3280835570961145</v>
       </c>
       <c r="J7" t="n">
-        <v>598.7677147239262</v>
+        <v>131.816209611452</v>
       </c>
       <c r="K7" t="n">
-        <v>64.39263803680981</v>
+        <v>54.28629856850716</v>
       </c>
       <c r="L7" t="n">
-        <v>5258606.375255628</v>
+        <v>3549957.210633946</v>
       </c>
       <c r="M7" t="n">
-        <v>2618171.039877301</v>
+        <v>1835572.532719836</v>
       </c>
       <c r="N7" t="n">
-        <v>22632.92229038855</v>
+        <v>7934.628834355828</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9637890151908798</v>
+        <v>0.8748960056789892</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2588085539760761</v>
+        <v>0.5821294188616518</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001129589124404576</v>
+        <v>5.379982887070306e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.05952289435396941</v>
+        <v>0.08693335561387526</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0009920482392328236</v>
+        <v>0.001448889260231254</v>
       </c>
       <c r="T7" t="n">
-        <v>3.863859925172484</v>
+        <v>1.717831065737049</v>
       </c>
       <c r="U7" t="n">
-        <v>8782.381290681667</v>
+        <v>26931.11280545826</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (low)</t>
+          <t>Opus 4.8 (high)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3864628427996264</v>
+        <v>0.5757636668124306</v>
       </c>
       <c r="F8" t="n">
-        <v>0.297935103244838</v>
+        <v>0.516224188790561</v>
       </c>
       <c r="G8" t="n">
-        <v>0.632958801498127</v>
+        <v>0.823970037453183</v>
       </c>
       <c r="H8" t="n">
-        <v>0.228494623655914</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4909580805725972</v>
+        <v>3.7823013803681</v>
       </c>
       <c r="J8" t="n">
-        <v>154.8149498977502</v>
+        <v>761.0308312883442</v>
       </c>
       <c r="K8" t="n">
-        <v>37.80981595092025</v>
+        <v>104.7627811860941</v>
       </c>
       <c r="L8" t="n">
-        <v>1657646.844580775</v>
+        <v>9188690.866053157</v>
       </c>
       <c r="M8" t="n">
-        <v>861642.4202453988</v>
+        <v>4574601.889570553</v>
       </c>
       <c r="N8" t="n">
-        <v>6854.071574642127</v>
+        <v>40682.70756646217</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8771903855272027</v>
+        <v>0.9682475638703767</v>
       </c>
       <c r="P8" t="n">
-        <v>0.787160570509198</v>
+        <v>0.152225750650361</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0002331394313952103</v>
+        <v>6.266003233818007e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1497773347037368</v>
+        <v>0.04539345659657893</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002496288911728947</v>
+        <v>0.0007565576099429822</v>
       </c>
       <c r="T8" t="n">
-        <v>1.270388834838514</v>
+        <v>6.569190795431485</v>
       </c>
       <c r="U8" t="n">
-        <v>10707.27888796005</v>
+        <v>12074.00605636132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (none)</t>
+          <t>Opus 5 (high)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.230919689668531</v>
+        <v>0.6561729860226817</v>
       </c>
       <c r="F9" t="n">
-        <v>0.132743362831858</v>
+        <v>0.6076696165191739</v>
       </c>
       <c r="G9" t="n">
-        <v>0.374531835205993</v>
+        <v>0.868913857677903</v>
       </c>
       <c r="H9" t="n">
-        <v>0.185483870967742</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3616287844580779</v>
+        <v>3.918602446063396</v>
       </c>
       <c r="J9" t="n">
-        <v>88.85438650306737</v>
+        <v>842.8052382413097</v>
       </c>
       <c r="K9" t="n">
-        <v>33.82924335378323</v>
+        <v>94.85071574642126</v>
       </c>
       <c r="L9" t="n">
-        <v>1105801.555214723</v>
+        <v>9911366.349693259</v>
       </c>
       <c r="M9" t="n">
-        <v>582183.7985685072</v>
+        <v>4937399.112474437</v>
       </c>
       <c r="N9" t="n">
-        <v>5133.394683026585</v>
+        <v>37331.49386503067</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8482758058887612</v>
+        <v>0.9702723303233403</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6385545055949509</v>
+        <v>0.1674507672197952</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0002088256148488518</v>
+        <v>6.620408961504982e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1559313155533808</v>
+        <v>0.04671349604271027</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002598855259223013</v>
+        <v>0.0007785582673785045</v>
       </c>
       <c r="T9" t="n">
-        <v>1.566037027752682</v>
+        <v>5.971904557997063</v>
       </c>
       <c r="U9" t="n">
-        <v>12445.098083892</v>
+        <v>11759.97241115327</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (xhigh)</t>
+          <t>DeepSeek V4 Pro (high)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.529584326329171</v>
+        <v>0.3282816619106221</v>
       </c>
       <c r="F10" t="n">
-        <v>0.566371681415929</v>
+        <v>0.08554572271386431</v>
       </c>
       <c r="G10" t="n">
-        <v>0.707865168539326</v>
+        <v>0.700374531835206</v>
       </c>
       <c r="H10" t="n">
-        <v>0.314516129032258</v>
+        <v>0.198924731182796</v>
       </c>
       <c r="I10" t="n">
-        <v>1.209317104846625</v>
+        <v>0.2547256318476481</v>
       </c>
       <c r="J10" t="n">
-        <v>413.8987709611449</v>
+        <v>1072.531835378324</v>
       </c>
       <c r="K10" t="n">
-        <v>96.1922290388548</v>
+        <v>128.1457055214724</v>
       </c>
       <c r="L10" t="n">
-        <v>12806609.00511247</v>
+        <v>9942165.528629865</v>
       </c>
       <c r="M10" t="n">
-        <v>6575104.906952964</v>
+        <v>5181244.880368099</v>
       </c>
       <c r="N10" t="n">
-        <v>30840.24642126789</v>
+        <v>41975.79754601227</v>
       </c>
       <c r="O10" t="n">
-        <v>0.910023539336985</v>
+        <v>0.8541357545221666</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4379201486580617</v>
+        <v>1.288765718351297</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.135242405837159e-05</v>
+        <v>3.301913058732415e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.07677012305681181</v>
+        <v>0.01836486252894251</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001279502050946864</v>
+        <v>0.0003060810421490419</v>
       </c>
       <c r="T10" t="n">
-        <v>2.283521329320756</v>
+        <v>0.77593622002864</v>
       </c>
       <c r="U10" t="n">
-        <v>30941.40380115963</v>
+        <v>9269.809250112256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (high)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.516945881593198</v>
+        <v>0.466554082589455</v>
       </c>
       <c r="F11" t="n">
-        <v>0.533923303834808</v>
+        <v>0.315634218289085</v>
       </c>
       <c r="G11" t="n">
-        <v>0.726591760299625</v>
+        <v>0.745318352059925</v>
       </c>
       <c r="H11" t="n">
-        <v>0.290322580645161</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9174253706543963</v>
+        <v>2.72490571101738</v>
       </c>
       <c r="J11" t="n">
-        <v>342.6686574642128</v>
+        <v>826.6777535787322</v>
       </c>
       <c r="K11" t="n">
-        <v>83.81901840490798</v>
+        <v>86.42229038854805</v>
       </c>
       <c r="L11" t="n">
-        <v>9641370.493865021</v>
+        <v>5728865.180470352</v>
       </c>
       <c r="M11" t="n">
-        <v>4959371.744376278</v>
+        <v>2855520.426380368</v>
       </c>
       <c r="N11" t="n">
-        <v>22230.90593047035</v>
+        <v>17872.17893660532</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9032288062243126</v>
+        <v>0.9538631453697446</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5634745867388236</v>
+        <v>0.1712184317802544</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.361746879472582e-05</v>
+        <v>8.143917999326175e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.09051528997463437</v>
+        <v>0.03386234216922258</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001508588166243906</v>
+        <v>0.0005643723694870431</v>
       </c>
       <c r="T11" t="n">
-        <v>1.774702929882995</v>
+        <v>5.840492694638288</v>
       </c>
       <c r="U11" t="n">
-        <v>28136.13175249894</v>
+        <v>6929.985905233071</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qwen3.7 Plus (thinking)</t>
+          <t>Gemini 3.6 Flash (high)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.3812184526692477</v>
+        <v>0.4724127134829677</v>
       </c>
       <c r="F12" t="n">
-        <v>0.191740412979351</v>
+        <v>0.412979351032448</v>
       </c>
       <c r="G12" t="n">
-        <v>0.715355805243446</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H12" t="n">
-        <v>0.236559139784946</v>
+        <v>0.217741935483871</v>
       </c>
       <c r="I12" t="n">
-        <v>6.300658805725953</v>
+        <v>2.083890154754602</v>
       </c>
       <c r="J12" t="n">
-        <v>643.9465817995912</v>
+        <v>626.0057290388548</v>
       </c>
       <c r="K12" t="n">
-        <v>145.9662576687116</v>
+        <v>65.01533742331287</v>
       </c>
       <c r="L12" t="n">
-        <v>8784635.035787327</v>
+        <v>13020159.54294479</v>
       </c>
       <c r="M12" t="n">
-        <v>4715248.469325154</v>
+        <v>6765842.061349694</v>
       </c>
       <c r="N12" t="n">
-        <v>32611.0408997955</v>
+        <v>42763.3517382413</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8105104948122452</v>
+        <v>0.837777048552074</v>
       </c>
       <c r="P12" t="n">
-        <v>0.06050453840204798</v>
+        <v>0.2266975120570109</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.339604902380339e-05</v>
+        <v>3.628317394458911e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>0.03552019345491832</v>
+        <v>0.04527875943323637</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0005920032242486387</v>
+        <v>0.0007546459905539396</v>
       </c>
       <c r="T12" t="n">
-        <v>16.52768579697406</v>
+        <v>4.411164423138952</v>
       </c>
       <c r="U12" t="n">
-        <v>13641.86919237546</v>
+        <v>20798.78655892725</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (none)</t>
+          <t>Muse Spark 1.2 (xhigh)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.1909870904304247</v>
+        <v>0.5888788742875287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0648967551622419</v>
+        <v>0.528023598820059</v>
       </c>
       <c r="G13" t="n">
-        <v>0.333333333333333</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="H13" t="n">
-        <v>0.174731182795699</v>
+        <v>0.440860215053763</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3280835570961145</v>
+        <v>1.914379785695295</v>
       </c>
       <c r="J13" t="n">
-        <v>131.816209611452</v>
+        <v>1064.740692229038</v>
       </c>
       <c r="K13" t="n">
-        <v>54.28629856850716</v>
+        <v>65.87116564417177</v>
       </c>
       <c r="L13" t="n">
-        <v>3549957.210633946</v>
+        <v>16350688.07453988</v>
       </c>
       <c r="M13" t="n">
-        <v>1835572.532719836</v>
+        <v>8360784.971370144</v>
       </c>
       <c r="N13" t="n">
-        <v>7934.628834355828</v>
+        <v>47157.38036809816</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8748960056789888</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5821294188616518</v>
+        <v>0.3076081761245981</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.379982887070306e-05</v>
+        <v>3.601554085081525e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08693335561387526</v>
+        <v>0.03318435438330296</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001448889260231254</v>
+        <v>0.0005530725730550494</v>
       </c>
       <c r="T13" t="n">
-        <v>1.717831065737049</v>
+        <v>3.250888882728999</v>
       </c>
       <c r="U13" t="n">
-        <v>26931.11280545826</v>
+        <v>15356.49777816762</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opus 4.8 (high)</t>
+          <t>GPT-5.6 Luna (high)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5757636668124306</v>
+        <v>0.516945881593198</v>
       </c>
       <c r="F14" t="n">
-        <v>0.516224188790561</v>
+        <v>0.533923303834808</v>
       </c>
       <c r="G14" t="n">
-        <v>0.823970037453183</v>
+        <v>0.726591760299625</v>
       </c>
       <c r="H14" t="n">
-        <v>0.387096774193548</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7823013803681</v>
+        <v>0.9174253706543963</v>
       </c>
       <c r="J14" t="n">
-        <v>761.0308312883442</v>
+        <v>342.6686574642128</v>
       </c>
       <c r="K14" t="n">
-        <v>104.7627811860941</v>
+        <v>83.81901840490798</v>
       </c>
       <c r="L14" t="n">
-        <v>9188690.866053157</v>
+        <v>9641370.493865021</v>
       </c>
       <c r="M14" t="n">
-        <v>4574601.889570553</v>
+        <v>4959371.744376278</v>
       </c>
       <c r="N14" t="n">
-        <v>40682.70756646217</v>
+        <v>22230.90593047035</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9682475638703767</v>
+        <v>0.9032288062243126</v>
       </c>
       <c r="P14" t="n">
-        <v>0.152225750650361</v>
+        <v>0.5634745867388236</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.266003233818007e-05</v>
+        <v>5.361746879472582e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.04539345659657893</v>
+        <v>0.09051528997463437</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0007565576099429822</v>
+        <v>0.001508588166243906</v>
       </c>
       <c r="T14" t="n">
-        <v>6.569190795431485</v>
+        <v>1.774702929882995</v>
       </c>
       <c r="U14" t="n">
-        <v>12074.00605636132</v>
+        <v>28136.13175249894</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1485,356 +1485,356 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.466554082589455</v>
+        <v>0.5127556084440553</v>
       </c>
       <c r="F15" t="n">
-        <v>0.315634218289085</v>
+        <v>0.395280235988201</v>
       </c>
       <c r="G15" t="n">
-        <v>0.745318352059925</v>
+        <v>0.782771535580524</v>
       </c>
       <c r="H15" t="n">
-        <v>0.338709677419355</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I15" t="n">
-        <v>2.72490571101738</v>
+        <v>2.942840985557261</v>
       </c>
       <c r="J15" t="n">
-        <v>826.6777535787322</v>
+        <v>752.2755521472382</v>
       </c>
       <c r="K15" t="n">
-        <v>86.42229038854805</v>
+        <v>54.41308793456033</v>
       </c>
       <c r="L15" t="n">
-        <v>5728865.180470356</v>
+        <v>7582747.093047047</v>
       </c>
       <c r="M15" t="n">
-        <v>2855520.426380368</v>
+        <v>3744700.533231084</v>
       </c>
       <c r="N15" t="n">
-        <v>17872.17893660532</v>
+        <v>25943.59151329243</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9538631453697446</v>
+        <v>0.9584168731547836</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1712184317802544</v>
+        <v>0.1742382993034736</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.14391799932617e-05</v>
+        <v>6.762135175446157e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.03386234216922258</v>
+        <v>0.04089636625679125</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0005643723694870431</v>
+        <v>0.0006816061042798542</v>
       </c>
       <c r="T15" t="n">
-        <v>5.840492694638288</v>
+        <v>5.739266303663147</v>
       </c>
       <c r="U15" t="n">
-        <v>6929.985905233076</v>
+        <v>10079.74680474918</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gemini 3.6 Flash (high)</t>
+          <t>Opus 4.8 (low)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4724127134829677</v>
+        <v>0.4904379267565557</v>
       </c>
       <c r="F16" t="n">
-        <v>0.412979351032448</v>
+        <v>0.410029498525074</v>
       </c>
       <c r="G16" t="n">
-        <v>0.786516853932584</v>
+        <v>0.779026217228464</v>
       </c>
       <c r="H16" t="n">
-        <v>0.217741935483871</v>
+        <v>0.282258064516129</v>
       </c>
       <c r="I16" t="n">
-        <v>2.083890154754598</v>
+        <v>2.182594679703477</v>
       </c>
       <c r="J16" t="n">
-        <v>626.0057290388545</v>
+        <v>516.6536431492842</v>
       </c>
       <c r="K16" t="n">
-        <v>65.01533742331287</v>
+        <v>68.16359918200409</v>
       </c>
       <c r="L16" t="n">
-        <v>13020159.54294479</v>
+        <v>5214050.029652352</v>
       </c>
       <c r="M16" t="n">
-        <v>6765842.061349694</v>
+        <v>2595804.632924335</v>
       </c>
       <c r="N16" t="n">
-        <v>42763.3517382413</v>
+        <v>23270.04396728017</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8377770485520734</v>
+        <v>0.966158217610491</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2266975120570113</v>
+        <v>0.2247040787358583</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.628317394458913e-05</v>
+        <v>9.406084022351733e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0452787594332364</v>
+        <v>0.0569555174836748</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0007546459905539399</v>
+        <v>0.0009492586247279134</v>
       </c>
       <c r="T16" t="n">
-        <v>4.411164423138944</v>
+        <v>4.450297500720978</v>
       </c>
       <c r="U16" t="n">
-        <v>20798.78655892726</v>
+        <v>10091.9641210113</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Muse Spark 1.2 (xhigh)</t>
+          <t>GPT-5.6 Terra (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5888788742875287</v>
+        <v>0.6042010361726691</v>
       </c>
       <c r="F17" t="n">
-        <v>0.528023598820059</v>
+        <v>0.669616519174041</v>
       </c>
       <c r="G17" t="n">
-        <v>0.797752808988764</v>
+        <v>0.782771535580525</v>
       </c>
       <c r="H17" t="n">
-        <v>0.440860215053763</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I17" t="n">
-        <v>1.914379785695295</v>
+        <v>2.695350269529651</v>
       </c>
       <c r="J17" t="n">
-        <v>1064.740692229038</v>
+        <v>491.0206543967283</v>
       </c>
       <c r="K17" t="n">
-        <v>65.87116564417177</v>
+        <v>95.80674846625767</v>
       </c>
       <c r="L17" t="n">
-        <v>16350688.07453988</v>
+        <v>9630511.582822077</v>
       </c>
       <c r="M17" t="n">
-        <v>8360784.971370144</v>
+        <v>4933733.868098159</v>
       </c>
       <c r="N17" t="n">
-        <v>47157.38036809816</v>
+        <v>37445.42126789366</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.9184675548550253</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3076081761245981</v>
+        <v>0.2241641997342722</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.601554085081526e-05</v>
+        <v>6.273820772412353e-05</v>
       </c>
       <c r="R17" t="n">
-        <v>0.03318435438330296</v>
+        <v>0.07383001477789097</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0005530725730550494</v>
+        <v>0.001230500246298183</v>
       </c>
       <c r="T17" t="n">
-        <v>3.250888882728999</v>
+        <v>4.461015635794725</v>
       </c>
       <c r="U17" t="n">
-        <v>15356.49777816762</v>
+        <v>19613.25149275889</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>GPT-5.6 Sol (none)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5127556084440553</v>
+        <v>0.4336881923573268</v>
       </c>
       <c r="F18" t="n">
-        <v>0.395280235988201</v>
+        <v>0.353982300884956</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782771535580524</v>
+        <v>0.602996254681648</v>
       </c>
       <c r="H18" t="n">
-        <v>0.360215053763441</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I18" t="n">
-        <v>2.942840985557261</v>
+        <v>1.39701781850716</v>
       </c>
       <c r="J18" t="n">
-        <v>752.2755521472382</v>
+        <v>197.8853650306747</v>
       </c>
       <c r="K18" t="n">
-        <v>54.41308793456033</v>
+        <v>55.10736196319019</v>
       </c>
       <c r="L18" t="n">
-        <v>7582747.093047047</v>
+        <v>3404912.347648262</v>
       </c>
       <c r="M18" t="n">
-        <v>3744700.533231084</v>
+        <v>1731981.235173824</v>
       </c>
       <c r="N18" t="n">
-        <v>25943.59151329243</v>
+        <v>7689.902862985686</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9584168731547833</v>
+        <v>0.891939654668184</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1742382993034736</v>
+        <v>0.3104385546211299</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.762135175446157e-05</v>
+        <v>0.0001273713235692751</v>
       </c>
       <c r="R18" t="n">
-        <v>0.04089636625679125</v>
+        <v>0.1314967963265297</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0006816061042798542</v>
+        <v>0.002191613272108827</v>
       </c>
       <c r="T18" t="n">
-        <v>5.739266303663147</v>
+        <v>3.221249374841456</v>
       </c>
       <c r="U18" t="n">
-        <v>10079.74680474918</v>
+        <v>17206.48895445329</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Opus 4.8 (low)</t>
+          <t>GPT-5.6 Sol (xhigh)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.490437926756556</v>
+        <v>0.633388342362512</v>
       </c>
       <c r="F19" t="n">
-        <v>0.410029498525074</v>
+        <v>0.669616519174041</v>
       </c>
       <c r="G19" t="n">
-        <v>0.779026217228465</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="H19" t="n">
-        <v>0.282258064516129</v>
+        <v>0.432795698924731</v>
       </c>
       <c r="I19" t="n">
-        <v>2.182594679703477</v>
+        <v>4.799269930470346</v>
       </c>
       <c r="J19" t="n">
-        <v>516.6536431492842</v>
+        <v>440.5130695296522</v>
       </c>
       <c r="K19" t="n">
-        <v>68.16359918200409</v>
+        <v>93.87525562372188</v>
       </c>
       <c r="L19" t="n">
-        <v>5214050.029652352</v>
+        <v>9886595.803681007</v>
       </c>
       <c r="M19" t="n">
-        <v>2595804.632924335</v>
+        <v>5095034.968302658</v>
       </c>
       <c r="N19" t="n">
-        <v>23270.04396728017</v>
+        <v>25684.60429447853</v>
       </c>
       <c r="O19" t="n">
-        <v>0.966158217610491</v>
+        <v>0.9080963249335335</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2247040787358585</v>
+        <v>0.1319759779172157</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.406084022351739e-05</v>
+        <v>6.406536232893095e-05</v>
       </c>
       <c r="R19" t="n">
-        <v>0.05695551748367484</v>
+        <v>0.08627054035497261</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0009492586247279141</v>
+        <v>0.001437842339249544</v>
       </c>
       <c r="T19" t="n">
-        <v>4.450297500720974</v>
+        <v>7.577136504548331</v>
       </c>
       <c r="U19" t="n">
-        <v>10091.9641210113</v>
+        <v>22443.36544710738</v>
       </c>
     </row>
     <row r="20">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (none)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1859,201 +1859,201 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4336881923573268</v>
+        <v>0.5716614223656344</v>
       </c>
       <c r="F20" t="n">
-        <v>0.353982300884956</v>
+        <v>0.634218289085546</v>
       </c>
       <c r="G20" t="n">
-        <v>0.602996254681648</v>
+        <v>0.752808988764045</v>
       </c>
       <c r="H20" t="n">
-        <v>0.344086021505376</v>
+        <v>0.327956989247312</v>
       </c>
       <c r="I20" t="n">
-        <v>1.397017818507157</v>
+        <v>1.508396035337423</v>
       </c>
       <c r="J20" t="n">
-        <v>197.8853650306747</v>
+        <v>482.0907147239265</v>
       </c>
       <c r="K20" t="n">
-        <v>55.10736196319019</v>
+        <v>114.6288343558282</v>
       </c>
       <c r="L20" t="n">
-        <v>3404912.347648262</v>
+        <v>15963259.28016359</v>
       </c>
       <c r="M20" t="n">
-        <v>1731981.235173824</v>
+        <v>8170928.992842535</v>
       </c>
       <c r="N20" t="n">
-        <v>7689.902862985686</v>
+        <v>41094.49386503067</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8919396546681836</v>
+        <v>0.9181831202060821</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3104385546211307</v>
+        <v>0.378986293369404</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0001273713235692751</v>
+        <v>3.58110716823348e-05</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1314967963265297</v>
+        <v>0.0711477825528751</v>
       </c>
       <c r="S20" t="n">
-        <v>0.002191613272108827</v>
+        <v>0.001185796375881252</v>
       </c>
       <c r="T20" t="n">
-        <v>3.221249374841448</v>
+        <v>2.638617853720858</v>
       </c>
       <c r="U20" t="n">
-        <v>17206.48895445329</v>
+        <v>33112.56324300934</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (xhigh)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.633388342362512</v>
+        <v>0.6131027159527611</v>
       </c>
       <c r="F21" t="n">
-        <v>0.669616519174041</v>
+        <v>0.519174041297935</v>
       </c>
       <c r="G21" t="n">
-        <v>0.797752808988764</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H21" t="n">
-        <v>0.432795698924731</v>
+        <v>0.481182795698925</v>
       </c>
       <c r="I21" t="n">
-        <v>4.799269930470346</v>
+        <v>3.230610966002048</v>
       </c>
       <c r="J21" t="n">
-        <v>440.5130695296522</v>
+        <v>1792.147180981595</v>
       </c>
       <c r="K21" t="n">
-        <v>93.87525562372188</v>
+        <v>159.5848670756646</v>
       </c>
       <c r="L21" t="n">
-        <v>9886595.803681007</v>
+        <v>12503741.56441715</v>
       </c>
       <c r="M21" t="n">
-        <v>5095034.968302658</v>
+        <v>6469207.32413088</v>
       </c>
       <c r="N21" t="n">
-        <v>25684.60429447853</v>
+        <v>63117.84253578731</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9080963249335335</v>
+        <v>0.8998815214008221</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1319759779172157</v>
+        <v>0.189779184929682</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.406536232893095e-05</v>
+        <v>4.903354030424894e-05</v>
       </c>
       <c r="R21" t="n">
-        <v>0.08627054035497261</v>
+        <v>0.02052630684998603</v>
       </c>
       <c r="S21" t="n">
-        <v>0.001437842339249544</v>
+        <v>0.0003421051141664338</v>
       </c>
       <c r="T21" t="n">
-        <v>7.577136504548331</v>
+        <v>5.269281772764097</v>
       </c>
       <c r="U21" t="n">
-        <v>22443.36544710738</v>
+        <v>6976.961321652501</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>GPT-5.6 Luna (low)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.6131027159527611</v>
+        <v>0.250636604330228</v>
       </c>
       <c r="F22" t="n">
-        <v>0.519174041297935</v>
+        <v>0.103244837758112</v>
       </c>
       <c r="G22" t="n">
-        <v>0.838951310861423</v>
+        <v>0.49812734082397</v>
       </c>
       <c r="H22" t="n">
-        <v>0.481182795698925</v>
+        <v>0.150537634408602</v>
       </c>
       <c r="I22" t="n">
-        <v>3.230610966002048</v>
+        <v>0.1920449385685073</v>
       </c>
       <c r="J22" t="n">
-        <v>1792.147180981595</v>
+        <v>100.0260337423312</v>
       </c>
       <c r="K22" t="n">
-        <v>159.5848670756646</v>
+        <v>34.30674846625767</v>
       </c>
       <c r="L22" t="n">
-        <v>12503741.56441715</v>
+        <v>1435665.844580776</v>
       </c>
       <c r="M22" t="n">
-        <v>6469207.32413088</v>
+        <v>762148.6063394684</v>
       </c>
       <c r="N22" t="n">
-        <v>63117.84253578731</v>
+        <v>5609.407975460122</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8998815214008221</v>
+        <v>0.8430087375482054</v>
       </c>
       <c r="P22" t="n">
-        <v>0.189779184929682</v>
+        <v>1.305093517165617</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.903354030424894e-05</v>
+        <v>0.0001745786495348544</v>
       </c>
       <c r="R22" t="n">
-        <v>0.02052630684998603</v>
+        <v>0.1503428227350525</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0003421051141664338</v>
+        <v>0.002505713712250875</v>
       </c>
       <c r="T22" t="n">
-        <v>5.269281772764097</v>
+        <v>0.7662286164533141</v>
       </c>
       <c r="U22" t="n">
-        <v>6976.961321652501</v>
+        <v>14352.92184311812</v>
       </c>
     </row>
     <row r="23">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (low)</t>
+          <t>GPT-5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2078,55 +2078,55 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.250636604330228</v>
+        <v>0.6103327520587847</v>
       </c>
       <c r="F23" t="n">
-        <v>0.103244837758112</v>
+        <v>0.64306784660767</v>
       </c>
       <c r="G23" t="n">
-        <v>0.49812734082397</v>
+        <v>0.827715355805243</v>
       </c>
       <c r="H23" t="n">
-        <v>0.150537634408602</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1920449385685069</v>
+        <v>4.75237007157464</v>
       </c>
       <c r="J23" t="n">
-        <v>100.0260337423312</v>
+        <v>614.9898987730064</v>
       </c>
       <c r="K23" t="n">
-        <v>34.30674846625767</v>
+        <v>107.1319018404908</v>
       </c>
       <c r="L23" t="n">
-        <v>1435665.844580776</v>
+        <v>12150851.17995908</v>
       </c>
       <c r="M23" t="n">
-        <v>762148.6063394684</v>
+        <v>6164087.486707566</v>
       </c>
       <c r="N23" t="n">
-        <v>5609.407975460122</v>
+        <v>25286.0654396728</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8430087375482054</v>
+        <v>0.9341674523911518</v>
       </c>
       <c r="P23" t="n">
-        <v>1.305093517165619</v>
+        <v>0.1284270254350285</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0001745786495348544</v>
+        <v>5.022962943249873e-05</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1503428227350525</v>
+        <v>0.0595456367601959</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002505713712250875</v>
+        <v>0.0009924272793365983</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7662286164533125</v>
+        <v>7.786523098332615</v>
       </c>
       <c r="U23" t="n">
-        <v>14352.92184311812</v>
+        <v>19757.80611063984</v>
       </c>
     </row>
     <row r="24">
@@ -2166,7 +2166,7 @@
         <v>0.8847820614519432</v>
       </c>
       <c r="J24" t="n">
-        <v>240.094656441718</v>
+        <v>240.0946564417176</v>
       </c>
       <c r="K24" t="n">
         <v>50.95501022494887</v>
@@ -2181,7 +2181,7 @@
         <v>11855.54703476483</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8944384528371322</v>
+        <v>0.8944384528371319</v>
       </c>
       <c r="P24" t="n">
         <v>0.5430681081556789</v>
@@ -2190,16 +2190,16 @@
         <v>0.0001518346476713713</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1200768715215685</v>
+        <v>0.1200768715215687</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002001281192026142</v>
+        <v>0.002001281192026145</v>
       </c>
       <c r="T24" t="n">
         <v>1.841389661779466</v>
       </c>
       <c r="U24" t="n">
-        <v>13180.66213949852</v>
+        <v>13180.66213949855</v>
       </c>
     </row>
     <row r="25">
@@ -2254,10 +2254,10 @@
         <v>26011.59611451943</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9104181527286717</v>
+        <v>0.910418152728672</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2981618883309736</v>
+        <v>0.2981618883309737</v>
       </c>
       <c r="Q25" t="n">
         <v>8.448750232568207e-05</v>
@@ -2269,7 +2269,7 @@
         <v>0.001389531632255757</v>
       </c>
       <c r="T25" t="n">
-        <v>3.353882703110444</v>
+        <v>3.353882703110443</v>
       </c>
       <c r="U25" t="n">
         <v>16446.59380389062</v>
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.6411644486641199</v>
+        <v>0.6411644486641197</v>
       </c>
       <c r="F26" t="n">
         <v>0.648967551622419</v>
       </c>
       <c r="G26" t="n">
-        <v>0.820224719101124</v>
+        <v>0.820224719101123</v>
       </c>
       <c r="H26" t="n">
         <v>0.454301075268817</v>
@@ -2330,19 +2330,19 @@
         <v>0.906019018469944</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1665114541695913</v>
+        <v>0.1665114541695912</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.984336388053805e-05</v>
+        <v>7.984336388053802e-05</v>
       </c>
       <c r="R26" t="n">
         <v>0.1039893988514825</v>
       </c>
       <c r="S26" t="n">
-        <v>0.001733156647524709</v>
+        <v>0.001733156647524708</v>
       </c>
       <c r="T26" t="n">
-        <v>6.005592858383808</v>
+        <v>6.00559285838381</v>
       </c>
       <c r="U26" t="n">
         <v>21706.95926737085</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Opus 4.8 (max)</t>
+          <t>Opus 4.8 (xhigh)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2370,55 +2370,55 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.6214051234130329</v>
+        <v>0.590718121759733</v>
       </c>
       <c r="F27" t="n">
-        <v>0.557522123893805</v>
+        <v>0.513274336283186</v>
       </c>
       <c r="G27" t="n">
-        <v>0.838951310861423</v>
+        <v>0.831460674157303</v>
       </c>
       <c r="H27" t="n">
-        <v>0.467741935483871</v>
+        <v>0.42741935483871</v>
       </c>
       <c r="I27" t="n">
-        <v>7.724725797009212</v>
+        <v>5.665366469580767</v>
       </c>
       <c r="J27" t="n">
-        <v>1386.687798057262</v>
+        <v>1065.615385480571</v>
       </c>
       <c r="K27" t="n">
-        <v>165.0175845341703</v>
+        <v>136.1303390500093</v>
       </c>
       <c r="L27" t="n">
-        <v>17920579.42791411</v>
+        <v>13628306.24233129</v>
       </c>
       <c r="M27" t="n">
-        <v>8919829.832822086</v>
+        <v>6783846.309815951</v>
       </c>
       <c r="N27" t="n">
-        <v>89374.98517382414</v>
+        <v>62541.86503067485</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9657541826994763</v>
+        <v>0.9687226730983397</v>
       </c>
       <c r="P27" t="n">
-        <v>0.08044364806497376</v>
+        <v>0.104268298428971</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.467550398761645e-05</v>
+        <v>4.3344940395079e-05</v>
       </c>
       <c r="R27" t="n">
-        <v>0.02688731195083492</v>
+        <v>0.03326067527600483</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0004481218658472487</v>
+        <v>0.000554344587933414</v>
       </c>
       <c r="T27" t="n">
-        <v>12.43106229086363</v>
+        <v>9.590642746330172</v>
       </c>
       <c r="U27" t="n">
-        <v>12923.29784182185</v>
+        <v>12789.14177481138</v>
       </c>
     </row>
     <row r="28">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Opus 4.8 (medium)</t>
+          <t>Opus 4.8 (max)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2443,347 +2443,347 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5576883805320427</v>
+        <v>0.6214051234130329</v>
       </c>
       <c r="F28" t="n">
-        <v>0.492625368731563</v>
+        <v>0.557522123893805</v>
       </c>
       <c r="G28" t="n">
-        <v>0.820224719101124</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H28" t="n">
-        <v>0.360215053763441</v>
+        <v>0.467741935483871</v>
       </c>
       <c r="I28" t="n">
-        <v>3.303841633946831</v>
+        <v>7.724725797009214</v>
       </c>
       <c r="J28" t="n">
-        <v>722.922882413088</v>
+        <v>1386.687798057262</v>
       </c>
       <c r="K28" t="n">
-        <v>92.91239658858525</v>
+        <v>165.0175845341703</v>
       </c>
       <c r="L28" t="n">
-        <v>7827354.369120649</v>
+        <v>17920579.42791411</v>
       </c>
       <c r="M28" t="n">
-        <v>3898584.399795501</v>
+        <v>8919829.832822086</v>
       </c>
       <c r="N28" t="n">
-        <v>34668.28732106339</v>
+        <v>89374.98517382414</v>
       </c>
       <c r="O28" t="n">
-        <v>0.963840128346697</v>
+        <v>0.9657541826994763</v>
       </c>
       <c r="P28" t="n">
-        <v>0.168799973582819</v>
+        <v>0.08044364806497373</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.12486434410271e-05</v>
+        <v>3.467550398761645e-05</v>
       </c>
       <c r="R28" t="n">
-        <v>0.04628613043791069</v>
+        <v>0.02688731195083492</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0007714355072985115</v>
+        <v>0.0004481218658472487</v>
       </c>
       <c r="T28" t="n">
-        <v>5.924171543245923</v>
+        <v>12.43106229086363</v>
       </c>
       <c r="U28" t="n">
-        <v>10827.37116162826</v>
+        <v>12923.29784182185</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (low)</t>
+          <t>Opus 4.8 (medium)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.5523451808562164</v>
+        <v>0.5576883805320427</v>
       </c>
       <c r="F29" t="n">
-        <v>0.533923303834808</v>
+        <v>0.492625368731563</v>
       </c>
       <c r="G29" t="n">
-        <v>0.779026217228465</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H29" t="n">
-        <v>0.344086021505376</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I29" t="n">
-        <v>1.660386587423313</v>
+        <v>3.303841633946831</v>
       </c>
       <c r="J29" t="n">
-        <v>212.899582822086</v>
+        <v>722.9228824130877</v>
       </c>
       <c r="K29" t="n">
-        <v>53.92126789366053</v>
+        <v>92.91239658858525</v>
       </c>
       <c r="L29" t="n">
-        <v>3200236.065439673</v>
+        <v>7827354.369120649</v>
       </c>
       <c r="M29" t="n">
-        <v>1658130.417177914</v>
+        <v>3898584.399795501</v>
       </c>
       <c r="N29" t="n">
-        <v>8962.606339468302</v>
+        <v>34668.28732106339</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8829664546361218</v>
+        <v>0.963840128346697</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3326605894313919</v>
+        <v>0.168799973582819</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0001725951365966907</v>
+        <v>7.12486434410271e-05</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1556635781624227</v>
+        <v>0.04628613043791071</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002594392969373712</v>
+        <v>0.0007714355072985119</v>
       </c>
       <c r="T29" t="n">
-        <v>3.006066939607346</v>
+        <v>5.924171543245923</v>
       </c>
       <c r="U29" t="n">
-        <v>15031.6690292156</v>
+        <v>10827.37116162827</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>GPT-5.6 Sol (medium)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.423892771774363</v>
+        <v>0.616195748748264</v>
       </c>
       <c r="F30" t="n">
-        <v>0.274336283185841</v>
+        <v>0.640117994100295</v>
       </c>
       <c r="G30" t="n">
-        <v>0.771535580524345</v>
+        <v>0.805243445692884</v>
       </c>
       <c r="H30" t="n">
-        <v>0.225806451612903</v>
+        <v>0.403225806451613</v>
       </c>
       <c r="I30" t="n">
-        <v>1.800661744734152</v>
+        <v>2.813450298568507</v>
       </c>
       <c r="J30" t="n">
-        <v>399.3926789366056</v>
+        <v>297.9599253578734</v>
       </c>
       <c r="K30" t="n">
-        <v>42.04907975460122</v>
+        <v>71.35378323108384</v>
       </c>
       <c r="L30" t="n">
-        <v>4636274.728016362</v>
+        <v>5765545.476482615</v>
       </c>
       <c r="M30" t="n">
-        <v>2310268.645194274</v>
+        <v>2974758.351738241</v>
       </c>
       <c r="N30" t="n">
-        <v>17168.18507157464</v>
+        <v>14440.59713701431</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9576237577125696</v>
+        <v>0.8970664465490255</v>
       </c>
       <c r="P30" t="n">
-        <v>0.23540943934306</v>
+        <v>0.21901781917448</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.142960601813308e-05</v>
+        <v>0.00010687553350532</v>
       </c>
       <c r="R30" t="n">
-        <v>0.06368060219375923</v>
+        <v>0.1240829446459615</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001061343369895987</v>
+        <v>0.002068049077432692</v>
       </c>
       <c r="T30" t="n">
-        <v>4.247918022279086</v>
+        <v>4.565838541216378</v>
       </c>
       <c r="U30" t="n">
-        <v>11608.31175063242</v>
+        <v>19350.07021349512</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GLM-5.1</t>
+          <t>Muse Spark 1.1 (xhigh)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>friendliai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.3691032797641257</v>
+        <v>0.5492139250715363</v>
       </c>
       <c r="F31" t="n">
-        <v>0.185840707964602</v>
+        <v>0.542772861356932</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6741573033707861</v>
+        <v>0.771535580524344</v>
       </c>
       <c r="H31" t="n">
-        <v>0.247311827956989</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I31" t="n">
-        <v>4.282000252842536</v>
+        <v>1.435218435173823</v>
       </c>
       <c r="J31" t="n">
-        <v>1140.250613496931</v>
+        <v>761.3780071574632</v>
       </c>
       <c r="K31" t="n">
-        <v>174.2367075664622</v>
+        <v>55.51329243353784</v>
       </c>
       <c r="L31" t="n">
-        <v>25761884.92944783</v>
+        <v>12289527.21472391</v>
       </c>
       <c r="M31" t="n">
-        <v>13139446.7402863</v>
+        <v>6284599.100204499</v>
       </c>
       <c r="N31" t="n">
-        <v>49883.45705521473</v>
+        <v>34558.96932515338</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8889225409991813</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P31" t="n">
-        <v>0.08619879915212579</v>
+        <v>0.3826692241484618</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.432749508721747e-05</v>
+        <v>4.46895893939297e-05</v>
       </c>
       <c r="R31" t="n">
-        <v>0.01942221869798375</v>
+        <v>0.04328051926180354</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0003237036449663959</v>
+        <v>0.0007213419876967256</v>
       </c>
       <c r="T31" t="n">
-        <v>11.60108968844421</v>
+        <v>2.61322295312684</v>
       </c>
       <c r="U31" t="n">
-        <v>22593.17787204784</v>
+        <v>16141.16391489395</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.8</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>GPT-5.6 Sol (low)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.5657152973570364</v>
+        <v>0.5523451808562161</v>
       </c>
       <c r="F32" t="n">
-        <v>0.56047197640118</v>
+        <v>0.533923303834808</v>
       </c>
       <c r="G32" t="n">
-        <v>0.865168539325843</v>
+        <v>0.779026217228464</v>
       </c>
       <c r="H32" t="n">
-        <v>0.271505376344086</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I32" t="n">
-        <v>1.396316917192255</v>
+        <v>1.660386587423309</v>
       </c>
       <c r="J32" t="n">
-        <v>384.9621257668713</v>
+        <v>212.899582822086</v>
       </c>
       <c r="K32" t="n">
-        <v>110.7985685071575</v>
+        <v>53.92126789366053</v>
       </c>
       <c r="L32" t="n">
-        <v>15113684.86595342</v>
+        <v>3200236.065439673</v>
       </c>
       <c r="M32" t="n">
-        <v>7938344.274012004</v>
+        <v>1658130.417177914</v>
       </c>
       <c r="N32" t="n">
-        <v>64430.0844098625</v>
+        <v>8962.606339468302</v>
       </c>
       <c r="O32" t="n">
-        <v>0.8677594149804605</v>
+        <v>0.8829664546361218</v>
       </c>
       <c r="P32" t="n">
-        <v>0.4051482083985556</v>
+        <v>0.3326605894313923</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.743066647045306e-05</v>
+        <v>0.0001725951365966906</v>
       </c>
       <c r="R32" t="n">
-        <v>0.08817209686227062</v>
+        <v>0.1556635781624227</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00146953494770451</v>
+        <v>0.002594392969373711</v>
       </c>
       <c r="T32" t="n">
-        <v>2.468232560999683</v>
+        <v>3.006066939607342</v>
       </c>
       <c r="U32" t="n">
-        <v>39260.1865335347</v>
+        <v>15031.6690292156</v>
       </c>
     </row>
     <row r="33">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>Sonnet 4.6 (medium)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2808,128 +2808,128 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.6702814566291138</v>
+        <v>0.386493136077762</v>
       </c>
       <c r="F33" t="n">
-        <v>0.631268436578171</v>
+        <v>0.289085545722714</v>
       </c>
       <c r="G33" t="n">
-        <v>0.887640449438202</v>
+        <v>0.6741573033707871</v>
       </c>
       <c r="H33" t="n">
-        <v>0.491935483870968</v>
+        <v>0.196236559139785</v>
       </c>
       <c r="I33" t="n">
-        <v>8.943547018021487</v>
+        <v>2.041513021472394</v>
       </c>
       <c r="J33" t="n">
-        <v>1451.329194274025</v>
+        <v>827.6555807770972</v>
       </c>
       <c r="K33" t="n">
-        <v>165.7202546941811</v>
+        <v>67.41768916155419</v>
       </c>
       <c r="L33" t="n">
-        <v>23699428.05214722</v>
+        <v>8444053.035787314</v>
       </c>
       <c r="M33" t="n">
-        <v>11810977.87014315</v>
+        <v>4205086.787321064</v>
       </c>
       <c r="N33" t="n">
-        <v>81385.06339468302</v>
+        <v>40070.1308793456</v>
       </c>
       <c r="O33" t="n">
-        <v>0.974703359327879</v>
+        <v>0.9487221679807681</v>
       </c>
       <c r="P33" t="n">
-        <v>0.07494581906691815</v>
+        <v>0.1893170075393459</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.828260054015881e-05</v>
+        <v>4.577104554409349e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>0.02771038270050364</v>
+        <v>0.0280184036732921</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0004618397116750606</v>
+        <v>0.0004669733945548682</v>
       </c>
       <c r="T33" t="n">
-        <v>13.34297246264148</v>
+        <v>5.282145608561709</v>
       </c>
       <c r="U33" t="n">
-        <v>16329.46415303249</v>
+        <v>10202.37551936649</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (medium)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.4196699779001627</v>
+        <v>0.423892771774363</v>
       </c>
       <c r="F34" t="n">
-        <v>0.365781710914454</v>
+        <v>0.274336283185841</v>
       </c>
       <c r="G34" t="n">
-        <v>0.621722846441948</v>
+        <v>0.771535580524345</v>
       </c>
       <c r="H34" t="n">
-        <v>0.271505376344086</v>
+        <v>0.225806451612903</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4430536771983641</v>
+        <v>1.800661744734149</v>
       </c>
       <c r="J34" t="n">
-        <v>191.3819171779141</v>
+        <v>399.3926789366056</v>
       </c>
       <c r="K34" t="n">
-        <v>57.08588957055215</v>
+        <v>42.04907975460122</v>
       </c>
       <c r="L34" t="n">
-        <v>4287327.734151328</v>
+        <v>4636274.728016358</v>
       </c>
       <c r="M34" t="n">
-        <v>2221162.702453987</v>
+        <v>2310268.645194274</v>
       </c>
       <c r="N34" t="n">
-        <v>11663.1390593047</v>
+        <v>17168.18507157464</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8832984632099323</v>
+        <v>0.9576237577125707</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9472215207735832</v>
+        <v>0.2354094393430604</v>
       </c>
       <c r="Q34" t="n">
-        <v>9.788614351947506e-05</v>
+        <v>9.142960601813316e-05</v>
       </c>
       <c r="R34" t="n">
-        <v>0.1315704171288112</v>
+        <v>0.06368060219375923</v>
       </c>
       <c r="S34" t="n">
-        <v>0.002192840285480187</v>
+        <v>0.001061343369895987</v>
       </c>
       <c r="T34" t="n">
-        <v>1.05571925686751</v>
+        <v>4.247918022279078</v>
       </c>
       <c r="U34" t="n">
-        <v>22401.94788186653</v>
+        <v>11608.31175063241</v>
       </c>
     </row>
     <row r="35">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Opus 4.8 (xhigh)</t>
+          <t>GLM-5.1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2950,205 +2950,205 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>friendliai</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.590718121759733</v>
+        <v>0.3691032797641257</v>
       </c>
       <c r="F35" t="n">
-        <v>0.513274336283186</v>
+        <v>0.185840707964602</v>
       </c>
       <c r="G35" t="n">
-        <v>0.831460674157303</v>
+        <v>0.6741573033707861</v>
       </c>
       <c r="H35" t="n">
-        <v>0.42741935483871</v>
+        <v>0.247311827956989</v>
       </c>
       <c r="I35" t="n">
-        <v>5.665366469580767</v>
+        <v>4.282000252842536</v>
       </c>
       <c r="J35" t="n">
-        <v>1065.615385480571</v>
+        <v>1140.250613496931</v>
       </c>
       <c r="K35" t="n">
-        <v>136.1303390500093</v>
+        <v>174.2367075664622</v>
       </c>
       <c r="L35" t="n">
-        <v>13628306.24233129</v>
+        <v>25761884.92944783</v>
       </c>
       <c r="M35" t="n">
-        <v>6783846.309815951</v>
+        <v>13139446.7402863</v>
       </c>
       <c r="N35" t="n">
-        <v>62541.86503067485</v>
+        <v>49883.45705521473</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9687226730983403</v>
+        <v>0.888922540999181</v>
       </c>
       <c r="P35" t="n">
-        <v>0.104268298428971</v>
+        <v>0.08619879915212579</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.3344940395079e-05</v>
+        <v>1.432749508721747e-05</v>
       </c>
       <c r="R35" t="n">
-        <v>0.03326067527600483</v>
+        <v>0.01942221869798375</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0005543445879334139</v>
+        <v>0.0003237036449663959</v>
       </c>
       <c r="T35" t="n">
-        <v>9.590642746330172</v>
+        <v>11.60108968844421</v>
       </c>
       <c r="U35" t="n">
-        <v>12789.14177481137</v>
+        <v>22593.17787204784</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kimi K2.6</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.3388925953605663</v>
+        <v>0.5657152973570364</v>
       </c>
       <c r="F36" t="n">
-        <v>0.165191740412979</v>
+        <v>0.56047197640118</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6928838951310859</v>
+        <v>0.865168539325843</v>
       </c>
       <c r="H36" t="n">
-        <v>0.158602150537634</v>
+        <v>0.271505376344086</v>
       </c>
       <c r="I36" t="n">
-        <v>1.21710007411043</v>
+        <v>1.396316917192255</v>
       </c>
       <c r="J36" t="n">
-        <v>2443.385067484662</v>
+        <v>384.9621257668713</v>
       </c>
       <c r="K36" t="n">
-        <v>133.7675410760877</v>
+        <v>110.7985685071575</v>
       </c>
       <c r="L36" t="n">
-        <v>11660527.81595092</v>
+        <v>15113684.86595342</v>
       </c>
       <c r="M36" t="n">
-        <v>5891966.377300614</v>
+        <v>7938344.274012004</v>
       </c>
       <c r="N36" t="n">
-        <v>36930.17791411043</v>
+        <v>64430.0844098625</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9554328157869921</v>
+        <v>0.8677594149804605</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2784426708775452</v>
+        <v>0.4051482083985556</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.906322944463811e-05</v>
+        <v>3.743066647045306e-05</v>
       </c>
       <c r="R36" t="n">
-        <v>0.008321879343629747</v>
+        <v>0.08817209686227062</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0001386979890604958</v>
+        <v>0.00146953494770451</v>
       </c>
       <c r="T36" t="n">
-        <v>3.591403561991346</v>
+        <v>2.468232560999683</v>
       </c>
       <c r="U36" t="n">
-        <v>4772.284144289555</v>
+        <v>39260.1865335347</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GPT-5.5 (xhigh)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.6103327520587847</v>
+        <v>0.4708693600598454</v>
       </c>
       <c r="F37" t="n">
-        <v>0.64306784660767</v>
+        <v>0.371681415929203</v>
       </c>
       <c r="G37" t="n">
-        <v>0.827715355805243</v>
+        <v>0.764044943820225</v>
       </c>
       <c r="H37" t="n">
-        <v>0.360215053763441</v>
+        <v>0.276881720430108</v>
       </c>
       <c r="I37" t="n">
-        <v>4.75237007157464</v>
+        <v>1.998031234219498</v>
       </c>
       <c r="J37" t="n">
-        <v>614.9898987730064</v>
+        <v>386.6294212678936</v>
       </c>
       <c r="K37" t="n">
-        <v>107.1319018404908</v>
+        <v>77.78698023176551</v>
       </c>
       <c r="L37" t="n">
-        <v>12150851.17995912</v>
+        <v>3955817.742194958</v>
       </c>
       <c r="M37" t="n">
-        <v>6164087.486707566</v>
+        <v>2043912.618541241</v>
       </c>
       <c r="N37" t="n">
-        <v>25286.0654396728</v>
+        <v>11032.14533060668</v>
       </c>
       <c r="O37" t="n">
-        <v>0.9341674523911524</v>
+        <v>0.8915632417465625</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1284270254350285</v>
+        <v>0.2356666662639954</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.022962943249859e-05</v>
+        <v>0.0001190321169343295</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0595456367601959</v>
+        <v>0.07307297388528261</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0009924272793365983</v>
+        <v>0.001217882898088044</v>
       </c>
       <c r="T37" t="n">
-        <v>7.786523098332615</v>
+        <v>4.243281478254516</v>
       </c>
       <c r="U37" t="n">
-        <v>19757.8061106399</v>
+        <v>10231.54867320351</v>
       </c>
     </row>
     <row r="38">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3173,201 +3173,201 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.5716614223656344</v>
+        <v>0.5531133827505798</v>
       </c>
       <c r="F38" t="n">
-        <v>0.634218289085546</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G38" t="n">
-        <v>0.752808988764045</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H38" t="n">
-        <v>0.327956989247312</v>
+        <v>0.306451612903226</v>
       </c>
       <c r="I38" t="n">
-        <v>1.508396035337423</v>
+        <v>2.65253587423313</v>
       </c>
       <c r="J38" t="n">
-        <v>482.0907147239265</v>
+        <v>386.3044764826176</v>
       </c>
       <c r="K38" t="n">
-        <v>114.6288343558282</v>
+        <v>78.53885480572598</v>
       </c>
       <c r="L38" t="n">
-        <v>15963259.28016359</v>
+        <v>6885560.579754606</v>
       </c>
       <c r="M38" t="n">
-        <v>8170928.992842535</v>
+        <v>3492715.358895706</v>
       </c>
       <c r="N38" t="n">
-        <v>41094.49386503067</v>
+        <v>13239.49488752556</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9181831202060821</v>
+        <v>0.9409891933709399</v>
       </c>
       <c r="P38" t="n">
-        <v>0.378986293369404</v>
+        <v>0.2085224890353234</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.58110716823348e-05</v>
+        <v>8.032946284386509e-05</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0711477825528751</v>
+        <v>0.085908409002162</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001185796375881252</v>
+        <v>0.0014318068167027</v>
       </c>
       <c r="T38" t="n">
-        <v>2.638617853720858</v>
+        <v>4.795645806005133</v>
       </c>
       <c r="U38" t="n">
-        <v>33112.56324300934</v>
+        <v>17824.1801452809</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (max)</t>
+          <t>Opus 5 (low)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.6042010361726687</v>
+        <v>0.5940064571013324</v>
       </c>
       <c r="F39" t="n">
-        <v>0.669616519174041</v>
+        <v>0.569321533923304</v>
       </c>
       <c r="G39" t="n">
-        <v>0.782771535580524</v>
+        <v>0.820224719101123</v>
       </c>
       <c r="H39" t="n">
-        <v>0.360215053763441</v>
+        <v>0.39247311827957</v>
       </c>
       <c r="I39" t="n">
-        <v>2.695350269529651</v>
+        <v>2.295157744887527</v>
       </c>
       <c r="J39" t="n">
-        <v>491.0206543967279</v>
+        <v>598.7677147239262</v>
       </c>
       <c r="K39" t="n">
-        <v>95.80674846625767</v>
+        <v>64.39263803680981</v>
       </c>
       <c r="L39" t="n">
-        <v>9630511.582822077</v>
+        <v>5258606.375255628</v>
       </c>
       <c r="M39" t="n">
-        <v>4933733.868098159</v>
+        <v>2618171.039877301</v>
       </c>
       <c r="N39" t="n">
-        <v>37445.42126789366</v>
+        <v>22632.92229038855</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9184675548550253</v>
+        <v>0.9637890151908801</v>
       </c>
       <c r="P39" t="n">
-        <v>0.2241641997342721</v>
+        <v>0.2588085539760759</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.273820772412349e-05</v>
+        <v>0.0001129589124404576</v>
       </c>
       <c r="R39" t="n">
-        <v>0.07383001477789099</v>
+        <v>0.05952289435396939</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001230500246298183</v>
+        <v>0.0009920482392328232</v>
       </c>
       <c r="T39" t="n">
-        <v>4.461015635794727</v>
+        <v>3.863859925172485</v>
       </c>
       <c r="U39" t="n">
-        <v>19613.2514927589</v>
+        <v>8782.381290681667</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (high)</t>
+          <t>GPT-5.6 Terra (low)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.3282816619106221</v>
+        <v>0.3864628427996264</v>
       </c>
       <c r="F40" t="n">
-        <v>0.08554572271386431</v>
+        <v>0.297935103244838</v>
       </c>
       <c r="G40" t="n">
-        <v>0.700374531835206</v>
+        <v>0.632958801498127</v>
       </c>
       <c r="H40" t="n">
-        <v>0.198924731182796</v>
+        <v>0.228494623655914</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2547256318476481</v>
+        <v>0.4909580805725969</v>
       </c>
       <c r="J40" t="n">
-        <v>1072.531835378324</v>
+        <v>154.8149498977502</v>
       </c>
       <c r="K40" t="n">
-        <v>128.1457055214724</v>
+        <v>37.80981595092025</v>
       </c>
       <c r="L40" t="n">
-        <v>9942165.528629862</v>
+        <v>1657646.844580778</v>
       </c>
       <c r="M40" t="n">
-        <v>5181244.880368099</v>
+        <v>861642.4202453988</v>
       </c>
       <c r="N40" t="n">
-        <v>41975.79754601227</v>
+        <v>6854.071574642127</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8541357545221669</v>
+        <v>0.8771903855272027</v>
       </c>
       <c r="P40" t="n">
-        <v>1.288765718351297</v>
+        <v>0.7871605705091984</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.301913058732416e-05</v>
+        <v>0.0002331394313952098</v>
       </c>
       <c r="R40" t="n">
-        <v>0.01836486252894252</v>
+        <v>0.1497773347037368</v>
       </c>
       <c r="S40" t="n">
-        <v>0.000306081042149042</v>
+        <v>0.002496288911728947</v>
       </c>
       <c r="T40" t="n">
-        <v>0.77593622002864</v>
+        <v>1.270388834838513</v>
       </c>
       <c r="U40" t="n">
-        <v>9269.809250112256</v>
+        <v>10707.27888796008</v>
       </c>
     </row>
     <row r="41">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Opus 5 (high)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3392,274 +3392,274 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.6561729860226817</v>
+        <v>0.6702814566291138</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6076696165191739</v>
+        <v>0.631268436578171</v>
       </c>
       <c r="G41" t="n">
-        <v>0.868913857677903</v>
+        <v>0.887640449438202</v>
       </c>
       <c r="H41" t="n">
         <v>0.491935483870968</v>
       </c>
       <c r="I41" t="n">
-        <v>3.918602446063396</v>
+        <v>8.943547018021484</v>
       </c>
       <c r="J41" t="n">
-        <v>842.8052382413097</v>
+        <v>1451.329194274025</v>
       </c>
       <c r="K41" t="n">
-        <v>94.85071574642126</v>
+        <v>165.7202546941811</v>
       </c>
       <c r="L41" t="n">
-        <v>9911366.349693259</v>
+        <v>23699428.05214722</v>
       </c>
       <c r="M41" t="n">
-        <v>4937399.112474437</v>
+        <v>11810977.87014315</v>
       </c>
       <c r="N41" t="n">
-        <v>37331.49386503067</v>
+        <v>81385.06339468302</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9702723303233399</v>
+        <v>0.974703359327879</v>
       </c>
       <c r="P41" t="n">
-        <v>0.1674507672197952</v>
+        <v>0.07494581906691818</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.620408961504982e-05</v>
+        <v>2.828260054015881e-05</v>
       </c>
       <c r="R41" t="n">
-        <v>0.04671349604271027</v>
+        <v>0.02771038270050364</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0007785582673785045</v>
+        <v>0.0004618397116750606</v>
       </c>
       <c r="T41" t="n">
-        <v>5.971904557997063</v>
+        <v>13.34297246264148</v>
       </c>
       <c r="U41" t="n">
-        <v>11759.97241115327</v>
+        <v>16329.46415303249</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Composer 2.5</t>
+          <t>GPT-5.6 Terra (none)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.3830075380367747</v>
+        <v>0.2309196896685307</v>
       </c>
       <c r="F42" t="n">
-        <v>0.15929203539823</v>
+        <v>0.132743362831858</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6779026217228465</v>
+        <v>0.374531835205992</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3118279569892475</v>
+        <v>0.185483870967742</v>
       </c>
       <c r="I42" t="n">
-        <v>0.08505141359918199</v>
+        <v>0.3616287844580776</v>
       </c>
       <c r="J42" t="n">
-        <v>625.1976421267898</v>
+        <v>88.85438650306735</v>
       </c>
       <c r="K42" t="n">
-        <v>116.8680981595092</v>
+        <v>33.82924335378323</v>
       </c>
       <c r="L42" t="n">
-        <v>3705076.4698364</v>
+        <v>1105801.555214723</v>
       </c>
       <c r="M42" t="n">
-        <v>1872461.576687117</v>
+        <v>582183.7985685072</v>
       </c>
       <c r="N42" t="n">
-        <v>18453.85787321063</v>
+        <v>5133.394683026585</v>
       </c>
       <c r="O42" t="n">
-        <v>1.052833075750478</v>
+        <v>0.8482758058887612</v>
       </c>
       <c r="P42" t="n">
-        <v>4.503247175194022</v>
+        <v>0.6385545055949505</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.0001033737201255894</v>
+        <v>0.0002088256148488515</v>
       </c>
       <c r="R42" t="n">
-        <v>0.03675710004924499</v>
+        <v>0.1559313155533806</v>
       </c>
       <c r="S42" t="n">
-        <v>0.0006126183341540833</v>
+        <v>0.00259885525922301</v>
       </c>
       <c r="T42" t="n">
-        <v>0.2220619835190182</v>
+        <v>1.566037027752682</v>
       </c>
       <c r="U42" t="n">
-        <v>5926.248309626562</v>
+        <v>12445.098083892</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gemini CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro (high)</t>
+          <t>GPT-5.6 Luna (medium)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.3293046837328304</v>
+        <v>0.4196699779001624</v>
       </c>
       <c r="F43" t="n">
-        <v>0.141592920353982</v>
+        <v>0.365781710914454</v>
       </c>
       <c r="G43" t="n">
-        <v>0.760299625468165</v>
+        <v>0.621722846441947</v>
       </c>
       <c r="H43" t="n">
-        <v>0.08602150537634411</v>
+        <v>0.271505376344086</v>
       </c>
       <c r="I43" t="n">
-        <v>1.040041561860939</v>
+        <v>0.4430536771983641</v>
       </c>
       <c r="J43" t="n">
-        <v>663.8363599182014</v>
+        <v>191.3819171779144</v>
       </c>
       <c r="K43" t="n">
-        <v>30.96883483789777</v>
+        <v>57.08588957055215</v>
       </c>
       <c r="L43" t="n">
-        <v>4727804.222392637</v>
+        <v>4287327.734151328</v>
       </c>
       <c r="M43" t="n">
-        <v>2465901.789877301</v>
+        <v>2221162.702453987</v>
       </c>
       <c r="N43" t="n">
-        <v>12977.50562372188</v>
+        <v>11663.1390593047</v>
       </c>
       <c r="O43" t="n">
-        <v>0.8650361016121304</v>
+        <v>0.8832984632099323</v>
       </c>
       <c r="P43" t="n">
-        <v>0.316626465526635</v>
+        <v>0.9472215207735825</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.965277499713736e-05</v>
+        <v>9.788614351947498e-05</v>
       </c>
       <c r="R43" t="n">
-        <v>0.02976378248760652</v>
+        <v>0.1315704171288109</v>
       </c>
       <c r="S43" t="n">
-        <v>0.0004960630414601087</v>
+        <v>0.002192840285480182</v>
       </c>
       <c r="T43" t="n">
-        <v>3.158295685538259</v>
+        <v>1.055719256867511</v>
       </c>
       <c r="U43" t="n">
-        <v>7121.942255430543</v>
+        <v>22401.94788186649</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (high)</t>
+          <t>Kimi K2.6</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.5464647209828707</v>
+        <v>0.3388925953605663</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6047197640117991</v>
+        <v>0.165191740412979</v>
       </c>
       <c r="G44" t="n">
-        <v>0.722846441947566</v>
+        <v>0.6928838951310859</v>
       </c>
       <c r="H44" t="n">
-        <v>0.311827956989247</v>
+        <v>0.158602150537634</v>
       </c>
       <c r="I44" t="n">
-        <v>1.561839053374232</v>
+        <v>1.21710007411043</v>
       </c>
       <c r="J44" t="n">
-        <v>358.7396482617585</v>
+        <v>2443.385067484662</v>
       </c>
       <c r="K44" t="n">
-        <v>67.06952965235175</v>
+        <v>133.7675410760877</v>
       </c>
       <c r="L44" t="n">
-        <v>5600275.774028629</v>
+        <v>11660527.81595092</v>
       </c>
       <c r="M44" t="n">
-        <v>2877096.291411043</v>
+        <v>5891966.377300614</v>
       </c>
       <c r="N44" t="n">
-        <v>20902.66564417178</v>
+        <v>36930.17791411043</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9049339862289001</v>
+        <v>0.9554328157869918</v>
       </c>
       <c r="P44" t="n">
-        <v>0.3498854250073181</v>
+        <v>0.2784426708775453</v>
       </c>
       <c r="Q44" t="n">
-        <v>9.757818061694565e-05</v>
+        <v>2.906322944463811e-05</v>
       </c>
       <c r="R44" t="n">
-        <v>0.09139743381542312</v>
+        <v>0.008321879343629747</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001523290563590385</v>
+        <v>0.0001386979890604958</v>
       </c>
       <c r="T44" t="n">
-        <v>2.85807846948493</v>
+        <v>3.591403561991346</v>
       </c>
       <c r="U44" t="n">
-        <v>15610.9752606501</v>
+        <v>4772.284144289555</v>
       </c>
     </row>
     <row r="45">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Opus 4.7 (max)</t>
+          <t>Opus 5 (medium)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3684,128 +3684,128 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.5158095272716129</v>
+        <v>0.640684745695058</v>
       </c>
       <c r="F45" t="n">
-        <v>0.40117994100295</v>
+        <v>0.628318584070797</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7752808988764049</v>
+        <v>0.850187265917603</v>
       </c>
       <c r="H45" t="n">
-        <v>0.370967741935484</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="I45" t="n">
-        <v>5.915424259100206</v>
+        <v>3.171867192484664</v>
       </c>
       <c r="J45" t="n">
-        <v>950.3123588957063</v>
+        <v>730.9243895705519</v>
       </c>
       <c r="K45" t="n">
-        <v>107.999326082915</v>
+        <v>83.47801635991821</v>
       </c>
       <c r="L45" t="n">
-        <v>16129723.11451944</v>
+        <v>7999358.108384448</v>
       </c>
       <c r="M45" t="n">
-        <v>8042457.98977505</v>
+        <v>3984815.59611452</v>
       </c>
       <c r="N45" t="n">
-        <v>47224.16462167689</v>
+        <v>30206.12781186094</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9665216325317725</v>
+        <v>0.9695331242878965</v>
       </c>
       <c r="P45" t="n">
-        <v>0.08719738512044993</v>
+        <v>0.2019897766252884</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.197882093879828e-05</v>
+        <v>8.009201951135686e-05</v>
       </c>
       <c r="R45" t="n">
-        <v>0.03256673592276545</v>
+        <v>0.05259242308809697</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0005427789320460909</v>
+        <v>0.0008765403848016162</v>
       </c>
       <c r="T45" t="n">
-        <v>11.46823380791353</v>
+        <v>4.950745610532072</v>
       </c>
       <c r="U45" t="n">
-        <v>16973.07518263016</v>
+        <v>10944.16634952406</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Opus 5 (medium)</t>
+          <t>GPT-5.6 Luna (xhigh)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.640684745695058</v>
+        <v>0.529584326329171</v>
       </c>
       <c r="F46" t="n">
-        <v>0.628318584070797</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G46" t="n">
-        <v>0.850187265917603</v>
+        <v>0.707865168539326</v>
       </c>
       <c r="H46" t="n">
-        <v>0.443548387096774</v>
+        <v>0.314516129032258</v>
       </c>
       <c r="I46" t="n">
-        <v>3.171867192484664</v>
+        <v>1.209317104846625</v>
       </c>
       <c r="J46" t="n">
-        <v>730.9243895705519</v>
+        <v>413.8987709611452</v>
       </c>
       <c r="K46" t="n">
-        <v>83.47801635991821</v>
+        <v>96.1922290388548</v>
       </c>
       <c r="L46" t="n">
-        <v>7999358.108384448</v>
+        <v>12806609.00511247</v>
       </c>
       <c r="M46" t="n">
-        <v>3984815.59611452</v>
+        <v>6575104.906952964</v>
       </c>
       <c r="N46" t="n">
-        <v>30206.12781186094</v>
+        <v>30840.24642126789</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9695331242878962</v>
+        <v>0.9100235393369858</v>
       </c>
       <c r="P46" t="n">
-        <v>0.2019897766252884</v>
+        <v>0.4379201486580617</v>
       </c>
       <c r="Q46" t="n">
-        <v>8.009201951135686e-05</v>
+        <v>4.135242405837159e-05</v>
       </c>
       <c r="R46" t="n">
-        <v>0.05259242308809697</v>
+        <v>0.07677012305681175</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0008765403848016162</v>
+        <v>0.001279502050946862</v>
       </c>
       <c r="T46" t="n">
-        <v>4.950745610532072</v>
+        <v>2.283521329320756</v>
       </c>
       <c r="U46" t="n">
-        <v>10944.16634952406</v>
+        <v>30941.40380115961</v>
       </c>
     </row>
     <row r="47">
@@ -3845,7 +3845,7 @@
         <v>2.072823051942737</v>
       </c>
       <c r="J47" t="n">
-        <v>2448.643313905933</v>
+        <v>2448.643313905929</v>
       </c>
       <c r="K47" t="n">
         <v>151.4345603271984</v>
@@ -3860,7 +3860,7 @@
         <v>58305.98057259714</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9538301727874863</v>
+        <v>0.9538301727874866</v>
       </c>
       <c r="P47" t="n">
         <v>0.2973743539749669</v>
@@ -3869,673 +3869,673 @@
         <v>3.087712875993296e-05</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01510398217189024</v>
+        <v>0.01510398217189026</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0002517330361981707</v>
+        <v>0.0002517330361981711</v>
       </c>
       <c r="T47" t="n">
         <v>3.362764766474046</v>
       </c>
       <c r="U47" t="n">
-        <v>8152.734606749663</v>
+        <v>8152.734606749675</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>Opus 5 (xhigh)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.5962784529614886</v>
+        <v>0.6814975428587517</v>
       </c>
       <c r="F48" t="n">
-        <v>0.572271386430678</v>
+        <v>0.6047197640117991</v>
       </c>
       <c r="G48" t="n">
-        <v>0.910112359550562</v>
+        <v>0.891385767790262</v>
       </c>
       <c r="H48" t="n">
-        <v>0.306451612903226</v>
+        <v>0.5483870967741939</v>
       </c>
       <c r="I48" t="n">
-        <v>1.26793256886503</v>
+        <v>8.170783921523503</v>
       </c>
       <c r="J48" t="n">
-        <v>527.0915644171779</v>
+        <v>1421.879982617589</v>
       </c>
       <c r="K48" t="n">
-        <v>83.44887525562373</v>
+        <v>152.0771983640082</v>
       </c>
       <c r="L48" t="n">
-        <v>18493123.37423313</v>
+        <v>21565879.13803681</v>
       </c>
       <c r="M48" t="n">
-        <v>9497213.109406954</v>
+        <v>10747525.6196319</v>
       </c>
       <c r="N48" t="n">
-        <v>49098.7944785276</v>
+        <v>73273.02862985685</v>
       </c>
       <c r="O48" t="n">
-        <v>0.8634331167917663</v>
+        <v>0.9740249879523308</v>
       </c>
       <c r="P48" t="n">
-        <v>0.4702761547447575</v>
+        <v>0.08340662896047819</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.224325285107308e-05</v>
+        <v>3.160073088125403e-05</v>
       </c>
       <c r="R48" t="n">
-        <v>0.06787569673449199</v>
+        <v>0.02875759773778482</v>
       </c>
       <c r="S48" t="n">
-        <v>0.001131261612241533</v>
+        <v>0.000479293295629747</v>
       </c>
       <c r="T48" t="n">
-        <v>2.126410173917388</v>
+        <v>11.98945470477946</v>
       </c>
       <c r="U48" t="n">
-        <v>35085.21976571865</v>
+        <v>15167.15855183179</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GLM-5.2</t>
+          <t>Composer 2.5 Fast</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>novita</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.433101571936022</v>
+        <v>0.3830075380367747</v>
       </c>
       <c r="F49" t="n">
-        <v>0.286135693215339</v>
+        <v>0.15929203539823</v>
       </c>
       <c r="G49" t="n">
-        <v>0.722846441947566</v>
+        <v>0.6779026217228465</v>
       </c>
       <c r="H49" t="n">
-        <v>0.290322580645161</v>
+        <v>0.3118279569892475</v>
       </c>
       <c r="I49" t="n">
-        <v>6.657531358159516</v>
+        <v>0.5573437730061347</v>
       </c>
       <c r="J49" t="n">
-        <v>1507.044470347651</v>
+        <v>472.3722024539875</v>
       </c>
       <c r="K49" t="n">
-        <v>127.4036879531512</v>
+        <v>116.8680981595092</v>
       </c>
       <c r="L49" t="n">
-        <v>6619529.539877302</v>
+        <v>4259887.413087938</v>
       </c>
       <c r="M49" t="n">
-        <v>5529735.922290388</v>
+        <v>2153033.982617587</v>
       </c>
       <c r="N49" t="n">
-        <v>28567.83231083845</v>
+        <v>20146.14621676892</v>
       </c>
       <c r="O49" t="n">
-        <v>0.3295602231414034</v>
+        <v>0.9355410155352533</v>
       </c>
       <c r="P49" t="n">
-        <v>0.06505437956446269</v>
+        <v>0.6872016098268293</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.542784790473944e-05</v>
+        <v>8.991024900330346e-05</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01724308394838989</v>
+        <v>0.04864903599920222</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0002873847324731648</v>
+        <v>0.0008108172666533704</v>
       </c>
       <c r="T49" t="n">
-        <v>15.37175524069206</v>
+        <v>1.455177033493845</v>
       </c>
       <c r="U49" t="n">
-        <v>4392.391644786887</v>
+        <v>9018.073864121761</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Grok 4.5 (high)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.4975760031619054</v>
+        <v>0.6408998279698193</v>
       </c>
       <c r="F50" t="n">
-        <v>0.427728613569322</v>
+        <v>0.59882005899705</v>
       </c>
       <c r="G50" t="n">
-        <v>0.677902621722846</v>
+        <v>0.842696629213483</v>
       </c>
       <c r="H50" t="n">
-        <v>0.387096774193548</v>
+        <v>0.481182795698925</v>
       </c>
       <c r="I50" t="n">
-        <v>0.05949917044417178</v>
+        <v>2.438982443762777</v>
       </c>
       <c r="J50" t="n">
-        <v>868.3750143149272</v>
+        <v>929.1851094069541</v>
       </c>
       <c r="K50" t="n">
-        <v>105.9314928425358</v>
+        <v>60.74437627811862</v>
       </c>
       <c r="L50" t="n">
-        <v>20844227.99386505</v>
+        <v>3598867.582822087</v>
       </c>
       <c r="M50" t="n">
-        <v>10443571.69734151</v>
+        <v>1837535.160531697</v>
       </c>
       <c r="N50" t="n">
-        <v>58411.25766871166</v>
+        <v>25699.40797546012</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9807621661364233</v>
+        <v>0.9238990226060748</v>
       </c>
       <c r="P50" t="n">
-        <v>8.362738496140583</v>
+        <v>0.2627734486604427</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.387116487635588e-05</v>
+        <v>0.0001780837480736792</v>
       </c>
       <c r="R50" t="n">
-        <v>0.03437980100483083</v>
+        <v>0.04138463831252327</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0005729966834138472</v>
+        <v>0.0006897439718753878</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1195780545405672</v>
+        <v>3.805559523223389</v>
       </c>
       <c r="U50" t="n">
-        <v>24003.71688527835</v>
+        <v>3873.143840110653</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Opus 5 (xhigh)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.6814975428587517</v>
+        <v>0.6263880112748017</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6047197640117991</v>
+        <v>0.63716814159292</v>
       </c>
       <c r="G51" t="n">
-        <v>0.891385767790262</v>
+        <v>0.8764044943820229</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5483870967741939</v>
+        <v>0.365591397849462</v>
       </c>
       <c r="I51" t="n">
-        <v>8.170783921523503</v>
+        <v>3.081635541610432</v>
       </c>
       <c r="J51" t="n">
-        <v>1421.879982617589</v>
+        <v>1447.373053169735</v>
       </c>
       <c r="K51" t="n">
-        <v>152.0771983640082</v>
+        <v>122.9498977505112</v>
       </c>
       <c r="L51" t="n">
-        <v>21565879.13803684</v>
+        <v>10383196.73788345</v>
       </c>
       <c r="M51" t="n">
-        <v>10747525.6196319</v>
+        <v>5296768.575664621</v>
       </c>
       <c r="N51" t="n">
-        <v>73273.02862985685</v>
+        <v>54498.01533742331</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9740249879523308</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P51" t="n">
-        <v>0.08340662896047819</v>
+        <v>0.2032647932621707</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.160073088125398e-05</v>
+        <v>6.032708683920082e-05</v>
       </c>
       <c r="R51" t="n">
-        <v>0.02875759773778482</v>
+        <v>0.02596654718296782</v>
       </c>
       <c r="S51" t="n">
-        <v>0.000479293295629747</v>
+        <v>0.0004327757863827969</v>
       </c>
       <c r="T51" t="n">
-        <v>11.98945470477946</v>
+        <v>4.919691127770471</v>
       </c>
       <c r="U51" t="n">
-        <v>15167.15855183182</v>
+        <v>7173.822060003356</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Grok 4.5 (high)</t>
+          <t>Fable 5 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.6408998279698193</v>
+        <v>0.6717276042685724</v>
       </c>
       <c r="F52" t="n">
-        <v>0.59882005899705</v>
+        <v>0.660766961651917</v>
       </c>
       <c r="G52" t="n">
-        <v>0.842696629213483</v>
+        <v>0.865168539325843</v>
       </c>
       <c r="H52" t="n">
-        <v>0.481182795698925</v>
+        <v>0.489247311827957</v>
       </c>
       <c r="I52" t="n">
-        <v>2.438982443762777</v>
+        <v>11.68740762091003</v>
       </c>
       <c r="J52" t="n">
-        <v>929.185109406954</v>
+        <v>1407.30630163599</v>
       </c>
       <c r="K52" t="n">
-        <v>60.74437627811862</v>
+        <v>137.007744236847</v>
       </c>
       <c r="L52" t="n">
-        <v>3598867.582822087</v>
+        <v>13868659.9989775</v>
       </c>
       <c r="M52" t="n">
-        <v>1837535.160531697</v>
+        <v>6901095.023517382</v>
       </c>
       <c r="N52" t="n">
-        <v>25699.40797546012</v>
+        <v>74265.48875255625</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9238990226060743</v>
+        <v>0.9619283373252908</v>
       </c>
       <c r="P52" t="n">
-        <v>0.2627734486604427</v>
+        <v>0.05747447390016408</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.0001780837480736792</v>
+        <v>4.84349320206925e-05</v>
       </c>
       <c r="R52" t="n">
-        <v>0.04138463831252327</v>
+        <v>0.02863886576025522</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0006897439718753878</v>
+        <v>0.0004773144293375869</v>
       </c>
       <c r="T52" t="n">
-        <v>3.805559523223389</v>
+        <v>17.39902833624972</v>
       </c>
       <c r="U52" t="n">
-        <v>3873.143840110653</v>
+        <v>9854.755843028073</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fable 5 (max) (with fallback)</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.6717276042685724</v>
+        <v>0.5962784529614886</v>
       </c>
       <c r="F53" t="n">
-        <v>0.660766961651917</v>
+        <v>0.572271386430678</v>
       </c>
       <c r="G53" t="n">
-        <v>0.865168539325843</v>
+        <v>0.910112359550562</v>
       </c>
       <c r="H53" t="n">
-        <v>0.489247311827957</v>
+        <v>0.306451612903226</v>
       </c>
       <c r="I53" t="n">
-        <v>11.68740762091003</v>
+        <v>1.26793256886503</v>
       </c>
       <c r="J53" t="n">
-        <v>1407.30630163599</v>
+        <v>527.0915644171779</v>
       </c>
       <c r="K53" t="n">
-        <v>137.007744236847</v>
+        <v>83.44887525562373</v>
       </c>
       <c r="L53" t="n">
-        <v>13868659.99897749</v>
+        <v>18493123.37423313</v>
       </c>
       <c r="M53" t="n">
-        <v>6901095.023517382</v>
+        <v>9497213.109406954</v>
       </c>
       <c r="N53" t="n">
-        <v>74265.48875255625</v>
+        <v>49098.7944785276</v>
       </c>
       <c r="O53" t="n">
-        <v>0.9619283373252908</v>
+        <v>0.8634331167917659</v>
       </c>
       <c r="P53" t="n">
-        <v>0.05747447390016408</v>
+        <v>0.4702761547447575</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.843493202069251e-05</v>
+        <v>3.224325285107308e-05</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02863886576025522</v>
+        <v>0.06787569673449199</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0004773144293375869</v>
+        <v>0.001131261612241533</v>
       </c>
       <c r="T53" t="n">
-        <v>17.39902833624972</v>
+        <v>2.126410173917388</v>
       </c>
       <c r="U53" t="n">
-        <v>9854.75584302807</v>
+        <v>35085.21976571864</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>GLM-5.2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>novita</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.6505240024334411</v>
+        <v>0.4331015719360217</v>
       </c>
       <c r="F54" t="n">
-        <v>0.687315634218289</v>
+        <v>0.286135693215339</v>
       </c>
       <c r="G54" t="n">
-        <v>0.831460674157303</v>
+        <v>0.722846441947565</v>
       </c>
       <c r="H54" t="n">
-        <v>0.432795698924731</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="I54" t="n">
-        <v>6.420249160020451</v>
+        <v>6.657531358159519</v>
       </c>
       <c r="J54" t="n">
-        <v>613.70177198364</v>
+        <v>1507.044470347651</v>
       </c>
       <c r="K54" t="n">
-        <v>112.2689161554192</v>
+        <v>127.4036879531512</v>
       </c>
       <c r="L54" t="n">
-        <v>13169248.79601226</v>
+        <v>6619529.539877302</v>
       </c>
       <c r="M54" t="n">
-        <v>6786107.398261759</v>
+        <v>5529735.922290388</v>
       </c>
       <c r="N54" t="n">
-        <v>35184.01329243354</v>
+        <v>28567.83231083845</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9025973208659727</v>
+        <v>0.3295602231414034</v>
       </c>
       <c r="P54" t="n">
-        <v>0.1013237938621324</v>
+        <v>0.06505437956446262</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.939719892226686e-05</v>
+        <v>6.542784790473939e-05</v>
       </c>
       <c r="R54" t="n">
-        <v>0.06360001213593849</v>
+        <v>0.01724308394838987</v>
       </c>
       <c r="S54" t="n">
-        <v>0.001060000202265642</v>
+        <v>0.0002873847324731645</v>
       </c>
       <c r="T54" t="n">
-        <v>9.869350148501775</v>
+        <v>15.37175524069208</v>
       </c>
       <c r="U54" t="n">
-        <v>21458.71072434076</v>
+        <v>4392.391644786887</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.6263880112748017</v>
+        <v>0.4975760031619054</v>
       </c>
       <c r="F55" t="n">
-        <v>0.63716814159292</v>
+        <v>0.427728613569322</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8764044943820229</v>
+        <v>0.677902621722846</v>
       </c>
       <c r="H55" t="n">
-        <v>0.365591397849462</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="I55" t="n">
-        <v>3.081635541610432</v>
+        <v>0.05949917044417178</v>
       </c>
       <c r="J55" t="n">
-        <v>1447.373053169734</v>
+        <v>868.3750143149272</v>
       </c>
       <c r="K55" t="n">
-        <v>122.9498977505112</v>
+        <v>105.9314928425358</v>
       </c>
       <c r="L55" t="n">
-        <v>10383196.73788345</v>
+        <v>20844227.99386501</v>
       </c>
       <c r="M55" t="n">
-        <v>5296768.575664621</v>
+        <v>10443571.69734151</v>
       </c>
       <c r="N55" t="n">
-        <v>54498.01533742331</v>
+        <v>58411.25766871166</v>
       </c>
       <c r="O55" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.980762166136423</v>
       </c>
       <c r="P55" t="n">
-        <v>0.2032647932621707</v>
+        <v>8.362738496140583</v>
       </c>
       <c r="Q55" t="n">
-        <v>6.032708683920082e-05</v>
+        <v>2.387116487635592e-05</v>
       </c>
       <c r="R55" t="n">
-        <v>0.02596654718296782</v>
+        <v>0.03437980100483083</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0004327757863827971</v>
+        <v>0.0005729966834138472</v>
       </c>
       <c r="T55" t="n">
-        <v>4.919691127770471</v>
+        <v>0.1195780545405672</v>
       </c>
       <c r="U55" t="n">
-        <v>7173.822060003357</v>
+        <v>24003.71688527831</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Composer 2.5 Fast</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.3830075380367747</v>
+        <v>0.6505240024334411</v>
       </c>
       <c r="F56" t="n">
-        <v>0.15929203539823</v>
+        <v>0.687315634218289</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6779026217228465</v>
+        <v>0.831460674157303</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3118279569892475</v>
+        <v>0.432795698924731</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5573437730061347</v>
+        <v>6.420249160020451</v>
       </c>
       <c r="J56" t="n">
-        <v>472.3722024539878</v>
+        <v>613.70177198364</v>
       </c>
       <c r="K56" t="n">
-        <v>116.8680981595092</v>
+        <v>112.2689161554192</v>
       </c>
       <c r="L56" t="n">
-        <v>4259887.413087931</v>
+        <v>13169248.79601226</v>
       </c>
       <c r="M56" t="n">
-        <v>2153033.982617587</v>
+        <v>6786107.398261759</v>
       </c>
       <c r="N56" t="n">
-        <v>20146.14621676892</v>
+        <v>35184.01329243354</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9355410155352526</v>
+        <v>0.902597320865973</v>
       </c>
       <c r="P56" t="n">
-        <v>0.6872016098268293</v>
+        <v>0.1013237938621324</v>
       </c>
       <c r="Q56" t="n">
-        <v>8.991024900330358e-05</v>
+        <v>4.939719892226686e-05</v>
       </c>
       <c r="R56" t="n">
-        <v>0.0486490359992022</v>
+        <v>0.06360001213593849</v>
       </c>
       <c r="S56" t="n">
-        <v>0.00081081726665337</v>
+        <v>0.001060000202265642</v>
       </c>
       <c r="T56" t="n">
-        <v>1.455177033493845</v>
+        <v>9.869350148501775</v>
       </c>
       <c r="U56" t="n">
-        <v>9018.073864121743</v>
+        <v>21458.71072434076</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:U58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,512 +526,512 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Opus 4.7 (max)</t>
+          <t>GPT-5.6 Terra (none)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5158095272716127</v>
+        <v>0.2309196896685307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.40117994100295</v>
+        <v>0.132743362831858</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7752808988764039</v>
+        <v>0.374531835205992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.370967741935484</v>
+        <v>0.185483870967742</v>
       </c>
       <c r="I2" t="n">
-        <v>5.915424259100202</v>
+        <v>0.3616287844580776</v>
       </c>
       <c r="J2" t="n">
-        <v>950.3123588957067</v>
+        <v>88.85438650306737</v>
       </c>
       <c r="K2" t="n">
-        <v>107.999326082915</v>
+        <v>33.82924335378323</v>
       </c>
       <c r="L2" t="n">
-        <v>16129723.11451944</v>
+        <v>1105801.555214723</v>
       </c>
       <c r="M2" t="n">
-        <v>8042457.98977505</v>
+        <v>582183.7985685072</v>
       </c>
       <c r="N2" t="n">
-        <v>47224.16462167689</v>
+        <v>5133.394683026585</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9665216325317721</v>
+        <v>0.8482758058887608</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08719738512044996</v>
+        <v>0.6385545055949505</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.197882093879827e-05</v>
+        <v>0.0002088256148488515</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03256673592276543</v>
+        <v>0.1559313155533806</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0005427789320460904</v>
+        <v>0.00259885525922301</v>
       </c>
       <c r="T2" t="n">
-        <v>11.46823380791353</v>
+        <v>1.566037027752682</v>
       </c>
       <c r="U2" t="n">
-        <v>16973.07518263015</v>
+        <v>12445.098083892</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qwen3.7 Plus (thinking)</t>
+          <t>GPT-5.6 Luna (xhigh)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3812184526692477</v>
+        <v>0.529584326329171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.191740412979351</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G3" t="n">
-        <v>0.715355805243446</v>
+        <v>0.707865168539326</v>
       </c>
       <c r="H3" t="n">
-        <v>0.236559139784946</v>
+        <v>0.314516129032258</v>
       </c>
       <c r="I3" t="n">
-        <v>6.300658805725988</v>
+        <v>1.209317104846625</v>
       </c>
       <c r="J3" t="n">
-        <v>643.9465817995912</v>
+        <v>413.8987709611451</v>
       </c>
       <c r="K3" t="n">
-        <v>145.9662576687116</v>
+        <v>96.1922290388548</v>
       </c>
       <c r="L3" t="n">
-        <v>8784635.035787323</v>
+        <v>12806609.00511247</v>
       </c>
       <c r="M3" t="n">
-        <v>4715248.469325154</v>
+        <v>6575104.906952964</v>
       </c>
       <c r="N3" t="n">
-        <v>32611.0408997955</v>
+        <v>30840.24642126789</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8105104948122446</v>
+        <v>0.9100235393369858</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06050453840204764</v>
+        <v>0.4379201486580617</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.339604902380341e-05</v>
+        <v>4.135242405837159e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03552019345491832</v>
+        <v>0.07677012305681176</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005920032242486387</v>
+        <v>0.001279502050946863</v>
       </c>
       <c r="T3" t="n">
-        <v>16.52768579697415</v>
+        <v>2.283521329320756</v>
       </c>
       <c r="U3" t="n">
-        <v>13641.86919237545</v>
+        <v>30941.40380115961</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (high)</t>
+          <t>Muse Spark 1.2 (xhigh)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5464647209828707</v>
+        <v>0.6164044159758908</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6047197640117991</v>
+        <v>0.581120943952802</v>
       </c>
       <c r="G4" t="n">
-        <v>0.722846441947566</v>
+        <v>0.816479400749064</v>
       </c>
       <c r="H4" t="n">
-        <v>0.311827956989247</v>
+        <v>0.451612903225806</v>
       </c>
       <c r="I4" t="n">
-        <v>1.561839053374232</v>
+        <v>2.072823051942737</v>
       </c>
       <c r="J4" t="n">
-        <v>358.7396482617588</v>
+        <v>2448.643313905933</v>
       </c>
       <c r="K4" t="n">
-        <v>67.06952965235175</v>
+        <v>151.4345603271984</v>
       </c>
       <c r="L4" t="n">
-        <v>5600275.774028629</v>
+        <v>19963139.08486708</v>
       </c>
       <c r="M4" t="n">
-        <v>2877096.291411043</v>
+        <v>10093761.29754601</v>
       </c>
       <c r="N4" t="n">
-        <v>20902.66564417178</v>
+        <v>58305.98057259714</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9049339862289001</v>
+        <v>0.9538301727874863</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3498854250073181</v>
+        <v>0.2973743539749669</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.757818061694565e-05</v>
+        <v>3.087712875993296e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.09139743381542303</v>
+        <v>0.01510398217189024</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001523290563590384</v>
+        <v>0.0002517330361981707</v>
       </c>
       <c r="T4" t="n">
-        <v>2.85807846948493</v>
+        <v>3.362764766474046</v>
       </c>
       <c r="U4" t="n">
-        <v>15610.97526065008</v>
+        <v>8152.734606749663</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gemini CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro (high)</t>
+          <t>Kimi K2.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3293046837328304</v>
+        <v>0.3388925953605663</v>
       </c>
       <c r="F5" t="n">
-        <v>0.141592920353982</v>
+        <v>0.165191740412979</v>
       </c>
       <c r="G5" t="n">
-        <v>0.760299625468165</v>
+        <v>0.6928838951310859</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08602150537634411</v>
+        <v>0.158602150537634</v>
       </c>
       <c r="I5" t="n">
-        <v>1.040041561860939</v>
+        <v>1.21710007411043</v>
       </c>
       <c r="J5" t="n">
-        <v>663.8363599182018</v>
+        <v>2443.385067484662</v>
       </c>
       <c r="K5" t="n">
-        <v>30.96883483789777</v>
+        <v>133.7675410760877</v>
       </c>
       <c r="L5" t="n">
-        <v>4727804.222392637</v>
+        <v>11660527.81595092</v>
       </c>
       <c r="M5" t="n">
-        <v>2465901.789877301</v>
+        <v>5891966.377300614</v>
       </c>
       <c r="N5" t="n">
-        <v>12977.50562372188</v>
+        <v>36930.17791411043</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8650361016121304</v>
+        <v>0.9554328157869921</v>
       </c>
       <c r="P5" t="n">
-        <v>0.316626465526635</v>
+        <v>0.2784426708775453</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.965277499713736e-05</v>
+        <v>2.906322944463811e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02976378248760651</v>
+        <v>0.008321879343629747</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004960630414601085</v>
+        <v>0.0001386979890604958</v>
       </c>
       <c r="T5" t="n">
-        <v>3.158295685538259</v>
+        <v>3.591403561991346</v>
       </c>
       <c r="U5" t="n">
-        <v>7121.942255430539</v>
+        <v>4772.284144289555</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Composer 2.5</t>
+          <t>GPT-5.6 Luna (medium)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3830075380367747</v>
+        <v>0.4196699779001624</v>
       </c>
       <c r="F6" t="n">
-        <v>0.15929203539823</v>
+        <v>0.365781710914454</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6779026217228465</v>
+        <v>0.621722846441947</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3118279569892475</v>
+        <v>0.271505376344086</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08505141359918204</v>
+        <v>0.4430536771983641</v>
       </c>
       <c r="J6" t="n">
-        <v>625.1976421267894</v>
+        <v>191.3819171779141</v>
       </c>
       <c r="K6" t="n">
-        <v>116.8680981595092</v>
+        <v>57.08588957055215</v>
       </c>
       <c r="L6" t="n">
-        <v>3705076.4698364</v>
+        <v>4287327.734151328</v>
       </c>
       <c r="M6" t="n">
-        <v>1872461.576687117</v>
+        <v>2221162.702453987</v>
       </c>
       <c r="N6" t="n">
-        <v>18453.85787321063</v>
+        <v>11663.1390593047</v>
       </c>
       <c r="O6" t="n">
-        <v>1.052833075750478</v>
+        <v>0.8832984632099325</v>
       </c>
       <c r="P6" t="n">
-        <v>4.503247175194018</v>
+        <v>0.9472215207735825</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001033737201255894</v>
+        <v>9.788614351947498e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03675710004924502</v>
+        <v>0.1315704171288111</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0006126183341540836</v>
+        <v>0.002192840285480186</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2220619835190183</v>
+        <v>1.055719256867511</v>
       </c>
       <c r="U6" t="n">
-        <v>5926.248309626565</v>
+        <v>22401.94788186653</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (none)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.1909870904304247</v>
+        <v>0.6702814566291138</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0648967551622419</v>
+        <v>0.631268436578171</v>
       </c>
       <c r="G7" t="n">
-        <v>0.333333333333333</v>
+        <v>0.887640449438202</v>
       </c>
       <c r="H7" t="n">
-        <v>0.174731182795699</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3280835570961145</v>
+        <v>8.943547018021487</v>
       </c>
       <c r="J7" t="n">
-        <v>131.816209611452</v>
+        <v>1451.329194274025</v>
       </c>
       <c r="K7" t="n">
-        <v>54.28629856850716</v>
+        <v>165.7202546941811</v>
       </c>
       <c r="L7" t="n">
-        <v>3549957.210633946</v>
+        <v>23699428.05214722</v>
       </c>
       <c r="M7" t="n">
-        <v>1835572.532719836</v>
+        <v>11810977.87014315</v>
       </c>
       <c r="N7" t="n">
-        <v>7934.628834355828</v>
+        <v>81385.06339468302</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8748960056789892</v>
+        <v>0.9747033593278783</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821294188616518</v>
+        <v>0.07494581906691815</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.379982887070306e-05</v>
+        <v>2.82826005401588e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.08693335561387526</v>
+        <v>0.02771038270050364</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001448889260231254</v>
+        <v>0.0004618397116750606</v>
       </c>
       <c r="T7" t="n">
-        <v>1.717831065737049</v>
+        <v>13.34297246264148</v>
       </c>
       <c r="U7" t="n">
-        <v>26931.11280545826</v>
+        <v>16329.4641530325</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opus 4.8 (high)</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5757636668124306</v>
+        <v>0.5657152973570364</v>
       </c>
       <c r="F8" t="n">
-        <v>0.516224188790561</v>
+        <v>0.56047197640118</v>
       </c>
       <c r="G8" t="n">
-        <v>0.823970037453183</v>
+        <v>0.865168539325843</v>
       </c>
       <c r="H8" t="n">
-        <v>0.387096774193548</v>
+        <v>0.271505376344086</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7823013803681</v>
+        <v>1.396316917192255</v>
       </c>
       <c r="J8" t="n">
-        <v>761.0308312883442</v>
+        <v>384.9621257668713</v>
       </c>
       <c r="K8" t="n">
-        <v>104.7627811860941</v>
+        <v>110.7985685071575</v>
       </c>
       <c r="L8" t="n">
-        <v>9188690.866053157</v>
+        <v>15113684.86595342</v>
       </c>
       <c r="M8" t="n">
-        <v>4574601.889570553</v>
+        <v>7938344.274012004</v>
       </c>
       <c r="N8" t="n">
-        <v>40682.70756646217</v>
+        <v>64430.0844098625</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9682475638703767</v>
+        <v>0.8677594149804605</v>
       </c>
       <c r="P8" t="n">
-        <v>0.152225750650361</v>
+        <v>0.4051482083985556</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.266003233818007e-05</v>
+        <v>3.743066647045306e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04539345659657893</v>
+        <v>0.08817209686227062</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0007565576099429822</v>
+        <v>0.00146953494770451</v>
       </c>
       <c r="T8" t="n">
-        <v>6.569190795431485</v>
+        <v>2.468232560999683</v>
       </c>
       <c r="U8" t="n">
-        <v>12074.00605636132</v>
+        <v>39260.1865335347</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Opus 5 (high)</t>
+          <t>GLM-5.1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1052,59 +1052,59 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>friendliai</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6561729860226817</v>
+        <v>0.3691032797641257</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6076696165191739</v>
+        <v>0.185840707964602</v>
       </c>
       <c r="G9" t="n">
-        <v>0.868913857677903</v>
+        <v>0.6741573033707861</v>
       </c>
       <c r="H9" t="n">
-        <v>0.491935483870968</v>
+        <v>0.247311827956989</v>
       </c>
       <c r="I9" t="n">
-        <v>3.918602446063396</v>
+        <v>4.282000252842536</v>
       </c>
       <c r="J9" t="n">
-        <v>842.8052382413097</v>
+        <v>1140.250613496931</v>
       </c>
       <c r="K9" t="n">
-        <v>94.85071574642126</v>
+        <v>174.2367075664622</v>
       </c>
       <c r="L9" t="n">
-        <v>9911366.349693259</v>
+        <v>25761884.92944783</v>
       </c>
       <c r="M9" t="n">
-        <v>4937399.112474437</v>
+        <v>13139446.7402863</v>
       </c>
       <c r="N9" t="n">
-        <v>37331.49386503067</v>
+        <v>49883.45705521473</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9702723303233403</v>
+        <v>0.8889225409991813</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1674507672197952</v>
+        <v>0.08619879915212579</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.620408961504982e-05</v>
+        <v>1.432749508721747e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04671349604271027</v>
+        <v>0.01942221869798375</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0007785582673785045</v>
+        <v>0.0003237036449663959</v>
       </c>
       <c r="T9" t="n">
-        <v>5.971904557997063</v>
+        <v>11.60108968844421</v>
       </c>
       <c r="U9" t="n">
-        <v>11759.97241115327</v>
+        <v>22593.17787204784</v>
       </c>
     </row>
     <row r="10">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (high)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1125,278 +1125,278 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.3282816619106221</v>
+        <v>0.423892771774363</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08554572271386431</v>
+        <v>0.274336283185841</v>
       </c>
       <c r="G10" t="n">
-        <v>0.700374531835206</v>
+        <v>0.771535580524345</v>
       </c>
       <c r="H10" t="n">
-        <v>0.198924731182796</v>
+        <v>0.225806451612903</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2547256318476481</v>
+        <v>1.800661744734149</v>
       </c>
       <c r="J10" t="n">
-        <v>1072.531835378324</v>
+        <v>399.3926789366056</v>
       </c>
       <c r="K10" t="n">
-        <v>128.1457055214724</v>
+        <v>42.04907975460122</v>
       </c>
       <c r="L10" t="n">
-        <v>9942165.528629865</v>
+        <v>4636274.728016362</v>
       </c>
       <c r="M10" t="n">
-        <v>5181244.880368099</v>
+        <v>2310268.645194274</v>
       </c>
       <c r="N10" t="n">
-        <v>41975.79754601227</v>
+        <v>17168.18507157464</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8541357545221666</v>
+        <v>0.9576237577125707</v>
       </c>
       <c r="P10" t="n">
-        <v>1.288765718351297</v>
+        <v>0.2354094393430604</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.301913058732415e-05</v>
+        <v>9.142960601813308e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01836486252894251</v>
+        <v>0.06368060219375923</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0003060810421490419</v>
+        <v>0.001061343369895987</v>
       </c>
       <c r="T10" t="n">
-        <v>0.77593622002864</v>
+        <v>4.247918022279078</v>
       </c>
       <c r="U10" t="n">
-        <v>9269.809250112256</v>
+        <v>11608.31175063242</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>GPT-5.6 Sol (low)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.466554082589455</v>
+        <v>0.5523451808562168</v>
       </c>
       <c r="F11" t="n">
-        <v>0.315634218289085</v>
+        <v>0.533923303834809</v>
       </c>
       <c r="G11" t="n">
-        <v>0.745318352059925</v>
+        <v>0.779026217228465</v>
       </c>
       <c r="H11" t="n">
-        <v>0.338709677419355</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I11" t="n">
-        <v>2.72490571101738</v>
+        <v>1.660386587423313</v>
       </c>
       <c r="J11" t="n">
-        <v>826.6777535787322</v>
+        <v>212.899582822086</v>
       </c>
       <c r="K11" t="n">
-        <v>86.42229038854805</v>
+        <v>53.92126789366053</v>
       </c>
       <c r="L11" t="n">
-        <v>5728865.180470352</v>
+        <v>3200236.065439673</v>
       </c>
       <c r="M11" t="n">
-        <v>2855520.426380368</v>
+        <v>1658130.417177914</v>
       </c>
       <c r="N11" t="n">
-        <v>17872.17893660532</v>
+        <v>8962.606339468302</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9538631453697446</v>
+        <v>0.8829664546361214</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1712184317802544</v>
+        <v>0.332660589431392</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.143917999326175e-05</v>
+        <v>0.0001725951365966908</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03386234216922258</v>
+        <v>0.1556635781624228</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0005643723694870431</v>
+        <v>0.002594392969373714</v>
       </c>
       <c r="T11" t="n">
-        <v>5.840492694638288</v>
+        <v>3.006066939607345</v>
       </c>
       <c r="U11" t="n">
-        <v>6929.985905233071</v>
+        <v>15031.6690292156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gemini 3.6 Flash (high)</t>
+          <t>Opus 4.8 (medium)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.4724127134829677</v>
+        <v>0.5576883805320427</v>
       </c>
       <c r="F12" t="n">
-        <v>0.412979351032448</v>
+        <v>0.492625368731563</v>
       </c>
       <c r="G12" t="n">
-        <v>0.786516853932584</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H12" t="n">
-        <v>0.217741935483871</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I12" t="n">
-        <v>2.083890154754602</v>
+        <v>3.303841633946828</v>
       </c>
       <c r="J12" t="n">
-        <v>626.0057290388548</v>
+        <v>722.922882413088</v>
       </c>
       <c r="K12" t="n">
-        <v>65.01533742331287</v>
+        <v>92.91239658858525</v>
       </c>
       <c r="L12" t="n">
-        <v>13020159.54294479</v>
+        <v>7827354.369120649</v>
       </c>
       <c r="M12" t="n">
-        <v>6765842.061349694</v>
+        <v>3898584.399795501</v>
       </c>
       <c r="N12" t="n">
-        <v>42763.3517382413</v>
+        <v>34668.28732106339</v>
       </c>
       <c r="O12" t="n">
-        <v>0.837777048552074</v>
+        <v>0.963840128346697</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2266975120570109</v>
+        <v>0.1687999735828192</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.628317394458911e-05</v>
+        <v>7.12486434410271e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>0.04527875943323637</v>
+        <v>0.04628613043791069</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0007546459905539396</v>
+        <v>0.0007714355072985115</v>
       </c>
       <c r="T12" t="n">
-        <v>4.411164423138952</v>
+        <v>5.924171543245917</v>
       </c>
       <c r="U12" t="n">
-        <v>20798.78655892725</v>
+        <v>10827.37116162826</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Muse Spark 1.2 (xhigh)</t>
+          <t>Opus 4.8 (max)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5888788742875287</v>
+        <v>0.6214051234130329</v>
       </c>
       <c r="F13" t="n">
-        <v>0.528023598820059</v>
+        <v>0.557522123893805</v>
       </c>
       <c r="G13" t="n">
-        <v>0.797752808988764</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H13" t="n">
-        <v>0.440860215053763</v>
+        <v>0.467741935483871</v>
       </c>
       <c r="I13" t="n">
-        <v>1.914379785695295</v>
+        <v>7.724725797009217</v>
       </c>
       <c r="J13" t="n">
-        <v>1064.740692229038</v>
+        <v>1386.687798057262</v>
       </c>
       <c r="K13" t="n">
-        <v>65.87116564417177</v>
+        <v>165.0175845341703</v>
       </c>
       <c r="L13" t="n">
-        <v>16350688.07453988</v>
+        <v>17920579.42791411</v>
       </c>
       <c r="M13" t="n">
-        <v>8360784.971370144</v>
+        <v>8919829.832822086</v>
       </c>
       <c r="N13" t="n">
-        <v>47157.38036809816</v>
+        <v>89374.98517382414</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.9657541826994763</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3076081761245981</v>
+        <v>0.0804436480649737</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.601554085081525e-05</v>
+        <v>3.467550398761645e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>0.03318435438330296</v>
+        <v>0.02688731195083492</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0005530725730550494</v>
+        <v>0.0004481218658472487</v>
       </c>
       <c r="T13" t="n">
-        <v>3.250888882728999</v>
+        <v>12.43106229086364</v>
       </c>
       <c r="U13" t="n">
-        <v>15356.49777816762</v>
+        <v>12923.29784182185</v>
       </c>
     </row>
     <row r="14">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (high)</t>
+          <t>GPT-5.6 Sol (high)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1421,201 +1421,201 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.516945881593198</v>
+        <v>0.6411644486641199</v>
       </c>
       <c r="F14" t="n">
-        <v>0.533923303834808</v>
+        <v>0.648967551622419</v>
       </c>
       <c r="G14" t="n">
-        <v>0.726591760299625</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H14" t="n">
-        <v>0.290322580645161</v>
+        <v>0.454301075268817</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9174253706543963</v>
+        <v>3.85057263394683</v>
       </c>
       <c r="J14" t="n">
-        <v>342.6686574642128</v>
+        <v>369.9402760736197</v>
       </c>
       <c r="K14" t="n">
-        <v>83.81901840490798</v>
+        <v>84.6717791411043</v>
       </c>
       <c r="L14" t="n">
-        <v>9641370.493865021</v>
+        <v>8030278.504089991</v>
       </c>
       <c r="M14" t="n">
-        <v>4959371.744376278</v>
+        <v>4136516.062372188</v>
       </c>
       <c r="N14" t="n">
-        <v>22230.90593047035</v>
+        <v>19997.77709611452</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9032288062243126</v>
+        <v>0.9060190184699437</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5634745867388236</v>
+        <v>0.1665114541695913</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.361746879472582e-05</v>
+        <v>7.984336388053805e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.09051528997463437</v>
+        <v>0.1039893988514825</v>
       </c>
       <c r="S14" t="n">
-        <v>0.001508588166243906</v>
+        <v>0.001733156647524709</v>
       </c>
       <c r="T14" t="n">
-        <v>1.774702929882995</v>
+        <v>6.005592858383808</v>
       </c>
       <c r="U14" t="n">
-        <v>28136.13175249894</v>
+        <v>21706.95926737085</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>GPT-5.6 Terra (xhigh)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.5127556084440553</v>
+        <v>0.5602917313962744</v>
       </c>
       <c r="F15" t="n">
-        <v>0.395280235988201</v>
+        <v>0.584070796460177</v>
       </c>
       <c r="G15" t="n">
-        <v>0.782771535580524</v>
+        <v>0.771535580524345</v>
       </c>
       <c r="H15" t="n">
-        <v>0.360215053763441</v>
+        <v>0.325268817204301</v>
       </c>
       <c r="I15" t="n">
-        <v>2.942840985557261</v>
+        <v>1.879152746625766</v>
       </c>
       <c r="J15" t="n">
-        <v>752.2755521472382</v>
+        <v>403.2234447852761</v>
       </c>
       <c r="K15" t="n">
-        <v>54.41308793456033</v>
+        <v>74.95092024539876</v>
       </c>
       <c r="L15" t="n">
-        <v>7582747.093047047</v>
+        <v>6631652.20858896</v>
       </c>
       <c r="M15" t="n">
-        <v>3744700.533231084</v>
+        <v>3404439.702453988</v>
       </c>
       <c r="N15" t="n">
-        <v>25943.59151329243</v>
+        <v>26011.59611451943</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9584168731547836</v>
+        <v>0.910418152728672</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1742382993034736</v>
+        <v>0.2981618883309738</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.762135175446157e-05</v>
+        <v>8.448750232568207e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.04089636625679125</v>
+        <v>0.08337189793534551</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0006816061042798542</v>
+        <v>0.001389531632255759</v>
       </c>
       <c r="T15" t="n">
-        <v>5.739266303663147</v>
+        <v>3.353882703110441</v>
       </c>
       <c r="U15" t="n">
-        <v>10079.74680474918</v>
+        <v>16446.59380389064</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Opus 4.8 (low)</t>
+          <t>GPT-5.6 Terra (medium)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4904379267565557</v>
+        <v>0.4804969202427884</v>
       </c>
       <c r="F16" t="n">
-        <v>0.410029498525074</v>
+        <v>0.457227138643068</v>
       </c>
       <c r="G16" t="n">
-        <v>0.779026217228464</v>
+        <v>0.696629213483146</v>
       </c>
       <c r="H16" t="n">
-        <v>0.282258064516129</v>
+        <v>0.287634408602151</v>
       </c>
       <c r="I16" t="n">
-        <v>2.182594679703477</v>
+        <v>0.8847820614519432</v>
       </c>
       <c r="J16" t="n">
-        <v>516.6536431492842</v>
+        <v>240.094656441718</v>
       </c>
       <c r="K16" t="n">
-        <v>68.16359918200409</v>
+        <v>50.95501022494887</v>
       </c>
       <c r="L16" t="n">
-        <v>5214050.029652352</v>
+        <v>3164606.548057258</v>
       </c>
       <c r="M16" t="n">
-        <v>2595804.632924335</v>
+        <v>1632285.212678937</v>
       </c>
       <c r="N16" t="n">
-        <v>23270.04396728017</v>
+        <v>11855.54703476483</v>
       </c>
       <c r="O16" t="n">
-        <v>0.966158217610491</v>
+        <v>0.894438452837132</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2247040787358583</v>
+        <v>0.5430681081556789</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.406084022351733e-05</v>
+        <v>0.0001518346476713713</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0569555174836748</v>
+        <v>0.1200768715215685</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0009492586247279134</v>
+        <v>0.002001281192026142</v>
       </c>
       <c r="T16" t="n">
-        <v>4.450297500720978</v>
+        <v>1.841389661779466</v>
       </c>
       <c r="U16" t="n">
-        <v>10091.9641210113</v>
+        <v>13180.66213949852</v>
       </c>
     </row>
     <row r="17">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (max)</t>
+          <t>GPT-5.6 Luna (low)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1640,128 +1640,128 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.6042010361726691</v>
+        <v>0.250636604330228</v>
       </c>
       <c r="F17" t="n">
-        <v>0.669616519174041</v>
+        <v>0.103244837758112</v>
       </c>
       <c r="G17" t="n">
-        <v>0.782771535580525</v>
+        <v>0.49812734082397</v>
       </c>
       <c r="H17" t="n">
-        <v>0.360215053763441</v>
+        <v>0.150537634408602</v>
       </c>
       <c r="I17" t="n">
-        <v>2.695350269529651</v>
+        <v>0.1920449385685073</v>
       </c>
       <c r="J17" t="n">
-        <v>491.0206543967283</v>
+        <v>100.0260337423312</v>
       </c>
       <c r="K17" t="n">
-        <v>95.80674846625767</v>
+        <v>34.30674846625767</v>
       </c>
       <c r="L17" t="n">
-        <v>9630511.582822077</v>
+        <v>1435665.844580776</v>
       </c>
       <c r="M17" t="n">
-        <v>4933733.868098159</v>
+        <v>762148.6063394684</v>
       </c>
       <c r="N17" t="n">
-        <v>37445.42126789366</v>
+        <v>5609.407975460122</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9184675548550253</v>
+        <v>0.8430087375482057</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2241641997342722</v>
+        <v>1.305093517165617</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.273820772412353e-05</v>
+        <v>0.0001745786495348544</v>
       </c>
       <c r="R17" t="n">
-        <v>0.07383001477789097</v>
+        <v>0.1503428227350525</v>
       </c>
       <c r="S17" t="n">
-        <v>0.001230500246298183</v>
+        <v>0.002505713712250875</v>
       </c>
       <c r="T17" t="n">
-        <v>4.461015635794725</v>
+        <v>0.7662286164533141</v>
       </c>
       <c r="U17" t="n">
-        <v>19613.25149275889</v>
+        <v>14352.92184311812</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (none)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.4336881923573268</v>
+        <v>0.6131027159527611</v>
       </c>
       <c r="F18" t="n">
-        <v>0.353982300884956</v>
+        <v>0.519174041297935</v>
       </c>
       <c r="G18" t="n">
-        <v>0.602996254681648</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H18" t="n">
-        <v>0.344086021505376</v>
+        <v>0.481182795698925</v>
       </c>
       <c r="I18" t="n">
-        <v>1.39701781850716</v>
+        <v>3.230610966002048</v>
       </c>
       <c r="J18" t="n">
-        <v>197.8853650306747</v>
+        <v>1792.147180981595</v>
       </c>
       <c r="K18" t="n">
-        <v>55.10736196319019</v>
+        <v>159.5848670756646</v>
       </c>
       <c r="L18" t="n">
-        <v>3404912.347648262</v>
+        <v>12503741.56441715</v>
       </c>
       <c r="M18" t="n">
-        <v>1731981.235173824</v>
+        <v>6469207.32413088</v>
       </c>
       <c r="N18" t="n">
-        <v>7689.902862985686</v>
+        <v>63117.84253578731</v>
       </c>
       <c r="O18" t="n">
-        <v>0.891939654668184</v>
+        <v>0.8998815214008218</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3104385546211299</v>
+        <v>0.189779184929682</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0001273713235692751</v>
+        <v>4.903354030424894e-05</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1314967963265297</v>
+        <v>0.02052630684998603</v>
       </c>
       <c r="S18" t="n">
-        <v>0.002191613272108827</v>
+        <v>0.0003421051141664338</v>
       </c>
       <c r="T18" t="n">
-        <v>3.221249374841456</v>
+        <v>5.269281772764097</v>
       </c>
       <c r="U18" t="n">
-        <v>17206.48895445329</v>
+        <v>6976.961321652501</v>
       </c>
     </row>
     <row r="19">
@@ -1798,7 +1798,7 @@
         <v>0.432795698924731</v>
       </c>
       <c r="I19" t="n">
-        <v>4.799269930470346</v>
+        <v>4.799269930470349</v>
       </c>
       <c r="J19" t="n">
         <v>440.5130695296522</v>
@@ -1831,7 +1831,7 @@
         <v>0.001437842339249544</v>
       </c>
       <c r="T19" t="n">
-        <v>7.577136504548331</v>
+        <v>7.577136504548336</v>
       </c>
       <c r="U19" t="n">
         <v>22443.36544710738</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>GPT-5.6 Sol (none)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1859,55 +1859,55 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5716614223656344</v>
+        <v>0.4336881923573268</v>
       </c>
       <c r="F20" t="n">
-        <v>0.634218289085546</v>
+        <v>0.353982300884956</v>
       </c>
       <c r="G20" t="n">
-        <v>0.752808988764045</v>
+        <v>0.602996254681648</v>
       </c>
       <c r="H20" t="n">
-        <v>0.327956989247312</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I20" t="n">
-        <v>1.508396035337423</v>
+        <v>1.397017818507157</v>
       </c>
       <c r="J20" t="n">
-        <v>482.0907147239265</v>
+        <v>197.8853650306747</v>
       </c>
       <c r="K20" t="n">
-        <v>114.6288343558282</v>
+        <v>55.10736196319019</v>
       </c>
       <c r="L20" t="n">
-        <v>15963259.28016359</v>
+        <v>3404912.347648262</v>
       </c>
       <c r="M20" t="n">
-        <v>8170928.992842535</v>
+        <v>1731981.235173824</v>
       </c>
       <c r="N20" t="n">
-        <v>41094.49386503067</v>
+        <v>7689.902862985686</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9181831202060821</v>
+        <v>0.8919396546681845</v>
       </c>
       <c r="P20" t="n">
-        <v>0.378986293369404</v>
+        <v>0.3104385546211307</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.58110716823348e-05</v>
+        <v>0.0001273713235692751</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0711477825528751</v>
+        <v>0.1314967963265297</v>
       </c>
       <c r="S20" t="n">
-        <v>0.001185796375881252</v>
+        <v>0.002191613272108827</v>
       </c>
       <c r="T20" t="n">
-        <v>2.638617853720858</v>
+        <v>3.221249374841448</v>
       </c>
       <c r="U20" t="n">
-        <v>33112.56324300934</v>
+        <v>17206.48895445329</v>
       </c>
     </row>
     <row r="21">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Opus 4.8 (low)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1928,424 +1928,424 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.6131027159527611</v>
+        <v>0.4904379267565557</v>
       </c>
       <c r="F21" t="n">
-        <v>0.519174041297935</v>
+        <v>0.410029498525074</v>
       </c>
       <c r="G21" t="n">
-        <v>0.838951310861423</v>
+        <v>0.779026217228464</v>
       </c>
       <c r="H21" t="n">
-        <v>0.481182795698925</v>
+        <v>0.282258064516129</v>
       </c>
       <c r="I21" t="n">
-        <v>3.230610966002048</v>
+        <v>2.182594679703477</v>
       </c>
       <c r="J21" t="n">
-        <v>1792.147180981595</v>
+        <v>516.6536431492842</v>
       </c>
       <c r="K21" t="n">
-        <v>159.5848670756646</v>
+        <v>68.16359918200409</v>
       </c>
       <c r="L21" t="n">
-        <v>12503741.56441715</v>
+        <v>5214050.029652352</v>
       </c>
       <c r="M21" t="n">
-        <v>6469207.32413088</v>
+        <v>2595804.632924335</v>
       </c>
       <c r="N21" t="n">
-        <v>63117.84253578731</v>
+        <v>23270.04396728017</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8998815214008221</v>
+        <v>0.966158217610491</v>
       </c>
       <c r="P21" t="n">
-        <v>0.189779184929682</v>
+        <v>0.2247040787358583</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.903354030424894e-05</v>
+        <v>9.406084022351733e-05</v>
       </c>
       <c r="R21" t="n">
-        <v>0.02052630684998603</v>
+        <v>0.0569555174836748</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0003421051141664338</v>
+        <v>0.0009492586247279134</v>
       </c>
       <c r="T21" t="n">
-        <v>5.269281772764097</v>
+        <v>4.450297500720978</v>
       </c>
       <c r="U21" t="n">
-        <v>6976.961321652501</v>
+        <v>10091.9641210113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (low)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.250636604330228</v>
+        <v>0.5127556084440553</v>
       </c>
       <c r="F22" t="n">
-        <v>0.103244837758112</v>
+        <v>0.395280235988201</v>
       </c>
       <c r="G22" t="n">
-        <v>0.49812734082397</v>
+        <v>0.782771535580524</v>
       </c>
       <c r="H22" t="n">
-        <v>0.150537634408602</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1920449385685073</v>
+        <v>2.942840985557261</v>
       </c>
       <c r="J22" t="n">
-        <v>100.0260337423312</v>
+        <v>752.2755521472382</v>
       </c>
       <c r="K22" t="n">
-        <v>34.30674846625767</v>
+        <v>54.41308793456033</v>
       </c>
       <c r="L22" t="n">
-        <v>1435665.844580776</v>
+        <v>7582747.093047052</v>
       </c>
       <c r="M22" t="n">
-        <v>762148.6063394684</v>
+        <v>3744700.533231084</v>
       </c>
       <c r="N22" t="n">
-        <v>5609.407975460122</v>
+        <v>25943.59151329243</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8430087375482054</v>
+        <v>0.9584168731547833</v>
       </c>
       <c r="P22" t="n">
-        <v>1.305093517165617</v>
+        <v>0.1742382993034736</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.0001745786495348544</v>
+        <v>6.762135175446153e-05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1503428227350525</v>
+        <v>0.04089636625679125</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002505713712250875</v>
+        <v>0.0006816061042798542</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7662286164533141</v>
+        <v>5.739266303663147</v>
       </c>
       <c r="U22" t="n">
-        <v>14352.92184311812</v>
+        <v>10079.74680474918</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-5.5 (xhigh)</t>
+          <t>Muse Spark 1.2 (xhigh)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.6103327520587847</v>
+        <v>0.5888788742875287</v>
       </c>
       <c r="F23" t="n">
-        <v>0.64306784660767</v>
+        <v>0.528023598820059</v>
       </c>
       <c r="G23" t="n">
-        <v>0.827715355805243</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="H23" t="n">
-        <v>0.360215053763441</v>
+        <v>0.440860215053763</v>
       </c>
       <c r="I23" t="n">
-        <v>4.75237007157464</v>
+        <v>1.914379785695295</v>
       </c>
       <c r="J23" t="n">
-        <v>614.9898987730064</v>
+        <v>1064.740692229039</v>
       </c>
       <c r="K23" t="n">
-        <v>107.1319018404908</v>
+        <v>65.87116564417177</v>
       </c>
       <c r="L23" t="n">
-        <v>12150851.17995908</v>
+        <v>16350688.07453988</v>
       </c>
       <c r="M23" t="n">
-        <v>6164087.486707566</v>
+        <v>8360784.971370144</v>
       </c>
       <c r="N23" t="n">
-        <v>25286.0654396728</v>
+        <v>47157.38036809816</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9341674523911518</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1284270254350285</v>
+        <v>0.3076081761245981</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.022962943249873e-05</v>
+        <v>3.601554085081526e-05</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0595456367601959</v>
+        <v>0.03318435438330295</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0009924272793365983</v>
+        <v>0.0005530725730550492</v>
       </c>
       <c r="T23" t="n">
-        <v>7.786523098332615</v>
+        <v>3.250888882728999</v>
       </c>
       <c r="U23" t="n">
-        <v>19757.80611063984</v>
+        <v>15356.49777816761</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (medium)</t>
+          <t>Gemini 3.6 Flash (high)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.4804969202427884</v>
+        <v>0.4724127134829677</v>
       </c>
       <c r="F24" t="n">
-        <v>0.457227138643068</v>
+        <v>0.412979351032448</v>
       </c>
       <c r="G24" t="n">
-        <v>0.696629213483146</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H24" t="n">
-        <v>0.287634408602151</v>
+        <v>0.217741935483871</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8847820614519432</v>
+        <v>2.083890154754602</v>
       </c>
       <c r="J24" t="n">
-        <v>240.0946564417176</v>
+        <v>626.0057290388545</v>
       </c>
       <c r="K24" t="n">
-        <v>50.95501022494887</v>
+        <v>65.01533742331287</v>
       </c>
       <c r="L24" t="n">
-        <v>3164606.548057258</v>
+        <v>13020159.54294479</v>
       </c>
       <c r="M24" t="n">
-        <v>1632285.212678937</v>
+        <v>6765842.061349694</v>
       </c>
       <c r="N24" t="n">
-        <v>11855.54703476483</v>
+        <v>42763.3517382413</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8944384528371319</v>
+        <v>0.8377770485520734</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5430681081556789</v>
+        <v>0.2266975120570109</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0001518346476713713</v>
+        <v>3.628317394458911e-05</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1200768715215687</v>
+        <v>0.0452787594332364</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002001281192026145</v>
+        <v>0.0007546459905539399</v>
       </c>
       <c r="T24" t="n">
-        <v>1.841389661779466</v>
+        <v>4.411164423138952</v>
       </c>
       <c r="U24" t="n">
-        <v>13180.66213949855</v>
+        <v>20798.78655892726</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (xhigh)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5602917313962741</v>
+        <v>0.466554082589455</v>
       </c>
       <c r="F25" t="n">
-        <v>0.584070796460177</v>
+        <v>0.315634218289085</v>
       </c>
       <c r="G25" t="n">
-        <v>0.771535580524344</v>
+        <v>0.745318352059925</v>
       </c>
       <c r="H25" t="n">
-        <v>0.325268817204301</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="I25" t="n">
-        <v>1.879152746625766</v>
+        <v>2.72490571101738</v>
       </c>
       <c r="J25" t="n">
-        <v>403.2234447852764</v>
+        <v>826.6777535787326</v>
       </c>
       <c r="K25" t="n">
-        <v>74.95092024539876</v>
+        <v>86.42229038854805</v>
       </c>
       <c r="L25" t="n">
-        <v>6631652.208588957</v>
+        <v>5728865.180470356</v>
       </c>
       <c r="M25" t="n">
-        <v>3404439.702453988</v>
+        <v>2855520.426380368</v>
       </c>
       <c r="N25" t="n">
-        <v>26011.59611451943</v>
+        <v>17872.17893660532</v>
       </c>
       <c r="O25" t="n">
-        <v>0.910418152728672</v>
+        <v>0.9538631453697453</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2981618883309737</v>
+        <v>0.1712184317802544</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.448750232568207e-05</v>
+        <v>8.14391799932617e-05</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0833718979353454</v>
+        <v>0.03386234216922257</v>
       </c>
       <c r="S25" t="n">
-        <v>0.001389531632255757</v>
+        <v>0.0005643723694870429</v>
       </c>
       <c r="T25" t="n">
-        <v>3.353882703110443</v>
+        <v>5.840492694638288</v>
       </c>
       <c r="U25" t="n">
-        <v>16446.59380389062</v>
+        <v>6929.985905233072</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin CLI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (high)</t>
+          <t>SWE-1.7 Lightning Max</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cognition</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.6411644486641197</v>
+        <v>0.5221389513465007</v>
       </c>
       <c r="F26" t="n">
-        <v>0.648967551622419</v>
+        <v>0.404129793510325</v>
       </c>
       <c r="G26" t="n">
-        <v>0.820224719101123</v>
+        <v>0.7940074906367039</v>
       </c>
       <c r="H26" t="n">
-        <v>0.454301075268817</v>
+        <v>0.368279569892473</v>
       </c>
       <c r="I26" t="n">
-        <v>3.85057263394683</v>
+        <v>8.521259638036815</v>
       </c>
       <c r="J26" t="n">
-        <v>369.9402760736197</v>
+        <v>637.3248271983654</v>
       </c>
       <c r="K26" t="n">
-        <v>84.6717791411043</v>
+        <v>86.57157464212679</v>
       </c>
       <c r="L26" t="n">
-        <v>8030278.504089991</v>
+        <v>15573672.60122699</v>
       </c>
       <c r="M26" t="n">
-        <v>4136516.062372188</v>
+        <v>7834231.955010225</v>
       </c>
       <c r="N26" t="n">
-        <v>19997.77709611452</v>
+        <v>38917.19427402863</v>
       </c>
       <c r="O26" t="n">
-        <v>0.906019018469944</v>
+        <v>0.9746033359706329</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1665114541695912</v>
+        <v>0.06127485530610995</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.984336388053802e-05</v>
+        <v>3.352702761359986e-05</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1039893988514825</v>
+        <v>0.04915599666579314</v>
       </c>
       <c r="S26" t="n">
-        <v>0.001733156647524708</v>
+        <v>0.0008192666110965524</v>
       </c>
       <c r="T26" t="n">
-        <v>6.00559285838381</v>
+        <v>16.31990797863681</v>
       </c>
       <c r="U26" t="n">
-        <v>21706.95926737085</v>
+        <v>24436.00490143738</v>
       </c>
     </row>
     <row r="27">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Opus 4.8 (xhigh)</t>
+          <t>Opus 4.8 (high)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2370,128 +2370,128 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.590718121759733</v>
+        <v>0.5757636668124304</v>
       </c>
       <c r="F27" t="n">
-        <v>0.513274336283186</v>
+        <v>0.51622418879056</v>
       </c>
       <c r="G27" t="n">
-        <v>0.831460674157303</v>
+        <v>0.823970037453183</v>
       </c>
       <c r="H27" t="n">
-        <v>0.42741935483871</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="I27" t="n">
-        <v>5.665366469580767</v>
+        <v>3.7823013803681</v>
       </c>
       <c r="J27" t="n">
-        <v>1065.615385480571</v>
+        <v>761.0308312883442</v>
       </c>
       <c r="K27" t="n">
-        <v>136.1303390500093</v>
+        <v>104.7627811860941</v>
       </c>
       <c r="L27" t="n">
-        <v>13628306.24233129</v>
+        <v>9188690.866053157</v>
       </c>
       <c r="M27" t="n">
-        <v>6783846.309815951</v>
+        <v>4574601.889570553</v>
       </c>
       <c r="N27" t="n">
-        <v>62541.86503067485</v>
+        <v>40682.70756646217</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9687226730983397</v>
+        <v>0.9682475638703767</v>
       </c>
       <c r="P27" t="n">
-        <v>0.104268298428971</v>
+        <v>0.152225750650361</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.3344940395079e-05</v>
+        <v>6.266003233818004e-05</v>
       </c>
       <c r="R27" t="n">
-        <v>0.03326067527600483</v>
+        <v>0.04539345659657892</v>
       </c>
       <c r="S27" t="n">
-        <v>0.000554344587933414</v>
+        <v>0.0007565576099429819</v>
       </c>
       <c r="T27" t="n">
-        <v>9.590642746330172</v>
+        <v>6.569190795431488</v>
       </c>
       <c r="U27" t="n">
-        <v>12789.14177481138</v>
+        <v>12074.00605636132</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Opus 4.8 (max)</t>
+          <t>GPT-5.6 Luna (none)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.6214051234130329</v>
+        <v>0.1909870904304247</v>
       </c>
       <c r="F28" t="n">
-        <v>0.557522123893805</v>
+        <v>0.0648967551622419</v>
       </c>
       <c r="G28" t="n">
-        <v>0.838951310861423</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="H28" t="n">
-        <v>0.467741935483871</v>
+        <v>0.174731182795699</v>
       </c>
       <c r="I28" t="n">
-        <v>7.724725797009214</v>
+        <v>0.3280835570961148</v>
       </c>
       <c r="J28" t="n">
-        <v>1386.687798057262</v>
+        <v>131.816209611452</v>
       </c>
       <c r="K28" t="n">
-        <v>165.0175845341703</v>
+        <v>54.28629856850716</v>
       </c>
       <c r="L28" t="n">
-        <v>17920579.42791411</v>
+        <v>3549957.21063395</v>
       </c>
       <c r="M28" t="n">
-        <v>8919829.832822086</v>
+        <v>1835572.532719836</v>
       </c>
       <c r="N28" t="n">
-        <v>89374.98517382414</v>
+        <v>7934.628834355828</v>
       </c>
       <c r="O28" t="n">
-        <v>0.9657541826994763</v>
+        <v>0.8748960056789888</v>
       </c>
       <c r="P28" t="n">
-        <v>0.08044364806497373</v>
+        <v>0.5821294188616513</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.467550398761645e-05</v>
+        <v>5.3799828870703e-05</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02688731195083492</v>
+        <v>0.08693335561387526</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0004481218658472487</v>
+        <v>0.001448889260231254</v>
       </c>
       <c r="T28" t="n">
-        <v>12.43106229086363</v>
+        <v>1.71783106573705</v>
       </c>
       <c r="U28" t="n">
-        <v>12923.29784182185</v>
+        <v>26931.11280545829</v>
       </c>
     </row>
     <row r="29">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Opus 4.8 (medium)</t>
+          <t>Qwen3.7 Plus (thinking)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2512,59 +2512,59 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.5576883805320427</v>
+        <v>0.3812184526692477</v>
       </c>
       <c r="F29" t="n">
-        <v>0.492625368731563</v>
+        <v>0.191740412979351</v>
       </c>
       <c r="G29" t="n">
-        <v>0.820224719101124</v>
+        <v>0.715355805243446</v>
       </c>
       <c r="H29" t="n">
-        <v>0.360215053763441</v>
+        <v>0.236559139784946</v>
       </c>
       <c r="I29" t="n">
-        <v>3.303841633946831</v>
+        <v>6.300658805725988</v>
       </c>
       <c r="J29" t="n">
-        <v>722.9228824130877</v>
+        <v>643.9465817995912</v>
       </c>
       <c r="K29" t="n">
-        <v>92.91239658858525</v>
+        <v>145.9662576687116</v>
       </c>
       <c r="L29" t="n">
-        <v>7827354.369120649</v>
+        <v>8784635.035787327</v>
       </c>
       <c r="M29" t="n">
-        <v>3898584.399795501</v>
+        <v>4715248.469325154</v>
       </c>
       <c r="N29" t="n">
-        <v>34668.28732106339</v>
+        <v>32611.0408997955</v>
       </c>
       <c r="O29" t="n">
-        <v>0.963840128346697</v>
+        <v>0.8105104948122449</v>
       </c>
       <c r="P29" t="n">
-        <v>0.168799973582819</v>
+        <v>0.06050453840204764</v>
       </c>
       <c r="Q29" t="n">
-        <v>7.12486434410271e-05</v>
+        <v>4.339604902380339e-05</v>
       </c>
       <c r="R29" t="n">
-        <v>0.04628613043791071</v>
+        <v>0.03552019345491832</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0007714355072985119</v>
+        <v>0.0005920032242486387</v>
       </c>
       <c r="T29" t="n">
-        <v>5.924171543245923</v>
+        <v>16.52768579697415</v>
       </c>
       <c r="U29" t="n">
-        <v>10827.37116162827</v>
+        <v>13641.86919237546</v>
       </c>
     </row>
     <row r="30">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (medium)</t>
+          <t>GPT-5.6 Luna (high)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2589,347 +2589,347 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.616195748748264</v>
+        <v>0.516945881593198</v>
       </c>
       <c r="F30" t="n">
-        <v>0.640117994100295</v>
+        <v>0.533923303834808</v>
       </c>
       <c r="G30" t="n">
-        <v>0.805243445692884</v>
+        <v>0.726591760299625</v>
       </c>
       <c r="H30" t="n">
-        <v>0.403225806451613</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="I30" t="n">
-        <v>2.813450298568507</v>
+        <v>0.9174253706543963</v>
       </c>
       <c r="J30" t="n">
-        <v>297.9599253578734</v>
+        <v>342.6686574642128</v>
       </c>
       <c r="K30" t="n">
-        <v>71.35378323108384</v>
+        <v>83.81901840490798</v>
       </c>
       <c r="L30" t="n">
-        <v>5765545.476482615</v>
+        <v>9641370.493865017</v>
       </c>
       <c r="M30" t="n">
-        <v>2974758.351738241</v>
+        <v>4959371.744376278</v>
       </c>
       <c r="N30" t="n">
-        <v>14440.59713701431</v>
+        <v>22230.90593047035</v>
       </c>
       <c r="O30" t="n">
-        <v>0.8970664465490255</v>
+        <v>0.9032288062243129</v>
       </c>
       <c r="P30" t="n">
-        <v>0.21901781917448</v>
+        <v>0.5634745867388236</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.00010687553350532</v>
+        <v>5.361746879472584e-05</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1240829446459615</v>
+        <v>0.09051528997463437</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002068049077432692</v>
+        <v>0.001508588166243906</v>
       </c>
       <c r="T30" t="n">
-        <v>4.565838541216378</v>
+        <v>1.774702929882995</v>
       </c>
       <c r="U30" t="n">
-        <v>19350.07021349512</v>
+        <v>28136.13175249893</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Muse Spark 1.1 (xhigh)</t>
+          <t>GPT-5.6 Terra (low)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5492139250715363</v>
+        <v>0.3864628427996264</v>
       </c>
       <c r="F31" t="n">
-        <v>0.542772861356932</v>
+        <v>0.297935103244838</v>
       </c>
       <c r="G31" t="n">
-        <v>0.771535580524344</v>
+        <v>0.632958801498127</v>
       </c>
       <c r="H31" t="n">
-        <v>0.333333333333333</v>
+        <v>0.228494623655914</v>
       </c>
       <c r="I31" t="n">
-        <v>1.435218435173823</v>
+        <v>0.4909580805725969</v>
       </c>
       <c r="J31" t="n">
-        <v>761.3780071574632</v>
+        <v>154.8149498977502</v>
       </c>
       <c r="K31" t="n">
-        <v>55.51329243353784</v>
+        <v>37.80981595092025</v>
       </c>
       <c r="L31" t="n">
-        <v>12289527.21472391</v>
+        <v>1657646.844580775</v>
       </c>
       <c r="M31" t="n">
-        <v>6284599.100204499</v>
+        <v>861642.4202453988</v>
       </c>
       <c r="N31" t="n">
-        <v>34558.96932515338</v>
+        <v>6854.071574642127</v>
       </c>
       <c r="O31" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.8771903855272027</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3826692241484618</v>
+        <v>0.7871605705091984</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.46895893939297e-05</v>
+        <v>0.0002331394313952103</v>
       </c>
       <c r="R31" t="n">
-        <v>0.04328051926180354</v>
+        <v>0.1497773347037368</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0007213419876967256</v>
+        <v>0.002496288911728947</v>
       </c>
       <c r="T31" t="n">
-        <v>2.61322295312684</v>
+        <v>1.270388834838513</v>
       </c>
       <c r="U31" t="n">
-        <v>16141.16391489395</v>
+        <v>10707.27888796005</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (low)</t>
+          <t>Opus 5 (low)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.5523451808562161</v>
+        <v>0.5940064571013326</v>
       </c>
       <c r="F32" t="n">
-        <v>0.533923303834808</v>
+        <v>0.569321533923304</v>
       </c>
       <c r="G32" t="n">
-        <v>0.779026217228464</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H32" t="n">
-        <v>0.344086021505376</v>
+        <v>0.39247311827957</v>
       </c>
       <c r="I32" t="n">
-        <v>1.660386587423309</v>
+        <v>2.295157744887527</v>
       </c>
       <c r="J32" t="n">
-        <v>212.899582822086</v>
+        <v>598.7677147239262</v>
       </c>
       <c r="K32" t="n">
-        <v>53.92126789366053</v>
+        <v>64.39263803680981</v>
       </c>
       <c r="L32" t="n">
-        <v>3200236.065439673</v>
+        <v>5258606.375255628</v>
       </c>
       <c r="M32" t="n">
-        <v>1658130.417177914</v>
+        <v>2618171.039877301</v>
       </c>
       <c r="N32" t="n">
-        <v>8962.606339468302</v>
+        <v>22632.92229038855</v>
       </c>
       <c r="O32" t="n">
-        <v>0.8829664546361218</v>
+        <v>0.9637890151908798</v>
       </c>
       <c r="P32" t="n">
-        <v>0.3326605894313923</v>
+        <v>0.2588085539760761</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.0001725951365966906</v>
+        <v>0.0001129589124404576</v>
       </c>
       <c r="R32" t="n">
-        <v>0.1556635781624227</v>
+        <v>0.05952289435396941</v>
       </c>
       <c r="S32" t="n">
-        <v>0.002594392969373711</v>
+        <v>0.0009920482392328236</v>
       </c>
       <c r="T32" t="n">
-        <v>3.006066939607342</v>
+        <v>3.863859925172484</v>
       </c>
       <c r="U32" t="n">
-        <v>15031.6690292156</v>
+        <v>8782.381290681667</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sonnet 4.6 (medium)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.386493136077762</v>
+        <v>0.5531133827505798</v>
       </c>
       <c r="F33" t="n">
-        <v>0.289085545722714</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6741573033707871</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H33" t="n">
-        <v>0.196236559139785</v>
+        <v>0.306451612903226</v>
       </c>
       <c r="I33" t="n">
-        <v>2.041513021472394</v>
+        <v>2.65253587423313</v>
       </c>
       <c r="J33" t="n">
-        <v>827.6555807770972</v>
+        <v>386.3044764826176</v>
       </c>
       <c r="K33" t="n">
-        <v>67.41768916155419</v>
+        <v>78.53885480572598</v>
       </c>
       <c r="L33" t="n">
-        <v>8444053.035787314</v>
+        <v>6885560.579754606</v>
       </c>
       <c r="M33" t="n">
-        <v>4205086.787321064</v>
+        <v>3492715.358895706</v>
       </c>
       <c r="N33" t="n">
-        <v>40070.1308793456</v>
+        <v>13239.49488752556</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9487221679807681</v>
+        <v>0.9409891933709401</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1893170075393459</v>
+        <v>0.2085224890353234</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.577104554409349e-05</v>
+        <v>8.032946284386509e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0280184036732921</v>
+        <v>0.085908409002162</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0004669733945548682</v>
+        <v>0.0014318068167027</v>
       </c>
       <c r="T33" t="n">
-        <v>5.282145608561709</v>
+        <v>4.795645806005133</v>
       </c>
       <c r="U33" t="n">
-        <v>10202.37551936649</v>
+        <v>17824.1801452809</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.423892771774363</v>
+        <v>0.4708693600598454</v>
       </c>
       <c r="F34" t="n">
-        <v>0.274336283185841</v>
+        <v>0.371681415929203</v>
       </c>
       <c r="G34" t="n">
-        <v>0.771535580524345</v>
+        <v>0.764044943820225</v>
       </c>
       <c r="H34" t="n">
-        <v>0.225806451612903</v>
+        <v>0.276881720430108</v>
       </c>
       <c r="I34" t="n">
-        <v>1.800661744734149</v>
+        <v>1.998031234219494</v>
       </c>
       <c r="J34" t="n">
-        <v>399.3926789366056</v>
+        <v>386.6294212678936</v>
       </c>
       <c r="K34" t="n">
-        <v>42.04907975460122</v>
+        <v>77.78698023176551</v>
       </c>
       <c r="L34" t="n">
-        <v>4636274.728016358</v>
+        <v>3955817.742194958</v>
       </c>
       <c r="M34" t="n">
-        <v>2310268.645194274</v>
+        <v>2043912.618541241</v>
       </c>
       <c r="N34" t="n">
-        <v>17168.18507157464</v>
+        <v>11032.14533060668</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9576237577125707</v>
+        <v>0.8915632417465622</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2354094393430604</v>
+        <v>0.2356666662639959</v>
       </c>
       <c r="Q34" t="n">
-        <v>9.142960601813316e-05</v>
+        <v>0.0001190321169343295</v>
       </c>
       <c r="R34" t="n">
-        <v>0.06368060219375923</v>
+        <v>0.07307297388528261</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001061343369895987</v>
+        <v>0.001217882898088044</v>
       </c>
       <c r="T34" t="n">
-        <v>4.247918022279078</v>
+        <v>4.243281478254507</v>
       </c>
       <c r="U34" t="n">
-        <v>11608.31175063241</v>
+        <v>10231.54867320351</v>
       </c>
     </row>
     <row r="35">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GLM-5.1</t>
+          <t>Sonnet 4.6 (medium)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2950,351 +2950,351 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>friendliai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.3691032797641257</v>
+        <v>0.3864931360777617</v>
       </c>
       <c r="F35" t="n">
-        <v>0.185840707964602</v>
+        <v>0.289085545722714</v>
       </c>
       <c r="G35" t="n">
         <v>0.6741573033707861</v>
       </c>
       <c r="H35" t="n">
-        <v>0.247311827956989</v>
+        <v>0.196236559139785</v>
       </c>
       <c r="I35" t="n">
-        <v>4.282000252842536</v>
+        <v>2.041513021472394</v>
       </c>
       <c r="J35" t="n">
-        <v>1140.250613496931</v>
+        <v>827.6555807770972</v>
       </c>
       <c r="K35" t="n">
-        <v>174.2367075664622</v>
+        <v>67.41768916155419</v>
       </c>
       <c r="L35" t="n">
-        <v>25761884.92944783</v>
+        <v>8444053.035787314</v>
       </c>
       <c r="M35" t="n">
-        <v>13139446.7402863</v>
+        <v>4205086.787321064</v>
       </c>
       <c r="N35" t="n">
-        <v>49883.45705521473</v>
+        <v>40070.1308793456</v>
       </c>
       <c r="O35" t="n">
-        <v>0.888922540999181</v>
+        <v>0.9487221679807678</v>
       </c>
       <c r="P35" t="n">
-        <v>0.08619879915212579</v>
+        <v>0.1893170075393457</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.432749508721747e-05</v>
+        <v>4.577104554409345e-05</v>
       </c>
       <c r="R35" t="n">
-        <v>0.01942221869798375</v>
+        <v>0.02801840367329207</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0003237036449663959</v>
+        <v>0.0004669733945548679</v>
       </c>
       <c r="T35" t="n">
-        <v>11.60108968844421</v>
+        <v>5.282145608561714</v>
       </c>
       <c r="U35" t="n">
-        <v>22593.17787204784</v>
+        <v>10202.37551936649</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.8</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>Muse Spark 1.1 (xhigh)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.5657152973570364</v>
+        <v>0.5492139250715367</v>
       </c>
       <c r="F36" t="n">
-        <v>0.56047197640118</v>
+        <v>0.542772861356932</v>
       </c>
       <c r="G36" t="n">
-        <v>0.865168539325843</v>
+        <v>0.771535580524345</v>
       </c>
       <c r="H36" t="n">
-        <v>0.271505376344086</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I36" t="n">
-        <v>1.396316917192255</v>
+        <v>1.435218435173823</v>
       </c>
       <c r="J36" t="n">
-        <v>384.9621257668713</v>
+        <v>761.3780071574632</v>
       </c>
       <c r="K36" t="n">
-        <v>110.7985685071575</v>
+        <v>55.51329243353784</v>
       </c>
       <c r="L36" t="n">
-        <v>15113684.86595342</v>
+        <v>12289527.21472391</v>
       </c>
       <c r="M36" t="n">
-        <v>7938344.274012004</v>
+        <v>6284599.100204499</v>
       </c>
       <c r="N36" t="n">
-        <v>64430.0844098625</v>
+        <v>34558.96932515338</v>
       </c>
       <c r="O36" t="n">
-        <v>0.8677594149804605</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P36" t="n">
-        <v>0.4051482083985556</v>
+        <v>0.3826692241484621</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.743066647045306e-05</v>
+        <v>4.468958939392973e-05</v>
       </c>
       <c r="R36" t="n">
-        <v>0.08817209686227062</v>
+        <v>0.04328051926180357</v>
       </c>
       <c r="S36" t="n">
-        <v>0.00146953494770451</v>
+        <v>0.0007213419876967261</v>
       </c>
       <c r="T36" t="n">
-        <v>2.468232560999683</v>
+        <v>2.613222953126838</v>
       </c>
       <c r="U36" t="n">
-        <v>39260.1865335347</v>
+        <v>16141.16391489395</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>GPT-5.6 Sol (medium)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.4708693600598454</v>
+        <v>0.616195748748264</v>
       </c>
       <c r="F37" t="n">
-        <v>0.371681415929203</v>
+        <v>0.640117994100295</v>
       </c>
       <c r="G37" t="n">
-        <v>0.764044943820225</v>
+        <v>0.805243445692884</v>
       </c>
       <c r="H37" t="n">
-        <v>0.276881720430108</v>
+        <v>0.403225806451613</v>
       </c>
       <c r="I37" t="n">
-        <v>1.998031234219498</v>
+        <v>2.813450298568507</v>
       </c>
       <c r="J37" t="n">
-        <v>386.6294212678936</v>
+        <v>297.9599253578734</v>
       </c>
       <c r="K37" t="n">
-        <v>77.78698023176551</v>
+        <v>71.35378323108384</v>
       </c>
       <c r="L37" t="n">
-        <v>3955817.742194958</v>
+        <v>5765545.476482615</v>
       </c>
       <c r="M37" t="n">
-        <v>2043912.618541241</v>
+        <v>2974758.351738241</v>
       </c>
       <c r="N37" t="n">
-        <v>11032.14533060668</v>
+        <v>14440.59713701431</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8915632417465625</v>
+        <v>0.8970664465490255</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2356666662639954</v>
+        <v>0.21901781917448</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.0001190321169343295</v>
+        <v>0.00010687553350532</v>
       </c>
       <c r="R37" t="n">
-        <v>0.07307297388528261</v>
+        <v>0.1240829446459615</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001217882898088044</v>
+        <v>0.002068049077432692</v>
       </c>
       <c r="T37" t="n">
-        <v>4.243281478254516</v>
+        <v>4.565838541216378</v>
       </c>
       <c r="U37" t="n">
-        <v>10231.54867320351</v>
+        <v>19350.07021349512</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>Opus 4.8 (xhigh)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.5531133827505798</v>
+        <v>0.5907181217597334</v>
       </c>
       <c r="F38" t="n">
-        <v>0.566371681415929</v>
+        <v>0.513274336283186</v>
       </c>
       <c r="G38" t="n">
-        <v>0.786516853932584</v>
+        <v>0.831460674157304</v>
       </c>
       <c r="H38" t="n">
-        <v>0.306451612903226</v>
+        <v>0.42741935483871</v>
       </c>
       <c r="I38" t="n">
-        <v>2.65253587423313</v>
+        <v>5.665366469580767</v>
       </c>
       <c r="J38" t="n">
-        <v>386.3044764826176</v>
+        <v>1065.615385480571</v>
       </c>
       <c r="K38" t="n">
-        <v>78.53885480572598</v>
+        <v>136.1303390500093</v>
       </c>
       <c r="L38" t="n">
-        <v>6885560.579754606</v>
+        <v>13628306.24233129</v>
       </c>
       <c r="M38" t="n">
-        <v>3492715.358895706</v>
+        <v>6783846.309815951</v>
       </c>
       <c r="N38" t="n">
-        <v>13239.49488752556</v>
+        <v>62541.86503067485</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9409891933709399</v>
+        <v>0.9687226730983397</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2085224890353234</v>
+        <v>0.104268298428971</v>
       </c>
       <c r="Q38" t="n">
-        <v>8.032946284386509e-05</v>
+        <v>4.334494039507902e-05</v>
       </c>
       <c r="R38" t="n">
-        <v>0.085908409002162</v>
+        <v>0.03326067527600485</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0014318068167027</v>
+        <v>0.0005543445879334143</v>
       </c>
       <c r="T38" t="n">
-        <v>4.795645806005133</v>
+        <v>9.590642746330166</v>
       </c>
       <c r="U38" t="n">
-        <v>17824.1801452809</v>
+        <v>12789.14177481138</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Opus 5 (low)</t>
+          <t>GPT-5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.5940064571013324</v>
+        <v>0.6103327520587847</v>
       </c>
       <c r="F39" t="n">
-        <v>0.569321533923304</v>
+        <v>0.64306784660767</v>
       </c>
       <c r="G39" t="n">
-        <v>0.820224719101123</v>
+        <v>0.827715355805243</v>
       </c>
       <c r="H39" t="n">
-        <v>0.39247311827957</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I39" t="n">
-        <v>2.295157744887527</v>
+        <v>4.752370071574643</v>
       </c>
       <c r="J39" t="n">
-        <v>598.7677147239262</v>
+        <v>614.9898987730061</v>
       </c>
       <c r="K39" t="n">
-        <v>64.39263803680981</v>
+        <v>107.1319018404908</v>
       </c>
       <c r="L39" t="n">
-        <v>5258606.375255628</v>
+        <v>12150851.17995912</v>
       </c>
       <c r="M39" t="n">
-        <v>2618171.039877301</v>
+        <v>6164087.486707566</v>
       </c>
       <c r="N39" t="n">
-        <v>22632.92229038855</v>
+        <v>25286.0654396728</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9637890151908801</v>
+        <v>0.9341674523911524</v>
       </c>
       <c r="P39" t="n">
-        <v>0.2588085539760759</v>
+        <v>0.1284270254350285</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.0001129589124404576</v>
+        <v>5.022962943249859e-05</v>
       </c>
       <c r="R39" t="n">
-        <v>0.05952289435396939</v>
+        <v>0.05954563676019593</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0009920482392328232</v>
+        <v>0.0009924272793365987</v>
       </c>
       <c r="T39" t="n">
-        <v>3.863859925172485</v>
+        <v>7.78652309833262</v>
       </c>
       <c r="U39" t="n">
-        <v>8782.381290681667</v>
+        <v>19757.80611063991</v>
       </c>
     </row>
     <row r="40">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (low)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3319,420 +3319,420 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.3864628427996264</v>
+        <v>0.5716614223656344</v>
       </c>
       <c r="F40" t="n">
-        <v>0.297935103244838</v>
+        <v>0.634218289085546</v>
       </c>
       <c r="G40" t="n">
-        <v>0.632958801498127</v>
+        <v>0.752808988764045</v>
       </c>
       <c r="H40" t="n">
-        <v>0.228494623655914</v>
+        <v>0.327956989247312</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4909580805725969</v>
+        <v>1.508396035337423</v>
       </c>
       <c r="J40" t="n">
-        <v>154.8149498977502</v>
+        <v>482.0907147239265</v>
       </c>
       <c r="K40" t="n">
-        <v>37.80981595092025</v>
+        <v>114.6288343558282</v>
       </c>
       <c r="L40" t="n">
-        <v>1657646.844580778</v>
+        <v>15963259.28016359</v>
       </c>
       <c r="M40" t="n">
-        <v>861642.4202453988</v>
+        <v>8170928.992842535</v>
       </c>
       <c r="N40" t="n">
-        <v>6854.071574642127</v>
+        <v>41094.49386503067</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8771903855272027</v>
+        <v>0.9181831202060817</v>
       </c>
       <c r="P40" t="n">
-        <v>0.7871605705091984</v>
+        <v>0.378986293369404</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0002331394313952098</v>
+        <v>3.58110716823348e-05</v>
       </c>
       <c r="R40" t="n">
-        <v>0.1497773347037368</v>
+        <v>0.0711477825528751</v>
       </c>
       <c r="S40" t="n">
-        <v>0.002496288911728947</v>
+        <v>0.001185796375881252</v>
       </c>
       <c r="T40" t="n">
-        <v>1.270388834838513</v>
+        <v>2.638617853720858</v>
       </c>
       <c r="U40" t="n">
-        <v>10707.27888796008</v>
+        <v>33112.56324300934</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-5.6 Terra (max)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.6702814566291138</v>
+        <v>0.6042010361726687</v>
       </c>
       <c r="F41" t="n">
-        <v>0.631268436578171</v>
+        <v>0.669616519174041</v>
       </c>
       <c r="G41" t="n">
-        <v>0.887640449438202</v>
+        <v>0.782771535580524</v>
       </c>
       <c r="H41" t="n">
-        <v>0.491935483870968</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I41" t="n">
-        <v>8.943547018021484</v>
+        <v>2.695350269529651</v>
       </c>
       <c r="J41" t="n">
-        <v>1451.329194274025</v>
+        <v>491.0206543967283</v>
       </c>
       <c r="K41" t="n">
-        <v>165.7202546941811</v>
+        <v>95.80674846625767</v>
       </c>
       <c r="L41" t="n">
-        <v>23699428.05214722</v>
+        <v>9630511.582822077</v>
       </c>
       <c r="M41" t="n">
-        <v>11810977.87014315</v>
+        <v>4933733.868098159</v>
       </c>
       <c r="N41" t="n">
-        <v>81385.06339468302</v>
+        <v>37445.42126789366</v>
       </c>
       <c r="O41" t="n">
-        <v>0.974703359327879</v>
+        <v>0.9184675548550253</v>
       </c>
       <c r="P41" t="n">
-        <v>0.07494581906691818</v>
+        <v>0.2241641997342721</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.828260054015881e-05</v>
+        <v>6.273820772412349e-05</v>
       </c>
       <c r="R41" t="n">
-        <v>0.02771038270050364</v>
+        <v>0.07383001477789093</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0004618397116750606</v>
+        <v>0.001230500246298182</v>
       </c>
       <c r="T41" t="n">
-        <v>13.34297246264148</v>
+        <v>4.461015635794728</v>
       </c>
       <c r="U41" t="n">
-        <v>16329.46415303249</v>
+        <v>19613.25149275889</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (none)</t>
+          <t>DeepSeek V4 Pro (high)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.2309196896685307</v>
+        <v>0.3282816619106221</v>
       </c>
       <c r="F42" t="n">
-        <v>0.132743362831858</v>
+        <v>0.08554572271386431</v>
       </c>
       <c r="G42" t="n">
-        <v>0.374531835205992</v>
+        <v>0.700374531835206</v>
       </c>
       <c r="H42" t="n">
-        <v>0.185483870967742</v>
+        <v>0.198924731182796</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3616287844580776</v>
+        <v>0.2547256318476481</v>
       </c>
       <c r="J42" t="n">
-        <v>88.85438650306735</v>
+        <v>1072.531835378324</v>
       </c>
       <c r="K42" t="n">
-        <v>33.82924335378323</v>
+        <v>128.1457055214724</v>
       </c>
       <c r="L42" t="n">
-        <v>1105801.555214723</v>
+        <v>9942165.52862986</v>
       </c>
       <c r="M42" t="n">
-        <v>582183.7985685072</v>
+        <v>5181244.880368099</v>
       </c>
       <c r="N42" t="n">
-        <v>5133.394683026585</v>
+        <v>41975.79754601227</v>
       </c>
       <c r="O42" t="n">
-        <v>0.8482758058887612</v>
+        <v>0.8541357545221669</v>
       </c>
       <c r="P42" t="n">
-        <v>0.6385545055949505</v>
+        <v>1.288765718351297</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.0002088256148488515</v>
+        <v>3.301913058732417e-05</v>
       </c>
       <c r="R42" t="n">
-        <v>0.1559313155533806</v>
+        <v>0.01836486252894252</v>
       </c>
       <c r="S42" t="n">
-        <v>0.00259885525922301</v>
+        <v>0.000306081042149042</v>
       </c>
       <c r="T42" t="n">
-        <v>1.566037027752682</v>
+        <v>0.77593622002864</v>
       </c>
       <c r="U42" t="n">
-        <v>12445.098083892</v>
+        <v>9269.809250112254</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (medium)</t>
+          <t>Opus 5 (high)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.4196699779001624</v>
+        <v>0.6561729860226817</v>
       </c>
       <c r="F43" t="n">
-        <v>0.365781710914454</v>
+        <v>0.6076696165191739</v>
       </c>
       <c r="G43" t="n">
-        <v>0.621722846441947</v>
+        <v>0.868913857677903</v>
       </c>
       <c r="H43" t="n">
-        <v>0.271505376344086</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4430536771983641</v>
+        <v>3.918602446063396</v>
       </c>
       <c r="J43" t="n">
-        <v>191.3819171779144</v>
+        <v>842.8052382413098</v>
       </c>
       <c r="K43" t="n">
-        <v>57.08588957055215</v>
+        <v>94.85071574642126</v>
       </c>
       <c r="L43" t="n">
-        <v>4287327.734151328</v>
+        <v>9911366.349693259</v>
       </c>
       <c r="M43" t="n">
-        <v>2221162.702453987</v>
+        <v>4937399.112474437</v>
       </c>
       <c r="N43" t="n">
-        <v>11663.1390593047</v>
+        <v>37331.49386503067</v>
       </c>
       <c r="O43" t="n">
-        <v>0.8832984632099323</v>
+        <v>0.9702723303233406</v>
       </c>
       <c r="P43" t="n">
-        <v>0.9472215207735825</v>
+        <v>0.1674507672197952</v>
       </c>
       <c r="Q43" t="n">
-        <v>9.788614351947498e-05</v>
+        <v>6.620408961504982e-05</v>
       </c>
       <c r="R43" t="n">
-        <v>0.1315704171288109</v>
+        <v>0.04671349604271026</v>
       </c>
       <c r="S43" t="n">
-        <v>0.002192840285480182</v>
+        <v>0.0007785582673785044</v>
       </c>
       <c r="T43" t="n">
-        <v>1.055719256867511</v>
+        <v>5.971904557997063</v>
       </c>
       <c r="U43" t="n">
-        <v>22401.94788186649</v>
+        <v>11759.97241115327</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kimi K2.6</t>
+          <t>Composer 2.5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.3388925953605663</v>
+        <v>0.3830075380367747</v>
       </c>
       <c r="F44" t="n">
-        <v>0.165191740412979</v>
+        <v>0.15929203539823</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6928838951310859</v>
+        <v>0.6779026217228465</v>
       </c>
       <c r="H44" t="n">
-        <v>0.158602150537634</v>
+        <v>0.3118279569892475</v>
       </c>
       <c r="I44" t="n">
-        <v>1.21710007411043</v>
+        <v>0.08505141359918204</v>
       </c>
       <c r="J44" t="n">
-        <v>2443.385067484662</v>
+        <v>625.1976421267894</v>
       </c>
       <c r="K44" t="n">
-        <v>133.7675410760877</v>
+        <v>116.8680981595092</v>
       </c>
       <c r="L44" t="n">
-        <v>11660527.81595092</v>
+        <v>3705076.4698364</v>
       </c>
       <c r="M44" t="n">
-        <v>5891966.377300614</v>
+        <v>1872461.576687117</v>
       </c>
       <c r="N44" t="n">
-        <v>36930.17791411043</v>
+        <v>18453.85787321063</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9554328157869918</v>
+        <v>1.052833075750478</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2784426708775453</v>
+        <v>4.503247175194018</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.906322944463811e-05</v>
+        <v>0.0001033737201255894</v>
       </c>
       <c r="R44" t="n">
-        <v>0.008321879343629747</v>
+        <v>0.03675710004924502</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0001386979890604958</v>
+        <v>0.0006126183341540836</v>
       </c>
       <c r="T44" t="n">
-        <v>3.591403561991346</v>
+        <v>0.2220619835190183</v>
       </c>
       <c r="U44" t="n">
-        <v>4772.284144289555</v>
+        <v>5926.248309626565</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Gemini CLI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Opus 5 (medium)</t>
+          <t>Gemini 3.1 Pro (high)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.640684745695058</v>
+        <v>0.3293046837328304</v>
       </c>
       <c r="F45" t="n">
-        <v>0.628318584070797</v>
+        <v>0.141592920353982</v>
       </c>
       <c r="G45" t="n">
-        <v>0.850187265917603</v>
+        <v>0.760299625468165</v>
       </c>
       <c r="H45" t="n">
-        <v>0.443548387096774</v>
+        <v>0.08602150537634411</v>
       </c>
       <c r="I45" t="n">
-        <v>3.171867192484664</v>
+        <v>1.040041561860939</v>
       </c>
       <c r="J45" t="n">
-        <v>730.9243895705519</v>
+        <v>663.8363599182014</v>
       </c>
       <c r="K45" t="n">
-        <v>83.47801635991821</v>
+        <v>30.96883483789777</v>
       </c>
       <c r="L45" t="n">
-        <v>7999358.108384448</v>
+        <v>4727804.222392637</v>
       </c>
       <c r="M45" t="n">
-        <v>3984815.59611452</v>
+        <v>2465901.789877301</v>
       </c>
       <c r="N45" t="n">
-        <v>30206.12781186094</v>
+        <v>12977.50562372188</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9695331242878965</v>
+        <v>0.8650361016121304</v>
       </c>
       <c r="P45" t="n">
-        <v>0.2019897766252884</v>
+        <v>0.316626465526635</v>
       </c>
       <c r="Q45" t="n">
-        <v>8.009201951135686e-05</v>
+        <v>6.965277499713736e-05</v>
       </c>
       <c r="R45" t="n">
-        <v>0.05259242308809697</v>
+        <v>0.02976378248760652</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0008765403848016162</v>
+        <v>0.0004960630414601087</v>
       </c>
       <c r="T45" t="n">
-        <v>4.950745610532072</v>
+        <v>3.158295685538259</v>
       </c>
       <c r="U45" t="n">
-        <v>10944.16634952406</v>
+        <v>7121.942255430543</v>
       </c>
     </row>
     <row r="46">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (xhigh)</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3753,132 +3753,132 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.529584326329171</v>
+        <v>0.4277969516408803</v>
       </c>
       <c r="F46" t="n">
-        <v>0.566371681415929</v>
+        <v>0.162241887905605</v>
       </c>
       <c r="G46" t="n">
-        <v>0.707865168539326</v>
+        <v>0.629213483146068</v>
       </c>
       <c r="H46" t="n">
-        <v>0.314516129032258</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I46" t="n">
-        <v>1.209317104846625</v>
+        <v>0.09081146755368102</v>
       </c>
       <c r="J46" t="n">
-        <v>413.8987709611452</v>
+        <v>743.5829417177914</v>
       </c>
       <c r="K46" t="n">
-        <v>96.1922290388548</v>
+        <v>66.08691206543966</v>
       </c>
       <c r="L46" t="n">
-        <v>12806609.00511247</v>
+        <v>12713750.95194274</v>
       </c>
       <c r="M46" t="n">
-        <v>6575104.906952964</v>
+        <v>6378205.537321064</v>
       </c>
       <c r="N46" t="n">
-        <v>30840.24642126789</v>
+        <v>37873.7581799591</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9100235393369858</v>
+        <v>0.9780317126088948</v>
       </c>
       <c r="P46" t="n">
-        <v>0.4379201486580617</v>
+        <v>4.71082522026195</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.135242405837159e-05</v>
+        <v>3.364836650158783e-05</v>
       </c>
       <c r="R46" t="n">
-        <v>0.07677012305681175</v>
+        <v>0.03451910426986961</v>
       </c>
       <c r="S46" t="n">
-        <v>0.001279502050946862</v>
+        <v>0.0005753184044978268</v>
       </c>
       <c r="T46" t="n">
-        <v>2.283521329320756</v>
+        <v>0.2122770328431743</v>
       </c>
       <c r="U46" t="n">
-        <v>30941.40380115961</v>
+        <v>17097.95940527093</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Muse Spark 1.2 (xhigh)</t>
+          <t>GPT-5.6 Terra (high)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.6164044159758908</v>
+        <v>0.5464647209828707</v>
       </c>
       <c r="F47" t="n">
-        <v>0.581120943952802</v>
+        <v>0.6047197640117991</v>
       </c>
       <c r="G47" t="n">
-        <v>0.816479400749064</v>
+        <v>0.722846441947566</v>
       </c>
       <c r="H47" t="n">
-        <v>0.451612903225806</v>
+        <v>0.311827956989247</v>
       </c>
       <c r="I47" t="n">
-        <v>2.072823051942737</v>
+        <v>1.561839053374232</v>
       </c>
       <c r="J47" t="n">
-        <v>2448.643313905929</v>
+        <v>358.7396482617585</v>
       </c>
       <c r="K47" t="n">
-        <v>151.4345603271984</v>
+        <v>67.06952965235175</v>
       </c>
       <c r="L47" t="n">
-        <v>19963139.08486708</v>
+        <v>5600275.774028626</v>
       </c>
       <c r="M47" t="n">
-        <v>10093761.29754601</v>
+        <v>2877096.291411043</v>
       </c>
       <c r="N47" t="n">
-        <v>58305.98057259714</v>
+        <v>20902.66564417178</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9538301727874866</v>
+        <v>0.9049339862289004</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2973743539749669</v>
+        <v>0.3498854250073181</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.087712875993296e-05</v>
+        <v>9.757818061694571e-05</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01510398217189026</v>
+        <v>0.09139743381542312</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0002517330361981711</v>
+        <v>0.001523290563590385</v>
       </c>
       <c r="T47" t="n">
-        <v>3.362764766474046</v>
+        <v>2.85807846948493</v>
       </c>
       <c r="U47" t="n">
-        <v>8152.734606749675</v>
+        <v>15610.97526065009</v>
       </c>
     </row>
     <row r="48">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Opus 5 (xhigh)</t>
+          <t>Opus 4.7 (max)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3903,639 +3903,785 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.6814975428587517</v>
+        <v>0.5158095272716129</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6047197640117991</v>
+        <v>0.40117994100295</v>
       </c>
       <c r="G48" t="n">
-        <v>0.891385767790262</v>
+        <v>0.7752808988764049</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5483870967741939</v>
+        <v>0.370967741935484</v>
       </c>
       <c r="I48" t="n">
-        <v>8.170783921523503</v>
+        <v>5.915424259100202</v>
       </c>
       <c r="J48" t="n">
-        <v>1421.879982617589</v>
+        <v>950.3123588957067</v>
       </c>
       <c r="K48" t="n">
-        <v>152.0771983640082</v>
+        <v>107.999326082915</v>
       </c>
       <c r="L48" t="n">
-        <v>21565879.13803681</v>
+        <v>16129723.11451944</v>
       </c>
       <c r="M48" t="n">
-        <v>10747525.6196319</v>
+        <v>8042457.98977505</v>
       </c>
       <c r="N48" t="n">
-        <v>73273.02862985685</v>
+        <v>47224.16462167689</v>
       </c>
       <c r="O48" t="n">
-        <v>0.9740249879523308</v>
+        <v>0.9665216325317725</v>
       </c>
       <c r="P48" t="n">
-        <v>0.08340662896047819</v>
+        <v>0.08719738512044999</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.160073088125403e-05</v>
+        <v>3.197882093879829e-05</v>
       </c>
       <c r="R48" t="n">
-        <v>0.02875759773778482</v>
+        <v>0.03256673592276544</v>
       </c>
       <c r="S48" t="n">
-        <v>0.000479293295629747</v>
+        <v>0.0005427789320460906</v>
       </c>
       <c r="T48" t="n">
-        <v>11.98945470477946</v>
+        <v>11.46823380791352</v>
       </c>
       <c r="U48" t="n">
-        <v>15167.15855183179</v>
+        <v>16973.07518263015</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Composer 2.5 Fast</t>
+          <t>Opus 5 (medium)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.3830075380367747</v>
+        <v>0.6406847456950576</v>
       </c>
       <c r="F49" t="n">
-        <v>0.15929203539823</v>
+        <v>0.628318584070796</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6779026217228465</v>
+        <v>0.850187265917603</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3118279569892475</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5573437730061347</v>
+        <v>3.171867192484664</v>
       </c>
       <c r="J49" t="n">
-        <v>472.3722024539875</v>
+        <v>730.9243895705523</v>
       </c>
       <c r="K49" t="n">
-        <v>116.8680981595092</v>
+        <v>83.47801635991821</v>
       </c>
       <c r="L49" t="n">
-        <v>4259887.413087938</v>
+        <v>7999358.108384448</v>
       </c>
       <c r="M49" t="n">
-        <v>2153033.982617587</v>
+        <v>3984815.59611452</v>
       </c>
       <c r="N49" t="n">
-        <v>20146.14621676892</v>
+        <v>30206.12781186094</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9355410155352533</v>
+        <v>0.9695331242878965</v>
       </c>
       <c r="P49" t="n">
-        <v>0.6872016098268293</v>
+        <v>0.2019897766252883</v>
       </c>
       <c r="Q49" t="n">
-        <v>8.991024900330346e-05</v>
+        <v>8.009201951135682e-05</v>
       </c>
       <c r="R49" t="n">
-        <v>0.04864903599920222</v>
+        <v>0.05259242308809691</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008108172666533704</v>
+        <v>0.0008765403848016152</v>
       </c>
       <c r="T49" t="n">
-        <v>1.455177033493845</v>
+        <v>4.950745610532073</v>
       </c>
       <c r="U49" t="n">
-        <v>9018.073864121761</v>
+        <v>10944.16634952405</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Grok 4.5 (high)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.6408998279698193</v>
+        <v>0.6505240024334411</v>
       </c>
       <c r="F50" t="n">
-        <v>0.59882005899705</v>
+        <v>0.687315634218289</v>
       </c>
       <c r="G50" t="n">
-        <v>0.842696629213483</v>
+        <v>0.831460674157303</v>
       </c>
       <c r="H50" t="n">
-        <v>0.481182795698925</v>
+        <v>0.432795698924731</v>
       </c>
       <c r="I50" t="n">
-        <v>2.438982443762777</v>
+        <v>6.420249160020451</v>
       </c>
       <c r="J50" t="n">
-        <v>929.1851094069541</v>
+        <v>613.70177198364</v>
       </c>
       <c r="K50" t="n">
-        <v>60.74437627811862</v>
+        <v>112.2689161554192</v>
       </c>
       <c r="L50" t="n">
-        <v>3598867.582822087</v>
+        <v>13169248.79601226</v>
       </c>
       <c r="M50" t="n">
-        <v>1837535.160531697</v>
+        <v>6786107.398261759</v>
       </c>
       <c r="N50" t="n">
-        <v>25699.40797546012</v>
+        <v>35184.01329243354</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9238990226060748</v>
+        <v>0.902597320865973</v>
       </c>
       <c r="P50" t="n">
-        <v>0.2627734486604427</v>
+        <v>0.1013237938621324</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.0001780837480736792</v>
+        <v>4.939719892226686e-05</v>
       </c>
       <c r="R50" t="n">
-        <v>0.04138463831252327</v>
+        <v>0.06360001213593849</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0006897439718753878</v>
+        <v>0.001060000202265642</v>
       </c>
       <c r="T50" t="n">
-        <v>3.805559523223389</v>
+        <v>9.869350148501775</v>
       </c>
       <c r="U50" t="n">
-        <v>3873.143840110653</v>
+        <v>21458.71072434076</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Fable 5 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.6263880112748017</v>
+        <v>0.6717276042685724</v>
       </c>
       <c r="F51" t="n">
-        <v>0.63716814159292</v>
+        <v>0.660766961651917</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8764044943820229</v>
+        <v>0.865168539325843</v>
       </c>
       <c r="H51" t="n">
-        <v>0.365591397849462</v>
+        <v>0.489247311827957</v>
       </c>
       <c r="I51" t="n">
-        <v>3.081635541610432</v>
+        <v>11.68740762091003</v>
       </c>
       <c r="J51" t="n">
-        <v>1447.373053169735</v>
+        <v>1407.30630163599</v>
       </c>
       <c r="K51" t="n">
-        <v>122.9498977505112</v>
+        <v>137.007744236847</v>
       </c>
       <c r="L51" t="n">
-        <v>10383196.73788345</v>
+        <v>13868659.99897749</v>
       </c>
       <c r="M51" t="n">
-        <v>5296768.575664621</v>
+        <v>6901095.023517382</v>
       </c>
       <c r="N51" t="n">
-        <v>54498.01533742331</v>
+        <v>74265.48875255625</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.9619283373252908</v>
       </c>
       <c r="P51" t="n">
-        <v>0.2032647932621707</v>
+        <v>0.05747447390016408</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.032708683920082e-05</v>
+        <v>4.843493202069251e-05</v>
       </c>
       <c r="R51" t="n">
-        <v>0.02596654718296782</v>
+        <v>0.02863886576025522</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0004327757863827969</v>
+        <v>0.0004773144293375869</v>
       </c>
       <c r="T51" t="n">
-        <v>4.919691127770471</v>
+        <v>17.39902833624972</v>
       </c>
       <c r="U51" t="n">
-        <v>7173.822060003356</v>
+        <v>9854.75584302807</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fable 5 (max) (with fallback)</t>
+          <t>Grok 4.5 (high)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.6717276042685724</v>
+        <v>0.6408998279698193</v>
       </c>
       <c r="F52" t="n">
-        <v>0.660766961651917</v>
+        <v>0.59882005899705</v>
       </c>
       <c r="G52" t="n">
-        <v>0.865168539325843</v>
+        <v>0.842696629213483</v>
       </c>
       <c r="H52" t="n">
-        <v>0.489247311827957</v>
+        <v>0.481182795698925</v>
       </c>
       <c r="I52" t="n">
-        <v>11.68740762091003</v>
+        <v>2.438982443762777</v>
       </c>
       <c r="J52" t="n">
-        <v>1407.30630163599</v>
+        <v>929.1851094069543</v>
       </c>
       <c r="K52" t="n">
-        <v>137.007744236847</v>
+        <v>60.74437627811862</v>
       </c>
       <c r="L52" t="n">
-        <v>13868659.9989775</v>
+        <v>3598867.582822087</v>
       </c>
       <c r="M52" t="n">
-        <v>6901095.023517382</v>
+        <v>1837535.160531697</v>
       </c>
       <c r="N52" t="n">
-        <v>74265.48875255625</v>
+        <v>25699.40797546012</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9619283373252908</v>
+        <v>0.9238990226060748</v>
       </c>
       <c r="P52" t="n">
-        <v>0.05747447390016408</v>
+        <v>0.2627734486604427</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.84349320206925e-05</v>
+        <v>0.0001780837480736792</v>
       </c>
       <c r="R52" t="n">
-        <v>0.02863886576025522</v>
+        <v>0.04138463831252326</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0004773144293375869</v>
+        <v>0.0006897439718753876</v>
       </c>
       <c r="T52" t="n">
-        <v>17.39902833624972</v>
+        <v>3.805559523223389</v>
       </c>
       <c r="U52" t="n">
-        <v>9854.755843028073</v>
+        <v>3873.143840110652</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>Opus 5 (xhigh)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.5962784529614886</v>
+        <v>0.6814975428587517</v>
       </c>
       <c r="F53" t="n">
-        <v>0.572271386430678</v>
+        <v>0.6047197640117991</v>
       </c>
       <c r="G53" t="n">
-        <v>0.910112359550562</v>
+        <v>0.891385767790262</v>
       </c>
       <c r="H53" t="n">
-        <v>0.306451612903226</v>
+        <v>0.5483870967741939</v>
       </c>
       <c r="I53" t="n">
-        <v>1.26793256886503</v>
+        <v>8.170783921523505</v>
       </c>
       <c r="J53" t="n">
-        <v>527.0915644171779</v>
+        <v>1421.879982617589</v>
       </c>
       <c r="K53" t="n">
-        <v>83.44887525562373</v>
+        <v>152.0771983640082</v>
       </c>
       <c r="L53" t="n">
-        <v>18493123.37423313</v>
+        <v>21565879.13803681</v>
       </c>
       <c r="M53" t="n">
-        <v>9497213.109406954</v>
+        <v>10747525.6196319</v>
       </c>
       <c r="N53" t="n">
-        <v>49098.7944785276</v>
+        <v>73273.02862985685</v>
       </c>
       <c r="O53" t="n">
-        <v>0.8634331167917659</v>
+        <v>0.9740249879523308</v>
       </c>
       <c r="P53" t="n">
-        <v>0.4702761547447575</v>
+        <v>0.08340662896047817</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.224325285107308e-05</v>
+        <v>3.160073088125403e-05</v>
       </c>
       <c r="R53" t="n">
-        <v>0.06787569673449199</v>
+        <v>0.02875759773778482</v>
       </c>
       <c r="S53" t="n">
-        <v>0.001131261612241533</v>
+        <v>0.000479293295629747</v>
       </c>
       <c r="T53" t="n">
-        <v>2.126410173917388</v>
+        <v>11.98945470477946</v>
       </c>
       <c r="U53" t="n">
-        <v>35085.21976571864</v>
+        <v>15167.15855183179</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GLM-5.2</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>novita</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.4331015719360217</v>
+        <v>0.4975760031619054</v>
       </c>
       <c r="F54" t="n">
-        <v>0.286135693215339</v>
+        <v>0.427728613569322</v>
       </c>
       <c r="G54" t="n">
-        <v>0.722846441947565</v>
+        <v>0.677902621722846</v>
       </c>
       <c r="H54" t="n">
-        <v>0.290322580645161</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="I54" t="n">
-        <v>6.657531358159519</v>
+        <v>0.05949917044417178</v>
       </c>
       <c r="J54" t="n">
-        <v>1507.044470347651</v>
+        <v>868.3750143149272</v>
       </c>
       <c r="K54" t="n">
-        <v>127.4036879531512</v>
+        <v>105.9314928425358</v>
       </c>
       <c r="L54" t="n">
-        <v>6619529.539877302</v>
+        <v>20844227.99386501</v>
       </c>
       <c r="M54" t="n">
-        <v>5529735.922290388</v>
+        <v>10443571.69734151</v>
       </c>
       <c r="N54" t="n">
-        <v>28567.83231083845</v>
+        <v>58411.25766871166</v>
       </c>
       <c r="O54" t="n">
-        <v>0.3295602231414034</v>
+        <v>0.9807621661364226</v>
       </c>
       <c r="P54" t="n">
-        <v>0.06505437956446262</v>
+        <v>8.362738496140583</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.542784790473939e-05</v>
+        <v>2.387116487635592e-05</v>
       </c>
       <c r="R54" t="n">
-        <v>0.01724308394838987</v>
+        <v>0.03437980100483083</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0002873847324731645</v>
+        <v>0.0005729966834138472</v>
       </c>
       <c r="T54" t="n">
-        <v>15.37175524069208</v>
+        <v>0.1195780545405672</v>
       </c>
       <c r="U54" t="n">
-        <v>4392.391644786887</v>
+        <v>24003.71688527831</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>GLM-5.2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>novita</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.4975760031619054</v>
+        <v>0.433101571936022</v>
       </c>
       <c r="F55" t="n">
-        <v>0.427728613569322</v>
+        <v>0.286135693215339</v>
       </c>
       <c r="G55" t="n">
-        <v>0.677902621722846</v>
+        <v>0.722846441947566</v>
       </c>
       <c r="H55" t="n">
-        <v>0.387096774193548</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="I55" t="n">
-        <v>0.05949917044417178</v>
+        <v>6.657531358159516</v>
       </c>
       <c r="J55" t="n">
-        <v>868.3750143149272</v>
+        <v>1507.044470347651</v>
       </c>
       <c r="K55" t="n">
-        <v>105.9314928425358</v>
+        <v>127.4036879531512</v>
       </c>
       <c r="L55" t="n">
-        <v>20844227.99386501</v>
+        <v>6619529.539877302</v>
       </c>
       <c r="M55" t="n">
-        <v>10443571.69734151</v>
+        <v>5529735.922290388</v>
       </c>
       <c r="N55" t="n">
-        <v>58411.25766871166</v>
+        <v>28567.83231083845</v>
       </c>
       <c r="O55" t="n">
-        <v>0.980762166136423</v>
+        <v>0.3295602231414034</v>
       </c>
       <c r="P55" t="n">
-        <v>8.362738496140583</v>
+        <v>0.06505437956446269</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.387116487635592e-05</v>
+        <v>6.542784790473944e-05</v>
       </c>
       <c r="R55" t="n">
-        <v>0.03437980100483083</v>
+        <v>0.01724308394838989</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0005729966834138472</v>
+        <v>0.0002873847324731648</v>
       </c>
       <c r="T55" t="n">
-        <v>0.1195780545405672</v>
+        <v>15.37175524069206</v>
       </c>
       <c r="U55" t="n">
-        <v>24003.71688527831</v>
+        <v>4392.391644786887</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.6505240024334411</v>
+        <v>0.5962784529614886</v>
       </c>
       <c r="F56" t="n">
-        <v>0.687315634218289</v>
+        <v>0.572271386430678</v>
       </c>
       <c r="G56" t="n">
-        <v>0.831460674157303</v>
+        <v>0.910112359550562</v>
       </c>
       <c r="H56" t="n">
-        <v>0.432795698924731</v>
+        <v>0.306451612903226</v>
       </c>
       <c r="I56" t="n">
-        <v>6.420249160020451</v>
+        <v>1.26793256886503</v>
       </c>
       <c r="J56" t="n">
-        <v>613.70177198364</v>
+        <v>527.0915644171779</v>
       </c>
       <c r="K56" t="n">
-        <v>112.2689161554192</v>
+        <v>83.44887525562373</v>
       </c>
       <c r="L56" t="n">
-        <v>13169248.79601226</v>
+        <v>18493123.3742331</v>
       </c>
       <c r="M56" t="n">
-        <v>6786107.398261759</v>
+        <v>9497213.109406954</v>
       </c>
       <c r="N56" t="n">
-        <v>35184.01329243354</v>
+        <v>49098.7944785276</v>
       </c>
       <c r="O56" t="n">
-        <v>0.902597320865973</v>
+        <v>0.8634331167917663</v>
       </c>
       <c r="P56" t="n">
-        <v>0.1013237938621324</v>
+        <v>0.4702761547447575</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.939719892226686e-05</v>
+        <v>3.224325285107313e-05</v>
       </c>
       <c r="R56" t="n">
-        <v>0.06360001213593849</v>
+        <v>0.06787569673449199</v>
       </c>
       <c r="S56" t="n">
-        <v>0.001060000202265642</v>
+        <v>0.001131261612241533</v>
       </c>
       <c r="T56" t="n">
-        <v>9.869350148501775</v>
+        <v>2.126410173917388</v>
       </c>
       <c r="U56" t="n">
-        <v>21458.71072434076</v>
+        <v>35085.21976571858</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Kimi Code CLI</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kimi K3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Moonshot AI</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>moonshotai</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.6263880112748017</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.63716814159292</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.8764044943820229</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.365591397849462</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3.081635541610432</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1447.373053169735</v>
+      </c>
+      <c r="K57" t="n">
+        <v>122.9498977505112</v>
+      </c>
+      <c r="L57" t="n">
+        <v>10383196.73788345</v>
+      </c>
+      <c r="M57" t="n">
+        <v>5296768.575664621</v>
+      </c>
+      <c r="N57" t="n">
+        <v>54498.01533742331</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.9500000000000018</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.2032647932621707</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>6.032708683920082e-05</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.02596654718296782</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.0004327757863827969</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4.919691127770471</v>
+      </c>
+      <c r="U57" t="n">
+        <v>7173.822060003356</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Cursor CLI</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Composer 2.5 Fast</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>cursor</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.3830075380367747</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.15929203539823</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.6779026217228465</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.3118279569892475</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.5573437730061354</v>
+      </c>
+      <c r="J58" t="n">
+        <v>472.3722024539878</v>
+      </c>
+      <c r="K58" t="n">
+        <v>116.8680981595092</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4259887.413087934</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2153033.982617587</v>
+      </c>
+      <c r="N58" t="n">
+        <v>20146.14621676892</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.9355410155352536</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.6872016098268284</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>8.991024900330353e-05</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.0486490359992022</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.00081081726665337</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.455177033493847</v>
+      </c>
+      <c r="U58" t="n">
+        <v>9018.073864121749</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (none)</t>
+          <t>GPT-5.6 Terra (high)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -545,55 +545,55 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2309196896685307</v>
+        <v>0.5464647209828707</v>
       </c>
       <c r="F2" t="n">
-        <v>0.132743362831858</v>
+        <v>0.6047197640117991</v>
       </c>
       <c r="G2" t="n">
-        <v>0.374531835205992</v>
+        <v>0.722846441947566</v>
       </c>
       <c r="H2" t="n">
-        <v>0.185483870967742</v>
+        <v>0.311827956989247</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3616287844580776</v>
+        <v>1.140926299999998</v>
       </c>
       <c r="J2" t="n">
-        <v>88.85438650306737</v>
+        <v>358.7396482617585</v>
       </c>
       <c r="K2" t="n">
-        <v>33.82924335378323</v>
+        <v>67.06952965235175</v>
       </c>
       <c r="L2" t="n">
-        <v>1105801.555214723</v>
+        <v>5610707.334355831</v>
       </c>
       <c r="M2" t="n">
-        <v>582183.7985685072</v>
+        <v>2877096.291411043</v>
       </c>
       <c r="N2" t="n">
-        <v>5133.394683026585</v>
+        <v>31334.22597137014</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8482758058887608</v>
+        <v>0.9049339862289006</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6385545055949505</v>
+        <v>0.4789658376556589</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002088256148488515</v>
+        <v>9.73967609461153e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1559313155533806</v>
+        <v>0.09139743381542312</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00259885525922301</v>
+        <v>0.001523290563590385</v>
       </c>
       <c r="T2" t="n">
-        <v>1.566037027752682</v>
+        <v>2.087831576662313</v>
       </c>
       <c r="U2" t="n">
-        <v>12445.098083892</v>
+        <v>15640.05361978254</v>
       </c>
     </row>
     <row r="3">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (xhigh)</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -614,278 +614,278 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.529584326329171</v>
+        <v>0.42779695164088</v>
       </c>
       <c r="F3" t="n">
-        <v>0.566371681415929</v>
+        <v>0.162241887905605</v>
       </c>
       <c r="G3" t="n">
-        <v>0.707865168539326</v>
+        <v>0.629213483146067</v>
       </c>
       <c r="H3" t="n">
-        <v>0.314516129032258</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I3" t="n">
-        <v>1.209317104846625</v>
+        <v>0.09081146755368105</v>
       </c>
       <c r="J3" t="n">
-        <v>413.8987709611451</v>
+        <v>743.5829417177911</v>
       </c>
       <c r="K3" t="n">
-        <v>96.1922290388548</v>
+        <v>66.08691206543966</v>
       </c>
       <c r="L3" t="n">
-        <v>12806609.00511247</v>
+        <v>12713750.95194274</v>
       </c>
       <c r="M3" t="n">
-        <v>6575104.906952964</v>
+        <v>6378205.537321064</v>
       </c>
       <c r="N3" t="n">
-        <v>30840.24642126789</v>
+        <v>37873.7581799591</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9100235393369858</v>
+        <v>0.9780317126088941</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4379201486580617</v>
+        <v>4.710825220261945</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.135242405837159e-05</v>
+        <v>3.36483665015878e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.07677012305681176</v>
+        <v>0.0345191042698696</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001279502050946863</v>
+        <v>0.0005753184044978266</v>
       </c>
       <c r="T3" t="n">
-        <v>2.283521329320756</v>
+        <v>0.2122770328431746</v>
       </c>
       <c r="U3" t="n">
-        <v>30941.40380115961</v>
+        <v>17097.95940527094</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Gemini CLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Muse Spark 1.2 (xhigh)</t>
+          <t>Gemini 3.1 Pro (high)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.6164044159758908</v>
+        <v>0.3293046837328304</v>
       </c>
       <c r="F4" t="n">
-        <v>0.581120943952802</v>
+        <v>0.141592920353982</v>
       </c>
       <c r="G4" t="n">
-        <v>0.816479400749064</v>
+        <v>0.760299625468165</v>
       </c>
       <c r="H4" t="n">
-        <v>0.451612903225806</v>
+        <v>0.08602150537634411</v>
       </c>
       <c r="I4" t="n">
-        <v>2.072823051942737</v>
+        <v>1.040041561860939</v>
       </c>
       <c r="J4" t="n">
-        <v>2448.643313905933</v>
+        <v>663.8363599182014</v>
       </c>
       <c r="K4" t="n">
-        <v>151.4345603271984</v>
+        <v>30.96883483789777</v>
       </c>
       <c r="L4" t="n">
-        <v>19963139.08486708</v>
+        <v>4727804.222392637</v>
       </c>
       <c r="M4" t="n">
-        <v>10093761.29754601</v>
+        <v>2465901.789877301</v>
       </c>
       <c r="N4" t="n">
-        <v>58305.98057259714</v>
+        <v>12977.50562372188</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9538301727874863</v>
+        <v>0.8650361016121313</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2973743539749669</v>
+        <v>0.316626465526635</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.087712875993296e-05</v>
+        <v>6.965277499713736e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01510398217189024</v>
+        <v>0.02976378248760652</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002517330361981707</v>
+        <v>0.0004960630414601087</v>
       </c>
       <c r="T4" t="n">
-        <v>3.362764766474046</v>
+        <v>3.158295685538259</v>
       </c>
       <c r="U4" t="n">
-        <v>8152.734606749663</v>
+        <v>7121.942255430543</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kimi K2.6</t>
+          <t>Composer 2.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3388925953605663</v>
+        <v>0.3830075380367747</v>
       </c>
       <c r="F5" t="n">
-        <v>0.165191740412979</v>
+        <v>0.15929203539823</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6928838951310859</v>
+        <v>0.6779026217228465</v>
       </c>
       <c r="H5" t="n">
-        <v>0.158602150537634</v>
+        <v>0.3118279569892475</v>
       </c>
       <c r="I5" t="n">
-        <v>1.21710007411043</v>
+        <v>0.08505141359918204</v>
       </c>
       <c r="J5" t="n">
-        <v>2443.385067484662</v>
+        <v>625.1976421267894</v>
       </c>
       <c r="K5" t="n">
-        <v>133.7675410760877</v>
+        <v>116.8680981595092</v>
       </c>
       <c r="L5" t="n">
-        <v>11660527.81595092</v>
+        <v>3705076.4698364</v>
       </c>
       <c r="M5" t="n">
-        <v>5891966.377300614</v>
+        <v>1872461.576687117</v>
       </c>
       <c r="N5" t="n">
-        <v>36930.17791411043</v>
+        <v>18453.85787321063</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9554328157869921</v>
+        <v>1.052833075750478</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2784426708775453</v>
+        <v>4.503247175194018</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.906322944463811e-05</v>
+        <v>0.0001033737201255894</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008321879343629747</v>
+        <v>0.03675710004924502</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001386979890604958</v>
+        <v>0.0006126183341540836</v>
       </c>
       <c r="T5" t="n">
-        <v>3.591403561991346</v>
+        <v>0.2220619835190183</v>
       </c>
       <c r="U5" t="n">
-        <v>4772.284144289555</v>
+        <v>5926.248309626565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (medium)</t>
+          <t>Opus 5 (high)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4196699779001624</v>
+        <v>0.6561729860226817</v>
       </c>
       <c r="F6" t="n">
-        <v>0.365781710914454</v>
+        <v>0.6076696165191739</v>
       </c>
       <c r="G6" t="n">
-        <v>0.621722846441947</v>
+        <v>0.868913857677903</v>
       </c>
       <c r="H6" t="n">
-        <v>0.271505376344086</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4430536771983641</v>
+        <v>3.918602446063396</v>
       </c>
       <c r="J6" t="n">
-        <v>191.3819171779141</v>
+        <v>842.8052382413097</v>
       </c>
       <c r="K6" t="n">
-        <v>57.08588957055215</v>
+        <v>94.85071574642126</v>
       </c>
       <c r="L6" t="n">
-        <v>4287327.734151328</v>
+        <v>9911366.349693259</v>
       </c>
       <c r="M6" t="n">
-        <v>2221162.702453987</v>
+        <v>4937399.112474437</v>
       </c>
       <c r="N6" t="n">
-        <v>11663.1390593047</v>
+        <v>37331.49386503067</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8832984632099325</v>
+        <v>0.9702723303233406</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9472215207735825</v>
+        <v>0.1674507672197952</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.788614351947498e-05</v>
+        <v>6.620408961504982e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1315704171288111</v>
+        <v>0.04671349604271027</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002192840285480186</v>
+        <v>0.0007785582673785045</v>
       </c>
       <c r="T6" t="n">
-        <v>1.055719256867511</v>
+        <v>5.971904557997063</v>
       </c>
       <c r="U6" t="n">
-        <v>22401.94788186653</v>
+        <v>11759.97241115327</v>
       </c>
     </row>
     <row r="7">
@@ -896,7 +896,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>DeepSeek V4 Pro (high)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -906,716 +906,716 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6702814566291138</v>
+        <v>0.3282816619106221</v>
       </c>
       <c r="F7" t="n">
-        <v>0.631268436578171</v>
+        <v>0.08554572271386431</v>
       </c>
       <c r="G7" t="n">
-        <v>0.887640449438202</v>
+        <v>0.700374531835206</v>
       </c>
       <c r="H7" t="n">
-        <v>0.491935483870968</v>
+        <v>0.198924731182796</v>
       </c>
       <c r="I7" t="n">
-        <v>8.943547018021487</v>
+        <v>0.2547256318476481</v>
       </c>
       <c r="J7" t="n">
-        <v>1451.329194274025</v>
+        <v>1072.531835378324</v>
       </c>
       <c r="K7" t="n">
-        <v>165.7202546941811</v>
+        <v>128.1457055214724</v>
       </c>
       <c r="L7" t="n">
-        <v>23699428.05214722</v>
+        <v>9942165.528629865</v>
       </c>
       <c r="M7" t="n">
-        <v>11810977.87014315</v>
+        <v>5181244.880368099</v>
       </c>
       <c r="N7" t="n">
-        <v>81385.06339468302</v>
+        <v>41975.79754601227</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9747033593278783</v>
+        <v>0.8541357545221669</v>
       </c>
       <c r="P7" t="n">
-        <v>0.07494581906691815</v>
+        <v>1.288765718351297</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.82826005401588e-05</v>
+        <v>3.301913058732415e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02771038270050364</v>
+        <v>0.01836486252894252</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004618397116750606</v>
+        <v>0.000306081042149042</v>
       </c>
       <c r="T7" t="n">
-        <v>13.34297246264148</v>
+        <v>0.77593622002864</v>
       </c>
       <c r="U7" t="n">
-        <v>16329.4641530325</v>
+        <v>9269.809250112259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.8</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>GPT-5.6 Terra (max)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5657152973570364</v>
+        <v>0.6042010361726691</v>
       </c>
       <c r="F8" t="n">
-        <v>0.56047197640118</v>
+        <v>0.669616519174042</v>
       </c>
       <c r="G8" t="n">
-        <v>0.865168539325843</v>
+        <v>0.782771535580524</v>
       </c>
       <c r="H8" t="n">
-        <v>0.271505376344086</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I8" t="n">
-        <v>1.396316917192255</v>
+        <v>1.930014663190181</v>
       </c>
       <c r="J8" t="n">
-        <v>384.9621257668713</v>
+        <v>491.0206543967283</v>
       </c>
       <c r="K8" t="n">
-        <v>110.7985685071575</v>
+        <v>95.80674846625767</v>
       </c>
       <c r="L8" t="n">
-        <v>15113684.86595342</v>
+        <v>9653668.778118595</v>
       </c>
       <c r="M8" t="n">
-        <v>7938344.274012004</v>
+        <v>4933733.868098159</v>
       </c>
       <c r="N8" t="n">
-        <v>64430.0844098625</v>
+        <v>60602.61656441716</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8677594149804605</v>
+        <v>0.9184675548550253</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4051482083985556</v>
+        <v>0.3130551532566941</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.743066647045306e-05</v>
+        <v>6.258771147630174e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.08817209686227062</v>
+        <v>0.07383001477789097</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00146953494770451</v>
+        <v>0.001230500246298183</v>
       </c>
       <c r="T8" t="n">
-        <v>2.468232560999683</v>
+        <v>3.194325311680895</v>
       </c>
       <c r="U8" t="n">
-        <v>39260.1865335347</v>
+        <v>19660.41283941338</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GLM-5.1</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>friendliai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.3691032797641257</v>
+        <v>0.5716614223656344</v>
       </c>
       <c r="F9" t="n">
-        <v>0.185840707964602</v>
+        <v>0.634218289085546</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6741573033707861</v>
+        <v>0.752808988764045</v>
       </c>
       <c r="H9" t="n">
-        <v>0.247311827956989</v>
+        <v>0.327956989247312</v>
       </c>
       <c r="I9" t="n">
-        <v>4.282000252842536</v>
+        <v>0.2882767483844579</v>
       </c>
       <c r="J9" t="n">
-        <v>1140.250613496931</v>
+        <v>482.0907147239265</v>
       </c>
       <c r="K9" t="n">
-        <v>174.2367075664622</v>
+        <v>114.6288343558282</v>
       </c>
       <c r="L9" t="n">
-        <v>25761884.92944783</v>
+        <v>15987867.69734152</v>
       </c>
       <c r="M9" t="n">
-        <v>13139446.7402863</v>
+        <v>8170928.992842535</v>
       </c>
       <c r="N9" t="n">
-        <v>49883.45705521473</v>
+        <v>65702.91104294479</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8889225409991813</v>
+        <v>0.9181831202060824</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08619879915212579</v>
+        <v>1.983029937618288</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.432749508721747e-05</v>
+        <v>3.57559515244607e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01942221869798375</v>
+        <v>0.0711477825528751</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0003237036449663959</v>
+        <v>0.001185796375881252</v>
       </c>
       <c r="T9" t="n">
-        <v>11.60108968844421</v>
+        <v>0.5042788215295665</v>
       </c>
       <c r="U9" t="n">
-        <v>22593.17787204784</v>
+        <v>33163.60844347958</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>GPT-5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.423892771774363</v>
+        <v>0.6103327520587847</v>
       </c>
       <c r="F10" t="n">
-        <v>0.274336283185841</v>
+        <v>0.64306784660767</v>
       </c>
       <c r="G10" t="n">
-        <v>0.771535580524345</v>
+        <v>0.827715355805243</v>
       </c>
       <c r="H10" t="n">
-        <v>0.225806451612903</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I10" t="n">
-        <v>1.800661744734149</v>
+        <v>4.75237007157464</v>
       </c>
       <c r="J10" t="n">
-        <v>399.3926789366056</v>
+        <v>614.9898987730064</v>
       </c>
       <c r="K10" t="n">
-        <v>42.04907975460122</v>
+        <v>107.1319018404908</v>
       </c>
       <c r="L10" t="n">
-        <v>4636274.728016362</v>
+        <v>12150851.17995912</v>
       </c>
       <c r="M10" t="n">
-        <v>2310268.645194274</v>
+        <v>6164087.486707566</v>
       </c>
       <c r="N10" t="n">
-        <v>17168.18507157464</v>
+        <v>25286.0654396728</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9576237577125707</v>
+        <v>0.9341674523911518</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2354094393430604</v>
+        <v>0.1284270254350285</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.142960601813308e-05</v>
+        <v>5.022962943249859e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.06368060219375923</v>
+        <v>0.0595456367601959</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001061343369895987</v>
+        <v>0.0009924272793365983</v>
       </c>
       <c r="T10" t="n">
-        <v>4.247918022279078</v>
+        <v>7.786523098332615</v>
       </c>
       <c r="U10" t="n">
-        <v>11608.31175063242</v>
+        <v>19757.8061106399</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (low)</t>
+          <t>Opus 4.8 (xhigh)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.5523451808562168</v>
+        <v>0.590718121759733</v>
       </c>
       <c r="F11" t="n">
-        <v>0.533923303834809</v>
+        <v>0.513274336283186</v>
       </c>
       <c r="G11" t="n">
-        <v>0.779026217228465</v>
+        <v>0.831460674157303</v>
       </c>
       <c r="H11" t="n">
-        <v>0.344086021505376</v>
+        <v>0.42741935483871</v>
       </c>
       <c r="I11" t="n">
-        <v>1.660386587423313</v>
+        <v>5.665366469580767</v>
       </c>
       <c r="J11" t="n">
-        <v>212.899582822086</v>
+        <v>1065.615385480574</v>
       </c>
       <c r="K11" t="n">
-        <v>53.92126789366053</v>
+        <v>136.1303390500093</v>
       </c>
       <c r="L11" t="n">
-        <v>3200236.065439673</v>
+        <v>13628306.24233129</v>
       </c>
       <c r="M11" t="n">
-        <v>1658130.417177914</v>
+        <v>6783846.309815951</v>
       </c>
       <c r="N11" t="n">
-        <v>8962.606339468302</v>
+        <v>62541.86503067485</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8829664546361214</v>
+        <v>0.9687226730983399</v>
       </c>
       <c r="P11" t="n">
-        <v>0.332660589431392</v>
+        <v>0.104268298428971</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0001725951365966908</v>
+        <v>4.3344940395079e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1556635781624228</v>
+        <v>0.03326067527600474</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002594392969373714</v>
+        <v>0.0005543445879334123</v>
       </c>
       <c r="T11" t="n">
-        <v>3.006066939607345</v>
+        <v>9.590642746330172</v>
       </c>
       <c r="U11" t="n">
-        <v>15031.6690292156</v>
+        <v>12789.14177481134</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Opus 4.8 (medium)</t>
+          <t>GPT-5.6 Sol (medium)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.5576883805320427</v>
+        <v>0.616195748748264</v>
       </c>
       <c r="F12" t="n">
-        <v>0.492625368731563</v>
+        <v>0.640117994100295</v>
       </c>
       <c r="G12" t="n">
-        <v>0.820224719101124</v>
+        <v>0.805243445692884</v>
       </c>
       <c r="H12" t="n">
-        <v>0.360215053763441</v>
+        <v>0.403225806451613</v>
       </c>
       <c r="I12" t="n">
-        <v>3.303841633946828</v>
+        <v>2.192997850306748</v>
       </c>
       <c r="J12" t="n">
-        <v>722.922882413088</v>
+        <v>297.9599253578734</v>
       </c>
       <c r="K12" t="n">
-        <v>92.91239658858525</v>
+        <v>71.35378323108384</v>
       </c>
       <c r="L12" t="n">
-        <v>7827354.369120649</v>
+        <v>5770064.36707567</v>
       </c>
       <c r="M12" t="n">
-        <v>3898584.399795501</v>
+        <v>2974758.351738241</v>
       </c>
       <c r="N12" t="n">
-        <v>34668.28732106339</v>
+        <v>18959.48773006135</v>
       </c>
       <c r="O12" t="n">
-        <v>0.963840128346697</v>
+        <v>0.8970664465490255</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1687999735828192</v>
+        <v>0.2809832889996098</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.12486434410271e-05</v>
+        <v>0.0001067918327331517</v>
       </c>
       <c r="R12" t="n">
-        <v>0.04628613043791069</v>
+        <v>0.1240829446459615</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0007714355072985115</v>
+        <v>0.002068049077432692</v>
       </c>
       <c r="T12" t="n">
-        <v>5.924171543245917</v>
+        <v>3.558930509925766</v>
       </c>
       <c r="U12" t="n">
-        <v>10827.37116162826</v>
+        <v>19365.23631540505</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Opus 4.8 (max)</t>
+          <t>GPT-5.6 Luna (xhigh)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6214051234130329</v>
+        <v>0.529584326329171</v>
       </c>
       <c r="F13" t="n">
-        <v>0.557522123893805</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G13" t="n">
-        <v>0.838951310861423</v>
+        <v>0.707865168539326</v>
       </c>
       <c r="H13" t="n">
-        <v>0.467741935483871</v>
+        <v>0.314516129032258</v>
       </c>
       <c r="I13" t="n">
-        <v>7.724725797009217</v>
+        <v>0.235909783783231</v>
       </c>
       <c r="J13" t="n">
-        <v>1386.687798057262</v>
+        <v>413.8987709611452</v>
       </c>
       <c r="K13" t="n">
-        <v>165.0175845341703</v>
+        <v>96.1922290388548</v>
       </c>
       <c r="L13" t="n">
-        <v>17920579.42791411</v>
+        <v>12823340.91104294</v>
       </c>
       <c r="M13" t="n">
-        <v>8919829.832822086</v>
+        <v>6575104.906952964</v>
       </c>
       <c r="N13" t="n">
-        <v>89374.98517382414</v>
+        <v>47572.15235173824</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9657541826994763</v>
+        <v>0.9100235393369853</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0804436480649737</v>
+        <v>2.244859529928555</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.467550398761645e-05</v>
+        <v>4.129846738092369e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02688731195083492</v>
+        <v>0.07677012305681175</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0004481218658472487</v>
+        <v>0.001279502050946862</v>
       </c>
       <c r="T13" t="n">
-        <v>12.43106229086364</v>
+        <v>0.4454621710926501</v>
       </c>
       <c r="U13" t="n">
-        <v>12923.29784182185</v>
+        <v>30981.8289174063</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (high)</t>
+          <t>Muse Spark 1.1 (xhigh)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6411644486641199</v>
+        <v>0.5492139250715363</v>
       </c>
       <c r="F14" t="n">
-        <v>0.648967551622419</v>
+        <v>0.542772861356932</v>
       </c>
       <c r="G14" t="n">
-        <v>0.820224719101124</v>
+        <v>0.771535580524344</v>
       </c>
       <c r="H14" t="n">
-        <v>0.454301075268817</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I14" t="n">
-        <v>3.85057263394683</v>
+        <v>1.435218435173823</v>
       </c>
       <c r="J14" t="n">
-        <v>369.9402760736197</v>
+        <v>761.3780071574632</v>
       </c>
       <c r="K14" t="n">
-        <v>84.6717791411043</v>
+        <v>55.51329243353784</v>
       </c>
       <c r="L14" t="n">
-        <v>8030278.504089991</v>
+        <v>12289527.21472391</v>
       </c>
       <c r="M14" t="n">
-        <v>4136516.062372188</v>
+        <v>6284599.100204499</v>
       </c>
       <c r="N14" t="n">
-        <v>19997.77709611452</v>
+        <v>34558.96932515338</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9060190184699437</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1665114541695913</v>
+        <v>0.3826692241484618</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.984336388053805e-05</v>
+        <v>4.46895893939297e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1039893988514825</v>
+        <v>0.04328051926180354</v>
       </c>
       <c r="S14" t="n">
-        <v>0.001733156647524709</v>
+        <v>0.0007213419876967256</v>
       </c>
       <c r="T14" t="n">
-        <v>6.005592858383808</v>
+        <v>2.61322295312684</v>
       </c>
       <c r="U14" t="n">
-        <v>21706.95926737085</v>
+        <v>16141.16391489395</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (xhigh)</t>
+          <t>Sonnet 4.6 (medium)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.5602917313962744</v>
+        <v>0.3864931360777617</v>
       </c>
       <c r="F15" t="n">
-        <v>0.584070796460177</v>
+        <v>0.289085545722714</v>
       </c>
       <c r="G15" t="n">
-        <v>0.771535580524345</v>
+        <v>0.6741573033707861</v>
       </c>
       <c r="H15" t="n">
-        <v>0.325268817204301</v>
+        <v>0.196236559139785</v>
       </c>
       <c r="I15" t="n">
-        <v>1.879152746625766</v>
+        <v>2.041513021472394</v>
       </c>
       <c r="J15" t="n">
-        <v>403.2234447852761</v>
+        <v>827.6555807770975</v>
       </c>
       <c r="K15" t="n">
-        <v>74.95092024539876</v>
+        <v>67.41768916155419</v>
       </c>
       <c r="L15" t="n">
-        <v>6631652.20858896</v>
+        <v>8444053.035787314</v>
       </c>
       <c r="M15" t="n">
-        <v>3404439.702453988</v>
+        <v>4205086.787321064</v>
       </c>
       <c r="N15" t="n">
-        <v>26011.59611451943</v>
+        <v>40070.1308793456</v>
       </c>
       <c r="O15" t="n">
-        <v>0.910418152728672</v>
+        <v>0.9487221679807681</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2981618883309738</v>
+        <v>0.1893170075393457</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.448750232568207e-05</v>
+        <v>4.577104554409345e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.08337189793534551</v>
+        <v>0.02801840367329206</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001389531632255759</v>
+        <v>0.0004669733945548676</v>
       </c>
       <c r="T15" t="n">
-        <v>3.353882703110441</v>
+        <v>5.282145608561714</v>
       </c>
       <c r="U15" t="n">
-        <v>16446.59380389064</v>
+        <v>10202.37551936649</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (medium)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4804969202427884</v>
+        <v>0.4708693600598454</v>
       </c>
       <c r="F16" t="n">
-        <v>0.457227138643068</v>
+        <v>0.371681415929203</v>
       </c>
       <c r="G16" t="n">
-        <v>0.696629213483146</v>
+        <v>0.764044943820225</v>
       </c>
       <c r="H16" t="n">
-        <v>0.287634408602151</v>
+        <v>0.276881720430108</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8847820614519432</v>
+        <v>1.998031234219494</v>
       </c>
       <c r="J16" t="n">
-        <v>240.094656441718</v>
+        <v>386.6294212678936</v>
       </c>
       <c r="K16" t="n">
-        <v>50.95501022494887</v>
+        <v>77.78698023176551</v>
       </c>
       <c r="L16" t="n">
-        <v>3164606.548057258</v>
+        <v>3955817.742194958</v>
       </c>
       <c r="M16" t="n">
-        <v>1632285.212678937</v>
+        <v>2043912.618541241</v>
       </c>
       <c r="N16" t="n">
-        <v>11855.54703476483</v>
+        <v>11032.14533060668</v>
       </c>
       <c r="O16" t="n">
-        <v>0.894438452837132</v>
+        <v>0.8915632417465622</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5430681081556789</v>
+        <v>0.2356666662639959</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0001518346476713713</v>
+        <v>0.0001190321169343295</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1200768715215685</v>
+        <v>0.07307297388528261</v>
       </c>
       <c r="S16" t="n">
-        <v>0.002001281192026142</v>
+        <v>0.001217882898088044</v>
       </c>
       <c r="T16" t="n">
-        <v>1.841389661779466</v>
+        <v>4.243281478254507</v>
       </c>
       <c r="U16" t="n">
-        <v>13180.66213949852</v>
+        <v>10231.54867320351</v>
       </c>
     </row>
     <row r="17">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (low)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1640,55 +1640,55 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.250636604330228</v>
+        <v>0.5531133827505798</v>
       </c>
       <c r="F17" t="n">
-        <v>0.103244837758112</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G17" t="n">
-        <v>0.49812734082397</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H17" t="n">
-        <v>0.150537634408602</v>
+        <v>0.306451612903226</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1920449385685073</v>
+        <v>2.65253587423313</v>
       </c>
       <c r="J17" t="n">
-        <v>100.0260337423312</v>
+        <v>386.3044764826171</v>
       </c>
       <c r="K17" t="n">
-        <v>34.30674846625767</v>
+        <v>78.53885480572598</v>
       </c>
       <c r="L17" t="n">
-        <v>1435665.844580776</v>
+        <v>6885560.579754606</v>
       </c>
       <c r="M17" t="n">
-        <v>762148.6063394684</v>
+        <v>3492715.358895706</v>
       </c>
       <c r="N17" t="n">
-        <v>5609.407975460122</v>
+        <v>13239.49488752556</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8430087375482057</v>
+        <v>0.9409891933709396</v>
       </c>
       <c r="P17" t="n">
-        <v>1.305093517165617</v>
+        <v>0.2085224890353234</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0001745786495348544</v>
+        <v>8.032946284386509e-05</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1503428227350525</v>
+        <v>0.08590840900216211</v>
       </c>
       <c r="S17" t="n">
-        <v>0.002505713712250875</v>
+        <v>0.001431806816702702</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7662286164533141</v>
+        <v>4.795645806005133</v>
       </c>
       <c r="U17" t="n">
-        <v>14352.92184311812</v>
+        <v>17824.18014528092</v>
       </c>
     </row>
     <row r="18">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Opus 5 (low)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1709,59 +1709,59 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.6131027159527611</v>
+        <v>0.5940064571013326</v>
       </c>
       <c r="F18" t="n">
-        <v>0.519174041297935</v>
+        <v>0.569321533923304</v>
       </c>
       <c r="G18" t="n">
-        <v>0.838951310861423</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H18" t="n">
-        <v>0.481182795698925</v>
+        <v>0.39247311827957</v>
       </c>
       <c r="I18" t="n">
-        <v>3.230610966002048</v>
+        <v>2.295157744887527</v>
       </c>
       <c r="J18" t="n">
-        <v>1792.147180981595</v>
+        <v>598.7677147239262</v>
       </c>
       <c r="K18" t="n">
-        <v>159.5848670756646</v>
+        <v>64.39263803680981</v>
       </c>
       <c r="L18" t="n">
-        <v>12503741.56441715</v>
+        <v>5258606.375255628</v>
       </c>
       <c r="M18" t="n">
-        <v>6469207.32413088</v>
+        <v>2618171.039877301</v>
       </c>
       <c r="N18" t="n">
-        <v>63117.84253578731</v>
+        <v>22632.92229038855</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8998815214008218</v>
+        <v>0.9637890151908798</v>
       </c>
       <c r="P18" t="n">
-        <v>0.189779184929682</v>
+        <v>0.2588085539760761</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.903354030424894e-05</v>
+        <v>0.0001129589124404576</v>
       </c>
       <c r="R18" t="n">
-        <v>0.02052630684998603</v>
+        <v>0.05952289435396941</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0003421051141664338</v>
+        <v>0.0009920482392328236</v>
       </c>
       <c r="T18" t="n">
-        <v>5.269281772764097</v>
+        <v>3.863859925172484</v>
       </c>
       <c r="U18" t="n">
-        <v>6976.961321652501</v>
+        <v>8782.381290681667</v>
       </c>
     </row>
     <row r="19">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (xhigh)</t>
+          <t>GPT-5.6 Terra (low)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1786,55 +1786,55 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.633388342362512</v>
+        <v>0.3864628427996264</v>
       </c>
       <c r="F19" t="n">
-        <v>0.669616519174041</v>
+        <v>0.297935103244838</v>
       </c>
       <c r="G19" t="n">
-        <v>0.797752808988764</v>
+        <v>0.632958801498127</v>
       </c>
       <c r="H19" t="n">
-        <v>0.432795698924731</v>
+        <v>0.228494623655914</v>
       </c>
       <c r="I19" t="n">
-        <v>4.799269930470349</v>
+        <v>0.3850630644171779</v>
       </c>
       <c r="J19" t="n">
-        <v>440.5130695296522</v>
+        <v>154.8149498977502</v>
       </c>
       <c r="K19" t="n">
-        <v>93.87525562372188</v>
+        <v>37.80981595092025</v>
       </c>
       <c r="L19" t="n">
-        <v>9886595.803681007</v>
+        <v>1659148.663599183</v>
       </c>
       <c r="M19" t="n">
-        <v>5095034.968302658</v>
+        <v>861642.4202453988</v>
       </c>
       <c r="N19" t="n">
-        <v>25684.60429447853</v>
+        <v>8355.890593047036</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9080963249335335</v>
+        <v>0.8771903855272027</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1319759779172157</v>
+        <v>1.003635192548439</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.406536232893095e-05</v>
+        <v>0.0002329283995330921</v>
       </c>
       <c r="R19" t="n">
-        <v>0.08627054035497261</v>
+        <v>0.1497773347037368</v>
       </c>
       <c r="S19" t="n">
-        <v>0.001437842339249544</v>
+        <v>0.002496288911728947</v>
       </c>
       <c r="T19" t="n">
-        <v>7.577136504548336</v>
+        <v>0.996377974212713</v>
       </c>
       <c r="U19" t="n">
-        <v>22443.36544710738</v>
+        <v>10716.97962435147</v>
       </c>
     </row>
     <row r="20">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (none)</t>
+          <t>GPT-5.6 Terra (none)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1859,785 +1859,785 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4336881923573268</v>
+        <v>0.2309196896685307</v>
       </c>
       <c r="F20" t="n">
-        <v>0.353982300884956</v>
+        <v>0.132743362831858</v>
       </c>
       <c r="G20" t="n">
-        <v>0.602996254681648</v>
+        <v>0.374531835205992</v>
       </c>
       <c r="H20" t="n">
-        <v>0.344086021505376</v>
+        <v>0.185483870967742</v>
       </c>
       <c r="I20" t="n">
-        <v>1.397017818507157</v>
+        <v>0.2926964817995911</v>
       </c>
       <c r="J20" t="n">
-        <v>197.8853650306747</v>
+        <v>88.85438650306737</v>
       </c>
       <c r="K20" t="n">
-        <v>55.10736196319019</v>
+        <v>33.82924335378323</v>
       </c>
       <c r="L20" t="n">
-        <v>3404912.347648262</v>
+        <v>1105802.151329243</v>
       </c>
       <c r="M20" t="n">
-        <v>1731981.235173824</v>
+        <v>582183.7985685072</v>
       </c>
       <c r="N20" t="n">
-        <v>7689.902862985686</v>
+        <v>5133.990797546012</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8919396546681845</v>
+        <v>0.8482758058887612</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3104385546211307</v>
+        <v>0.7889390683781471</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0001273713235692751</v>
+        <v>0.0002088255022753852</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1314967963265297</v>
+        <v>0.1559313155533806</v>
       </c>
       <c r="S20" t="n">
-        <v>0.002191613272108827</v>
+        <v>0.00259885525922301</v>
       </c>
       <c r="T20" t="n">
-        <v>3.221249374841448</v>
+        <v>1.267525009321365</v>
       </c>
       <c r="U20" t="n">
-        <v>17206.48895445329</v>
+        <v>12445.10479278442</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Opus 4.8 (low)</t>
+          <t>GPT-5.6 Luna (high)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4904379267565557</v>
+        <v>0.516945881593198</v>
       </c>
       <c r="F21" t="n">
-        <v>0.410029498525074</v>
+        <v>0.533923303834808</v>
       </c>
       <c r="G21" t="n">
-        <v>0.779026217228464</v>
+        <v>0.726591760299625</v>
       </c>
       <c r="H21" t="n">
-        <v>0.282258064516129</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="I21" t="n">
-        <v>2.182594679703477</v>
+        <v>0.1797932241513293</v>
       </c>
       <c r="J21" t="n">
-        <v>516.6536431492842</v>
+        <v>342.6686574642128</v>
       </c>
       <c r="K21" t="n">
-        <v>68.16359918200409</v>
+        <v>83.81901840490798</v>
       </c>
       <c r="L21" t="n">
-        <v>5214050.029652352</v>
+        <v>9651632.293456044</v>
       </c>
       <c r="M21" t="n">
-        <v>2595804.632924335</v>
+        <v>4959371.744376278</v>
       </c>
       <c r="N21" t="n">
-        <v>23270.04396728017</v>
+        <v>32492.70552147239</v>
       </c>
       <c r="O21" t="n">
-        <v>0.966158217610491</v>
+        <v>0.9032288062243129</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2247040787358583</v>
+        <v>2.875224492098168</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.406084022351733e-05</v>
+        <v>5.356046167897375e-05</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0569555174836748</v>
+        <v>0.09051528997463437</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0009492586247279134</v>
+        <v>0.001508588166243906</v>
       </c>
       <c r="T21" t="n">
-        <v>4.450297500720978</v>
+        <v>0.3477989293525597</v>
       </c>
       <c r="U21" t="n">
-        <v>10091.9641210113</v>
+        <v>28166.07846448294</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>Qwen3.7 Plus (thinking)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5127556084440553</v>
+        <v>0.3812184526692477</v>
       </c>
       <c r="F22" t="n">
-        <v>0.395280235988201</v>
+        <v>0.191740412979351</v>
       </c>
       <c r="G22" t="n">
-        <v>0.782771535580524</v>
+        <v>0.715355805243446</v>
       </c>
       <c r="H22" t="n">
-        <v>0.360215053763441</v>
+        <v>0.236559139784946</v>
       </c>
       <c r="I22" t="n">
-        <v>2.942840985557261</v>
+        <v>6.300658805725988</v>
       </c>
       <c r="J22" t="n">
-        <v>752.2755521472382</v>
+        <v>643.9465817995912</v>
       </c>
       <c r="K22" t="n">
-        <v>54.41308793456033</v>
+        <v>145.9662576687116</v>
       </c>
       <c r="L22" t="n">
-        <v>7582747.093047052</v>
+        <v>8784635.035787327</v>
       </c>
       <c r="M22" t="n">
-        <v>3744700.533231084</v>
+        <v>4715248.469325154</v>
       </c>
       <c r="N22" t="n">
-        <v>25943.59151329243</v>
+        <v>32611.0408997955</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9584168731547833</v>
+        <v>0.8105104948122446</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1742382993034736</v>
+        <v>0.06050453840204764</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.762135175446153e-05</v>
+        <v>4.339604902380339e-05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.04089636625679125</v>
+        <v>0.03552019345491832</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0006816061042798542</v>
+        <v>0.0005920032242486387</v>
       </c>
       <c r="T22" t="n">
-        <v>5.739266303663147</v>
+        <v>16.52768579697415</v>
       </c>
       <c r="U22" t="n">
-        <v>10079.74680474918</v>
+        <v>13641.86919237546</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Muse Spark 1.2 (xhigh)</t>
+          <t>GPT-5.6 Luna (none)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.5888788742875287</v>
+        <v>0.1909870904304247</v>
       </c>
       <c r="F23" t="n">
-        <v>0.528023598820059</v>
+        <v>0.0648967551622419</v>
       </c>
       <c r="G23" t="n">
-        <v>0.797752808988764</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>0.440860215053763</v>
+        <v>0.174731182795699</v>
       </c>
       <c r="I23" t="n">
-        <v>1.914379785695295</v>
+        <v>0.06947505231083853</v>
       </c>
       <c r="J23" t="n">
-        <v>1064.740692229039</v>
+        <v>131.816209611452</v>
       </c>
       <c r="K23" t="n">
-        <v>65.87116564417177</v>
+        <v>54.28629856850716</v>
       </c>
       <c r="L23" t="n">
-        <v>16350688.07453988</v>
+        <v>3549958.812883432</v>
       </c>
       <c r="M23" t="n">
-        <v>8360784.971370144</v>
+        <v>1835572.532719836</v>
       </c>
       <c r="N23" t="n">
-        <v>47157.38036809816</v>
+        <v>7936.23108384458</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.8748960056789888</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3076081761245981</v>
+        <v>2.749002470353369</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.601554085081526e-05</v>
+        <v>5.379980458852045e-05</v>
       </c>
       <c r="R23" t="n">
-        <v>0.03318435438330295</v>
+        <v>0.08693335561387526</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0005530725730550492</v>
+        <v>0.001448889260231254</v>
       </c>
       <c r="T23" t="n">
-        <v>3.250888882728999</v>
+        <v>0.3637683162472588</v>
       </c>
       <c r="U23" t="n">
-        <v>15356.49777816761</v>
+        <v>26931.12496063622</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gemini 3.6 Flash (high)</t>
+          <t>Opus 4.8 (high)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.4724127134829677</v>
+        <v>0.5757636668124304</v>
       </c>
       <c r="F24" t="n">
-        <v>0.412979351032448</v>
+        <v>0.51622418879056</v>
       </c>
       <c r="G24" t="n">
-        <v>0.786516853932584</v>
+        <v>0.823970037453183</v>
       </c>
       <c r="H24" t="n">
-        <v>0.217741935483871</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="I24" t="n">
-        <v>2.083890154754602</v>
+        <v>3.7823013803681</v>
       </c>
       <c r="J24" t="n">
-        <v>626.0057290388545</v>
+        <v>761.0308312883442</v>
       </c>
       <c r="K24" t="n">
-        <v>65.01533742331287</v>
+        <v>104.7627811860941</v>
       </c>
       <c r="L24" t="n">
-        <v>13020159.54294479</v>
+        <v>9188690.866053157</v>
       </c>
       <c r="M24" t="n">
-        <v>6765842.061349694</v>
+        <v>4574601.889570553</v>
       </c>
       <c r="N24" t="n">
-        <v>42763.3517382413</v>
+        <v>40682.70756646217</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8377770485520734</v>
+        <v>0.9682475638703767</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2266975120570109</v>
+        <v>0.152225750650361</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.628317394458911e-05</v>
+        <v>6.266003233818004e-05</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0452787594332364</v>
+        <v>0.04539345659657892</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0007546459905539399</v>
+        <v>0.0007565576099429819</v>
       </c>
       <c r="T24" t="n">
-        <v>4.411164423138952</v>
+        <v>6.569190795431488</v>
       </c>
       <c r="U24" t="n">
-        <v>20798.78655892726</v>
+        <v>12074.00605636132</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Devin CLI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>SWE-1.7 Lightning Max</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Cognition</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.466554082589455</v>
+        <v>0.5221389513465003</v>
       </c>
       <c r="F25" t="n">
-        <v>0.315634218289085</v>
+        <v>0.404129793510324</v>
       </c>
       <c r="G25" t="n">
-        <v>0.745318352059925</v>
+        <v>0.7940074906367039</v>
       </c>
       <c r="H25" t="n">
-        <v>0.338709677419355</v>
+        <v>0.368279569892473</v>
       </c>
       <c r="I25" t="n">
-        <v>2.72490571101738</v>
+        <v>8.521259638036815</v>
       </c>
       <c r="J25" t="n">
-        <v>826.6777535787326</v>
+        <v>637.3248271983654</v>
       </c>
       <c r="K25" t="n">
-        <v>86.42229038854805</v>
+        <v>86.57157464212679</v>
       </c>
       <c r="L25" t="n">
-        <v>5728865.180470356</v>
+        <v>15573672.60122699</v>
       </c>
       <c r="M25" t="n">
-        <v>2855520.426380368</v>
+        <v>7834231.955010225</v>
       </c>
       <c r="N25" t="n">
-        <v>17872.17893660532</v>
+        <v>38917.19427402863</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9538631453697453</v>
+        <v>0.9746033359706325</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1712184317802544</v>
+        <v>0.06127485530610991</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.14391799932617e-05</v>
+        <v>3.352702761359984e-05</v>
       </c>
       <c r="R25" t="n">
-        <v>0.03386234216922257</v>
+        <v>0.04915599666579311</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0005643723694870429</v>
+        <v>0.0008192666110965519</v>
       </c>
       <c r="T25" t="n">
-        <v>5.840492694638288</v>
+        <v>16.31990797863682</v>
       </c>
       <c r="U25" t="n">
-        <v>6929.985905233072</v>
+        <v>24436.00490143738</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Devin CLI</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SWE-1.7 Lightning Max</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cognition</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.5221389513465007</v>
+        <v>0.4665540825894554</v>
       </c>
       <c r="F26" t="n">
-        <v>0.404129793510325</v>
+        <v>0.315634218289086</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7940074906367039</v>
+        <v>0.745318352059925</v>
       </c>
       <c r="H26" t="n">
-        <v>0.368279569892473</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="I26" t="n">
-        <v>8.521259638036815</v>
+        <v>2.72490571101738</v>
       </c>
       <c r="J26" t="n">
-        <v>637.3248271983654</v>
+        <v>826.6777535787322</v>
       </c>
       <c r="K26" t="n">
-        <v>86.57157464212679</v>
+        <v>86.42229038854805</v>
       </c>
       <c r="L26" t="n">
-        <v>15573672.60122699</v>
+        <v>5728865.180470356</v>
       </c>
       <c r="M26" t="n">
-        <v>7834231.955010225</v>
+        <v>2855520.426380368</v>
       </c>
       <c r="N26" t="n">
-        <v>38917.19427402863</v>
+        <v>17872.17893660532</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9746033359706329</v>
+        <v>0.9538631453697446</v>
       </c>
       <c r="P26" t="n">
-        <v>0.06127485530610995</v>
+        <v>0.1712184317802546</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.352702761359986e-05</v>
+        <v>8.143917999326177e-05</v>
       </c>
       <c r="R26" t="n">
-        <v>0.04915599666579314</v>
+        <v>0.03386234216922261</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0008192666110965524</v>
+        <v>0.0005643723694870434</v>
       </c>
       <c r="T26" t="n">
-        <v>16.31990797863681</v>
+        <v>5.840492694638283</v>
       </c>
       <c r="U26" t="n">
-        <v>24436.00490143738</v>
+        <v>6929.985905233076</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Opus 4.8 (high)</t>
+          <t>Gemini 3.6 Flash (high)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.5757636668124304</v>
+        <v>0.4724127134829677</v>
       </c>
       <c r="F27" t="n">
-        <v>0.51622418879056</v>
+        <v>0.412979351032448</v>
       </c>
       <c r="G27" t="n">
-        <v>0.823970037453183</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H27" t="n">
-        <v>0.387096774193548</v>
+        <v>0.217741935483871</v>
       </c>
       <c r="I27" t="n">
-        <v>3.7823013803681</v>
+        <v>2.083890154754602</v>
       </c>
       <c r="J27" t="n">
-        <v>761.0308312883442</v>
+        <v>626.0057290388548</v>
       </c>
       <c r="K27" t="n">
-        <v>104.7627811860941</v>
+        <v>65.01533742331287</v>
       </c>
       <c r="L27" t="n">
-        <v>9188690.866053157</v>
+        <v>13020159.54294479</v>
       </c>
       <c r="M27" t="n">
-        <v>4574601.889570553</v>
+        <v>6765842.061349694</v>
       </c>
       <c r="N27" t="n">
-        <v>40682.70756646217</v>
+        <v>42763.3517382413</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9682475638703767</v>
+        <v>0.8377770485520734</v>
       </c>
       <c r="P27" t="n">
-        <v>0.152225750650361</v>
+        <v>0.2266975120570109</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.266003233818004e-05</v>
+        <v>3.628317394458911e-05</v>
       </c>
       <c r="R27" t="n">
-        <v>0.04539345659657892</v>
+        <v>0.04527875943323637</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0007565576099429819</v>
+        <v>0.0007546459905539396</v>
       </c>
       <c r="T27" t="n">
-        <v>6.569190795431488</v>
+        <v>4.411164423138952</v>
       </c>
       <c r="U27" t="n">
-        <v>12074.00605636132</v>
+        <v>20798.78655892725</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (none)</t>
+          <t>Muse Spark 1.2 (xhigh)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.1909870904304247</v>
+        <v>0.5888788742875287</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0648967551622419</v>
+        <v>0.528023598820059</v>
       </c>
       <c r="G28" t="n">
-        <v>0.333333333333333</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="H28" t="n">
-        <v>0.174731182795699</v>
+        <v>0.440860215053763</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3280835570961148</v>
+        <v>1.914379785695295</v>
       </c>
       <c r="J28" t="n">
-        <v>131.816209611452</v>
+        <v>1064.740692229038</v>
       </c>
       <c r="K28" t="n">
-        <v>54.28629856850716</v>
+        <v>65.87116564417177</v>
       </c>
       <c r="L28" t="n">
-        <v>3549957.21063395</v>
+        <v>16350688.07453988</v>
       </c>
       <c r="M28" t="n">
-        <v>1835572.532719836</v>
+        <v>8360784.971370144</v>
       </c>
       <c r="N28" t="n">
-        <v>7934.628834355828</v>
+        <v>47157.38036809816</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8748960056789888</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P28" t="n">
-        <v>0.5821294188616513</v>
+        <v>0.3076081761245981</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.3799828870703e-05</v>
+        <v>3.601554085081526e-05</v>
       </c>
       <c r="R28" t="n">
-        <v>0.08693335561387526</v>
+        <v>0.03318435438330296</v>
       </c>
       <c r="S28" t="n">
-        <v>0.001448889260231254</v>
+        <v>0.0005530725730550494</v>
       </c>
       <c r="T28" t="n">
-        <v>1.71783106573705</v>
+        <v>3.250888882728999</v>
       </c>
       <c r="U28" t="n">
-        <v>26931.11280545829</v>
+        <v>15356.49777816762</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Qwen3.7 Plus (thinking)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.3812184526692477</v>
+        <v>0.5127556084440553</v>
       </c>
       <c r="F29" t="n">
-        <v>0.191740412979351</v>
+        <v>0.395280235988201</v>
       </c>
       <c r="G29" t="n">
-        <v>0.715355805243446</v>
+        <v>0.782771535580524</v>
       </c>
       <c r="H29" t="n">
-        <v>0.236559139784946</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I29" t="n">
-        <v>6.300658805725988</v>
+        <v>2.942840985557261</v>
       </c>
       <c r="J29" t="n">
-        <v>643.9465817995912</v>
+        <v>752.2755521472382</v>
       </c>
       <c r="K29" t="n">
-        <v>145.9662576687116</v>
+        <v>54.41308793456033</v>
       </c>
       <c r="L29" t="n">
-        <v>8784635.035787327</v>
+        <v>7582747.093047047</v>
       </c>
       <c r="M29" t="n">
-        <v>4715248.469325154</v>
+        <v>3744700.533231084</v>
       </c>
       <c r="N29" t="n">
-        <v>32611.0408997955</v>
+        <v>25943.59151329243</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8105104948122449</v>
+        <v>0.958416873154783</v>
       </c>
       <c r="P29" t="n">
-        <v>0.06050453840204764</v>
+        <v>0.1742382993034736</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.339604902380339e-05</v>
+        <v>6.762135175446157e-05</v>
       </c>
       <c r="R29" t="n">
-        <v>0.03552019345491832</v>
+        <v>0.04089636625679125</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0005920032242486387</v>
+        <v>0.0006816061042798542</v>
       </c>
       <c r="T29" t="n">
-        <v>16.52768579697415</v>
+        <v>5.739266303663147</v>
       </c>
       <c r="U29" t="n">
-        <v>13641.86919237546</v>
+        <v>10079.74680474918</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (high)</t>
+          <t>Opus 4.8 (low)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.516945881593198</v>
+        <v>0.4904379267565557</v>
       </c>
       <c r="F30" t="n">
-        <v>0.533923303834808</v>
+        <v>0.410029498525074</v>
       </c>
       <c r="G30" t="n">
-        <v>0.726591760299625</v>
+        <v>0.779026217228464</v>
       </c>
       <c r="H30" t="n">
-        <v>0.290322580645161</v>
+        <v>0.282258064516129</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9174253706543963</v>
+        <v>2.182594679703477</v>
       </c>
       <c r="J30" t="n">
-        <v>342.6686574642128</v>
+        <v>516.6536431492841</v>
       </c>
       <c r="K30" t="n">
-        <v>83.81901840490798</v>
+        <v>68.16359918200409</v>
       </c>
       <c r="L30" t="n">
-        <v>9641370.493865017</v>
+        <v>5214050.029652352</v>
       </c>
       <c r="M30" t="n">
-        <v>4959371.744376278</v>
+        <v>2595804.632924335</v>
       </c>
       <c r="N30" t="n">
-        <v>22230.90593047035</v>
+        <v>23270.04396728017</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9032288062243129</v>
+        <v>0.966158217610491</v>
       </c>
       <c r="P30" t="n">
-        <v>0.5634745867388236</v>
+        <v>0.2247040787358583</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.361746879472584e-05</v>
+        <v>9.406084022351733e-05</v>
       </c>
       <c r="R30" t="n">
-        <v>0.09051528997463437</v>
+        <v>0.05695551748367481</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001508588166243906</v>
+        <v>0.0009492586247279136</v>
       </c>
       <c r="T30" t="n">
-        <v>1.774702929882995</v>
+        <v>4.450297500720978</v>
       </c>
       <c r="U30" t="n">
-        <v>28136.13175249893</v>
+        <v>10091.9641210113</v>
       </c>
     </row>
     <row r="31">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (low)</t>
+          <t>GPT-5.6 Sol (none)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2662,420 +2662,420 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.3864628427996264</v>
+        <v>0.4336881923573268</v>
       </c>
       <c r="F31" t="n">
-        <v>0.297935103244838</v>
+        <v>0.353982300884956</v>
       </c>
       <c r="G31" t="n">
-        <v>0.632958801498127</v>
+        <v>0.602996254681648</v>
       </c>
       <c r="H31" t="n">
-        <v>0.228494623655914</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4909580805725969</v>
+        <v>1.086854643353786</v>
       </c>
       <c r="J31" t="n">
-        <v>154.8149498977502</v>
+        <v>197.8853650306747</v>
       </c>
       <c r="K31" t="n">
-        <v>37.80981595092025</v>
+        <v>55.10736196319019</v>
       </c>
       <c r="L31" t="n">
-        <v>1657646.844580775</v>
+        <v>3404914.234151331</v>
       </c>
       <c r="M31" t="n">
-        <v>861642.4202453988</v>
+        <v>1731981.235173824</v>
       </c>
       <c r="N31" t="n">
-        <v>6854.071574642127</v>
+        <v>7691.78936605317</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8771903855272027</v>
+        <v>0.8919396546681844</v>
       </c>
       <c r="P31" t="n">
-        <v>0.7871605705091984</v>
+        <v>0.399030537348641</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0002331394313952103</v>
+        <v>0.0001273712529988065</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1497773347037368</v>
+        <v>0.1314967963265297</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002496288911728947</v>
+        <v>0.002191613272108827</v>
       </c>
       <c r="T31" t="n">
-        <v>1.270388834838513</v>
+        <v>2.50607386252817</v>
       </c>
       <c r="U31" t="n">
-        <v>10707.27888796005</v>
+        <v>17206.49848776602</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Opus 5 (low)</t>
+          <t>GPT-5.6 Sol (xhigh)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.5940064571013326</v>
+        <v>0.633388342362512</v>
       </c>
       <c r="F32" t="n">
-        <v>0.569321533923304</v>
+        <v>0.669616519174041</v>
       </c>
       <c r="G32" t="n">
-        <v>0.820224719101124</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="H32" t="n">
-        <v>0.39247311827957</v>
+        <v>0.432795698924731</v>
       </c>
       <c r="I32" t="n">
-        <v>2.295157744887527</v>
+        <v>3.736677527198365</v>
       </c>
       <c r="J32" t="n">
-        <v>598.7677147239262</v>
+        <v>440.5130695296522</v>
       </c>
       <c r="K32" t="n">
-        <v>64.39263803680981</v>
+        <v>93.87525562372188</v>
       </c>
       <c r="L32" t="n">
-        <v>5258606.375255628</v>
+        <v>9898822.473415133</v>
       </c>
       <c r="M32" t="n">
-        <v>2618171.039877301</v>
+        <v>5095034.968302658</v>
       </c>
       <c r="N32" t="n">
-        <v>22632.92229038855</v>
+        <v>37911.27402862985</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9637890151908798</v>
+        <v>0.9080963249335335</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2588085539760761</v>
+        <v>0.1695057541766001</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.0001129589124404576</v>
+        <v>6.398623109602961e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.05952289435396941</v>
+        <v>0.08627054035497261</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0009920482392328236</v>
+        <v>0.001437842339249544</v>
       </c>
       <c r="T32" t="n">
-        <v>3.863859925172484</v>
+        <v>5.89950473868956</v>
       </c>
       <c r="U32" t="n">
-        <v>8782.381290681667</v>
+        <v>22471.12096806657</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.5531133827505798</v>
+        <v>0.6131027159527611</v>
       </c>
       <c r="F33" t="n">
-        <v>0.566371681415929</v>
+        <v>0.519174041297935</v>
       </c>
       <c r="G33" t="n">
-        <v>0.786516853932584</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H33" t="n">
-        <v>0.306451612903226</v>
+        <v>0.481182795698925</v>
       </c>
       <c r="I33" t="n">
-        <v>2.65253587423313</v>
+        <v>3.230610966002044</v>
       </c>
       <c r="J33" t="n">
-        <v>386.3044764826176</v>
+        <v>1792.147180981595</v>
       </c>
       <c r="K33" t="n">
-        <v>78.53885480572598</v>
+        <v>159.5848670756646</v>
       </c>
       <c r="L33" t="n">
-        <v>6885560.579754606</v>
+        <v>12503741.56441719</v>
       </c>
       <c r="M33" t="n">
-        <v>3492715.358895706</v>
+        <v>6469207.32413088</v>
       </c>
       <c r="N33" t="n">
-        <v>13239.49488752556</v>
+        <v>63117.84253578731</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9409891933709401</v>
+        <v>0.8998815214008218</v>
       </c>
       <c r="P33" t="n">
-        <v>0.2085224890353234</v>
+        <v>0.1897791849296822</v>
       </c>
       <c r="Q33" t="n">
-        <v>8.032946284386509e-05</v>
+        <v>4.90335403042488e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>0.085908409002162</v>
+        <v>0.02052630684998603</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0014318068167027</v>
+        <v>0.0003421051141664338</v>
       </c>
       <c r="T33" t="n">
-        <v>4.795645806005133</v>
+        <v>5.26928177276409</v>
       </c>
       <c r="U33" t="n">
-        <v>17824.1801452809</v>
+        <v>6976.96132165252</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>GPT-5.6 Luna (low)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.4708693600598454</v>
+        <v>0.250636604330228</v>
       </c>
       <c r="F34" t="n">
-        <v>0.371681415929203</v>
+        <v>0.103244837758112</v>
       </c>
       <c r="G34" t="n">
-        <v>0.764044943820225</v>
+        <v>0.49812734082397</v>
       </c>
       <c r="H34" t="n">
-        <v>0.276881720430108</v>
+        <v>0.150537634408602</v>
       </c>
       <c r="I34" t="n">
-        <v>1.998031234219494</v>
+        <v>0.03893760139059304</v>
       </c>
       <c r="J34" t="n">
-        <v>386.6294212678936</v>
+        <v>100.0260337423312</v>
       </c>
       <c r="K34" t="n">
-        <v>77.78698023176551</v>
+        <v>34.30674846625767</v>
       </c>
       <c r="L34" t="n">
-        <v>3955817.742194958</v>
+        <v>1436684.32822086</v>
       </c>
       <c r="M34" t="n">
-        <v>2043912.618541241</v>
+        <v>762148.6063394684</v>
       </c>
       <c r="N34" t="n">
-        <v>11032.14533060668</v>
+        <v>6627.891615541922</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8915632417465622</v>
+        <v>0.8430087375482054</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2356666662639959</v>
+        <v>6.436878374094698</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0001190321169343295</v>
+        <v>0.0001744548885283712</v>
       </c>
       <c r="R34" t="n">
-        <v>0.07307297388528261</v>
+        <v>0.1503428227350525</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001217882898088044</v>
+        <v>0.002505713712250875</v>
       </c>
       <c r="T34" t="n">
-        <v>4.243281478254507</v>
+        <v>0.1553548073899474</v>
       </c>
       <c r="U34" t="n">
-        <v>10231.54867320351</v>
+        <v>14363.104028715</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sonnet 4.6 (medium)</t>
+          <t>GPT-5.6 Terra (medium)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.3864931360777617</v>
+        <v>0.4804969202427884</v>
       </c>
       <c r="F35" t="n">
-        <v>0.289085545722714</v>
+        <v>0.457227138643068</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6741573033707861</v>
+        <v>0.696629213483146</v>
       </c>
       <c r="H35" t="n">
-        <v>0.196236559139785</v>
+        <v>0.287634408602151</v>
       </c>
       <c r="I35" t="n">
-        <v>2.041513021472394</v>
+        <v>0.6699985707566459</v>
       </c>
       <c r="J35" t="n">
-        <v>827.6555807770972</v>
+        <v>240.094656441718</v>
       </c>
       <c r="K35" t="n">
-        <v>67.41768916155419</v>
+        <v>50.95501022494887</v>
       </c>
       <c r="L35" t="n">
-        <v>8444053.035787314</v>
+        <v>3168659.037832314</v>
       </c>
       <c r="M35" t="n">
-        <v>4205086.787321064</v>
+        <v>1632285.212678937</v>
       </c>
       <c r="N35" t="n">
-        <v>40070.1308793456</v>
+        <v>15908.03680981595</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9487221679807678</v>
+        <v>0.894438452837132</v>
       </c>
       <c r="P35" t="n">
-        <v>0.1893170075393457</v>
+        <v>0.7171611122993163</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.577104554409345e-05</v>
+        <v>0.0001516404619449044</v>
       </c>
       <c r="R35" t="n">
-        <v>0.02801840367329207</v>
+        <v>0.1200768715215685</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0004669733945548679</v>
+        <v>0.002001281192026142</v>
       </c>
       <c r="T35" t="n">
-        <v>5.282145608561714</v>
+        <v>1.394386816086365</v>
       </c>
       <c r="U35" t="n">
-        <v>10202.37551936649</v>
+        <v>13197.54085656418</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Muse Spark 1.1 (xhigh)</t>
+          <t>GPT-5.6 Terra (xhigh)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.5492139250715367</v>
+        <v>0.5602917313962744</v>
       </c>
       <c r="F36" t="n">
-        <v>0.542772861356932</v>
+        <v>0.584070796460177</v>
       </c>
       <c r="G36" t="n">
         <v>0.771535580524345</v>
       </c>
       <c r="H36" t="n">
-        <v>0.333333333333333</v>
+        <v>0.325268817204301</v>
       </c>
       <c r="I36" t="n">
-        <v>1.435218435173823</v>
+        <v>1.358856920245396</v>
       </c>
       <c r="J36" t="n">
-        <v>761.3780071574632</v>
+        <v>403.2234447852764</v>
       </c>
       <c r="K36" t="n">
-        <v>55.51329243353784</v>
+        <v>74.95092024539876</v>
       </c>
       <c r="L36" t="n">
-        <v>12289527.21472391</v>
+        <v>6645929.991820038</v>
       </c>
       <c r="M36" t="n">
-        <v>6284599.100204499</v>
+        <v>3404439.702453988</v>
       </c>
       <c r="N36" t="n">
-        <v>34558.96932515338</v>
+        <v>40289.37934560327</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.910418152728672</v>
       </c>
       <c r="P36" t="n">
-        <v>0.3826692241484621</v>
+        <v>0.4123257740006146</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.468958939392973e-05</v>
+        <v>8.430599360599558e-05</v>
       </c>
       <c r="R36" t="n">
-        <v>0.04328051926180357</v>
+        <v>0.08337189793534545</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0007213419876967261</v>
+        <v>0.001389531632255758</v>
       </c>
       <c r="T36" t="n">
-        <v>2.613222953126838</v>
+        <v>2.425266774612322</v>
       </c>
       <c r="U36" t="n">
-        <v>16141.16391489395</v>
+        <v>16482.00291369246</v>
       </c>
     </row>
     <row r="37">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (medium)</t>
+          <t>GPT-5.6 Sol (high)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3100,55 +3100,55 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.616195748748264</v>
+        <v>0.6411644486641199</v>
       </c>
       <c r="F37" t="n">
-        <v>0.640117994100295</v>
+        <v>0.648967551622419</v>
       </c>
       <c r="G37" t="n">
-        <v>0.805243445692884</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H37" t="n">
-        <v>0.403225806451613</v>
+        <v>0.454301075268817</v>
       </c>
       <c r="I37" t="n">
-        <v>2.813450298568507</v>
+        <v>3.000466998773005</v>
       </c>
       <c r="J37" t="n">
-        <v>297.9599253578734</v>
+        <v>369.9402760736197</v>
       </c>
       <c r="K37" t="n">
-        <v>71.35378323108384</v>
+        <v>84.6717791411043</v>
       </c>
       <c r="L37" t="n">
-        <v>5765545.476482615</v>
+        <v>8038341.598159516</v>
       </c>
       <c r="M37" t="n">
-        <v>2974758.351738241</v>
+        <v>4136516.062372188</v>
       </c>
       <c r="N37" t="n">
-        <v>14440.59713701431</v>
+        <v>28060.87116564417</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8970664465490255</v>
+        <v>0.906019018469944</v>
       </c>
       <c r="P37" t="n">
-        <v>0.21901781917448</v>
+        <v>0.2136882188427049</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.00010687553350532</v>
+        <v>7.976327465492671e-05</v>
       </c>
       <c r="R37" t="n">
-        <v>0.1240829446459615</v>
+        <v>0.1039893988514825</v>
       </c>
       <c r="S37" t="n">
-        <v>0.002068049077432692</v>
+        <v>0.001733156647524709</v>
       </c>
       <c r="T37" t="n">
-        <v>4.565838541216378</v>
+        <v>4.679715172955305</v>
       </c>
       <c r="U37" t="n">
-        <v>19350.07021349512</v>
+        <v>21728.75493167403</v>
       </c>
     </row>
     <row r="38">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Opus 4.8 (xhigh)</t>
+          <t>Opus 4.8 (max)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3173,128 +3173,128 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.5907181217597334</v>
+        <v>0.6214051234130329</v>
       </c>
       <c r="F38" t="n">
-        <v>0.513274336283186</v>
+        <v>0.557522123893805</v>
       </c>
       <c r="G38" t="n">
-        <v>0.831460674157304</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H38" t="n">
-        <v>0.42741935483871</v>
+        <v>0.467741935483871</v>
       </c>
       <c r="I38" t="n">
-        <v>5.665366469580767</v>
+        <v>7.724725797009214</v>
       </c>
       <c r="J38" t="n">
-        <v>1065.615385480571</v>
+        <v>1386.687798057258</v>
       </c>
       <c r="K38" t="n">
-        <v>136.1303390500093</v>
+        <v>165.0175845341703</v>
       </c>
       <c r="L38" t="n">
-        <v>13628306.24233129</v>
+        <v>17920579.42791411</v>
       </c>
       <c r="M38" t="n">
-        <v>6783846.309815951</v>
+        <v>8919829.832822086</v>
       </c>
       <c r="N38" t="n">
-        <v>62541.86503067485</v>
+        <v>89374.98517382414</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9687226730983397</v>
+        <v>0.9657541826994763</v>
       </c>
       <c r="P38" t="n">
-        <v>0.104268298428971</v>
+        <v>0.08044364806497373</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.334494039507902e-05</v>
+        <v>3.467550398761645e-05</v>
       </c>
       <c r="R38" t="n">
-        <v>0.03326067527600485</v>
+        <v>0.02688731195083498</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0005543445879334143</v>
+        <v>0.0004481218658472497</v>
       </c>
       <c r="T38" t="n">
-        <v>9.590642746330166</v>
+        <v>12.43106229086363</v>
       </c>
       <c r="U38" t="n">
-        <v>12789.14177481138</v>
+        <v>12923.29784182189</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GPT-5.5 (xhigh)</t>
+          <t>Opus 4.8 (medium)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.6103327520587847</v>
+        <v>0.5576883805320427</v>
       </c>
       <c r="F39" t="n">
-        <v>0.64306784660767</v>
+        <v>0.492625368731563</v>
       </c>
       <c r="G39" t="n">
-        <v>0.827715355805243</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H39" t="n">
         <v>0.360215053763441</v>
       </c>
       <c r="I39" t="n">
-        <v>4.752370071574643</v>
+        <v>3.303841633946831</v>
       </c>
       <c r="J39" t="n">
-        <v>614.9898987730061</v>
+        <v>722.9228824130884</v>
       </c>
       <c r="K39" t="n">
-        <v>107.1319018404908</v>
+        <v>92.91239658858525</v>
       </c>
       <c r="L39" t="n">
-        <v>12150851.17995912</v>
+        <v>7827354.369120649</v>
       </c>
       <c r="M39" t="n">
-        <v>6164087.486707566</v>
+        <v>3898584.399795501</v>
       </c>
       <c r="N39" t="n">
-        <v>25286.0654396728</v>
+        <v>34668.28732106339</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9341674523911524</v>
+        <v>0.963840128346697</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1284270254350285</v>
+        <v>0.168799973582819</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.022962943249859e-05</v>
+        <v>7.12486434410271e-05</v>
       </c>
       <c r="R39" t="n">
-        <v>0.05954563676019593</v>
+        <v>0.04628613043791067</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0009924272793365987</v>
+        <v>0.0007714355072985111</v>
       </c>
       <c r="T39" t="n">
-        <v>7.78652309833262</v>
+        <v>5.924171543245923</v>
       </c>
       <c r="U39" t="n">
-        <v>19757.80611063991</v>
+        <v>10827.37116162826</v>
       </c>
     </row>
     <row r="40">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>GPT-5.6 Sol (low)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3319,128 +3319,128 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.5716614223656344</v>
+        <v>0.5523451808562164</v>
       </c>
       <c r="F40" t="n">
-        <v>0.634218289085546</v>
+        <v>0.533923303834808</v>
       </c>
       <c r="G40" t="n">
-        <v>0.752808988764045</v>
+        <v>0.779026217228465</v>
       </c>
       <c r="H40" t="n">
-        <v>0.327956989247312</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I40" t="n">
-        <v>1.508396035337423</v>
+        <v>1.292458844580775</v>
       </c>
       <c r="J40" t="n">
-        <v>482.0907147239265</v>
+        <v>212.899582822086</v>
       </c>
       <c r="K40" t="n">
-        <v>114.6288343558282</v>
+        <v>53.92126789366053</v>
       </c>
       <c r="L40" t="n">
-        <v>15963259.28016359</v>
+        <v>3201864.840490799</v>
       </c>
       <c r="M40" t="n">
-        <v>8170928.992842535</v>
+        <v>1658130.417177914</v>
       </c>
       <c r="N40" t="n">
-        <v>41094.49386503067</v>
+        <v>10591.38139059305</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9181831202060817</v>
+        <v>0.8829664546361214</v>
       </c>
       <c r="P40" t="n">
-        <v>0.378986293369404</v>
+        <v>0.4273599760427007</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.58110716823348e-05</v>
+        <v>0.0001725073381834412</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0711477825528751</v>
+        <v>0.1556635781624227</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001185796375881252</v>
+        <v>0.002594392969373712</v>
       </c>
       <c r="T40" t="n">
-        <v>2.638617853720858</v>
+        <v>2.339947716348811</v>
       </c>
       <c r="U40" t="n">
-        <v>33112.56324300934</v>
+        <v>15039.31946718047</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (max)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.6042010361726687</v>
+        <v>0.423892771774363</v>
       </c>
       <c r="F41" t="n">
-        <v>0.669616519174041</v>
+        <v>0.274336283185841</v>
       </c>
       <c r="G41" t="n">
-        <v>0.782771535580524</v>
+        <v>0.771535580524345</v>
       </c>
       <c r="H41" t="n">
-        <v>0.360215053763441</v>
+        <v>0.225806451612903</v>
       </c>
       <c r="I41" t="n">
-        <v>2.695350269529651</v>
+        <v>1.800661744734152</v>
       </c>
       <c r="J41" t="n">
-        <v>491.0206543967283</v>
+        <v>399.3926789366056</v>
       </c>
       <c r="K41" t="n">
-        <v>95.80674846625767</v>
+        <v>42.04907975460122</v>
       </c>
       <c r="L41" t="n">
-        <v>9630511.582822077</v>
+        <v>4636274.728016362</v>
       </c>
       <c r="M41" t="n">
-        <v>4933733.868098159</v>
+        <v>2310268.645194274</v>
       </c>
       <c r="N41" t="n">
-        <v>37445.42126789366</v>
+        <v>17168.18507157464</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9184675548550253</v>
+        <v>0.9576237577125704</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2241641997342721</v>
+        <v>0.23540943934306</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.273820772412349e-05</v>
+        <v>9.142960601813308e-05</v>
       </c>
       <c r="R41" t="n">
-        <v>0.07383001477789093</v>
+        <v>0.06368060219375923</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001230500246298182</v>
+        <v>0.001061343369895987</v>
       </c>
       <c r="T41" t="n">
-        <v>4.461015635794728</v>
+        <v>4.247918022279086</v>
       </c>
       <c r="U41" t="n">
-        <v>19613.25149275889</v>
+        <v>11608.31175063242</v>
       </c>
     </row>
     <row r="42">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (high)</t>
+          <t>GLM-5.1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3461,424 +3461,424 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>friendliai</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.3282816619106221</v>
+        <v>0.3691032797641257</v>
       </c>
       <c r="F42" t="n">
-        <v>0.08554572271386431</v>
+        <v>0.185840707964602</v>
       </c>
       <c r="G42" t="n">
-        <v>0.700374531835206</v>
+        <v>0.6741573033707861</v>
       </c>
       <c r="H42" t="n">
-        <v>0.198924731182796</v>
+        <v>0.247311827956989</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2547256318476481</v>
+        <v>4.282000252842536</v>
       </c>
       <c r="J42" t="n">
-        <v>1072.531835378324</v>
+        <v>1140.250613496931</v>
       </c>
       <c r="K42" t="n">
-        <v>128.1457055214724</v>
+        <v>174.2367075664622</v>
       </c>
       <c r="L42" t="n">
-        <v>9942165.52862986</v>
+        <v>25761884.92944787</v>
       </c>
       <c r="M42" t="n">
-        <v>5181244.880368099</v>
+        <v>13139446.7402863</v>
       </c>
       <c r="N42" t="n">
-        <v>41975.79754601227</v>
+        <v>49883.45705521473</v>
       </c>
       <c r="O42" t="n">
-        <v>0.8541357545221669</v>
+        <v>0.888922540999181</v>
       </c>
       <c r="P42" t="n">
-        <v>1.288765718351297</v>
+        <v>0.08619879915212579</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.301913058732417e-05</v>
+        <v>1.432749508721745e-05</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01836486252894252</v>
+        <v>0.01942221869798375</v>
       </c>
       <c r="S42" t="n">
-        <v>0.000306081042149042</v>
+        <v>0.0003237036449663959</v>
       </c>
       <c r="T42" t="n">
-        <v>0.77593622002864</v>
+        <v>11.60108968844421</v>
       </c>
       <c r="U42" t="n">
-        <v>9269.809250112254</v>
+        <v>22593.17787204787</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Opus 5 (high)</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.6561729860226817</v>
+        <v>0.5657152973570364</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6076696165191739</v>
+        <v>0.56047197640118</v>
       </c>
       <c r="G43" t="n">
-        <v>0.868913857677903</v>
+        <v>0.865168539325843</v>
       </c>
       <c r="H43" t="n">
-        <v>0.491935483870968</v>
+        <v>0.271505376344086</v>
       </c>
       <c r="I43" t="n">
-        <v>3.918602446063396</v>
+        <v>1.396316917192254</v>
       </c>
       <c r="J43" t="n">
-        <v>842.8052382413098</v>
+        <v>384.9621257668713</v>
       </c>
       <c r="K43" t="n">
-        <v>94.85071574642126</v>
+        <v>110.7985685071575</v>
       </c>
       <c r="L43" t="n">
-        <v>9911366.349693259</v>
+        <v>15113684.86595342</v>
       </c>
       <c r="M43" t="n">
-        <v>4937399.112474437</v>
+        <v>7938344.274012004</v>
       </c>
       <c r="N43" t="n">
-        <v>37331.49386503067</v>
+        <v>64430.0844098625</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9702723303233406</v>
+        <v>0.8677594149804605</v>
       </c>
       <c r="P43" t="n">
-        <v>0.1674507672197952</v>
+        <v>0.4051482083985558</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.620408961504982e-05</v>
+        <v>3.743066647045306e-05</v>
       </c>
       <c r="R43" t="n">
-        <v>0.04671349604271026</v>
+        <v>0.08817209686227062</v>
       </c>
       <c r="S43" t="n">
-        <v>0.0007785582673785044</v>
+        <v>0.00146953494770451</v>
       </c>
       <c r="T43" t="n">
-        <v>5.971904557997063</v>
+        <v>2.468232560999682</v>
       </c>
       <c r="U43" t="n">
-        <v>11759.97241115327</v>
+        <v>39260.1865335347</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Composer 2.5</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.3830075380367747</v>
+        <v>0.6702814566291138</v>
       </c>
       <c r="F44" t="n">
-        <v>0.15929203539823</v>
+        <v>0.631268436578171</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6779026217228465</v>
+        <v>0.887640449438202</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3118279569892475</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I44" t="n">
-        <v>0.08505141359918204</v>
+        <v>8.943547018021487</v>
       </c>
       <c r="J44" t="n">
-        <v>625.1976421267894</v>
+        <v>1451.329194274025</v>
       </c>
       <c r="K44" t="n">
-        <v>116.8680981595092</v>
+        <v>165.7202546941811</v>
       </c>
       <c r="L44" t="n">
-        <v>3705076.4698364</v>
+        <v>23699428.05214722</v>
       </c>
       <c r="M44" t="n">
-        <v>1872461.576687117</v>
+        <v>11810977.87014315</v>
       </c>
       <c r="N44" t="n">
-        <v>18453.85787321063</v>
+        <v>81385.06339468302</v>
       </c>
       <c r="O44" t="n">
-        <v>1.052833075750478</v>
+        <v>0.9747033593278787</v>
       </c>
       <c r="P44" t="n">
-        <v>4.503247175194018</v>
+        <v>0.07494581906691815</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.0001033737201255894</v>
+        <v>2.82826005401588e-05</v>
       </c>
       <c r="R44" t="n">
-        <v>0.03675710004924502</v>
+        <v>0.02771038270050364</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0006126183341540836</v>
+        <v>0.0004618397116750606</v>
       </c>
       <c r="T44" t="n">
-        <v>0.2220619835190183</v>
+        <v>13.34297246264148</v>
       </c>
       <c r="U44" t="n">
-        <v>5926.248309626565</v>
+        <v>16329.4641530325</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Gemini CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro (high)</t>
+          <t>GPT-5.6 Luna (medium)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.3293046837328304</v>
+        <v>0.4196699779001624</v>
       </c>
       <c r="F45" t="n">
-        <v>0.141592920353982</v>
+        <v>0.365781710914454</v>
       </c>
       <c r="G45" t="n">
-        <v>0.760299625468165</v>
+        <v>0.621722846441947</v>
       </c>
       <c r="H45" t="n">
-        <v>0.08602150537634411</v>
+        <v>0.271505376344086</v>
       </c>
       <c r="I45" t="n">
-        <v>1.040041561860939</v>
+        <v>0.08841796668711666</v>
       </c>
       <c r="J45" t="n">
-        <v>663.8363599182014</v>
+        <v>191.3819171779141</v>
       </c>
       <c r="K45" t="n">
-        <v>30.96883483789777</v>
+        <v>57.08588957055215</v>
       </c>
       <c r="L45" t="n">
-        <v>4727804.222392637</v>
+        <v>4290985.346625767</v>
       </c>
       <c r="M45" t="n">
-        <v>2465901.789877301</v>
+        <v>2221162.702453987</v>
       </c>
       <c r="N45" t="n">
-        <v>12977.50562372188</v>
+        <v>15320.75153374233</v>
       </c>
       <c r="O45" t="n">
-        <v>0.8650361016121304</v>
+        <v>0.8832984632099327</v>
       </c>
       <c r="P45" t="n">
-        <v>0.316626465526635</v>
+        <v>4.746433260394262</v>
       </c>
       <c r="Q45" t="n">
-        <v>6.965277499713736e-05</v>
+        <v>9.780270590533979e-05</v>
       </c>
       <c r="R45" t="n">
-        <v>0.02976378248760652</v>
+        <v>0.1315704171288111</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0004960630414601087</v>
+        <v>0.002192840285480186</v>
       </c>
       <c r="T45" t="n">
-        <v>3.158295685538259</v>
+        <v>0.2106845172235573</v>
       </c>
       <c r="U45" t="n">
-        <v>7121.942255430543</v>
+        <v>22421.05947050757</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>Opus 4.7 (max)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.4277969516408803</v>
+        <v>0.5158095272716129</v>
       </c>
       <c r="F46" t="n">
-        <v>0.162241887905605</v>
+        <v>0.40117994100295</v>
       </c>
       <c r="G46" t="n">
-        <v>0.629213483146068</v>
+        <v>0.7752808988764049</v>
       </c>
       <c r="H46" t="n">
-        <v>0.491935483870968</v>
+        <v>0.370967741935484</v>
       </c>
       <c r="I46" t="n">
-        <v>0.09081146755368102</v>
+        <v>5.915424259100206</v>
       </c>
       <c r="J46" t="n">
-        <v>743.5829417177914</v>
+        <v>950.3123588957067</v>
       </c>
       <c r="K46" t="n">
-        <v>66.08691206543966</v>
+        <v>107.999326082915</v>
       </c>
       <c r="L46" t="n">
-        <v>12713750.95194274</v>
+        <v>16129723.11451944</v>
       </c>
       <c r="M46" t="n">
-        <v>6378205.537321064</v>
+        <v>8042457.98977505</v>
       </c>
       <c r="N46" t="n">
-        <v>37873.7581799591</v>
+        <v>47224.16462167689</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9780317126088948</v>
+        <v>0.9665216325317721</v>
       </c>
       <c r="P46" t="n">
-        <v>4.71082522026195</v>
+        <v>0.08719738512044993</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.364836650158783e-05</v>
+        <v>3.197882093879828e-05</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03451910426986961</v>
+        <v>0.03256673592276544</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0005753184044978268</v>
+        <v>0.0005427789320460906</v>
       </c>
       <c r="T46" t="n">
-        <v>0.2122770328431743</v>
+        <v>11.46823380791353</v>
       </c>
       <c r="U46" t="n">
-        <v>17097.95940527093</v>
+        <v>16973.07518263015</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (high)</t>
+          <t>Kimi K2.6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.5464647209828707</v>
+        <v>0.3388925953605663</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6047197640117991</v>
+        <v>0.165191740412979</v>
       </c>
       <c r="G47" t="n">
-        <v>0.722846441947566</v>
+        <v>0.6928838951310859</v>
       </c>
       <c r="H47" t="n">
-        <v>0.311827956989247</v>
+        <v>0.158602150537634</v>
       </c>
       <c r="I47" t="n">
-        <v>1.561839053374232</v>
+        <v>1.21710007411043</v>
       </c>
       <c r="J47" t="n">
-        <v>358.7396482617585</v>
+        <v>2443.385067484662</v>
       </c>
       <c r="K47" t="n">
-        <v>67.06952965235175</v>
+        <v>133.7675410760877</v>
       </c>
       <c r="L47" t="n">
-        <v>5600275.774028626</v>
+        <v>11660527.81595092</v>
       </c>
       <c r="M47" t="n">
-        <v>2877096.291411043</v>
+        <v>5891966.377300614</v>
       </c>
       <c r="N47" t="n">
-        <v>20902.66564417178</v>
+        <v>36930.17791411043</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9049339862289004</v>
+        <v>0.9554328157869918</v>
       </c>
       <c r="P47" t="n">
-        <v>0.3498854250073181</v>
+        <v>0.2784426708775453</v>
       </c>
       <c r="Q47" t="n">
-        <v>9.757818061694571e-05</v>
+        <v>2.906322944463811e-05</v>
       </c>
       <c r="R47" t="n">
-        <v>0.09139743381542312</v>
+        <v>0.008321879343629747</v>
       </c>
       <c r="S47" t="n">
-        <v>0.001523290563590385</v>
+        <v>0.0001386979890604958</v>
       </c>
       <c r="T47" t="n">
-        <v>2.85807846948493</v>
+        <v>3.591403561991346</v>
       </c>
       <c r="U47" t="n">
-        <v>15610.97526065009</v>
+        <v>4772.284144289555</v>
       </c>
     </row>
     <row r="48">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Opus 4.7 (max)</t>
+          <t>Opus 5 (medium)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3903,347 +3903,347 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.5158095272716129</v>
+        <v>0.6406847456950576</v>
       </c>
       <c r="F48" t="n">
-        <v>0.40117994100295</v>
+        <v>0.628318584070796</v>
       </c>
       <c r="G48" t="n">
-        <v>0.7752808988764049</v>
+        <v>0.850187265917603</v>
       </c>
       <c r="H48" t="n">
-        <v>0.370967741935484</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="I48" t="n">
-        <v>5.915424259100202</v>
+        <v>3.171867192484664</v>
       </c>
       <c r="J48" t="n">
-        <v>950.3123588957067</v>
+        <v>730.9243895705522</v>
       </c>
       <c r="K48" t="n">
-        <v>107.999326082915</v>
+        <v>83.47801635991821</v>
       </c>
       <c r="L48" t="n">
-        <v>16129723.11451944</v>
+        <v>7999358.108384448</v>
       </c>
       <c r="M48" t="n">
-        <v>8042457.98977505</v>
+        <v>3984815.59611452</v>
       </c>
       <c r="N48" t="n">
-        <v>47224.16462167689</v>
+        <v>30206.12781186094</v>
       </c>
       <c r="O48" t="n">
-        <v>0.9665216325317725</v>
+        <v>0.9695331242878964</v>
       </c>
       <c r="P48" t="n">
-        <v>0.08719738512044999</v>
+        <v>0.2019897766252883</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.197882093879829e-05</v>
+        <v>8.009201951135682e-05</v>
       </c>
       <c r="R48" t="n">
-        <v>0.03256673592276544</v>
+        <v>0.05259242308809692</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0005427789320460906</v>
+        <v>0.0008765403848016154</v>
       </c>
       <c r="T48" t="n">
-        <v>11.46823380791352</v>
+        <v>4.950745610532073</v>
       </c>
       <c r="U48" t="n">
-        <v>16973.07518263015</v>
+        <v>10944.16634952405</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Opus 5 (medium)</t>
+          <t>Muse Spark 1.2 (xhigh)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6406847456950576</v>
+        <v>0.6164044159758908</v>
       </c>
       <c r="F49" t="n">
-        <v>0.628318584070796</v>
+        <v>0.581120943952802</v>
       </c>
       <c r="G49" t="n">
-        <v>0.850187265917603</v>
+        <v>0.816479400749064</v>
       </c>
       <c r="H49" t="n">
-        <v>0.443548387096774</v>
+        <v>0.451612903225806</v>
       </c>
       <c r="I49" t="n">
-        <v>3.171867192484664</v>
+        <v>2.072823051942737</v>
       </c>
       <c r="J49" t="n">
-        <v>730.9243895705523</v>
+        <v>2448.643313905933</v>
       </c>
       <c r="K49" t="n">
-        <v>83.47801635991821</v>
+        <v>151.4345603271984</v>
       </c>
       <c r="L49" t="n">
-        <v>7999358.108384448</v>
+        <v>19963139.08486708</v>
       </c>
       <c r="M49" t="n">
-        <v>3984815.59611452</v>
+        <v>10093761.29754601</v>
       </c>
       <c r="N49" t="n">
-        <v>30206.12781186094</v>
+        <v>58305.98057259714</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9695331242878965</v>
+        <v>0.9538301727874863</v>
       </c>
       <c r="P49" t="n">
-        <v>0.2019897766252883</v>
+        <v>0.2973743539749669</v>
       </c>
       <c r="Q49" t="n">
-        <v>8.009201951135682e-05</v>
+        <v>3.087712875993296e-05</v>
       </c>
       <c r="R49" t="n">
-        <v>0.05259242308809691</v>
+        <v>0.01510398217189024</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008765403848016152</v>
+        <v>0.0002517330361981707</v>
       </c>
       <c r="T49" t="n">
-        <v>4.950745610532073</v>
+        <v>3.362764766474046</v>
       </c>
       <c r="U49" t="n">
-        <v>10944.16634952405</v>
+        <v>8152.734606749663</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Composer 2.5 Fast</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.6505240024334411</v>
+        <v>0.3830075380367747</v>
       </c>
       <c r="F50" t="n">
-        <v>0.687315634218289</v>
+        <v>0.15929203539823</v>
       </c>
       <c r="G50" t="n">
-        <v>0.831460674157303</v>
+        <v>0.6779026217228465</v>
       </c>
       <c r="H50" t="n">
-        <v>0.432795698924731</v>
+        <v>0.3118279569892475</v>
       </c>
       <c r="I50" t="n">
-        <v>6.420249160020451</v>
+        <v>0.5573437730061347</v>
       </c>
       <c r="J50" t="n">
-        <v>613.70177198364</v>
+        <v>472.3722024539875</v>
       </c>
       <c r="K50" t="n">
-        <v>112.2689161554192</v>
+        <v>116.8680981595092</v>
       </c>
       <c r="L50" t="n">
-        <v>13169248.79601226</v>
+        <v>4259887.413087934</v>
       </c>
       <c r="M50" t="n">
-        <v>6786107.398261759</v>
+        <v>2153033.982617587</v>
       </c>
       <c r="N50" t="n">
-        <v>35184.01329243354</v>
+        <v>20146.14621676892</v>
       </c>
       <c r="O50" t="n">
-        <v>0.902597320865973</v>
+        <v>0.9355410155352533</v>
       </c>
       <c r="P50" t="n">
-        <v>0.1013237938621324</v>
+        <v>0.6872016098268293</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.939719892226686e-05</v>
+        <v>8.991024900330353e-05</v>
       </c>
       <c r="R50" t="n">
-        <v>0.06360001213593849</v>
+        <v>0.04864903599920222</v>
       </c>
       <c r="S50" t="n">
-        <v>0.001060000202265642</v>
+        <v>0.0008108172666533704</v>
       </c>
       <c r="T50" t="n">
-        <v>9.869350148501775</v>
+        <v>1.455177033493845</v>
       </c>
       <c r="U50" t="n">
-        <v>21458.71072434076</v>
+        <v>9018.073864121752</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fable 5 (max) (with fallback)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.6717276042685724</v>
+        <v>0.6263880112748017</v>
       </c>
       <c r="F51" t="n">
-        <v>0.660766961651917</v>
+        <v>0.63716814159292</v>
       </c>
       <c r="G51" t="n">
-        <v>0.865168539325843</v>
+        <v>0.8764044943820229</v>
       </c>
       <c r="H51" t="n">
-        <v>0.489247311827957</v>
+        <v>0.365591397849462</v>
       </c>
       <c r="I51" t="n">
-        <v>11.68740762091003</v>
+        <v>3.081635541610427</v>
       </c>
       <c r="J51" t="n">
-        <v>1407.30630163599</v>
+        <v>1447.373053169734</v>
       </c>
       <c r="K51" t="n">
-        <v>137.007744236847</v>
+        <v>122.9498977505112</v>
       </c>
       <c r="L51" t="n">
-        <v>13868659.99897749</v>
+        <v>10383196.73788345</v>
       </c>
       <c r="M51" t="n">
-        <v>6901095.023517382</v>
+        <v>5296768.575664621</v>
       </c>
       <c r="N51" t="n">
-        <v>74265.48875255625</v>
+        <v>54498.01533742331</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9619283373252908</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P51" t="n">
-        <v>0.05747447390016408</v>
+        <v>0.203264793262171</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.843493202069251e-05</v>
+        <v>6.032708683920082e-05</v>
       </c>
       <c r="R51" t="n">
-        <v>0.02863886576025522</v>
+        <v>0.02596654718296782</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0004773144293375869</v>
+        <v>0.0004327757863827971</v>
       </c>
       <c r="T51" t="n">
-        <v>17.39902833624972</v>
+        <v>4.919691127770464</v>
       </c>
       <c r="U51" t="n">
-        <v>9854.75584302807</v>
+        <v>7173.822060003357</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Grok 4.5 (high)</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.6408998279698193</v>
+        <v>0.5962784529614886</v>
       </c>
       <c r="F52" t="n">
-        <v>0.59882005899705</v>
+        <v>0.572271386430678</v>
       </c>
       <c r="G52" t="n">
-        <v>0.842696629213483</v>
+        <v>0.910112359550562</v>
       </c>
       <c r="H52" t="n">
-        <v>0.481182795698925</v>
+        <v>0.306451612903226</v>
       </c>
       <c r="I52" t="n">
-        <v>2.438982443762777</v>
+        <v>1.26793256886503</v>
       </c>
       <c r="J52" t="n">
-        <v>929.1851094069543</v>
+        <v>527.0915644171779</v>
       </c>
       <c r="K52" t="n">
-        <v>60.74437627811862</v>
+        <v>83.44887525562373</v>
       </c>
       <c r="L52" t="n">
-        <v>3598867.582822087</v>
+        <v>18493123.37423313</v>
       </c>
       <c r="M52" t="n">
-        <v>1837535.160531697</v>
+        <v>9497213.109406954</v>
       </c>
       <c r="N52" t="n">
-        <v>25699.40797546012</v>
+        <v>49098.7944785276</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9238990226060748</v>
+        <v>0.8634331167917663</v>
       </c>
       <c r="P52" t="n">
-        <v>0.2627734486604427</v>
+        <v>0.4702761547447575</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.0001780837480736792</v>
+        <v>3.224325285107308e-05</v>
       </c>
       <c r="R52" t="n">
-        <v>0.04138463831252326</v>
+        <v>0.06787569673449199</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0006897439718753876</v>
+        <v>0.001131261612241533</v>
       </c>
       <c r="T52" t="n">
-        <v>3.805559523223389</v>
+        <v>2.126410173917388</v>
       </c>
       <c r="U52" t="n">
-        <v>3873.143840110652</v>
+        <v>35085.21976571864</v>
       </c>
     </row>
     <row r="53">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Opus 5 (xhigh)</t>
+          <t>GLM-5.2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4264,59 +4264,59 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>novita</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.6814975428587517</v>
+        <v>0.433101571936022</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6047197640117991</v>
+        <v>0.286135693215339</v>
       </c>
       <c r="G53" t="n">
-        <v>0.891385767790262</v>
+        <v>0.722846441947566</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5483870967741939</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="I53" t="n">
-        <v>8.170783921523505</v>
+        <v>6.657531358159519</v>
       </c>
       <c r="J53" t="n">
-        <v>1421.879982617589</v>
+        <v>1507.044470347651</v>
       </c>
       <c r="K53" t="n">
-        <v>152.0771983640082</v>
+        <v>127.4036879531512</v>
       </c>
       <c r="L53" t="n">
-        <v>21565879.13803681</v>
+        <v>6619529.539877302</v>
       </c>
       <c r="M53" t="n">
-        <v>10747525.6196319</v>
+        <v>5529735.922290388</v>
       </c>
       <c r="N53" t="n">
-        <v>73273.02862985685</v>
+        <v>28567.83231083845</v>
       </c>
       <c r="O53" t="n">
-        <v>0.9740249879523308</v>
+        <v>0.3295602231414034</v>
       </c>
       <c r="P53" t="n">
-        <v>0.08340662896047817</v>
+        <v>0.06505437956446267</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.160073088125403e-05</v>
+        <v>6.542784790473944e-05</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02875759773778482</v>
+        <v>0.01724308394838989</v>
       </c>
       <c r="S53" t="n">
-        <v>0.000479293295629747</v>
+        <v>0.0002873847324731648</v>
       </c>
       <c r="T53" t="n">
-        <v>11.98945470477946</v>
+        <v>15.37175524069207</v>
       </c>
       <c r="U53" t="n">
-        <v>15167.15855183179</v>
+        <v>4392.391644786887</v>
       </c>
     </row>
     <row r="54">
@@ -4362,7 +4362,7 @@
         <v>105.9314928425358</v>
       </c>
       <c r="L54" t="n">
-        <v>20844227.99386501</v>
+        <v>20844227.99386505</v>
       </c>
       <c r="M54" t="n">
         <v>10443571.69734151</v>
@@ -4377,7 +4377,7 @@
         <v>8.362738496140583</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.387116487635592e-05</v>
+        <v>2.387116487635588e-05</v>
       </c>
       <c r="R54" t="n">
         <v>0.03437980100483083</v>
@@ -4389,7 +4389,7 @@
         <v>0.1195780545405672</v>
       </c>
       <c r="U54" t="n">
-        <v>24003.71688527831</v>
+        <v>24003.71688527835</v>
       </c>
     </row>
     <row r="55">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GLM-5.2</t>
+          <t>Opus 5 (xhigh)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4410,278 +4410,278 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>novita</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.433101571936022</v>
+        <v>0.6814975428587517</v>
       </c>
       <c r="F55" t="n">
-        <v>0.286135693215339</v>
+        <v>0.6047197640117991</v>
       </c>
       <c r="G55" t="n">
-        <v>0.722846441947566</v>
+        <v>0.891385767790262</v>
       </c>
       <c r="H55" t="n">
-        <v>0.290322580645161</v>
+        <v>0.5483870967741939</v>
       </c>
       <c r="I55" t="n">
-        <v>6.657531358159516</v>
+        <v>8.170783921523505</v>
       </c>
       <c r="J55" t="n">
-        <v>1507.044470347651</v>
+        <v>1421.879982617589</v>
       </c>
       <c r="K55" t="n">
-        <v>127.4036879531512</v>
+        <v>152.0771983640082</v>
       </c>
       <c r="L55" t="n">
-        <v>6619529.539877302</v>
+        <v>21565879.13803681</v>
       </c>
       <c r="M55" t="n">
-        <v>5529735.922290388</v>
+        <v>10747525.6196319</v>
       </c>
       <c r="N55" t="n">
-        <v>28567.83231083845</v>
+        <v>73273.02862985685</v>
       </c>
       <c r="O55" t="n">
-        <v>0.3295602231414034</v>
+        <v>0.9740249879523308</v>
       </c>
       <c r="P55" t="n">
-        <v>0.06505437956446269</v>
+        <v>0.08340662896047817</v>
       </c>
       <c r="Q55" t="n">
-        <v>6.542784790473944e-05</v>
+        <v>3.160073088125403e-05</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01724308394838989</v>
+        <v>0.02875759773778482</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0002873847324731648</v>
+        <v>0.000479293295629747</v>
       </c>
       <c r="T55" t="n">
-        <v>15.37175524069206</v>
+        <v>11.98945470477946</v>
       </c>
       <c r="U55" t="n">
-        <v>4392.391644786887</v>
+        <v>15167.15855183179</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>Grok 4.5 (high)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.5962784529614886</v>
+        <v>0.6408998279698193</v>
       </c>
       <c r="F56" t="n">
-        <v>0.572271386430678</v>
+        <v>0.59882005899705</v>
       </c>
       <c r="G56" t="n">
-        <v>0.910112359550562</v>
+        <v>0.842696629213483</v>
       </c>
       <c r="H56" t="n">
-        <v>0.306451612903226</v>
+        <v>0.481182795698925</v>
       </c>
       <c r="I56" t="n">
-        <v>1.26793256886503</v>
+        <v>2.438982443762781</v>
       </c>
       <c r="J56" t="n">
-        <v>527.0915644171779</v>
+        <v>929.1851094069543</v>
       </c>
       <c r="K56" t="n">
-        <v>83.44887525562373</v>
+        <v>60.74437627811862</v>
       </c>
       <c r="L56" t="n">
-        <v>18493123.3742331</v>
+        <v>3598867.582822083</v>
       </c>
       <c r="M56" t="n">
-        <v>9497213.109406954</v>
+        <v>1837535.160531697</v>
       </c>
       <c r="N56" t="n">
-        <v>49098.7944785276</v>
+        <v>25699.40797546012</v>
       </c>
       <c r="O56" t="n">
-        <v>0.8634331167917663</v>
+        <v>0.9238990226060741</v>
       </c>
       <c r="P56" t="n">
-        <v>0.4702761547447575</v>
+        <v>0.2627734486604423</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.224325285107313e-05</v>
+        <v>0.0001780837480736794</v>
       </c>
       <c r="R56" t="n">
-        <v>0.06787569673449199</v>
+        <v>0.04138463831252326</v>
       </c>
       <c r="S56" t="n">
-        <v>0.001131261612241533</v>
+        <v>0.0006897439718753876</v>
       </c>
       <c r="T56" t="n">
-        <v>2.126410173917388</v>
+        <v>3.805559523223395</v>
       </c>
       <c r="U56" t="n">
-        <v>35085.21976571858</v>
+        <v>3873.143840110648</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Fable 5 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.6263880112748017</v>
+        <v>0.6717276042685724</v>
       </c>
       <c r="F57" t="n">
-        <v>0.63716814159292</v>
+        <v>0.660766961651917</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8764044943820229</v>
+        <v>0.865168539325843</v>
       </c>
       <c r="H57" t="n">
-        <v>0.365591397849462</v>
+        <v>0.489247311827957</v>
       </c>
       <c r="I57" t="n">
-        <v>3.081635541610432</v>
+        <v>11.68740762091003</v>
       </c>
       <c r="J57" t="n">
-        <v>1447.373053169735</v>
+        <v>1407.30630163599</v>
       </c>
       <c r="K57" t="n">
-        <v>122.9498977505112</v>
+        <v>137.007744236847</v>
       </c>
       <c r="L57" t="n">
-        <v>10383196.73788345</v>
+        <v>13868659.99897749</v>
       </c>
       <c r="M57" t="n">
-        <v>5296768.575664621</v>
+        <v>6901095.023517382</v>
       </c>
       <c r="N57" t="n">
-        <v>54498.01533742331</v>
+        <v>74265.48875255625</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.9619283373252909</v>
       </c>
       <c r="P57" t="n">
-        <v>0.2032647932621707</v>
+        <v>0.05747447390016408</v>
       </c>
       <c r="Q57" t="n">
-        <v>6.032708683920082e-05</v>
+        <v>4.843493202069251e-05</v>
       </c>
       <c r="R57" t="n">
-        <v>0.02596654718296782</v>
+        <v>0.02863886576025522</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0004327757863827969</v>
+        <v>0.0004773144293375869</v>
       </c>
       <c r="T57" t="n">
-        <v>4.919691127770471</v>
+        <v>17.39902833624972</v>
       </c>
       <c r="U57" t="n">
-        <v>7173.822060003356</v>
+        <v>9854.75584302807</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Composer 2.5 Fast</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.3830075380367747</v>
+        <v>0.6505240024334411</v>
       </c>
       <c r="F58" t="n">
-        <v>0.15929203539823</v>
+        <v>0.687315634218289</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6779026217228465</v>
+        <v>0.831460674157303</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3118279569892475</v>
+        <v>0.432795698924731</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5573437730061354</v>
+        <v>4.995463274846626</v>
       </c>
       <c r="J58" t="n">
-        <v>472.3722024539878</v>
+        <v>613.70177198364</v>
       </c>
       <c r="K58" t="n">
-        <v>116.8680981595092</v>
+        <v>112.2689161554192</v>
       </c>
       <c r="L58" t="n">
-        <v>4259887.413087934</v>
+        <v>13188716.58946831</v>
       </c>
       <c r="M58" t="n">
-        <v>2153033.982617587</v>
+        <v>6786107.398261759</v>
       </c>
       <c r="N58" t="n">
-        <v>20146.14621676892</v>
+        <v>54651.80674846626</v>
       </c>
       <c r="O58" t="n">
-        <v>0.9355410155352536</v>
+        <v>0.902597320865973</v>
       </c>
       <c r="P58" t="n">
-        <v>0.6872016098268284</v>
+        <v>0.1302229576401828</v>
       </c>
       <c r="Q58" t="n">
-        <v>8.991024900330353e-05</v>
+        <v>4.932428398324287e-05</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0486490359992022</v>
+        <v>0.06360001213593849</v>
       </c>
       <c r="S58" t="n">
-        <v>0.00081081726665337</v>
+        <v>0.001060000202265642</v>
       </c>
       <c r="T58" t="n">
-        <v>1.455177033493847</v>
+        <v>7.679137520152826</v>
       </c>
       <c r="U58" t="n">
-        <v>9018.073864121749</v>
+        <v>21490.43263609786</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U58"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (high)</t>
+          <t>GPT-5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -545,274 +545,274 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5464647209828707</v>
+        <v>0.6103327520587847</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6047197640117991</v>
+        <v>0.64306784660767</v>
       </c>
       <c r="G2" t="n">
-        <v>0.722846441947566</v>
+        <v>0.827715355805243</v>
       </c>
       <c r="H2" t="n">
-        <v>0.311827956989247</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I2" t="n">
-        <v>1.140926299999998</v>
+        <v>4.75237007157464</v>
       </c>
       <c r="J2" t="n">
-        <v>358.7396482617585</v>
+        <v>614.9898987730061</v>
       </c>
       <c r="K2" t="n">
-        <v>67.06952965235175</v>
+        <v>107.1319018404908</v>
       </c>
       <c r="L2" t="n">
-        <v>5610707.334355831</v>
+        <v>12150851.17995912</v>
       </c>
       <c r="M2" t="n">
-        <v>2877096.291411043</v>
+        <v>6164087.486707566</v>
       </c>
       <c r="N2" t="n">
-        <v>31334.22597137014</v>
+        <v>25286.0654396728</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9049339862289006</v>
+        <v>0.9341674523911524</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4789658376556589</v>
+        <v>0.1284270254350285</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.73967609461153e-05</v>
+        <v>5.022962943249859e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.09139743381542312</v>
+        <v>0.05954563676019593</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001523290563590385</v>
+        <v>0.0009924272793365987</v>
       </c>
       <c r="T2" t="n">
-        <v>2.087831576662313</v>
+        <v>7.786523098332615</v>
       </c>
       <c r="U2" t="n">
-        <v>15640.05361978254</v>
+        <v>19757.80611063991</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>Opus 4.8 (xhigh)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.42779695164088</v>
+        <v>0.590718121759733</v>
       </c>
       <c r="F3" t="n">
-        <v>0.162241887905605</v>
+        <v>0.513274336283186</v>
       </c>
       <c r="G3" t="n">
-        <v>0.629213483146067</v>
+        <v>0.831460674157303</v>
       </c>
       <c r="H3" t="n">
-        <v>0.491935483870968</v>
+        <v>0.42741935483871</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09081146755368105</v>
+        <v>5.665366469580767</v>
       </c>
       <c r="J3" t="n">
-        <v>743.5829417177911</v>
+        <v>1065.615385480574</v>
       </c>
       <c r="K3" t="n">
-        <v>66.08691206543966</v>
+        <v>136.1303390500093</v>
       </c>
       <c r="L3" t="n">
-        <v>12713750.95194274</v>
+        <v>13628306.24233129</v>
       </c>
       <c r="M3" t="n">
-        <v>6378205.537321064</v>
+        <v>6783846.309815951</v>
       </c>
       <c r="N3" t="n">
-        <v>37873.7581799591</v>
+        <v>62541.86503067485</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9780317126088941</v>
+        <v>0.9687226730983399</v>
       </c>
       <c r="P3" t="n">
-        <v>4.710825220261945</v>
+        <v>0.104268298428971</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.36483665015878e-05</v>
+        <v>4.3344940395079e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0345191042698696</v>
+        <v>0.03326067527600474</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005753184044978266</v>
+        <v>0.0005543445879334123</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2122770328431746</v>
+        <v>9.590642746330172</v>
       </c>
       <c r="U3" t="n">
-        <v>17097.95940527094</v>
+        <v>12789.14177481134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gemini CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro (high)</t>
+          <t>GPT-5.6 Sol (medium)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.3293046837328304</v>
+        <v>0.616195748748264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.141592920353982</v>
+        <v>0.640117994100295</v>
       </c>
       <c r="G4" t="n">
-        <v>0.760299625468165</v>
+        <v>0.805243445692884</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08602150537634411</v>
+        <v>0.403225806451613</v>
       </c>
       <c r="I4" t="n">
-        <v>1.040041561860939</v>
+        <v>2.192997850306748</v>
       </c>
       <c r="J4" t="n">
-        <v>663.8363599182014</v>
+        <v>297.9599253578734</v>
       </c>
       <c r="K4" t="n">
-        <v>30.96883483789777</v>
+        <v>71.35378323108384</v>
       </c>
       <c r="L4" t="n">
-        <v>4727804.222392637</v>
+        <v>5765545.476482615</v>
       </c>
       <c r="M4" t="n">
-        <v>2465901.789877301</v>
+        <v>2974758.351738241</v>
       </c>
       <c r="N4" t="n">
-        <v>12977.50562372188</v>
+        <v>14440.59713701431</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8650361016121313</v>
+        <v>0.8970664465490255</v>
       </c>
       <c r="P4" t="n">
-        <v>0.316626465526635</v>
+        <v>0.2809832889996098</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.965277499713736e-05</v>
+        <v>0.00010687553350532</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02976378248760652</v>
+        <v>0.1240829446459615</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004960630414601087</v>
+        <v>0.002068049077432692</v>
       </c>
       <c r="T4" t="n">
-        <v>3.158295685538259</v>
+        <v>3.558930509925766</v>
       </c>
       <c r="U4" t="n">
-        <v>7121.942255430543</v>
+        <v>19350.07021349512</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Composer 2.5</t>
+          <t>Muse Spark 1.1 (xhigh)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3830075380367747</v>
+        <v>0.5492139250715363</v>
       </c>
       <c r="F5" t="n">
-        <v>0.15929203539823</v>
+        <v>0.542772861356932</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6779026217228465</v>
+        <v>0.771535580524344</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3118279569892475</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08505141359918204</v>
+        <v>1.435218435173823</v>
       </c>
       <c r="J5" t="n">
-        <v>625.1976421267894</v>
+        <v>761.3780071574635</v>
       </c>
       <c r="K5" t="n">
-        <v>116.8680981595092</v>
+        <v>55.51329243353784</v>
       </c>
       <c r="L5" t="n">
-        <v>3705076.4698364</v>
+        <v>12289527.21472391</v>
       </c>
       <c r="M5" t="n">
-        <v>1872461.576687117</v>
+        <v>6284599.100204499</v>
       </c>
       <c r="N5" t="n">
-        <v>18453.85787321063</v>
+        <v>34558.96932515338</v>
       </c>
       <c r="O5" t="n">
-        <v>1.052833075750478</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P5" t="n">
-        <v>4.503247175194018</v>
+        <v>0.3826692241484618</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0001033737201255894</v>
+        <v>4.46895893939297e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03675710004924502</v>
+        <v>0.04328051926180353</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0006126183341540836</v>
+        <v>0.0007213419876967254</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2220619835190183</v>
+        <v>2.61322295312684</v>
       </c>
       <c r="U5" t="n">
-        <v>5926.248309626565</v>
+        <v>16141.16391489395</v>
       </c>
     </row>
     <row r="6">
@@ -823,7 +823,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Opus 5 (high)</t>
+          <t>Sonnet 4.6 (medium)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -837,201 +837,201 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6561729860226817</v>
+        <v>0.386493136077762</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6076696165191739</v>
+        <v>0.289085545722714</v>
       </c>
       <c r="G6" t="n">
-        <v>0.868913857677903</v>
+        <v>0.6741573033707871</v>
       </c>
       <c r="H6" t="n">
-        <v>0.491935483870968</v>
+        <v>0.196236559139785</v>
       </c>
       <c r="I6" t="n">
-        <v>3.918602446063396</v>
+        <v>2.041513021472394</v>
       </c>
       <c r="J6" t="n">
-        <v>842.8052382413097</v>
+        <v>827.6555807770972</v>
       </c>
       <c r="K6" t="n">
-        <v>94.85071574642126</v>
+        <v>67.41768916155419</v>
       </c>
       <c r="L6" t="n">
-        <v>9911366.349693259</v>
+        <v>8444053.035787314</v>
       </c>
       <c r="M6" t="n">
-        <v>4937399.112474437</v>
+        <v>4205086.787321064</v>
       </c>
       <c r="N6" t="n">
-        <v>37331.49386503067</v>
+        <v>40070.1308793456</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9702723303233406</v>
+        <v>0.9487221679807678</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1674507672197952</v>
+        <v>0.1893170075393459</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.620408961504982e-05</v>
+        <v>4.577104554409349e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04671349604271027</v>
+        <v>0.0280184036732921</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0007785582673785045</v>
+        <v>0.0004669733945548682</v>
       </c>
       <c r="T6" t="n">
-        <v>5.971904557997063</v>
+        <v>5.282145608561709</v>
       </c>
       <c r="U6" t="n">
-        <v>11759.97241115327</v>
+        <v>10202.37551936649</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (high)</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.3282816619106221</v>
+        <v>0.5962784529614886</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08554572271386431</v>
+        <v>0.572271386430678</v>
       </c>
       <c r="G7" t="n">
-        <v>0.700374531835206</v>
+        <v>0.910112359550562</v>
       </c>
       <c r="H7" t="n">
-        <v>0.198924731182796</v>
+        <v>0.306451612903226</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2547256318476481</v>
+        <v>1.26793256886503</v>
       </c>
       <c r="J7" t="n">
-        <v>1072.531835378324</v>
+        <v>527.0915644171779</v>
       </c>
       <c r="K7" t="n">
-        <v>128.1457055214724</v>
+        <v>83.44887525562373</v>
       </c>
       <c r="L7" t="n">
-        <v>9942165.528629865</v>
+        <v>18493123.3742331</v>
       </c>
       <c r="M7" t="n">
-        <v>5181244.880368099</v>
+        <v>9497213.109406954</v>
       </c>
       <c r="N7" t="n">
-        <v>41975.79754601227</v>
+        <v>49098.7944785276</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8541357545221669</v>
+        <v>0.8634331167917663</v>
       </c>
       <c r="P7" t="n">
-        <v>1.288765718351297</v>
+        <v>0.4702761547447575</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.301913058732415e-05</v>
+        <v>3.224325285107314e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01836486252894252</v>
+        <v>0.06787569673449199</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000306081042149042</v>
+        <v>0.001131261612241533</v>
       </c>
       <c r="T7" t="n">
-        <v>0.77593622002864</v>
+        <v>2.126410173917388</v>
       </c>
       <c r="U7" t="n">
-        <v>9269.809250112259</v>
+        <v>35085.21976571858</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (max)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.6042010361726691</v>
+        <v>0.4708693600598457</v>
       </c>
       <c r="F8" t="n">
-        <v>0.669616519174042</v>
+        <v>0.371681415929204</v>
       </c>
       <c r="G8" t="n">
-        <v>0.782771535580524</v>
+        <v>0.764044943820225</v>
       </c>
       <c r="H8" t="n">
-        <v>0.360215053763441</v>
+        <v>0.276881720430108</v>
       </c>
       <c r="I8" t="n">
-        <v>1.930014663190181</v>
+        <v>1.998031234219494</v>
       </c>
       <c r="J8" t="n">
-        <v>491.0206543967283</v>
+        <v>386.6294212678936</v>
       </c>
       <c r="K8" t="n">
-        <v>95.80674846625767</v>
+        <v>77.78698023176551</v>
       </c>
       <c r="L8" t="n">
-        <v>9653668.778118595</v>
+        <v>3955817.742194954</v>
       </c>
       <c r="M8" t="n">
-        <v>4933733.868098159</v>
+        <v>2043912.618541241</v>
       </c>
       <c r="N8" t="n">
-        <v>60602.61656441716</v>
+        <v>11032.14533060668</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9184675548550253</v>
+        <v>0.8915632417465625</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3130551532566941</v>
+        <v>0.235666666263996</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.258771147630174e-05</v>
+        <v>0.0001190321169343297</v>
       </c>
       <c r="R8" t="n">
-        <v>0.07383001477789097</v>
+        <v>0.07307297388528267</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001230500246298183</v>
+        <v>0.001217882898088044</v>
       </c>
       <c r="T8" t="n">
-        <v>3.194325311680895</v>
+        <v>4.243281478254504</v>
       </c>
       <c r="U8" t="n">
-        <v>19660.41283941338</v>
+        <v>10231.5486732035</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1056,201 +1056,201 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5716614223656344</v>
+        <v>0.5531133827505798</v>
       </c>
       <c r="F9" t="n">
-        <v>0.634218289085546</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G9" t="n">
-        <v>0.752808988764045</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H9" t="n">
-        <v>0.327956989247312</v>
+        <v>0.306451612903226</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2882767483844579</v>
+        <v>2.65253587423313</v>
       </c>
       <c r="J9" t="n">
-        <v>482.0907147239265</v>
+        <v>386.3044764826171</v>
       </c>
       <c r="K9" t="n">
-        <v>114.6288343558282</v>
+        <v>78.53885480572598</v>
       </c>
       <c r="L9" t="n">
-        <v>15987867.69734152</v>
+        <v>6885560.579754606</v>
       </c>
       <c r="M9" t="n">
-        <v>8170928.992842535</v>
+        <v>3492715.358895706</v>
       </c>
       <c r="N9" t="n">
-        <v>65702.91104294479</v>
+        <v>13239.49488752556</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9181831202060824</v>
+        <v>0.9409891933709398</v>
       </c>
       <c r="P9" t="n">
-        <v>1.983029937618288</v>
+        <v>0.2085224890353234</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.57559515244607e-05</v>
+        <v>8.032946284386509e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0711477825528751</v>
+        <v>0.08590840900216211</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001185796375881252</v>
+        <v>0.001431806816702702</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5042788215295665</v>
+        <v>4.795645806005133</v>
       </c>
       <c r="U9" t="n">
-        <v>33163.60844347958</v>
+        <v>17824.18014528092</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-5.5 (xhigh)</t>
+          <t>Opus 5 (low)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6103327520587847</v>
+        <v>0.5940064571013326</v>
       </c>
       <c r="F10" t="n">
-        <v>0.64306784660767</v>
+        <v>0.569321533923304</v>
       </c>
       <c r="G10" t="n">
-        <v>0.827715355805243</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H10" t="n">
-        <v>0.360215053763441</v>
+        <v>0.39247311827957</v>
       </c>
       <c r="I10" t="n">
-        <v>4.75237007157464</v>
+        <v>2.295157744887527</v>
       </c>
       <c r="J10" t="n">
-        <v>614.9898987730064</v>
+        <v>598.7677147239262</v>
       </c>
       <c r="K10" t="n">
-        <v>107.1319018404908</v>
+        <v>64.39263803680981</v>
       </c>
       <c r="L10" t="n">
-        <v>12150851.17995912</v>
+        <v>5258606.375255628</v>
       </c>
       <c r="M10" t="n">
-        <v>6164087.486707566</v>
+        <v>2618171.039877301</v>
       </c>
       <c r="N10" t="n">
-        <v>25286.0654396728</v>
+        <v>22632.92229038855</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9341674523911518</v>
+        <v>0.9637890151908798</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1284270254350285</v>
+        <v>0.2588085539760761</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.022962943249859e-05</v>
+        <v>0.0001129589124404576</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0595456367601959</v>
+        <v>0.05952289435396941</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0009924272793365983</v>
+        <v>0.0009920482392328236</v>
       </c>
       <c r="T10" t="n">
-        <v>7.786523098332615</v>
+        <v>3.863859925172484</v>
       </c>
       <c r="U10" t="n">
-        <v>19757.8061106399</v>
+        <v>8782.381290681667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Opus 4.8 (xhigh)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.590718121759733</v>
+        <v>0.6797281481220124</v>
       </c>
       <c r="F11" t="n">
-        <v>0.513274336283186</v>
+        <v>0.681415929203539</v>
       </c>
       <c r="G11" t="n">
-        <v>0.831460674157303</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H11" t="n">
-        <v>0.42741935483871</v>
+        <v>0.518817204301075</v>
       </c>
       <c r="I11" t="n">
-        <v>5.665366469580767</v>
+        <v>1.584232134037035</v>
       </c>
       <c r="J11" t="n">
-        <v>1065.615385480574</v>
+        <v>1475.134529652353</v>
       </c>
       <c r="K11" t="n">
-        <v>136.1303390500093</v>
+        <v>128.5444491455704</v>
       </c>
       <c r="L11" t="n">
-        <v>13628306.24233129</v>
+        <v>14182668.81449944</v>
       </c>
       <c r="M11" t="n">
-        <v>6783846.309815951</v>
+        <v>7211413.368985498</v>
       </c>
       <c r="N11" t="n">
-        <v>62541.86503067485</v>
+        <v>44550.73137766495</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9687226730983399</v>
+        <v>0.9520877069904663</v>
       </c>
       <c r="P11" t="n">
-        <v>0.104268298428971</v>
+        <v>0.4290584274350556</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.3344940395079e-05</v>
+        <v>4.792667423969616e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03326067527600474</v>
+        <v>0.02764743694050216</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0005543445879334123</v>
+        <v>0.0004607906156750361</v>
       </c>
       <c r="T11" t="n">
-        <v>9.590642746330172</v>
+        <v>2.330684904566675</v>
       </c>
       <c r="U11" t="n">
-        <v>12789.14177481134</v>
+        <v>9614.491783228672</v>
       </c>
     </row>
     <row r="12">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (medium)</t>
+          <t>GPT-5.6 Terra (low)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1275,55 +1275,55 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.616195748748264</v>
+        <v>0.3864628427996264</v>
       </c>
       <c r="F12" t="n">
-        <v>0.640117994100295</v>
+        <v>0.297935103244838</v>
       </c>
       <c r="G12" t="n">
-        <v>0.805243445692884</v>
+        <v>0.632958801498127</v>
       </c>
       <c r="H12" t="n">
-        <v>0.403225806451613</v>
+        <v>0.228494623655914</v>
       </c>
       <c r="I12" t="n">
-        <v>2.192997850306748</v>
+        <v>0.3850630644171779</v>
       </c>
       <c r="J12" t="n">
-        <v>297.9599253578734</v>
+        <v>154.8149498977502</v>
       </c>
       <c r="K12" t="n">
-        <v>71.35378323108384</v>
+        <v>37.80981595092025</v>
       </c>
       <c r="L12" t="n">
-        <v>5770064.36707567</v>
+        <v>1657646.844580775</v>
       </c>
       <c r="M12" t="n">
-        <v>2974758.351738241</v>
+        <v>861642.4202453988</v>
       </c>
       <c r="N12" t="n">
-        <v>18959.48773006135</v>
+        <v>6854.071574642127</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8970664465490255</v>
+        <v>0.8771903855272027</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2809832889996098</v>
+        <v>1.003635192548439</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0001067918327331517</v>
+        <v>0.0002331394313952103</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1240829446459615</v>
+        <v>0.1497773347037368</v>
       </c>
       <c r="S12" t="n">
-        <v>0.002068049077432692</v>
+        <v>0.002496288911728947</v>
       </c>
       <c r="T12" t="n">
-        <v>3.558930509925766</v>
+        <v>0.996377974212713</v>
       </c>
       <c r="U12" t="n">
-        <v>19365.23631540505</v>
+        <v>10707.27888796005</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (xhigh)</t>
+          <t>GPT-5.6 Terra (none)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1348,128 +1348,128 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.529584326329171</v>
+        <v>0.2309196896685307</v>
       </c>
       <c r="F13" t="n">
-        <v>0.566371681415929</v>
+        <v>0.132743362831858</v>
       </c>
       <c r="G13" t="n">
-        <v>0.707865168539326</v>
+        <v>0.374531835205992</v>
       </c>
       <c r="H13" t="n">
-        <v>0.314516129032258</v>
+        <v>0.185483870967742</v>
       </c>
       <c r="I13" t="n">
-        <v>0.235909783783231</v>
+        <v>0.2926964817995911</v>
       </c>
       <c r="J13" t="n">
-        <v>413.8987709611452</v>
+        <v>88.85438650306735</v>
       </c>
       <c r="K13" t="n">
-        <v>96.1922290388548</v>
+        <v>33.82924335378323</v>
       </c>
       <c r="L13" t="n">
-        <v>12823340.91104294</v>
+        <v>1105801.555214722</v>
       </c>
       <c r="M13" t="n">
-        <v>6575104.906952964</v>
+        <v>582183.7985685072</v>
       </c>
       <c r="N13" t="n">
-        <v>47572.15235173824</v>
+        <v>5133.394683026585</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9100235393369853</v>
+        <v>0.8482758058887612</v>
       </c>
       <c r="P13" t="n">
-        <v>2.244859529928555</v>
+        <v>0.7889390683781471</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.129846738092369e-05</v>
+        <v>0.0002088256148488515</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07677012305681175</v>
+        <v>0.1559313155533806</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001279502050946862</v>
+        <v>0.00259885525922301</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4454621710926501</v>
+        <v>1.267525009321365</v>
       </c>
       <c r="U13" t="n">
-        <v>30981.8289174063</v>
+        <v>12445.098083892</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Muse Spark 1.1 (xhigh)</t>
+          <t>GPT-5.6 Luna (high)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5492139250715363</v>
+        <v>0.516945881593198</v>
       </c>
       <c r="F14" t="n">
-        <v>0.542772861356932</v>
+        <v>0.533923303834808</v>
       </c>
       <c r="G14" t="n">
-        <v>0.771535580524344</v>
+        <v>0.726591760299625</v>
       </c>
       <c r="H14" t="n">
-        <v>0.333333333333333</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="I14" t="n">
-        <v>1.435218435173823</v>
+        <v>0.1797932241513293</v>
       </c>
       <c r="J14" t="n">
-        <v>761.3780071574632</v>
+        <v>342.6686574642128</v>
       </c>
       <c r="K14" t="n">
-        <v>55.51329243353784</v>
+        <v>83.81901840490798</v>
       </c>
       <c r="L14" t="n">
-        <v>12289527.21472391</v>
+        <v>9641370.493865021</v>
       </c>
       <c r="M14" t="n">
-        <v>6284599.100204499</v>
+        <v>4959371.744376278</v>
       </c>
       <c r="N14" t="n">
-        <v>34558.96932515338</v>
+        <v>22230.90593047035</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.9032288062243126</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3826692241484618</v>
+        <v>2.875224492098168</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.46895893939297e-05</v>
+        <v>5.361746879472582e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.04328051926180354</v>
+        <v>0.09051528997463437</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0007213419876967256</v>
+        <v>0.001508588166243906</v>
       </c>
       <c r="T14" t="n">
-        <v>2.61322295312684</v>
+        <v>0.3477989293525597</v>
       </c>
       <c r="U14" t="n">
-        <v>16141.16391489395</v>
+        <v>28136.13175249894</v>
       </c>
     </row>
     <row r="15">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sonnet 4.6 (medium)</t>
+          <t>Qwen3.7 Plus (thinking)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1490,659 +1490,659 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.3864931360777617</v>
+        <v>0.3812184526692477</v>
       </c>
       <c r="F15" t="n">
-        <v>0.289085545722714</v>
+        <v>0.191740412979351</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6741573033707861</v>
+        <v>0.715355805243446</v>
       </c>
       <c r="H15" t="n">
-        <v>0.196236559139785</v>
+        <v>0.236559139784946</v>
       </c>
       <c r="I15" t="n">
-        <v>2.041513021472394</v>
+        <v>6.300658805725988</v>
       </c>
       <c r="J15" t="n">
-        <v>827.6555807770975</v>
+        <v>643.9465817995908</v>
       </c>
       <c r="K15" t="n">
-        <v>67.41768916155419</v>
+        <v>145.9662576687116</v>
       </c>
       <c r="L15" t="n">
-        <v>8444053.035787314</v>
+        <v>8784635.035787327</v>
       </c>
       <c r="M15" t="n">
-        <v>4205086.787321064</v>
+        <v>4715248.469325154</v>
       </c>
       <c r="N15" t="n">
-        <v>40070.1308793456</v>
+        <v>32611.0408997955</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9487221679807681</v>
+        <v>0.8105104948122446</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1893170075393457</v>
+        <v>0.06050453840204764</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.577104554409345e-05</v>
+        <v>4.339604902380339e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.02801840367329206</v>
+        <v>0.03552019345491834</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0004669733945548676</v>
+        <v>0.000592003224248639</v>
       </c>
       <c r="T15" t="n">
-        <v>5.282145608561714</v>
+        <v>16.52768579697415</v>
       </c>
       <c r="U15" t="n">
-        <v>10202.37551936649</v>
+        <v>13641.86919237547</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>GPT-5.6 Luna (none)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4708693600598454</v>
+        <v>0.1909870904304247</v>
       </c>
       <c r="F16" t="n">
-        <v>0.371681415929203</v>
+        <v>0.0648967551622419</v>
       </c>
       <c r="G16" t="n">
-        <v>0.764044943820225</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>0.276881720430108</v>
+        <v>0.174731182795699</v>
       </c>
       <c r="I16" t="n">
-        <v>1.998031234219494</v>
+        <v>0.06947505231083852</v>
       </c>
       <c r="J16" t="n">
-        <v>386.6294212678936</v>
+        <v>131.816209611452</v>
       </c>
       <c r="K16" t="n">
-        <v>77.78698023176551</v>
+        <v>54.28629856850716</v>
       </c>
       <c r="L16" t="n">
-        <v>3955817.742194958</v>
+        <v>3549957.210633946</v>
       </c>
       <c r="M16" t="n">
-        <v>2043912.618541241</v>
+        <v>1835572.532719836</v>
       </c>
       <c r="N16" t="n">
-        <v>11032.14533060668</v>
+        <v>7934.628834355828</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8915632417465622</v>
+        <v>0.8748960056789888</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2356666662639959</v>
+        <v>2.74900247035337</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0001190321169343295</v>
+        <v>5.379982887070306e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>0.07307297388528261</v>
+        <v>0.08693335561387526</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001217882898088044</v>
+        <v>0.001448889260231254</v>
       </c>
       <c r="T16" t="n">
-        <v>4.243281478254507</v>
+        <v>0.3637683162472587</v>
       </c>
       <c r="U16" t="n">
-        <v>10231.54867320351</v>
+        <v>26931.11280545826</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>Opus 4.8 (high)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5531133827505798</v>
+        <v>0.5757636668124306</v>
       </c>
       <c r="F17" t="n">
-        <v>0.566371681415929</v>
+        <v>0.516224188790561</v>
       </c>
       <c r="G17" t="n">
-        <v>0.786516853932584</v>
+        <v>0.823970037453183</v>
       </c>
       <c r="H17" t="n">
-        <v>0.306451612903226</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="I17" t="n">
-        <v>2.65253587423313</v>
+        <v>3.7823013803681</v>
       </c>
       <c r="J17" t="n">
-        <v>386.3044764826171</v>
+        <v>761.030831288344</v>
       </c>
       <c r="K17" t="n">
-        <v>78.53885480572598</v>
+        <v>104.7627811860941</v>
       </c>
       <c r="L17" t="n">
-        <v>6885560.579754606</v>
+        <v>9188690.866053157</v>
       </c>
       <c r="M17" t="n">
-        <v>3492715.358895706</v>
+        <v>4574601.889570553</v>
       </c>
       <c r="N17" t="n">
-        <v>13239.49488752556</v>
+        <v>40682.70756646217</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9409891933709396</v>
+        <v>0.9682475638703767</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2085224890353234</v>
+        <v>0.152225750650361</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.032946284386509e-05</v>
+        <v>6.266003233818007e-05</v>
       </c>
       <c r="R17" t="n">
-        <v>0.08590840900216211</v>
+        <v>0.04539345659657895</v>
       </c>
       <c r="S17" t="n">
-        <v>0.001431806816702702</v>
+        <v>0.0007565576099429824</v>
       </c>
       <c r="T17" t="n">
-        <v>4.795645806005133</v>
+        <v>6.569190795431485</v>
       </c>
       <c r="U17" t="n">
-        <v>17824.18014528092</v>
+        <v>12074.00605636132</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin CLI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Opus 5 (low)</t>
+          <t>SWE-1.7 Lightning Max</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Cognition</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5940064571013326</v>
+        <v>0.5221389513465007</v>
       </c>
       <c r="F18" t="n">
-        <v>0.569321533923304</v>
+        <v>0.404129793510325</v>
       </c>
       <c r="G18" t="n">
-        <v>0.820224719101124</v>
+        <v>0.7940074906367039</v>
       </c>
       <c r="H18" t="n">
-        <v>0.39247311827957</v>
+        <v>0.368279569892473</v>
       </c>
       <c r="I18" t="n">
-        <v>2.295157744887527</v>
+        <v>8.521259638036815</v>
       </c>
       <c r="J18" t="n">
-        <v>598.7677147239262</v>
+        <v>637.3248271983654</v>
       </c>
       <c r="K18" t="n">
-        <v>64.39263803680981</v>
+        <v>86.57157464212679</v>
       </c>
       <c r="L18" t="n">
-        <v>5258606.375255628</v>
+        <v>15573672.60122699</v>
       </c>
       <c r="M18" t="n">
-        <v>2618171.039877301</v>
+        <v>7834231.955010225</v>
       </c>
       <c r="N18" t="n">
-        <v>22632.92229038855</v>
+        <v>38917.19427402863</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9637890151908798</v>
+        <v>0.9746033359706325</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2588085539760761</v>
+        <v>0.06127485530610995</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0001129589124404576</v>
+        <v>3.352702761359986e-05</v>
       </c>
       <c r="R18" t="n">
-        <v>0.05952289435396941</v>
+        <v>0.04915599666579314</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0009920482392328236</v>
+        <v>0.0008192666110965524</v>
       </c>
       <c r="T18" t="n">
-        <v>3.863859925172484</v>
+        <v>16.31990797863681</v>
       </c>
       <c r="U18" t="n">
-        <v>8782.381290681667</v>
+        <v>24436.00490143738</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (low)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.3864628427996264</v>
+        <v>0.4665540825894554</v>
       </c>
       <c r="F19" t="n">
-        <v>0.297935103244838</v>
+        <v>0.315634218289086</v>
       </c>
       <c r="G19" t="n">
-        <v>0.632958801498127</v>
+        <v>0.745318352059925</v>
       </c>
       <c r="H19" t="n">
-        <v>0.228494623655914</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3850630644171779</v>
+        <v>2.72490571101738</v>
       </c>
       <c r="J19" t="n">
-        <v>154.8149498977502</v>
+        <v>826.6777535787322</v>
       </c>
       <c r="K19" t="n">
-        <v>37.80981595092025</v>
+        <v>86.42229038854805</v>
       </c>
       <c r="L19" t="n">
-        <v>1659148.663599183</v>
+        <v>5728865.180470352</v>
       </c>
       <c r="M19" t="n">
-        <v>861642.4202453988</v>
+        <v>2855520.426380368</v>
       </c>
       <c r="N19" t="n">
-        <v>8355.890593047036</v>
+        <v>17872.17893660532</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8771903855272027</v>
+        <v>0.9538631453697446</v>
       </c>
       <c r="P19" t="n">
-        <v>1.003635192548439</v>
+        <v>0.1712184317802546</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0002329283995330921</v>
+        <v>8.143917999326182e-05</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1497773347037368</v>
+        <v>0.03386234216922261</v>
       </c>
       <c r="S19" t="n">
-        <v>0.002496288911728947</v>
+        <v>0.0005643723694870434</v>
       </c>
       <c r="T19" t="n">
-        <v>0.996377974212713</v>
+        <v>5.840492694638283</v>
       </c>
       <c r="U19" t="n">
-        <v>10716.97962435147</v>
+        <v>6929.985905233071</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (none)</t>
+          <t>Gemini 3.6 Flash (high)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.2309196896685307</v>
+        <v>0.4724127134829677</v>
       </c>
       <c r="F20" t="n">
-        <v>0.132743362831858</v>
+        <v>0.412979351032448</v>
       </c>
       <c r="G20" t="n">
-        <v>0.374531835205992</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H20" t="n">
-        <v>0.185483870967742</v>
+        <v>0.217741935483871</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2926964817995911</v>
+        <v>2.083890154754598</v>
       </c>
       <c r="J20" t="n">
-        <v>88.85438650306737</v>
+        <v>626.0057290388548</v>
       </c>
       <c r="K20" t="n">
-        <v>33.82924335378323</v>
+        <v>65.01533742331287</v>
       </c>
       <c r="L20" t="n">
-        <v>1105802.151329243</v>
+        <v>13020159.54294479</v>
       </c>
       <c r="M20" t="n">
-        <v>582183.7985685072</v>
+        <v>6765842.061349694</v>
       </c>
       <c r="N20" t="n">
-        <v>5133.990797546012</v>
+        <v>42763.3517382413</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8482758058887612</v>
+        <v>0.8377770485520737</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7889390683781471</v>
+        <v>0.2266975120570113</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0002088255022753852</v>
+        <v>3.628317394458911e-05</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1559313155533806</v>
+        <v>0.04527875943323637</v>
       </c>
       <c r="S20" t="n">
-        <v>0.00259885525922301</v>
+        <v>0.0007546459905539396</v>
       </c>
       <c r="T20" t="n">
-        <v>1.267525009321365</v>
+        <v>4.411164423138944</v>
       </c>
       <c r="U20" t="n">
-        <v>12445.10479278442</v>
+        <v>20798.78655892725</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (high)</t>
+          <t>Fable 5 (low) (with fallback)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.516945881593198</v>
+        <v>0.58556576973616</v>
       </c>
       <c r="F21" t="n">
-        <v>0.533923303834808</v>
+        <v>0.59882005899705</v>
       </c>
       <c r="G21" t="n">
-        <v>0.726591760299625</v>
+        <v>0.816479400749064</v>
       </c>
       <c r="H21" t="n">
-        <v>0.290322580645161</v>
+        <v>0.341397849462366</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1797932241513293</v>
+        <v>3.166078810327201</v>
       </c>
       <c r="J21" t="n">
-        <v>342.6686574642128</v>
+        <v>490.7785531697341</v>
       </c>
       <c r="K21" t="n">
-        <v>83.81901840490798</v>
+        <v>54.85276073619632</v>
       </c>
       <c r="L21" t="n">
-        <v>9651632.293456044</v>
+        <v>3748013.195296523</v>
       </c>
       <c r="M21" t="n">
-        <v>4959371.744376278</v>
+        <v>1864095.536809816</v>
       </c>
       <c r="N21" t="n">
-        <v>32492.70552147239</v>
+        <v>20218.93047034765</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9032288062243129</v>
+        <v>0.9618678651037137</v>
       </c>
       <c r="P21" t="n">
-        <v>2.875224492098168</v>
+        <v>0.1849498401069948</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.356046167897375e-05</v>
+        <v>0.0001562336467947875</v>
       </c>
       <c r="R21" t="n">
-        <v>0.09051528997463437</v>
+        <v>0.07158818566388871</v>
       </c>
       <c r="S21" t="n">
-        <v>0.001508588166243906</v>
+        <v>0.001193136427731479</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3477989293525597</v>
+        <v>5.406871395084705</v>
       </c>
       <c r="U21" t="n">
-        <v>28166.07846448294</v>
+        <v>7636.872416469033</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qwen3.7 Plus (thinking)</t>
+          <t>Muse Spark 1.2 (xhigh)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.3812184526692477</v>
+        <v>0.5888788742875287</v>
       </c>
       <c r="F22" t="n">
-        <v>0.191740412979351</v>
+        <v>0.528023598820059</v>
       </c>
       <c r="G22" t="n">
-        <v>0.715355805243446</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="H22" t="n">
-        <v>0.236559139784946</v>
+        <v>0.440860215053763</v>
       </c>
       <c r="I22" t="n">
-        <v>6.300658805725988</v>
+        <v>1.914379785695299</v>
       </c>
       <c r="J22" t="n">
-        <v>643.9465817995912</v>
+        <v>1064.740692229039</v>
       </c>
       <c r="K22" t="n">
-        <v>145.9662576687116</v>
+        <v>65.87116564417177</v>
       </c>
       <c r="L22" t="n">
-        <v>8784635.035787327</v>
+        <v>16350688.07453988</v>
       </c>
       <c r="M22" t="n">
-        <v>4715248.469325154</v>
+        <v>8360784.971370144</v>
       </c>
       <c r="N22" t="n">
-        <v>32611.0408997955</v>
+        <v>47157.38036809816</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8105104948122446</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P22" t="n">
-        <v>0.06050453840204764</v>
+        <v>0.3076081761245976</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.339604902380339e-05</v>
+        <v>3.601554085081526e-05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.03552019345491832</v>
+        <v>0.03318435438330295</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0005920032242486387</v>
+        <v>0.0005530725730550492</v>
       </c>
       <c r="T22" t="n">
-        <v>16.52768579697415</v>
+        <v>3.250888882729005</v>
       </c>
       <c r="U22" t="n">
-        <v>13641.86919237546</v>
+        <v>15356.49777816761</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (none)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.1909870904304247</v>
+        <v>0.590851412183529</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0648967551622419</v>
+        <v>0.6076696165191739</v>
       </c>
       <c r="G23" t="n">
-        <v>0.333333333333333</v>
+        <v>0.812734082397004</v>
       </c>
       <c r="H23" t="n">
-        <v>0.174731182795699</v>
+        <v>0.352150537634409</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06947505231083853</v>
+        <v>2.008975153911043</v>
       </c>
       <c r="J23" t="n">
-        <v>131.816209611452</v>
+        <v>457.9304969325156</v>
       </c>
       <c r="K23" t="n">
-        <v>54.28629856850716</v>
+        <v>147.3926380368098</v>
       </c>
       <c r="L23" t="n">
-        <v>3549958.812883432</v>
+        <v>19759750.71472392</v>
       </c>
       <c r="M23" t="n">
-        <v>1835572.532719836</v>
+        <v>10510296.86707566</v>
       </c>
       <c r="N23" t="n">
-        <v>7936.23108384458</v>
+        <v>83533.0736196319</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8748960056789888</v>
+        <v>0.8589224031432205</v>
       </c>
       <c r="P23" t="n">
-        <v>2.749002470353369</v>
+        <v>0.2941058833073512</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.379980458852045e-05</v>
+        <v>2.990176448649516e-05</v>
       </c>
       <c r="R23" t="n">
-        <v>0.08693335561387526</v>
+        <v>0.07741586325541473</v>
       </c>
       <c r="S23" t="n">
-        <v>0.001448889260231254</v>
+        <v>0.001290264387590245</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3637683162472588</v>
+        <v>3.400135994406355</v>
       </c>
       <c r="U23" t="n">
-        <v>26931.12496063622</v>
+        <v>43150.10868917053</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Opus 4.8 (high)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2151,493 +2151,493 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5757636668124304</v>
+        <v>0.5127556084440553</v>
       </c>
       <c r="F24" t="n">
-        <v>0.51622418879056</v>
+        <v>0.395280235988201</v>
       </c>
       <c r="G24" t="n">
-        <v>0.823970037453183</v>
+        <v>0.782771535580524</v>
       </c>
       <c r="H24" t="n">
-        <v>0.387096774193548</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I24" t="n">
-        <v>3.7823013803681</v>
+        <v>2.942840985557257</v>
       </c>
       <c r="J24" t="n">
-        <v>761.0308312883442</v>
+        <v>752.2755521472382</v>
       </c>
       <c r="K24" t="n">
-        <v>104.7627811860941</v>
+        <v>54.41308793456033</v>
       </c>
       <c r="L24" t="n">
-        <v>9188690.866053157</v>
+        <v>7582747.093047047</v>
       </c>
       <c r="M24" t="n">
-        <v>4574601.889570553</v>
+        <v>3744700.533231084</v>
       </c>
       <c r="N24" t="n">
-        <v>40682.70756646217</v>
+        <v>25943.59151329243</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9682475638703767</v>
+        <v>0.9584168731547833</v>
       </c>
       <c r="P24" t="n">
-        <v>0.152225750650361</v>
+        <v>0.1742382993034738</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.266003233818004e-05</v>
+        <v>6.762135175446157e-05</v>
       </c>
       <c r="R24" t="n">
-        <v>0.04539345659657892</v>
+        <v>0.04089636625679125</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0007565576099429819</v>
+        <v>0.0006816061042798542</v>
       </c>
       <c r="T24" t="n">
-        <v>6.569190795431488</v>
+        <v>5.73926630366314</v>
       </c>
       <c r="U24" t="n">
-        <v>12074.00605636132</v>
+        <v>10079.74680474918</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Devin CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SWE-1.7 Lightning Max</t>
+          <t>Opus 4.8 (low)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cognition</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5221389513465003</v>
+        <v>0.4904379267565557</v>
       </c>
       <c r="F25" t="n">
-        <v>0.404129793510324</v>
+        <v>0.410029498525074</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7940074906367039</v>
+        <v>0.779026217228464</v>
       </c>
       <c r="H25" t="n">
-        <v>0.368279569892473</v>
+        <v>0.282258064516129</v>
       </c>
       <c r="I25" t="n">
-        <v>8.521259638036815</v>
+        <v>2.182594679703477</v>
       </c>
       <c r="J25" t="n">
-        <v>637.3248271983654</v>
+        <v>516.6536431492842</v>
       </c>
       <c r="K25" t="n">
-        <v>86.57157464212679</v>
+        <v>68.16359918200409</v>
       </c>
       <c r="L25" t="n">
-        <v>15573672.60122699</v>
+        <v>5214050.029652352</v>
       </c>
       <c r="M25" t="n">
-        <v>7834231.955010225</v>
+        <v>2595804.632924335</v>
       </c>
       <c r="N25" t="n">
-        <v>38917.19427402863</v>
+        <v>23270.04396728017</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9746033359706325</v>
+        <v>0.9661582176104914</v>
       </c>
       <c r="P25" t="n">
-        <v>0.06127485530610991</v>
+        <v>0.2247040787358583</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.352702761359984e-05</v>
+        <v>9.406084022351733e-05</v>
       </c>
       <c r="R25" t="n">
-        <v>0.04915599666579311</v>
+        <v>0.0569555174836748</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0008192666110965519</v>
+        <v>0.0009492586247279134</v>
       </c>
       <c r="T25" t="n">
-        <v>16.31990797863682</v>
+        <v>4.450297500720978</v>
       </c>
       <c r="U25" t="n">
-        <v>24436.00490143738</v>
+        <v>10091.9641210113</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>Fable 5 (xhigh) (with fallback)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.4665540825894554</v>
+        <v>0.6601695603875121</v>
       </c>
       <c r="F26" t="n">
-        <v>0.315634218289086</v>
+        <v>0.651917404129794</v>
       </c>
       <c r="G26" t="n">
-        <v>0.745318352059925</v>
+        <v>0.868913857677903</v>
       </c>
       <c r="H26" t="n">
-        <v>0.338709677419355</v>
+        <v>0.459677419354839</v>
       </c>
       <c r="I26" t="n">
-        <v>2.72490571101738</v>
+        <v>8.525764661042945</v>
       </c>
       <c r="J26" t="n">
-        <v>826.6777535787322</v>
+        <v>1028.54882822086</v>
       </c>
       <c r="K26" t="n">
-        <v>86.42229038854805</v>
+        <v>108.2208588957055</v>
       </c>
       <c r="L26" t="n">
-        <v>5728865.180470356</v>
+        <v>10319338.81901841</v>
       </c>
       <c r="M26" t="n">
-        <v>2855520.426380368</v>
+        <v>5134138.567484663</v>
       </c>
       <c r="N26" t="n">
-        <v>17872.17893660532</v>
+        <v>52975.96319018405</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9538631453697446</v>
+        <v>0.9637652234526964</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1712184317802546</v>
+        <v>0.07743229922871861</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.143917999326177e-05</v>
+        <v>6.397401732471733e-05</v>
       </c>
       <c r="R26" t="n">
-        <v>0.03386234216922261</v>
+        <v>0.03851073720220626</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0005643723694870434</v>
+        <v>0.000641845620036771</v>
       </c>
       <c r="T26" t="n">
-        <v>5.840492694638283</v>
+        <v>12.91450738207078</v>
       </c>
       <c r="U26" t="n">
-        <v>6929.985905233076</v>
+        <v>10032.91096725896</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gemini 3.6 Flash (high)</t>
+          <t>GPT-5.6 Sol (none)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.4724127134829677</v>
+        <v>0.4336881923573268</v>
       </c>
       <c r="F27" t="n">
-        <v>0.412979351032448</v>
+        <v>0.353982300884956</v>
       </c>
       <c r="G27" t="n">
-        <v>0.786516853932584</v>
+        <v>0.602996254681648</v>
       </c>
       <c r="H27" t="n">
-        <v>0.217741935483871</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I27" t="n">
-        <v>2.083890154754602</v>
+        <v>1.086854643353786</v>
       </c>
       <c r="J27" t="n">
-        <v>626.0057290388548</v>
+        <v>197.8853650306747</v>
       </c>
       <c r="K27" t="n">
-        <v>65.01533742331287</v>
+        <v>55.10736196319019</v>
       </c>
       <c r="L27" t="n">
-        <v>13020159.54294479</v>
+        <v>3404912.347648262</v>
       </c>
       <c r="M27" t="n">
-        <v>6765842.061349694</v>
+        <v>1731981.235173824</v>
       </c>
       <c r="N27" t="n">
-        <v>42763.3517382413</v>
+        <v>7689.902862985686</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8377770485520734</v>
+        <v>0.891939654668184</v>
       </c>
       <c r="P27" t="n">
-        <v>0.2266975120570109</v>
+        <v>0.3990305373486411</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.628317394458911e-05</v>
+        <v>0.0001273713235692751</v>
       </c>
       <c r="R27" t="n">
-        <v>0.04527875943323637</v>
+        <v>0.1314967963265297</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0007546459905539396</v>
+        <v>0.002191613272108827</v>
       </c>
       <c r="T27" t="n">
-        <v>4.411164423138952</v>
+        <v>2.50607386252817</v>
       </c>
       <c r="U27" t="n">
-        <v>20798.78655892725</v>
+        <v>17206.48895445329</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Muse Spark 1.2 (xhigh)</t>
+          <t>GPT-5.6 Sol (xhigh)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5888788742875287</v>
+        <v>0.633388342362512</v>
       </c>
       <c r="F28" t="n">
-        <v>0.528023598820059</v>
+        <v>0.669616519174041</v>
       </c>
       <c r="G28" t="n">
         <v>0.797752808988764</v>
       </c>
       <c r="H28" t="n">
-        <v>0.440860215053763</v>
+        <v>0.432795698924731</v>
       </c>
       <c r="I28" t="n">
-        <v>1.914379785695295</v>
+        <v>3.736677527198365</v>
       </c>
       <c r="J28" t="n">
-        <v>1064.740692229038</v>
+        <v>440.5130695296522</v>
       </c>
       <c r="K28" t="n">
-        <v>65.87116564417177</v>
+        <v>93.87525562372188</v>
       </c>
       <c r="L28" t="n">
-        <v>16350688.07453988</v>
+        <v>9886595.803681007</v>
       </c>
       <c r="M28" t="n">
-        <v>8360784.971370144</v>
+        <v>5095034.968302658</v>
       </c>
       <c r="N28" t="n">
-        <v>47157.38036809816</v>
+        <v>25684.60429447853</v>
       </c>
       <c r="O28" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.9080963249335335</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3076081761245981</v>
+        <v>0.1695057541766001</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.601554085081526e-05</v>
+        <v>6.406536232893095e-05</v>
       </c>
       <c r="R28" t="n">
-        <v>0.03318435438330296</v>
+        <v>0.08627054035497261</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0005530725730550494</v>
+        <v>0.001437842339249544</v>
       </c>
       <c r="T28" t="n">
-        <v>3.250888882728999</v>
+        <v>5.89950473868956</v>
       </c>
       <c r="U28" t="n">
-        <v>15356.49777816762</v>
+        <v>22443.36544710738</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.5127556084440553</v>
+        <v>0.6131027159527611</v>
       </c>
       <c r="F29" t="n">
-        <v>0.395280235988201</v>
+        <v>0.519174041297935</v>
       </c>
       <c r="G29" t="n">
-        <v>0.782771535580524</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H29" t="n">
-        <v>0.360215053763441</v>
+        <v>0.481182795698925</v>
       </c>
       <c r="I29" t="n">
-        <v>2.942840985557261</v>
+        <v>3.230610966002044</v>
       </c>
       <c r="J29" t="n">
-        <v>752.2755521472382</v>
+        <v>1792.147180981595</v>
       </c>
       <c r="K29" t="n">
-        <v>54.41308793456033</v>
+        <v>159.5848670756646</v>
       </c>
       <c r="L29" t="n">
-        <v>7582747.093047047</v>
+        <v>12503741.56441719</v>
       </c>
       <c r="M29" t="n">
-        <v>3744700.533231084</v>
+        <v>6469207.32413088</v>
       </c>
       <c r="N29" t="n">
-        <v>25943.59151329243</v>
+        <v>63117.84253578731</v>
       </c>
       <c r="O29" t="n">
-        <v>0.958416873154783</v>
+        <v>0.8998815214008218</v>
       </c>
       <c r="P29" t="n">
-        <v>0.1742382993034736</v>
+        <v>0.1897791849296822</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.762135175446157e-05</v>
+        <v>4.90335403042488e-05</v>
       </c>
       <c r="R29" t="n">
-        <v>0.04089636625679125</v>
+        <v>0.02052630684998603</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0006816061042798542</v>
+        <v>0.0003421051141664338</v>
       </c>
       <c r="T29" t="n">
-        <v>5.739266303663147</v>
+        <v>5.26928177276409</v>
       </c>
       <c r="U29" t="n">
-        <v>10079.74680474918</v>
+        <v>6976.96132165252</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Opus 4.8 (low)</t>
+          <t>GPT-5.6 Luna (low)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.4904379267565557</v>
+        <v>0.250636604330228</v>
       </c>
       <c r="F30" t="n">
-        <v>0.410029498525074</v>
+        <v>0.103244837758112</v>
       </c>
       <c r="G30" t="n">
-        <v>0.779026217228464</v>
+        <v>0.49812734082397</v>
       </c>
       <c r="H30" t="n">
-        <v>0.282258064516129</v>
+        <v>0.150537634408602</v>
       </c>
       <c r="I30" t="n">
-        <v>2.182594679703477</v>
+        <v>0.03893760139059304</v>
       </c>
       <c r="J30" t="n">
-        <v>516.6536431492841</v>
+        <v>100.0260337423312</v>
       </c>
       <c r="K30" t="n">
-        <v>68.16359918200409</v>
+        <v>34.30674846625767</v>
       </c>
       <c r="L30" t="n">
-        <v>5214050.029652352</v>
+        <v>1435665.844580776</v>
       </c>
       <c r="M30" t="n">
-        <v>2595804.632924335</v>
+        <v>762148.6063394684</v>
       </c>
       <c r="N30" t="n">
-        <v>23270.04396728017</v>
+        <v>5609.407975460122</v>
       </c>
       <c r="O30" t="n">
-        <v>0.966158217610491</v>
+        <v>0.8430087375482054</v>
       </c>
       <c r="P30" t="n">
-        <v>0.2247040787358583</v>
+        <v>6.436878374094698</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.406084022351733e-05</v>
+        <v>0.0001745786495348544</v>
       </c>
       <c r="R30" t="n">
-        <v>0.05695551748367481</v>
+        <v>0.1503428227350525</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0009492586247279136</v>
+        <v>0.002505713712250876</v>
       </c>
       <c r="T30" t="n">
-        <v>4.450297500720978</v>
+        <v>0.1553548073899474</v>
       </c>
       <c r="U30" t="n">
-        <v>10091.9641210113</v>
+        <v>14352.92184311813</v>
       </c>
     </row>
     <row r="31">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (none)</t>
+          <t>GPT-5.6 Terra (medium)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2662,201 +2662,201 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.4336881923573268</v>
+        <v>0.4804969202427884</v>
       </c>
       <c r="F31" t="n">
-        <v>0.353982300884956</v>
+        <v>0.457227138643068</v>
       </c>
       <c r="G31" t="n">
-        <v>0.602996254681648</v>
+        <v>0.696629213483146</v>
       </c>
       <c r="H31" t="n">
-        <v>0.344086021505376</v>
+        <v>0.287634408602151</v>
       </c>
       <c r="I31" t="n">
-        <v>1.086854643353786</v>
+        <v>0.6699985707566459</v>
       </c>
       <c r="J31" t="n">
-        <v>197.8853650306747</v>
+        <v>240.094656441718</v>
       </c>
       <c r="K31" t="n">
-        <v>55.10736196319019</v>
+        <v>50.95501022494887</v>
       </c>
       <c r="L31" t="n">
-        <v>3404914.234151331</v>
+        <v>3164606.54805726</v>
       </c>
       <c r="M31" t="n">
-        <v>1731981.235173824</v>
+        <v>1632285.212678937</v>
       </c>
       <c r="N31" t="n">
-        <v>7691.78936605317</v>
+        <v>11855.54703476483</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8919396546681844</v>
+        <v>0.894438452837132</v>
       </c>
       <c r="P31" t="n">
-        <v>0.399030537348641</v>
+        <v>0.7171611122993163</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0001273712529988065</v>
+        <v>0.0001518346476713712</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1314967963265297</v>
+        <v>0.1200768715215685</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002191613272108827</v>
+        <v>0.002001281192026142</v>
       </c>
       <c r="T31" t="n">
-        <v>2.50607386252817</v>
+        <v>1.394386816086365</v>
       </c>
       <c r="U31" t="n">
-        <v>17206.49848776602</v>
+        <v>13180.66213949853</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (xhigh)</t>
+          <t>Fable 5 (medium) (with fallback)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.633388342362512</v>
+        <v>0.6319556485024607</v>
       </c>
       <c r="F32" t="n">
-        <v>0.669616519174041</v>
+        <v>0.63716814159292</v>
       </c>
       <c r="G32" t="n">
-        <v>0.797752808988764</v>
+        <v>0.868913857677903</v>
       </c>
       <c r="H32" t="n">
-        <v>0.432795698924731</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="I32" t="n">
-        <v>3.736677527198365</v>
+        <v>4.735521248977506</v>
       </c>
       <c r="J32" t="n">
-        <v>440.5130695296522</v>
+        <v>661.8129744376279</v>
       </c>
       <c r="K32" t="n">
-        <v>93.87525562372188</v>
+        <v>72.83793456032718</v>
       </c>
       <c r="L32" t="n">
-        <v>9898822.473415133</v>
+        <v>5651155.150306753</v>
       </c>
       <c r="M32" t="n">
-        <v>5095034.968302658</v>
+        <v>2811199.134969325</v>
       </c>
       <c r="N32" t="n">
-        <v>37911.27402862985</v>
+        <v>29358.40797546012</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9080963249335335</v>
+        <v>0.9633202755012389</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1695057541766001</v>
+        <v>0.1334500713388019</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.398623109602961e-05</v>
+        <v>0.0001118276939305333</v>
       </c>
       <c r="R32" t="n">
-        <v>0.08627054035497261</v>
+        <v>0.0572931332184409</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001437842339249544</v>
+        <v>0.0009548855536406817</v>
       </c>
       <c r="T32" t="n">
-        <v>5.89950473868956</v>
+        <v>7.493439231375218</v>
       </c>
       <c r="U32" t="n">
-        <v>22471.12096806657</v>
+        <v>8538.90051809394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>GPT-5.6 Terra (xhigh)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.6131027159527611</v>
+        <v>0.5602917313962744</v>
       </c>
       <c r="F33" t="n">
-        <v>0.519174041297935</v>
+        <v>0.584070796460177</v>
       </c>
       <c r="G33" t="n">
-        <v>0.838951310861423</v>
+        <v>0.771535580524345</v>
       </c>
       <c r="H33" t="n">
-        <v>0.481182795698925</v>
+        <v>0.325268817204301</v>
       </c>
       <c r="I33" t="n">
-        <v>3.230610966002044</v>
+        <v>1.358856920245396</v>
       </c>
       <c r="J33" t="n">
-        <v>1792.147180981595</v>
+        <v>403.2234447852761</v>
       </c>
       <c r="K33" t="n">
-        <v>159.5848670756646</v>
+        <v>74.95092024539876</v>
       </c>
       <c r="L33" t="n">
-        <v>12503741.56441719</v>
+        <v>6631652.208588957</v>
       </c>
       <c r="M33" t="n">
-        <v>6469207.32413088</v>
+        <v>3404439.702453988</v>
       </c>
       <c r="N33" t="n">
-        <v>63117.84253578731</v>
+        <v>26011.59611451943</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8998815214008218</v>
+        <v>0.9104181527286717</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1897791849296822</v>
+        <v>0.4123257740006146</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.90335403042488e-05</v>
+        <v>8.448750232568211e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>0.02052630684998603</v>
+        <v>0.08337189793534551</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0003421051141664338</v>
+        <v>0.001389531632255759</v>
       </c>
       <c r="T33" t="n">
-        <v>5.26928177276409</v>
+        <v>2.425266774612322</v>
       </c>
       <c r="U33" t="n">
-        <v>6976.96132165252</v>
+        <v>16446.59380389063</v>
       </c>
     </row>
     <row r="34">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (low)</t>
+          <t>GPT-5.6 Sol (high)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2881,347 +2881,347 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.250636604330228</v>
+        <v>0.6411644486641199</v>
       </c>
       <c r="F34" t="n">
-        <v>0.103244837758112</v>
+        <v>0.648967551622419</v>
       </c>
       <c r="G34" t="n">
-        <v>0.49812734082397</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H34" t="n">
-        <v>0.150537634408602</v>
+        <v>0.454301075268817</v>
       </c>
       <c r="I34" t="n">
-        <v>0.03893760139059304</v>
+        <v>3.000466998773005</v>
       </c>
       <c r="J34" t="n">
-        <v>100.0260337423312</v>
+        <v>369.9402760736197</v>
       </c>
       <c r="K34" t="n">
-        <v>34.30674846625767</v>
+        <v>84.6717791411043</v>
       </c>
       <c r="L34" t="n">
-        <v>1436684.32822086</v>
+        <v>8030278.504089991</v>
       </c>
       <c r="M34" t="n">
-        <v>762148.6063394684</v>
+        <v>4136516.062372188</v>
       </c>
       <c r="N34" t="n">
-        <v>6627.891615541922</v>
+        <v>19997.77709611452</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8430087375482054</v>
+        <v>0.906019018469944</v>
       </c>
       <c r="P34" t="n">
-        <v>6.436878374094698</v>
+        <v>0.2136882188427049</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0001744548885283712</v>
+        <v>7.984336388053805e-05</v>
       </c>
       <c r="R34" t="n">
-        <v>0.1503428227350525</v>
+        <v>0.1039893988514825</v>
       </c>
       <c r="S34" t="n">
-        <v>0.002505713712250875</v>
+        <v>0.001733156647524709</v>
       </c>
       <c r="T34" t="n">
-        <v>0.1553548073899474</v>
+        <v>4.679715172955305</v>
       </c>
       <c r="U34" t="n">
-        <v>14363.104028715</v>
+        <v>21706.95926737085</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (medium)</t>
+          <t>Opus 4.8 (max)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.4804969202427884</v>
+        <v>0.6214051234130329</v>
       </c>
       <c r="F35" t="n">
-        <v>0.457227138643068</v>
+        <v>0.557522123893805</v>
       </c>
       <c r="G35" t="n">
-        <v>0.696629213483146</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H35" t="n">
-        <v>0.287634408602151</v>
+        <v>0.467741935483871</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6699985707566459</v>
+        <v>7.724725797009217</v>
       </c>
       <c r="J35" t="n">
-        <v>240.094656441718</v>
+        <v>1386.687798057262</v>
       </c>
       <c r="K35" t="n">
-        <v>50.95501022494887</v>
+        <v>165.0175845341703</v>
       </c>
       <c r="L35" t="n">
-        <v>3168659.037832314</v>
+        <v>17920579.42791411</v>
       </c>
       <c r="M35" t="n">
-        <v>1632285.212678937</v>
+        <v>8919829.832822086</v>
       </c>
       <c r="N35" t="n">
-        <v>15908.03680981595</v>
+        <v>89374.98517382414</v>
       </c>
       <c r="O35" t="n">
-        <v>0.894438452837132</v>
+        <v>0.9657541826994763</v>
       </c>
       <c r="P35" t="n">
-        <v>0.7171611122993163</v>
+        <v>0.0804436480649737</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0001516404619449044</v>
+        <v>3.467550398761645e-05</v>
       </c>
       <c r="R35" t="n">
-        <v>0.1200768715215685</v>
+        <v>0.02688731195083492</v>
       </c>
       <c r="S35" t="n">
-        <v>0.002001281192026142</v>
+        <v>0.0004481218658472487</v>
       </c>
       <c r="T35" t="n">
-        <v>1.394386816086365</v>
+        <v>12.43106229086364</v>
       </c>
       <c r="U35" t="n">
-        <v>13197.54085656418</v>
+        <v>12923.29784182185</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (xhigh)</t>
+          <t>Opus 4.8 (medium)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.5602917313962744</v>
+        <v>0.5576883805320431</v>
       </c>
       <c r="F36" t="n">
-        <v>0.584070796460177</v>
+        <v>0.492625368731564</v>
       </c>
       <c r="G36" t="n">
-        <v>0.771535580524345</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H36" t="n">
-        <v>0.325268817204301</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I36" t="n">
-        <v>1.358856920245396</v>
+        <v>3.303841633946831</v>
       </c>
       <c r="J36" t="n">
-        <v>403.2234447852764</v>
+        <v>722.9228824130877</v>
       </c>
       <c r="K36" t="n">
-        <v>74.95092024539876</v>
+        <v>92.91239658858525</v>
       </c>
       <c r="L36" t="n">
-        <v>6645929.991820038</v>
+        <v>7827354.369120649</v>
       </c>
       <c r="M36" t="n">
-        <v>3404439.702453988</v>
+        <v>3898584.399795501</v>
       </c>
       <c r="N36" t="n">
-        <v>40289.37934560327</v>
+        <v>34668.28732106339</v>
       </c>
       <c r="O36" t="n">
-        <v>0.910418152728672</v>
+        <v>0.963840128346697</v>
       </c>
       <c r="P36" t="n">
-        <v>0.4123257740006146</v>
+        <v>0.1687999735828191</v>
       </c>
       <c r="Q36" t="n">
-        <v>8.430599360599558e-05</v>
+        <v>7.124864344102714e-05</v>
       </c>
       <c r="R36" t="n">
-        <v>0.08337189793534545</v>
+        <v>0.04628613043791074</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001389531632255758</v>
+        <v>0.0007714355072985123</v>
       </c>
       <c r="T36" t="n">
-        <v>2.425266774612322</v>
+        <v>5.92417154324592</v>
       </c>
       <c r="U36" t="n">
-        <v>16482.00291369246</v>
+        <v>10827.37116162827</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (high)</t>
+          <t>Opus 5 (none)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.6411644486641199</v>
+        <v>0.591695436371108</v>
       </c>
       <c r="F37" t="n">
-        <v>0.648967551622419</v>
+        <v>0.442477876106195</v>
       </c>
       <c r="G37" t="n">
-        <v>0.820224719101124</v>
+        <v>0.816479400749064</v>
       </c>
       <c r="H37" t="n">
-        <v>0.454301075268817</v>
+        <v>0.5161290322580649</v>
       </c>
       <c r="I37" t="n">
-        <v>3.000466998773005</v>
+        <v>3.53093715925358</v>
       </c>
       <c r="J37" t="n">
-        <v>369.9402760736197</v>
+        <v>708.6105337423306</v>
       </c>
       <c r="K37" t="n">
-        <v>84.6717791411043</v>
+        <v>60.88548057259713</v>
       </c>
       <c r="L37" t="n">
-        <v>8038341.598159516</v>
+        <v>9164445.860940678</v>
       </c>
       <c r="M37" t="n">
-        <v>4136516.062372188</v>
+        <v>4567008.523517382</v>
       </c>
       <c r="N37" t="n">
-        <v>28060.87116564417</v>
+        <v>31222.43967280163</v>
       </c>
       <c r="O37" t="n">
-        <v>0.906019018469944</v>
+        <v>0.9712292805469996</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2136882188427049</v>
+        <v>0.1675746153738372</v>
       </c>
       <c r="Q37" t="n">
-        <v>7.976327465492671e-05</v>
+        <v>6.456423501751952e-05</v>
       </c>
       <c r="R37" t="n">
-        <v>0.1039893988514825</v>
+        <v>0.05010047761324395</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001733156647524709</v>
+        <v>0.0008350079602207325</v>
       </c>
       <c r="T37" t="n">
-        <v>4.679715172955305</v>
+        <v>5.967490945863906</v>
       </c>
       <c r="U37" t="n">
-        <v>21728.75493167403</v>
+        <v>12932.98000036944</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Opus 4.8 (max)</t>
+          <t>GPT-5.6 Sol (low)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.6214051234130329</v>
+        <v>0.5523451808562164</v>
       </c>
       <c r="F38" t="n">
-        <v>0.557522123893805</v>
+        <v>0.533923303834808</v>
       </c>
       <c r="G38" t="n">
-        <v>0.838951310861423</v>
+        <v>0.779026217228465</v>
       </c>
       <c r="H38" t="n">
-        <v>0.467741935483871</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I38" t="n">
-        <v>7.724725797009214</v>
+        <v>1.292458844580775</v>
       </c>
       <c r="J38" t="n">
-        <v>1386.687798057258</v>
+        <v>212.899582822086</v>
       </c>
       <c r="K38" t="n">
-        <v>165.0175845341703</v>
+        <v>53.92126789366053</v>
       </c>
       <c r="L38" t="n">
-        <v>17920579.42791411</v>
+        <v>3200236.065439673</v>
       </c>
       <c r="M38" t="n">
-        <v>8919829.832822086</v>
+        <v>1658130.417177914</v>
       </c>
       <c r="N38" t="n">
-        <v>89374.98517382414</v>
+        <v>8962.606339468302</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9657541826994763</v>
+        <v>0.8829664546361214</v>
       </c>
       <c r="P38" t="n">
-        <v>0.08044364806497373</v>
+        <v>0.4273599760427007</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.467550398761645e-05</v>
+        <v>0.0001725951365966907</v>
       </c>
       <c r="R38" t="n">
-        <v>0.02688731195083498</v>
+        <v>0.1556635781624227</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0004481218658472497</v>
+        <v>0.002594392969373712</v>
       </c>
       <c r="T38" t="n">
-        <v>12.43106229086363</v>
+        <v>2.339947716348811</v>
       </c>
       <c r="U38" t="n">
-        <v>12923.29784182189</v>
+        <v>15031.6690292156</v>
       </c>
     </row>
     <row r="39">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Opus 4.8 (medium)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3246,128 +3246,128 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.5576883805320427</v>
+        <v>0.4238927717743627</v>
       </c>
       <c r="F39" t="n">
-        <v>0.492625368731563</v>
+        <v>0.274336283185841</v>
       </c>
       <c r="G39" t="n">
-        <v>0.820224719101124</v>
+        <v>0.771535580524344</v>
       </c>
       <c r="H39" t="n">
-        <v>0.360215053763441</v>
+        <v>0.225806451612903</v>
       </c>
       <c r="I39" t="n">
-        <v>3.303841633946831</v>
+        <v>1.800661744734149</v>
       </c>
       <c r="J39" t="n">
-        <v>722.9228824130884</v>
+        <v>399.3926789366056</v>
       </c>
       <c r="K39" t="n">
-        <v>92.91239658858525</v>
+        <v>42.04907975460122</v>
       </c>
       <c r="L39" t="n">
-        <v>7827354.369120649</v>
+        <v>4636274.728016362</v>
       </c>
       <c r="M39" t="n">
-        <v>3898584.399795501</v>
+        <v>2310268.645194274</v>
       </c>
       <c r="N39" t="n">
-        <v>34668.28732106339</v>
+        <v>17168.18507157464</v>
       </c>
       <c r="O39" t="n">
-        <v>0.963840128346697</v>
+        <v>0.9576237577125707</v>
       </c>
       <c r="P39" t="n">
-        <v>0.168799973582819</v>
+        <v>0.2354094393430603</v>
       </c>
       <c r="Q39" t="n">
-        <v>7.12486434410271e-05</v>
+        <v>9.142960601813301e-05</v>
       </c>
       <c r="R39" t="n">
-        <v>0.04628613043791067</v>
+        <v>0.06368060219375918</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0007714355072985111</v>
+        <v>0.001061343369895986</v>
       </c>
       <c r="T39" t="n">
-        <v>5.924171543245923</v>
+        <v>4.247918022279082</v>
       </c>
       <c r="U39" t="n">
-        <v>10827.37116162826</v>
+        <v>11608.31175063242</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (low)</t>
+          <t>Fable 5 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.5523451808562164</v>
+        <v>0.6717276042685724</v>
       </c>
       <c r="F40" t="n">
-        <v>0.533923303834808</v>
+        <v>0.660766961651917</v>
       </c>
       <c r="G40" t="n">
-        <v>0.779026217228465</v>
+        <v>0.865168539325843</v>
       </c>
       <c r="H40" t="n">
-        <v>0.344086021505376</v>
+        <v>0.489247311827957</v>
       </c>
       <c r="I40" t="n">
-        <v>1.292458844580775</v>
+        <v>11.68740762091003</v>
       </c>
       <c r="J40" t="n">
-        <v>212.899582822086</v>
+        <v>1407.30630163599</v>
       </c>
       <c r="K40" t="n">
-        <v>53.92126789366053</v>
+        <v>137.007744236847</v>
       </c>
       <c r="L40" t="n">
-        <v>3201864.840490799</v>
+        <v>13868659.99897749</v>
       </c>
       <c r="M40" t="n">
-        <v>1658130.417177914</v>
+        <v>6901095.023517382</v>
       </c>
       <c r="N40" t="n">
-        <v>10591.38139059305</v>
+        <v>74265.48875255625</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8829664546361214</v>
+        <v>0.9619283373252908</v>
       </c>
       <c r="P40" t="n">
-        <v>0.4273599760427007</v>
+        <v>0.05747447390016411</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0001725073381834412</v>
+        <v>4.843493202069251e-05</v>
       </c>
       <c r="R40" t="n">
-        <v>0.1556635781624227</v>
+        <v>0.02863886576025522</v>
       </c>
       <c r="S40" t="n">
-        <v>0.002594392969373712</v>
+        <v>0.0004773144293375869</v>
       </c>
       <c r="T40" t="n">
-        <v>2.339947716348811</v>
+        <v>17.39902833624971</v>
       </c>
       <c r="U40" t="n">
-        <v>15039.31946718047</v>
+        <v>9854.75584302807</v>
       </c>
     </row>
     <row r="41">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>GLM-5.1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3388,278 +3388,278 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>friendliai</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.423892771774363</v>
+        <v>0.3691032797641257</v>
       </c>
       <c r="F41" t="n">
-        <v>0.274336283185841</v>
+        <v>0.185840707964602</v>
       </c>
       <c r="G41" t="n">
-        <v>0.771535580524345</v>
+        <v>0.6741573033707861</v>
       </c>
       <c r="H41" t="n">
-        <v>0.225806451612903</v>
+        <v>0.247311827956989</v>
       </c>
       <c r="I41" t="n">
-        <v>1.800661744734152</v>
+        <v>4.282000252842536</v>
       </c>
       <c r="J41" t="n">
-        <v>399.3926789366056</v>
+        <v>1140.250613496931</v>
       </c>
       <c r="K41" t="n">
-        <v>42.04907975460122</v>
+        <v>174.2367075664622</v>
       </c>
       <c r="L41" t="n">
-        <v>4636274.728016362</v>
+        <v>25761884.92944783</v>
       </c>
       <c r="M41" t="n">
-        <v>2310268.645194274</v>
+        <v>13139446.7402863</v>
       </c>
       <c r="N41" t="n">
-        <v>17168.18507157464</v>
+        <v>49883.45705521473</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9576237577125704</v>
+        <v>0.8889225409991813</v>
       </c>
       <c r="P41" t="n">
-        <v>0.23540943934306</v>
+        <v>0.08619879915212579</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.142960601813308e-05</v>
+        <v>1.432749508721747e-05</v>
       </c>
       <c r="R41" t="n">
-        <v>0.06368060219375923</v>
+        <v>0.01942221869798375</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001061343369895987</v>
+        <v>0.0003237036449663959</v>
       </c>
       <c r="T41" t="n">
-        <v>4.247918022279086</v>
+        <v>11.60108968844421</v>
       </c>
       <c r="U41" t="n">
-        <v>11608.31175063242</v>
+        <v>22593.17787204784</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GLM-5.1</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>friendliai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.3691032797641257</v>
+        <v>0.5657152973570364</v>
       </c>
       <c r="F42" t="n">
-        <v>0.185840707964602</v>
+        <v>0.56047197640118</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6741573033707861</v>
+        <v>0.865168539325843</v>
       </c>
       <c r="H42" t="n">
-        <v>0.247311827956989</v>
+        <v>0.271505376344086</v>
       </c>
       <c r="I42" t="n">
-        <v>4.282000252842536</v>
+        <v>1.396316917192255</v>
       </c>
       <c r="J42" t="n">
-        <v>1140.250613496931</v>
+        <v>384.9621257668713</v>
       </c>
       <c r="K42" t="n">
-        <v>174.2367075664622</v>
+        <v>110.7985685071575</v>
       </c>
       <c r="L42" t="n">
-        <v>25761884.92944787</v>
+        <v>15113684.86595342</v>
       </c>
       <c r="M42" t="n">
-        <v>13139446.7402863</v>
+        <v>7938344.274012004</v>
       </c>
       <c r="N42" t="n">
-        <v>49883.45705521473</v>
+        <v>64430.0844098625</v>
       </c>
       <c r="O42" t="n">
-        <v>0.888922540999181</v>
+        <v>0.8677594149804605</v>
       </c>
       <c r="P42" t="n">
-        <v>0.08619879915212579</v>
+        <v>0.4051482083985556</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.432749508721745e-05</v>
+        <v>3.743066647045306e-05</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01942221869798375</v>
+        <v>0.08817209686227062</v>
       </c>
       <c r="S42" t="n">
-        <v>0.0003237036449663959</v>
+        <v>0.00146953494770451</v>
       </c>
       <c r="T42" t="n">
-        <v>11.60108968844421</v>
+        <v>2.468232560999683</v>
       </c>
       <c r="U42" t="n">
-        <v>22593.17787204787</v>
+        <v>39260.1865335347</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.8</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.5657152973570364</v>
+        <v>0.6702814566291138</v>
       </c>
       <c r="F43" t="n">
-        <v>0.56047197640118</v>
+        <v>0.631268436578171</v>
       </c>
       <c r="G43" t="n">
-        <v>0.865168539325843</v>
+        <v>0.887640449438202</v>
       </c>
       <c r="H43" t="n">
-        <v>0.271505376344086</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I43" t="n">
-        <v>1.396316917192254</v>
+        <v>8.943547018021487</v>
       </c>
       <c r="J43" t="n">
-        <v>384.9621257668713</v>
+        <v>1451.329194274025</v>
       </c>
       <c r="K43" t="n">
-        <v>110.7985685071575</v>
+        <v>165.7202546941811</v>
       </c>
       <c r="L43" t="n">
-        <v>15113684.86595342</v>
+        <v>23699428.05214722</v>
       </c>
       <c r="M43" t="n">
-        <v>7938344.274012004</v>
+        <v>11810977.87014315</v>
       </c>
       <c r="N43" t="n">
-        <v>64430.0844098625</v>
+        <v>81385.06339468302</v>
       </c>
       <c r="O43" t="n">
-        <v>0.8677594149804605</v>
+        <v>0.9747033593278783</v>
       </c>
       <c r="P43" t="n">
-        <v>0.4051482083985558</v>
+        <v>0.07494581906691815</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.743066647045306e-05</v>
+        <v>2.82826005401588e-05</v>
       </c>
       <c r="R43" t="n">
-        <v>0.08817209686227062</v>
+        <v>0.02771038270050364</v>
       </c>
       <c r="S43" t="n">
-        <v>0.00146953494770451</v>
+        <v>0.0004618397116750606</v>
       </c>
       <c r="T43" t="n">
-        <v>2.468232560999682</v>
+        <v>13.34297246264148</v>
       </c>
       <c r="U43" t="n">
-        <v>39260.1865335347</v>
+        <v>16329.4641530325</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-5.6 Luna (medium)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.6702814566291138</v>
+        <v>0.4196699779001627</v>
       </c>
       <c r="F44" t="n">
-        <v>0.631268436578171</v>
+        <v>0.365781710914454</v>
       </c>
       <c r="G44" t="n">
-        <v>0.887640449438202</v>
+        <v>0.621722846441948</v>
       </c>
       <c r="H44" t="n">
-        <v>0.491935483870968</v>
+        <v>0.271505376344086</v>
       </c>
       <c r="I44" t="n">
-        <v>8.943547018021487</v>
+        <v>0.08841796668711666</v>
       </c>
       <c r="J44" t="n">
-        <v>1451.329194274025</v>
+        <v>191.3819171779141</v>
       </c>
       <c r="K44" t="n">
-        <v>165.7202546941811</v>
+        <v>57.08588957055215</v>
       </c>
       <c r="L44" t="n">
-        <v>23699428.05214722</v>
+        <v>4287327.734151328</v>
       </c>
       <c r="M44" t="n">
-        <v>11810977.87014315</v>
+        <v>2221162.702453987</v>
       </c>
       <c r="N44" t="n">
-        <v>81385.06339468302</v>
+        <v>11663.1390593047</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9747033593278787</v>
+        <v>0.8832984632099318</v>
       </c>
       <c r="P44" t="n">
-        <v>0.07494581906691815</v>
+        <v>4.746433260394266</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.82826005401588e-05</v>
+        <v>9.788614351947506e-05</v>
       </c>
       <c r="R44" t="n">
-        <v>0.02771038270050364</v>
+        <v>0.1315704171288112</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0004618397116750606</v>
+        <v>0.002192840285480187</v>
       </c>
       <c r="T44" t="n">
-        <v>13.34297246264148</v>
+        <v>0.2106845172235571</v>
       </c>
       <c r="U44" t="n">
-        <v>16329.4641530325</v>
+        <v>22401.94788186653</v>
       </c>
     </row>
     <row r="45">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (medium)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3684,55 +3684,55 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.4196699779001624</v>
+        <v>0.6505240024334414</v>
       </c>
       <c r="F45" t="n">
-        <v>0.365781710914454</v>
+        <v>0.687315634218289</v>
       </c>
       <c r="G45" t="n">
-        <v>0.621722846441947</v>
+        <v>0.831460674157304</v>
       </c>
       <c r="H45" t="n">
-        <v>0.271505376344086</v>
+        <v>0.432795698924731</v>
       </c>
       <c r="I45" t="n">
-        <v>0.08841796668711666</v>
+        <v>4.995463274846626</v>
       </c>
       <c r="J45" t="n">
-        <v>191.3819171779141</v>
+        <v>613.70177198364</v>
       </c>
       <c r="K45" t="n">
-        <v>57.08588957055215</v>
+        <v>112.2689161554192</v>
       </c>
       <c r="L45" t="n">
-        <v>4290985.346625767</v>
+        <v>13169248.79601226</v>
       </c>
       <c r="M45" t="n">
-        <v>2221162.702453987</v>
+        <v>6786107.398261759</v>
       </c>
       <c r="N45" t="n">
-        <v>15320.75153374233</v>
+        <v>35184.01329243354</v>
       </c>
       <c r="O45" t="n">
-        <v>0.8832984632099327</v>
+        <v>0.902597320865973</v>
       </c>
       <c r="P45" t="n">
-        <v>4.746433260394262</v>
+        <v>0.1302229576401829</v>
       </c>
       <c r="Q45" t="n">
-        <v>9.780270590533979e-05</v>
+        <v>4.939719892226689e-05</v>
       </c>
       <c r="R45" t="n">
-        <v>0.1315704171288111</v>
+        <v>0.06360001213593852</v>
       </c>
       <c r="S45" t="n">
-        <v>0.002192840285480186</v>
+        <v>0.001060000202265642</v>
       </c>
       <c r="T45" t="n">
-        <v>0.2106845172235573</v>
+        <v>7.679137520152823</v>
       </c>
       <c r="U45" t="n">
-        <v>22421.05947050757</v>
+        <v>21458.71072434076</v>
       </c>
     </row>
     <row r="46">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Opus 4.7 (max)</t>
+          <t>Kimi K2.6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3753,789 +3753,789 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.5158095272716129</v>
+        <v>0.3388925953605663</v>
       </c>
       <c r="F46" t="n">
-        <v>0.40117994100295</v>
+        <v>0.165191740412979</v>
       </c>
       <c r="G46" t="n">
-        <v>0.7752808988764049</v>
+        <v>0.6928838951310859</v>
       </c>
       <c r="H46" t="n">
-        <v>0.370967741935484</v>
+        <v>0.158602150537634</v>
       </c>
       <c r="I46" t="n">
-        <v>5.915424259100206</v>
+        <v>1.21710007411043</v>
       </c>
       <c r="J46" t="n">
-        <v>950.3123588957067</v>
+        <v>2443.385067484662</v>
       </c>
       <c r="K46" t="n">
-        <v>107.999326082915</v>
+        <v>133.7675410760877</v>
       </c>
       <c r="L46" t="n">
-        <v>16129723.11451944</v>
+        <v>11660527.81595092</v>
       </c>
       <c r="M46" t="n">
-        <v>8042457.98977505</v>
+        <v>5891966.377300614</v>
       </c>
       <c r="N46" t="n">
-        <v>47224.16462167689</v>
+        <v>36930.17791411043</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9665216325317721</v>
+        <v>0.9554328157869918</v>
       </c>
       <c r="P46" t="n">
-        <v>0.08719738512044993</v>
+        <v>0.2784426708775453</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.197882093879828e-05</v>
+        <v>2.906322944463811e-05</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03256673592276544</v>
+        <v>0.008321879343629747</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0005427789320460906</v>
+        <v>0.0001386979890604958</v>
       </c>
       <c r="T46" t="n">
-        <v>11.46823380791353</v>
+        <v>3.591403561991346</v>
       </c>
       <c r="U46" t="n">
-        <v>16973.07518263015</v>
+        <v>4772.284144289555</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kimi K2.6</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.3388925953605663</v>
+        <v>0.5716614223656344</v>
       </c>
       <c r="F47" t="n">
-        <v>0.165191740412979</v>
+        <v>0.634218289085546</v>
       </c>
       <c r="G47" t="n">
-        <v>0.6928838951310859</v>
+        <v>0.752808988764045</v>
       </c>
       <c r="H47" t="n">
-        <v>0.158602150537634</v>
+        <v>0.327956989247312</v>
       </c>
       <c r="I47" t="n">
-        <v>1.21710007411043</v>
+        <v>0.2882767483844579</v>
       </c>
       <c r="J47" t="n">
-        <v>2443.385067484662</v>
+        <v>482.0907147239265</v>
       </c>
       <c r="K47" t="n">
-        <v>133.7675410760877</v>
+        <v>114.6288343558282</v>
       </c>
       <c r="L47" t="n">
-        <v>11660527.81595092</v>
+        <v>15963259.28016359</v>
       </c>
       <c r="M47" t="n">
-        <v>5891966.377300614</v>
+        <v>8170928.992842535</v>
       </c>
       <c r="N47" t="n">
-        <v>36930.17791411043</v>
+        <v>41094.49386503067</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9554328157869918</v>
+        <v>0.9181831202060824</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2784426708775453</v>
+        <v>1.983029937618288</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.906322944463811e-05</v>
+        <v>3.58110716823348e-05</v>
       </c>
       <c r="R47" t="n">
-        <v>0.008321879343629747</v>
+        <v>0.0711477825528751</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0001386979890604958</v>
+        <v>0.001185796375881252</v>
       </c>
       <c r="T47" t="n">
-        <v>3.591403561991346</v>
+        <v>0.5042788215295665</v>
       </c>
       <c r="U47" t="n">
-        <v>4772.284144289555</v>
+        <v>33112.56324300934</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Opus 5 (medium)</t>
+          <t>GPT-5.6 Luna (xhigh)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.6406847456950576</v>
+        <v>0.529584326329171</v>
       </c>
       <c r="F48" t="n">
-        <v>0.628318584070796</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G48" t="n">
-        <v>0.850187265917603</v>
+        <v>0.707865168539326</v>
       </c>
       <c r="H48" t="n">
-        <v>0.443548387096774</v>
+        <v>0.314516129032258</v>
       </c>
       <c r="I48" t="n">
-        <v>3.171867192484664</v>
+        <v>0.235909783783231</v>
       </c>
       <c r="J48" t="n">
-        <v>730.9243895705522</v>
+        <v>413.8987709611455</v>
       </c>
       <c r="K48" t="n">
-        <v>83.47801635991821</v>
+        <v>96.1922290388548</v>
       </c>
       <c r="L48" t="n">
-        <v>7999358.108384448</v>
+        <v>12806609.00511247</v>
       </c>
       <c r="M48" t="n">
-        <v>3984815.59611452</v>
+        <v>6575104.906952964</v>
       </c>
       <c r="N48" t="n">
-        <v>30206.12781186094</v>
+        <v>30840.24642126789</v>
       </c>
       <c r="O48" t="n">
-        <v>0.9695331242878964</v>
+        <v>0.9100235393369858</v>
       </c>
       <c r="P48" t="n">
-        <v>0.2019897766252883</v>
+        <v>2.244859529928555</v>
       </c>
       <c r="Q48" t="n">
-        <v>8.009201951135682e-05</v>
+        <v>4.135242405837159e-05</v>
       </c>
       <c r="R48" t="n">
-        <v>0.05259242308809692</v>
+        <v>0.07677012305681169</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008765403848016154</v>
+        <v>0.001279502050946862</v>
       </c>
       <c r="T48" t="n">
-        <v>4.950745610532073</v>
+        <v>0.4454621710926501</v>
       </c>
       <c r="U48" t="n">
-        <v>10944.16634952405</v>
+        <v>30941.40380115958</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Muse Spark 1.2 (xhigh)</t>
+          <t>GPT-5.6 Terra (max)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6164044159758908</v>
+        <v>0.6042010361726687</v>
       </c>
       <c r="F49" t="n">
-        <v>0.581120943952802</v>
+        <v>0.669616519174041</v>
       </c>
       <c r="G49" t="n">
-        <v>0.816479400749064</v>
+        <v>0.782771535580524</v>
       </c>
       <c r="H49" t="n">
-        <v>0.451612903225806</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I49" t="n">
-        <v>2.072823051942737</v>
+        <v>1.930014663190181</v>
       </c>
       <c r="J49" t="n">
-        <v>2448.643313905933</v>
+        <v>491.0206543967283</v>
       </c>
       <c r="K49" t="n">
-        <v>151.4345603271984</v>
+        <v>95.80674846625767</v>
       </c>
       <c r="L49" t="n">
-        <v>19963139.08486708</v>
+        <v>9630511.582822077</v>
       </c>
       <c r="M49" t="n">
-        <v>10093761.29754601</v>
+        <v>4933733.868098159</v>
       </c>
       <c r="N49" t="n">
-        <v>58305.98057259714</v>
+        <v>37445.42126789366</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9538301727874863</v>
+        <v>0.9184675548550253</v>
       </c>
       <c r="P49" t="n">
-        <v>0.2973743539749669</v>
+        <v>0.313055153256694</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.087712875993296e-05</v>
+        <v>6.273820772412349e-05</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01510398217189024</v>
+        <v>0.07383001477789093</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0002517330361981707</v>
+        <v>0.001230500246298182</v>
       </c>
       <c r="T49" t="n">
-        <v>3.362764766474046</v>
+        <v>3.194325311680897</v>
       </c>
       <c r="U49" t="n">
-        <v>8152.734606749663</v>
+        <v>19613.25149275889</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Composer 2.5 Fast</t>
+          <t>DeepSeek V4 Pro (high)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.3830075380367747</v>
+        <v>0.3282816619106221</v>
       </c>
       <c r="F50" t="n">
-        <v>0.15929203539823</v>
+        <v>0.08554572271386431</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6779026217228465</v>
+        <v>0.700374531835206</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3118279569892475</v>
+        <v>0.198924731182796</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5573437730061347</v>
+        <v>0.2547256318476481</v>
       </c>
       <c r="J50" t="n">
-        <v>472.3722024539875</v>
+        <v>1072.531835378324</v>
       </c>
       <c r="K50" t="n">
-        <v>116.8680981595092</v>
+        <v>128.1457055214724</v>
       </c>
       <c r="L50" t="n">
-        <v>4259887.413087934</v>
+        <v>9942165.528629858</v>
       </c>
       <c r="M50" t="n">
-        <v>2153033.982617587</v>
+        <v>5181244.880368099</v>
       </c>
       <c r="N50" t="n">
-        <v>20146.14621676892</v>
+        <v>41975.79754601227</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9355410155352533</v>
+        <v>0.8541357545221669</v>
       </c>
       <c r="P50" t="n">
-        <v>0.6872016098268293</v>
+        <v>1.288765718351297</v>
       </c>
       <c r="Q50" t="n">
-        <v>8.991024900330353e-05</v>
+        <v>3.301913058732417e-05</v>
       </c>
       <c r="R50" t="n">
-        <v>0.04864903599920222</v>
+        <v>0.01836486252894252</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008108172666533704</v>
+        <v>0.000306081042149042</v>
       </c>
       <c r="T50" t="n">
-        <v>1.455177033493845</v>
+        <v>0.77593622002864</v>
       </c>
       <c r="U50" t="n">
-        <v>9018.073864121752</v>
+        <v>9269.809250112252</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Opus 5 (high)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.6263880112748017</v>
+        <v>0.6561729860226817</v>
       </c>
       <c r="F51" t="n">
-        <v>0.63716814159292</v>
+        <v>0.6076696165191739</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8764044943820229</v>
+        <v>0.868913857677903</v>
       </c>
       <c r="H51" t="n">
-        <v>0.365591397849462</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I51" t="n">
-        <v>3.081635541610427</v>
+        <v>3.918602446063396</v>
       </c>
       <c r="J51" t="n">
-        <v>1447.373053169734</v>
+        <v>842.8052382413097</v>
       </c>
       <c r="K51" t="n">
-        <v>122.9498977505112</v>
+        <v>94.85071574642126</v>
       </c>
       <c r="L51" t="n">
-        <v>10383196.73788345</v>
+        <v>9911366.349693259</v>
       </c>
       <c r="M51" t="n">
-        <v>5296768.575664621</v>
+        <v>4937399.112474437</v>
       </c>
       <c r="N51" t="n">
-        <v>54498.01533742331</v>
+        <v>37331.49386503067</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.9702723303233399</v>
       </c>
       <c r="P51" t="n">
-        <v>0.203264793262171</v>
+        <v>0.1674507672197952</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.032708683920082e-05</v>
+        <v>6.620408961504982e-05</v>
       </c>
       <c r="R51" t="n">
-        <v>0.02596654718296782</v>
+        <v>0.04671349604271027</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0004327757863827971</v>
+        <v>0.0007785582673785045</v>
       </c>
       <c r="T51" t="n">
-        <v>4.919691127770464</v>
+        <v>5.971904557997063</v>
       </c>
       <c r="U51" t="n">
-        <v>7173.822060003357</v>
+        <v>11759.97241115327</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>Composer 2.5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.5962784529614886</v>
+        <v>0.3830075380367747</v>
       </c>
       <c r="F52" t="n">
-        <v>0.572271386430678</v>
+        <v>0.15929203539823</v>
       </c>
       <c r="G52" t="n">
-        <v>0.910112359550562</v>
+        <v>0.6779026217228465</v>
       </c>
       <c r="H52" t="n">
-        <v>0.306451612903226</v>
+        <v>0.3118279569892475</v>
       </c>
       <c r="I52" t="n">
-        <v>1.26793256886503</v>
+        <v>0.08505141359918204</v>
       </c>
       <c r="J52" t="n">
-        <v>527.0915644171779</v>
+        <v>625.1976421267894</v>
       </c>
       <c r="K52" t="n">
-        <v>83.44887525562373</v>
+        <v>116.8680981595092</v>
       </c>
       <c r="L52" t="n">
-        <v>18493123.37423313</v>
+        <v>3705076.4698364</v>
       </c>
       <c r="M52" t="n">
-        <v>9497213.109406954</v>
+        <v>1872461.576687117</v>
       </c>
       <c r="N52" t="n">
-        <v>49098.7944785276</v>
+        <v>18453.85787321063</v>
       </c>
       <c r="O52" t="n">
-        <v>0.8634331167917663</v>
+        <v>1.052833075750478</v>
       </c>
       <c r="P52" t="n">
-        <v>0.4702761547447575</v>
+        <v>4.503247175194018</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.224325285107308e-05</v>
+        <v>0.0001033737201255894</v>
       </c>
       <c r="R52" t="n">
-        <v>0.06787569673449199</v>
+        <v>0.03675710004924502</v>
       </c>
       <c r="S52" t="n">
-        <v>0.001131261612241533</v>
+        <v>0.0006126183341540836</v>
       </c>
       <c r="T52" t="n">
-        <v>2.126410173917388</v>
+        <v>0.2220619835190183</v>
       </c>
       <c r="U52" t="n">
-        <v>35085.21976571864</v>
+        <v>5926.248309626565</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Gemini CLI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GLM-5.2</t>
+          <t>Gemini 3.1 Pro (high)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>novita</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.433101571936022</v>
+        <v>0.3293046837328304</v>
       </c>
       <c r="F53" t="n">
-        <v>0.286135693215339</v>
+        <v>0.141592920353982</v>
       </c>
       <c r="G53" t="n">
-        <v>0.722846441947566</v>
+        <v>0.760299625468165</v>
       </c>
       <c r="H53" t="n">
-        <v>0.290322580645161</v>
+        <v>0.08602150537634411</v>
       </c>
       <c r="I53" t="n">
-        <v>6.657531358159519</v>
+        <v>1.040041561860939</v>
       </c>
       <c r="J53" t="n">
-        <v>1507.044470347651</v>
+        <v>663.8363599182014</v>
       </c>
       <c r="K53" t="n">
-        <v>127.4036879531512</v>
+        <v>30.96883483789777</v>
       </c>
       <c r="L53" t="n">
-        <v>6619529.539877302</v>
+        <v>4727804.222392637</v>
       </c>
       <c r="M53" t="n">
-        <v>5529735.922290388</v>
+        <v>2465901.789877301</v>
       </c>
       <c r="N53" t="n">
-        <v>28567.83231083845</v>
+        <v>12977.50562372188</v>
       </c>
       <c r="O53" t="n">
-        <v>0.3295602231414034</v>
+        <v>0.8650361016121304</v>
       </c>
       <c r="P53" t="n">
-        <v>0.06505437956446267</v>
+        <v>0.316626465526635</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.542784790473944e-05</v>
+        <v>6.965277499713736e-05</v>
       </c>
       <c r="R53" t="n">
-        <v>0.01724308394838989</v>
+        <v>0.02976378248760652</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0002873847324731648</v>
+        <v>0.0004960630414601087</v>
       </c>
       <c r="T53" t="n">
-        <v>15.37175524069207</v>
+        <v>3.158295685538259</v>
       </c>
       <c r="U53" t="n">
-        <v>4392.391644786887</v>
+        <v>7121.942255430543</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Fable 5 (high) (with fallback)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.4975760031619054</v>
+        <v>0.6512694843692031</v>
       </c>
       <c r="F54" t="n">
-        <v>0.427728613569322</v>
+        <v>0.64306784660767</v>
       </c>
       <c r="G54" t="n">
-        <v>0.677902621722846</v>
+        <v>0.891385767790262</v>
       </c>
       <c r="H54" t="n">
-        <v>0.387096774193548</v>
+        <v>0.419354838709677</v>
       </c>
       <c r="I54" t="n">
-        <v>0.05949917044417178</v>
+        <v>5.970994269427395</v>
       </c>
       <c r="J54" t="n">
-        <v>868.3750143149272</v>
+        <v>731.3774856850721</v>
       </c>
       <c r="K54" t="n">
-        <v>105.9314928425358</v>
+        <v>85.64621676891616</v>
       </c>
       <c r="L54" t="n">
-        <v>20844227.99386505</v>
+        <v>7097848.362985685</v>
       </c>
       <c r="M54" t="n">
-        <v>10443571.69734151</v>
+        <v>3530817.211656442</v>
       </c>
       <c r="N54" t="n">
-        <v>58411.25766871166</v>
+        <v>37468.96625766872</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9807621661364226</v>
+        <v>0.9637766239989285</v>
       </c>
       <c r="P54" t="n">
-        <v>8.362738496140583</v>
+        <v>0.1090722005384973</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.387116487635588e-05</v>
+        <v>9.175590278393167e-05</v>
       </c>
       <c r="R54" t="n">
-        <v>0.03437980100483083</v>
+        <v>0.05342818151634792</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0005729966834138472</v>
+        <v>0.000890469691939132</v>
       </c>
       <c r="T54" t="n">
-        <v>0.1195780545405672</v>
+        <v>9.168238974394281</v>
       </c>
       <c r="U54" t="n">
-        <v>24003.71688527835</v>
+        <v>9704.767376503558</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Opus 5 (xhigh)</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.6814975428587517</v>
+        <v>0.4277969516408803</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6047197640117991</v>
+        <v>0.162241887905605</v>
       </c>
       <c r="G55" t="n">
-        <v>0.891385767790262</v>
+        <v>0.629213483146068</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5483870967741939</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I55" t="n">
-        <v>8.170783921523505</v>
+        <v>0.09081146755368105</v>
       </c>
       <c r="J55" t="n">
-        <v>1421.879982617589</v>
+        <v>743.5829417177918</v>
       </c>
       <c r="K55" t="n">
-        <v>152.0771983640082</v>
+        <v>66.08691206543966</v>
       </c>
       <c r="L55" t="n">
-        <v>21565879.13803681</v>
+        <v>12713750.95194277</v>
       </c>
       <c r="M55" t="n">
-        <v>10747525.6196319</v>
+        <v>6378205.537321064</v>
       </c>
       <c r="N55" t="n">
-        <v>73273.02862985685</v>
+        <v>37873.7581799591</v>
       </c>
       <c r="O55" t="n">
-        <v>0.9740249879523308</v>
+        <v>0.9780317126088944</v>
       </c>
       <c r="P55" t="n">
-        <v>0.08340662896047817</v>
+        <v>4.710825220261948</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.160073088125403e-05</v>
+        <v>3.364836650158773e-05</v>
       </c>
       <c r="R55" t="n">
-        <v>0.02875759773778482</v>
+        <v>0.03451910426986959</v>
       </c>
       <c r="S55" t="n">
-        <v>0.000479293295629747</v>
+        <v>0.0005753184044978266</v>
       </c>
       <c r="T55" t="n">
-        <v>11.98945470477946</v>
+        <v>0.2122770328431744</v>
       </c>
       <c r="U55" t="n">
-        <v>15167.15855183179</v>
+        <v>17097.95940527097</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Grok 4.5 (high)</t>
+          <t>GPT-5.6 Terra (high)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.6408998279698193</v>
+        <v>0.5464647209828707</v>
       </c>
       <c r="F56" t="n">
-        <v>0.59882005899705</v>
+        <v>0.6047197640117991</v>
       </c>
       <c r="G56" t="n">
-        <v>0.842696629213483</v>
+        <v>0.722846441947566</v>
       </c>
       <c r="H56" t="n">
-        <v>0.481182795698925</v>
+        <v>0.311827956989247</v>
       </c>
       <c r="I56" t="n">
-        <v>2.438982443762781</v>
+        <v>1.140926299999998</v>
       </c>
       <c r="J56" t="n">
-        <v>929.1851094069543</v>
+        <v>358.7396482617588</v>
       </c>
       <c r="K56" t="n">
-        <v>60.74437627811862</v>
+        <v>67.06952965235175</v>
       </c>
       <c r="L56" t="n">
-        <v>3598867.582822083</v>
+        <v>5600275.774028629</v>
       </c>
       <c r="M56" t="n">
-        <v>1837535.160531697</v>
+        <v>2877096.291411043</v>
       </c>
       <c r="N56" t="n">
-        <v>25699.40797546012</v>
+        <v>20902.66564417178</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9238990226060741</v>
+        <v>0.9049339862289006</v>
       </c>
       <c r="P56" t="n">
-        <v>0.2627734486604423</v>
+        <v>0.478965837655659</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.0001780837480736794</v>
+        <v>9.757818061694565e-05</v>
       </c>
       <c r="R56" t="n">
-        <v>0.04138463831252326</v>
+        <v>0.09139743381542303</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0006897439718753876</v>
+        <v>0.001523290563590384</v>
       </c>
       <c r="T56" t="n">
-        <v>3.805559523223395</v>
+        <v>2.087831576662313</v>
       </c>
       <c r="U56" t="n">
-        <v>3873.143840110648</v>
+        <v>15610.97526065008</v>
       </c>
     </row>
     <row r="57">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fable 5 (max) (with fallback)</t>
+          <t>Opus 4.7 (max)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4560,128 +4560,931 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.6717276042685724</v>
+        <v>0.5158095272716129</v>
       </c>
       <c r="F57" t="n">
-        <v>0.660766961651917</v>
+        <v>0.40117994100295</v>
       </c>
       <c r="G57" t="n">
-        <v>0.865168539325843</v>
+        <v>0.7752808988764049</v>
       </c>
       <c r="H57" t="n">
-        <v>0.489247311827957</v>
+        <v>0.370967741935484</v>
       </c>
       <c r="I57" t="n">
-        <v>11.68740762091003</v>
+        <v>5.915424259100206</v>
       </c>
       <c r="J57" t="n">
-        <v>1407.30630163599</v>
+        <v>950.312358895707</v>
       </c>
       <c r="K57" t="n">
-        <v>137.007744236847</v>
+        <v>107.999326082915</v>
       </c>
       <c r="L57" t="n">
-        <v>13868659.99897749</v>
+        <v>16129723.11451944</v>
       </c>
       <c r="M57" t="n">
-        <v>6901095.023517382</v>
+        <v>8042457.98977505</v>
       </c>
       <c r="N57" t="n">
-        <v>74265.48875255625</v>
+        <v>47224.16462167689</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9619283373252909</v>
+        <v>0.9665216325317721</v>
       </c>
       <c r="P57" t="n">
-        <v>0.05747447390016408</v>
+        <v>0.08719738512044993</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.843493202069251e-05</v>
+        <v>3.197882093879829e-05</v>
       </c>
       <c r="R57" t="n">
-        <v>0.02863886576025522</v>
+        <v>0.03256673592276543</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0004773144293375869</v>
+        <v>0.0005427789320460904</v>
       </c>
       <c r="T57" t="n">
-        <v>17.39902833624972</v>
+        <v>11.46823380791353</v>
       </c>
       <c r="U57" t="n">
-        <v>9854.75584302807</v>
+        <v>16973.07518263015</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Opus 5 (medium)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.640684745695058</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.628318584070797</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.850187265917603</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.443548387096774</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3.171867192484664</v>
+      </c>
+      <c r="J58" t="n">
+        <v>730.9243895705519</v>
+      </c>
+      <c r="K58" t="n">
+        <v>83.47801635991821</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7999358.108384448</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3984815.59611452</v>
+      </c>
+      <c r="N58" t="n">
+        <v>30206.12781186094</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.9695331242878965</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.2019897766252884</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>8.009201951135686e-05</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.05259242308809697</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.0008765403848016162</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4.950745610532072</v>
+      </c>
+      <c r="U58" t="n">
+        <v>10944.16634952406</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Muse Code</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Muse Spark 1.2 (xhigh)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.616404415975891</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.581120943952803</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.816479400749064</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.451612903225806</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.072823051942737</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2448.643313905929</v>
+      </c>
+      <c r="K59" t="n">
+        <v>151.4345603271984</v>
+      </c>
+      <c r="L59" t="n">
+        <v>19963139.08486708</v>
+      </c>
+      <c r="M59" t="n">
+        <v>10093761.29754601</v>
+      </c>
+      <c r="N59" t="n">
+        <v>58305.98057259714</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.9538301727874866</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.297374353974967</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>3.087712875993297e-05</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.01510398217189027</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.0002517330361981712</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3.362764766474045</v>
+      </c>
+      <c r="U59" t="n">
+        <v>8152.734606749675</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Fable 5.1 (max) (with fallback)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7043078467074591</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.660766961651917</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.887640449438202</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.564516129032258</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9.183238026073614</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1438.866784253578</v>
+      </c>
+      <c r="K60" t="n">
+        <v>25.38548057259714</v>
+      </c>
+      <c r="L60" t="n">
+        <v>7135668.150306755</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3522976.932515338</v>
+      </c>
+      <c r="N60" t="n">
+        <v>101478.4161554192</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.9015196331153521</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.07669493534935552</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>9.8702438492348e-05</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.02936927258653026</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.0004894878764421709</v>
+      </c>
+      <c r="T60" t="n">
+        <v>13.03867061683889</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4959.227795371226</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Kimi Code CLI</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kimi K3</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Moonshot AI</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>moonshotai</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.6263880112748013</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.63716814159292</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.8764044943820219</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.365591397849462</v>
+      </c>
+      <c r="I61" t="n">
+        <v>3.081635541610432</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1447.373053169734</v>
+      </c>
+      <c r="K61" t="n">
+        <v>122.9498977505112</v>
+      </c>
+      <c r="L61" t="n">
+        <v>10383196.73788345</v>
+      </c>
+      <c r="M61" t="n">
+        <v>5296768.575664621</v>
+      </c>
+      <c r="N61" t="n">
+        <v>54498.01533742331</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.9500000000000018</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.2032647932621705</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>6.032708683920077e-05</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.02596654718296781</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.0004327757863827968</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4.919691127770474</v>
+      </c>
+      <c r="U61" t="n">
+        <v>7173.822060003357</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GLM-5.2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>novita</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.433101571936022</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.286135693215339</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.722846441947566</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.290322580645161</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.909399563940518</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1507.044470347651</v>
+      </c>
+      <c r="K62" t="n">
+        <v>127.4036879531512</v>
+      </c>
+      <c r="L62" t="n">
+        <v>10784557.42954308</v>
+      </c>
+      <c r="M62" t="n">
+        <v>5529735.922290388</v>
+      </c>
+      <c r="N62" t="n">
+        <v>28567.83231083845</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.9451181301216958</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.2268260557482321</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>4.015942005645859e-05</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.01724308394838989</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.0002873847324731648</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4.408664589706397</v>
+      </c>
+      <c r="U62" t="n">
+        <v>7156.097674447032</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Codex</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>GPT-5.6 Sol (max)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.4975760031619054</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.427728613569322</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.677902621722846</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.387096774193548</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.05949917044417178</v>
+      </c>
+      <c r="J63" t="n">
+        <v>868.3750143149272</v>
+      </c>
+      <c r="K63" t="n">
+        <v>105.9314928425358</v>
+      </c>
+      <c r="L63" t="n">
+        <v>20844227.99386501</v>
+      </c>
+      <c r="M63" t="n">
+        <v>10443571.69734151</v>
+      </c>
+      <c r="N63" t="n">
+        <v>58411.25766871166</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.9807621661364226</v>
+      </c>
+      <c r="P63" t="n">
+        <v>8.362738496140583</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.387116487635592e-05</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.03437980100483083</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.0005729966834138472</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.1195780545405672</v>
+      </c>
+      <c r="U63" t="n">
+        <v>24003.71688527831</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Opus 5 (xhigh)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.6814975428587517</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.6047197640117991</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.891385767790262</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.5483870967741939</v>
+      </c>
+      <c r="I64" t="n">
+        <v>8.170783921523503</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1421.879982617589</v>
+      </c>
+      <c r="K64" t="n">
+        <v>152.0771983640082</v>
+      </c>
+      <c r="L64" t="n">
+        <v>21565879.13803681</v>
+      </c>
+      <c r="M64" t="n">
+        <v>10747525.6196319</v>
+      </c>
+      <c r="N64" t="n">
+        <v>73273.02862985685</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.9740249879523305</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.08340662896047819</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>3.160073088125403e-05</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.02875759773778482</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.000479293295629747</v>
+      </c>
+      <c r="T64" t="n">
+        <v>11.98945470477946</v>
+      </c>
+      <c r="U64" t="n">
+        <v>15167.15855183179</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Opencode</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Gemini 3.8 Flash (high)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SST</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.6115009143224124</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.616519174041298</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.838951310861423</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.379032258064516</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2.037777941104297</v>
+      </c>
+      <c r="J65" t="n">
+        <v>711.0750562372191</v>
+      </c>
+      <c r="K65" t="n">
+        <v>119.5439672801636</v>
+      </c>
+      <c r="L65" t="n">
+        <v>27777783.86094069</v>
+      </c>
+      <c r="M65" t="n">
+        <v>14366013.18404908</v>
+      </c>
+      <c r="N65" t="n">
+        <v>71460.62372188139</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.8832095692173221</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.3000822130752051</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2.201402809466975e-05</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.05159800577662889</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0.0008599667629438148</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3.332420104984313</v>
+      </c>
+      <c r="U65" t="n">
+        <v>39064.48920868046</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Grok Build</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Grok 4.5 (high)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>xai</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.6408998279698193</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.59882005899705</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.842696629213483</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.481182795698925</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2.438982443762777</v>
+      </c>
+      <c r="J66" t="n">
+        <v>929.1851094069543</v>
+      </c>
+      <c r="K66" t="n">
+        <v>60.74437627811862</v>
+      </c>
+      <c r="L66" t="n">
+        <v>3598867.582822083</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1837535.160531697</v>
+      </c>
+      <c r="N66" t="n">
+        <v>25699.40797546012</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.9238990226060743</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.2627734486604427</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.0001780837480736794</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.04138463831252326</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.0006897439718753876</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3.805559523223388</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3873.143840110648</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>GPT-6 Astra (max)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>openai</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v>0.6505240024334411</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.687315634218289</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="E67" t="n">
+        <v>0.6697139031534587</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.669616519174041</v>
+      </c>
+      <c r="G67" t="n">
         <v>0.831460674157303</v>
       </c>
-      <c r="H58" t="n">
-        <v>0.432795698924731</v>
-      </c>
-      <c r="I58" t="n">
-        <v>4.995463274846626</v>
-      </c>
-      <c r="J58" t="n">
-        <v>613.70177198364</v>
-      </c>
-      <c r="K58" t="n">
-        <v>112.2689161554192</v>
-      </c>
-      <c r="L58" t="n">
-        <v>13188716.58946831</v>
-      </c>
-      <c r="M58" t="n">
-        <v>6786107.398261759</v>
-      </c>
-      <c r="N58" t="n">
-        <v>54651.80674846626</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0.902597320865973</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.1302229576401828</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>4.932428398324287e-05</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.06360001213593849</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.001060000202265642</v>
-      </c>
-      <c r="T58" t="n">
-        <v>7.679137520152826</v>
-      </c>
-      <c r="U58" t="n">
-        <v>21490.43263609786</v>
+      <c r="H67" t="n">
+        <v>0.508064516129032</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4.717329430604444</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1609.089816462168</v>
+      </c>
+      <c r="K67" t="n">
+        <v>29.18660531697342</v>
+      </c>
+      <c r="L67" t="n">
+        <v>4035764.689496797</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2061908.266988501</v>
+      </c>
+      <c r="N67" t="n">
+        <v>31575.50107278152</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.9133755788574922</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.1419688645886337</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.0001659447353054082</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.02497239978657977</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.0004162066631096628</v>
+      </c>
+      <c r="T67" t="n">
+        <v>7.043797968643204</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2508.10405249475</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Muse Code 1.0.2 RC</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Muse Spark 1.3 (xhigh)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.6417750364143022</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.669616519174041</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.820224719101124</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.435483870967742</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.615020825613495</v>
+      </c>
+      <c r="J68" t="n">
+        <v>769.975962167688</v>
+      </c>
+      <c r="K68" t="n">
+        <v>130.7924335378323</v>
+      </c>
+      <c r="L68" t="n">
+        <v>14753563.55112475</v>
+      </c>
+      <c r="M68" t="n">
+        <v>7495698.047034764</v>
+      </c>
+      <c r="N68" t="n">
+        <v>42813.14417177914</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.9474470984376897</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.3973787992303519</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>4.349966258595037e-05</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.05001000560647639</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.0008335000934412733</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2.516490567531062</v>
+      </c>
+      <c r="U68" t="n">
+        <v>19161.07031392191</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cursor CLI</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Composer 2.5 Fast</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>cursor</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.3830075380367747</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.15929203539823</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.6779026217228465</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.3118279569892475</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.5573437730061347</v>
+      </c>
+      <c r="J69" t="n">
+        <v>472.3722024539875</v>
+      </c>
+      <c r="K69" t="n">
+        <v>116.8680981595092</v>
+      </c>
+      <c r="L69" t="n">
+        <v>4259887.413087938</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2153033.982617587</v>
+      </c>
+      <c r="N69" t="n">
+        <v>20146.14621676892</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.9355410155352533</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.6872016098268293</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>8.991024900330346e-05</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.04864903599920222</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.0008108172666533704</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1.455177033493845</v>
+      </c>
+      <c r="U69" t="n">
+        <v>9018.073864121761</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Coding Agents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coding Agents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-5.5 (xhigh)</t>
+          <t>GPT-5.6 Sol (medium)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -545,201 +545,201 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6103327520587847</v>
+        <v>0.616195748748264</v>
       </c>
       <c r="F2" t="n">
-        <v>0.64306784660767</v>
+        <v>0.640117994100295</v>
       </c>
       <c r="G2" t="n">
-        <v>0.827715355805243</v>
+        <v>0.805243445692884</v>
       </c>
       <c r="H2" t="n">
-        <v>0.360215053763441</v>
+        <v>0.403225806451613</v>
       </c>
       <c r="I2" t="n">
-        <v>4.75237007157464</v>
+        <v>2.192997850306748</v>
       </c>
       <c r="J2" t="n">
-        <v>614.9898987730061</v>
+        <v>297.9599253578734</v>
       </c>
       <c r="K2" t="n">
-        <v>107.1319018404908</v>
+        <v>71.35378323108384</v>
       </c>
       <c r="L2" t="n">
-        <v>12150851.17995912</v>
+        <v>5765545.476482623</v>
       </c>
       <c r="M2" t="n">
-        <v>6164087.486707566</v>
+        <v>2974758.351738241</v>
       </c>
       <c r="N2" t="n">
-        <v>25286.0654396728</v>
+        <v>14440.59713701431</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9341674523911524</v>
+        <v>0.8970664465490251</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1284270254350285</v>
+        <v>0.2809832889996098</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.022962943249859e-05</v>
+        <v>0.0001068755335053199</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05954563676019593</v>
+        <v>0.1240829446459615</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0009924272793365987</v>
+        <v>0.002068049077432692</v>
       </c>
       <c r="T2" t="n">
-        <v>7.786523098332615</v>
+        <v>3.558930509925766</v>
       </c>
       <c r="U2" t="n">
-        <v>19757.80611063991</v>
+        <v>19350.07021349515</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Opus 4.8 (xhigh)</t>
+          <t>Muse Spark 1.1 (xhigh)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.590718121759733</v>
+        <v>0.5492139250715363</v>
       </c>
       <c r="F3" t="n">
-        <v>0.513274336283186</v>
+        <v>0.542772861356932</v>
       </c>
       <c r="G3" t="n">
-        <v>0.831460674157303</v>
+        <v>0.771535580524344</v>
       </c>
       <c r="H3" t="n">
-        <v>0.42741935483871</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>5.665366469580767</v>
+        <v>1.435218435173823</v>
       </c>
       <c r="J3" t="n">
-        <v>1065.615385480574</v>
+        <v>761.3780071574635</v>
       </c>
       <c r="K3" t="n">
-        <v>136.1303390500093</v>
+        <v>55.51329243353784</v>
       </c>
       <c r="L3" t="n">
-        <v>13628306.24233129</v>
+        <v>12289527.21472391</v>
       </c>
       <c r="M3" t="n">
-        <v>6783846.309815951</v>
+        <v>6284599.100204499</v>
       </c>
       <c r="N3" t="n">
-        <v>62541.86503067485</v>
+        <v>34558.96932515338</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9687226730983399</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P3" t="n">
-        <v>0.104268298428971</v>
+        <v>0.3826692241484618</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.3344940395079e-05</v>
+        <v>4.46895893939297e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03326067527600474</v>
+        <v>0.04328051926180353</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005543445879334123</v>
+        <v>0.0007213419876967254</v>
       </c>
       <c r="T3" t="n">
-        <v>9.590642746330172</v>
+        <v>2.61322295312684</v>
       </c>
       <c r="U3" t="n">
-        <v>12789.14177481134</v>
+        <v>16141.16391489395</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (medium)</t>
+          <t>Sonnet 4.6 (medium)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.616195748748264</v>
+        <v>0.3864931360777617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.640117994100295</v>
+        <v>0.289085545722714</v>
       </c>
       <c r="G4" t="n">
-        <v>0.805243445692884</v>
+        <v>0.6741573033707861</v>
       </c>
       <c r="H4" t="n">
-        <v>0.403225806451613</v>
+        <v>0.196236559139785</v>
       </c>
       <c r="I4" t="n">
-        <v>2.192997850306748</v>
+        <v>2.041513021472394</v>
       </c>
       <c r="J4" t="n">
-        <v>297.9599253578734</v>
+        <v>827.6555807770975</v>
       </c>
       <c r="K4" t="n">
-        <v>71.35378323108384</v>
+        <v>67.41768916155419</v>
       </c>
       <c r="L4" t="n">
-        <v>5765545.476482615</v>
+        <v>8444053.035787314</v>
       </c>
       <c r="M4" t="n">
-        <v>2974758.351738241</v>
+        <v>4205086.787321064</v>
       </c>
       <c r="N4" t="n">
-        <v>14440.59713701431</v>
+        <v>40070.1308793456</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8970664465490255</v>
+        <v>0.9487221679807678</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2809832889996098</v>
+        <v>0.1893170075393457</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00010687553350532</v>
+        <v>4.577104554409345e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1240829446459615</v>
+        <v>0.02801840367329206</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002068049077432692</v>
+        <v>0.0004669733945548676</v>
       </c>
       <c r="T4" t="n">
-        <v>3.558930509925766</v>
+        <v>5.282145608561714</v>
       </c>
       <c r="U4" t="n">
-        <v>19350.07021349512</v>
+        <v>10202.37551936649</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Muse Spark 1.1 (xhigh)</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -760,570 +760,570 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5492139250715363</v>
+        <v>0.5962784529614886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.542772861356932</v>
+        <v>0.572271386430678</v>
       </c>
       <c r="G5" t="n">
-        <v>0.771535580524344</v>
+        <v>0.910112359550562</v>
       </c>
       <c r="H5" t="n">
-        <v>0.333333333333333</v>
+        <v>0.306451612903226</v>
       </c>
       <c r="I5" t="n">
-        <v>1.435218435173823</v>
+        <v>1.26793256886503</v>
       </c>
       <c r="J5" t="n">
-        <v>761.3780071574635</v>
+        <v>527.0915644171779</v>
       </c>
       <c r="K5" t="n">
-        <v>55.51329243353784</v>
+        <v>83.44887525562373</v>
       </c>
       <c r="L5" t="n">
-        <v>12289527.21472391</v>
+        <v>18493123.3742331</v>
       </c>
       <c r="M5" t="n">
-        <v>6284599.100204499</v>
+        <v>9497213.109406954</v>
       </c>
       <c r="N5" t="n">
-        <v>34558.96932515338</v>
+        <v>49098.7944785276</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.8634331167917663</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3826692241484618</v>
+        <v>0.4702761547447575</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.46895893939297e-05</v>
+        <v>3.224325285107313e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04328051926180353</v>
+        <v>0.06787569673449199</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0007213419876967254</v>
+        <v>0.001131261612241533</v>
       </c>
       <c r="T5" t="n">
-        <v>2.61322295312684</v>
+        <v>2.126410173917388</v>
       </c>
       <c r="U5" t="n">
-        <v>16141.16391489395</v>
+        <v>35085.21976571858</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sonnet 4.6 (medium)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.386493136077762</v>
+        <v>0.4708693600598457</v>
       </c>
       <c r="F6" t="n">
-        <v>0.289085545722714</v>
+        <v>0.371681415929204</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6741573033707871</v>
+        <v>0.764044943820225</v>
       </c>
       <c r="H6" t="n">
-        <v>0.196236559139785</v>
+        <v>0.276881720430108</v>
       </c>
       <c r="I6" t="n">
-        <v>2.041513021472394</v>
+        <v>1.998031234219494</v>
       </c>
       <c r="J6" t="n">
-        <v>827.6555807770972</v>
+        <v>386.6294212678939</v>
       </c>
       <c r="K6" t="n">
-        <v>67.41768916155419</v>
+        <v>77.78698023176551</v>
       </c>
       <c r="L6" t="n">
-        <v>8444053.035787314</v>
+        <v>3955817.742194958</v>
       </c>
       <c r="M6" t="n">
-        <v>4205086.787321064</v>
+        <v>2043912.618541241</v>
       </c>
       <c r="N6" t="n">
-        <v>40070.1308793456</v>
+        <v>11032.14533060668</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9487221679807678</v>
+        <v>0.8915632417465625</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1893170075393459</v>
+        <v>0.235666666263996</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.577104554409349e-05</v>
+        <v>0.0001190321169343296</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0280184036732921</v>
+        <v>0.07307297388528261</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004669733945548682</v>
+        <v>0.001217882898088044</v>
       </c>
       <c r="T6" t="n">
-        <v>5.282145608561709</v>
+        <v>4.243281478254504</v>
       </c>
       <c r="U6" t="n">
-        <v>10202.37551936649</v>
+        <v>10231.5486732035</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>GPT-5.5 (medium)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5962784529614886</v>
+        <v>0.5531133827505798</v>
       </c>
       <c r="F7" t="n">
-        <v>0.572271386430678</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G7" t="n">
-        <v>0.910112359550562</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H7" t="n">
         <v>0.306451612903226</v>
       </c>
       <c r="I7" t="n">
-        <v>1.26793256886503</v>
+        <v>2.652535874233126</v>
       </c>
       <c r="J7" t="n">
-        <v>527.0915644171779</v>
+        <v>386.3044764826171</v>
       </c>
       <c r="K7" t="n">
-        <v>83.44887525562373</v>
+        <v>78.53885480572598</v>
       </c>
       <c r="L7" t="n">
-        <v>18493123.3742331</v>
+        <v>6885560.579754606</v>
       </c>
       <c r="M7" t="n">
-        <v>9497213.109406954</v>
+        <v>3492715.358895706</v>
       </c>
       <c r="N7" t="n">
-        <v>49098.7944785276</v>
+        <v>13239.49488752556</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8634331167917663</v>
+        <v>0.9409891933709401</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4702761547447575</v>
+        <v>0.2085224890353237</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.224325285107314e-05</v>
+        <v>8.032946284386509e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.06787569673449199</v>
+        <v>0.08590840900216211</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001131261612241533</v>
+        <v>0.001431806816702702</v>
       </c>
       <c r="T7" t="n">
-        <v>2.126410173917388</v>
+        <v>4.795645806005126</v>
       </c>
       <c r="U7" t="n">
-        <v>35085.21976571858</v>
+        <v>17824.18014528092</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>Opus 5 (low)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4708693600598457</v>
+        <v>0.5940064571013326</v>
       </c>
       <c r="F8" t="n">
-        <v>0.371681415929204</v>
+        <v>0.569321533923304</v>
       </c>
       <c r="G8" t="n">
-        <v>0.764044943820225</v>
+        <v>0.820224719101124</v>
       </c>
       <c r="H8" t="n">
-        <v>0.276881720430108</v>
+        <v>0.39247311827957</v>
       </c>
       <c r="I8" t="n">
-        <v>1.998031234219494</v>
+        <v>2.295157744887527</v>
       </c>
       <c r="J8" t="n">
-        <v>386.6294212678936</v>
+        <v>598.7677147239262</v>
       </c>
       <c r="K8" t="n">
-        <v>77.78698023176551</v>
+        <v>64.39263803680981</v>
       </c>
       <c r="L8" t="n">
-        <v>3955817.742194954</v>
+        <v>5258606.375255628</v>
       </c>
       <c r="M8" t="n">
-        <v>2043912.618541241</v>
+        <v>2618171.039877301</v>
       </c>
       <c r="N8" t="n">
-        <v>11032.14533060668</v>
+        <v>22632.92229038855</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8915632417465625</v>
+        <v>0.9637890151908798</v>
       </c>
       <c r="P8" t="n">
-        <v>0.235666666263996</v>
+        <v>0.2588085539760761</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0001190321169343297</v>
+        <v>0.0001129589124404576</v>
       </c>
       <c r="R8" t="n">
-        <v>0.07307297388528267</v>
+        <v>0.05952289435396941</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001217882898088044</v>
+        <v>0.0009920482392328236</v>
       </c>
       <c r="T8" t="n">
-        <v>4.243281478254504</v>
+        <v>3.863859925172484</v>
       </c>
       <c r="U8" t="n">
-        <v>10231.5486732035</v>
+        <v>8782.381290681667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-5.5 (medium)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5531133827505798</v>
+        <v>0.6797281481220127</v>
       </c>
       <c r="F9" t="n">
-        <v>0.566371681415929</v>
+        <v>0.68141592920354</v>
       </c>
       <c r="G9" t="n">
-        <v>0.786516853932584</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H9" t="n">
-        <v>0.306451612903226</v>
+        <v>0.518817204301075</v>
       </c>
       <c r="I9" t="n">
-        <v>2.65253587423313</v>
+        <v>1.584232134037035</v>
       </c>
       <c r="J9" t="n">
-        <v>386.3044764826171</v>
+        <v>1475.134529652353</v>
       </c>
       <c r="K9" t="n">
-        <v>78.53885480572598</v>
+        <v>128.5444491455704</v>
       </c>
       <c r="L9" t="n">
-        <v>6885560.579754606</v>
+        <v>14182668.81449944</v>
       </c>
       <c r="M9" t="n">
-        <v>3492715.358895706</v>
+        <v>7211413.368985498</v>
       </c>
       <c r="N9" t="n">
-        <v>13239.49488752556</v>
+        <v>44550.73137766495</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9409891933709398</v>
+        <v>0.9520877069904671</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2085224890353234</v>
+        <v>0.4290584274350558</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.032946284386509e-05</v>
+        <v>4.792667423969617e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08590840900216211</v>
+        <v>0.02764743694050217</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001431806816702702</v>
+        <v>0.0004607906156750362</v>
       </c>
       <c r="T9" t="n">
-        <v>4.795645806005133</v>
+        <v>2.330684904566673</v>
       </c>
       <c r="U9" t="n">
-        <v>17824.18014528092</v>
+        <v>9614.491783228672</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Opus 5 (low)</t>
+          <t>GPT-5.6 Terra (low)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.5940064571013326</v>
+        <v>0.3864628427996264</v>
       </c>
       <c r="F10" t="n">
-        <v>0.569321533923304</v>
+        <v>0.297935103244838</v>
       </c>
       <c r="G10" t="n">
-        <v>0.820224719101124</v>
+        <v>0.632958801498127</v>
       </c>
       <c r="H10" t="n">
-        <v>0.39247311827957</v>
+        <v>0.228494623655914</v>
       </c>
       <c r="I10" t="n">
-        <v>2.295157744887527</v>
+        <v>0.3850630644171779</v>
       </c>
       <c r="J10" t="n">
-        <v>598.7677147239262</v>
+        <v>154.8149498977502</v>
       </c>
       <c r="K10" t="n">
-        <v>64.39263803680981</v>
+        <v>37.80981595092025</v>
       </c>
       <c r="L10" t="n">
-        <v>5258606.375255628</v>
+        <v>1657646.844580775</v>
       </c>
       <c r="M10" t="n">
-        <v>2618171.039877301</v>
+        <v>861642.4202453988</v>
       </c>
       <c r="N10" t="n">
-        <v>22632.92229038855</v>
+        <v>6854.071574642127</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9637890151908798</v>
+        <v>0.8771903855272027</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2588085539760761</v>
+        <v>1.003635192548439</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0001129589124404576</v>
+        <v>0.0002331394313952103</v>
       </c>
       <c r="R10" t="n">
-        <v>0.05952289435396941</v>
+        <v>0.1497773347037368</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0009920482392328236</v>
+        <v>0.002496288911728947</v>
       </c>
       <c r="T10" t="n">
-        <v>3.863859925172484</v>
+        <v>0.996377974212713</v>
       </c>
       <c r="U10" t="n">
-        <v>8782.381290681667</v>
+        <v>10707.27888796005</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>GPT-5.6 Terra (none)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6797281481220124</v>
+        <v>0.2309196896685307</v>
       </c>
       <c r="F11" t="n">
-        <v>0.681415929203539</v>
+        <v>0.132743362831858</v>
       </c>
       <c r="G11" t="n">
-        <v>0.838951310861423</v>
+        <v>0.374531835205992</v>
       </c>
       <c r="H11" t="n">
-        <v>0.518817204301075</v>
+        <v>0.185483870967742</v>
       </c>
       <c r="I11" t="n">
-        <v>1.584232134037035</v>
+        <v>0.2926964817995911</v>
       </c>
       <c r="J11" t="n">
-        <v>1475.134529652353</v>
+        <v>88.85438650306735</v>
       </c>
       <c r="K11" t="n">
-        <v>128.5444491455704</v>
+        <v>33.82924335378323</v>
       </c>
       <c r="L11" t="n">
-        <v>14182668.81449944</v>
+        <v>1105801.555214723</v>
       </c>
       <c r="M11" t="n">
-        <v>7211413.368985498</v>
+        <v>582183.7985685072</v>
       </c>
       <c r="N11" t="n">
-        <v>44550.73137766495</v>
+        <v>5133.394683026585</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9520877069904663</v>
+        <v>0.8482758058887612</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4290584274350556</v>
+        <v>0.7889390683781471</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.792667423969616e-05</v>
+        <v>0.0002088256148488514</v>
       </c>
       <c r="R11" t="n">
-        <v>0.02764743694050216</v>
+        <v>0.1559313155533806</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004607906156750361</v>
+        <v>0.00259885525922301</v>
       </c>
       <c r="T11" t="n">
-        <v>2.330684904566675</v>
+        <v>1.267525009321365</v>
       </c>
       <c r="U11" t="n">
-        <v>9614.491783228672</v>
+        <v>12445.09808389201</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (low)</t>
+          <t>Fable 5 (low) (with fallback)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.3864628427996264</v>
+        <v>0.58556576973616</v>
       </c>
       <c r="F12" t="n">
-        <v>0.297935103244838</v>
+        <v>0.59882005899705</v>
       </c>
       <c r="G12" t="n">
-        <v>0.632958801498127</v>
+        <v>0.816479400749064</v>
       </c>
       <c r="H12" t="n">
-        <v>0.228494623655914</v>
+        <v>0.341397849462366</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3850630644171779</v>
+        <v>3.166078810327201</v>
       </c>
       <c r="J12" t="n">
-        <v>154.8149498977502</v>
+        <v>490.7785531697345</v>
       </c>
       <c r="K12" t="n">
-        <v>37.80981595092025</v>
+        <v>54.85276073619632</v>
       </c>
       <c r="L12" t="n">
-        <v>1657646.844580775</v>
+        <v>3748013.195296523</v>
       </c>
       <c r="M12" t="n">
-        <v>861642.4202453988</v>
+        <v>1864095.536809816</v>
       </c>
       <c r="N12" t="n">
-        <v>6854.071574642127</v>
+        <v>20218.93047034765</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8771903855272027</v>
+        <v>0.9618678651037137</v>
       </c>
       <c r="P12" t="n">
-        <v>1.003635192548439</v>
+        <v>0.1849498401069948</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0002331394313952103</v>
+        <v>0.0001562336467947875</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1497773347037368</v>
+        <v>0.07158818566388866</v>
       </c>
       <c r="S12" t="n">
-        <v>0.002496288911728947</v>
+        <v>0.001193136427731478</v>
       </c>
       <c r="T12" t="n">
-        <v>0.996377974212713</v>
+        <v>5.406871395084705</v>
       </c>
       <c r="U12" t="n">
-        <v>10707.27888796005</v>
+        <v>7636.872416469027</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (none)</t>
+          <t>GPT-5.6 Luna (high)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1348,493 +1348,493 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.2309196896685307</v>
+        <v>0.516945881593198</v>
       </c>
       <c r="F13" t="n">
-        <v>0.132743362831858</v>
+        <v>0.533923303834808</v>
       </c>
       <c r="G13" t="n">
-        <v>0.374531835205992</v>
+        <v>0.726591760299625</v>
       </c>
       <c r="H13" t="n">
-        <v>0.185483870967742</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2926964817995911</v>
+        <v>0.1797932241513293</v>
       </c>
       <c r="J13" t="n">
-        <v>88.85438650306735</v>
+        <v>342.6686574642128</v>
       </c>
       <c r="K13" t="n">
-        <v>33.82924335378323</v>
+        <v>83.81901840490798</v>
       </c>
       <c r="L13" t="n">
-        <v>1105801.555214722</v>
+        <v>9641370.493865021</v>
       </c>
       <c r="M13" t="n">
-        <v>582183.7985685072</v>
+        <v>4959371.744376278</v>
       </c>
       <c r="N13" t="n">
-        <v>5133.394683026585</v>
+        <v>22230.90593047035</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8482758058887612</v>
+        <v>0.9032288062243126</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7889390683781471</v>
+        <v>2.875224492098168</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0002088256148488515</v>
+        <v>5.361746879472582e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1559313155533806</v>
+        <v>0.09051528997463437</v>
       </c>
       <c r="S13" t="n">
-        <v>0.00259885525922301</v>
+        <v>0.001508588166243906</v>
       </c>
       <c r="T13" t="n">
-        <v>1.267525009321365</v>
+        <v>0.3477989293525597</v>
       </c>
       <c r="U13" t="n">
-        <v>12445.098083892</v>
+        <v>28136.13175249894</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (high)</t>
+          <t>Qwen3.7 Plus (thinking)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.516945881593198</v>
+        <v>0.3812184526692477</v>
       </c>
       <c r="F14" t="n">
-        <v>0.533923303834808</v>
+        <v>0.191740412979351</v>
       </c>
       <c r="G14" t="n">
-        <v>0.726591760299625</v>
+        <v>0.715355805243446</v>
       </c>
       <c r="H14" t="n">
-        <v>0.290322580645161</v>
+        <v>0.236559139784946</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1797932241513293</v>
+        <v>6.300658805725988</v>
       </c>
       <c r="J14" t="n">
-        <v>342.6686574642128</v>
+        <v>643.9465817995908</v>
       </c>
       <c r="K14" t="n">
-        <v>83.81901840490798</v>
+        <v>145.9662576687116</v>
       </c>
       <c r="L14" t="n">
-        <v>9641370.493865021</v>
+        <v>8784635.035787327</v>
       </c>
       <c r="M14" t="n">
-        <v>4959371.744376278</v>
+        <v>4715248.469325154</v>
       </c>
       <c r="N14" t="n">
-        <v>22230.90593047035</v>
+        <v>32611.0408997955</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9032288062243126</v>
+        <v>0.8105104948122446</v>
       </c>
       <c r="P14" t="n">
-        <v>2.875224492098168</v>
+        <v>0.06050453840204764</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.361746879472582e-05</v>
+        <v>4.339604902380339e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.09051528997463437</v>
+        <v>0.03552019345491834</v>
       </c>
       <c r="S14" t="n">
-        <v>0.001508588166243906</v>
+        <v>0.000592003224248639</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3477989293525597</v>
+        <v>16.52768579697415</v>
       </c>
       <c r="U14" t="n">
-        <v>28136.13175249894</v>
+        <v>13641.86919237547</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qwen3.7 Plus (thinking)</t>
+          <t>GPT-5.6 Luna (none)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.3812184526692477</v>
+        <v>0.1909870904304247</v>
       </c>
       <c r="F15" t="n">
-        <v>0.191740412979351</v>
+        <v>0.0648967551622419</v>
       </c>
       <c r="G15" t="n">
-        <v>0.715355805243446</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>0.236559139784946</v>
+        <v>0.174731182795699</v>
       </c>
       <c r="I15" t="n">
-        <v>6.300658805725988</v>
+        <v>0.06947505231083852</v>
       </c>
       <c r="J15" t="n">
-        <v>643.9465817995908</v>
+        <v>131.816209611452</v>
       </c>
       <c r="K15" t="n">
-        <v>145.9662576687116</v>
+        <v>54.28629856850716</v>
       </c>
       <c r="L15" t="n">
-        <v>8784635.035787327</v>
+        <v>3549957.210633946</v>
       </c>
       <c r="M15" t="n">
-        <v>4715248.469325154</v>
+        <v>1835572.532719836</v>
       </c>
       <c r="N15" t="n">
-        <v>32611.0408997955</v>
+        <v>7934.628834355828</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8105104948122446</v>
+        <v>0.8748960056789888</v>
       </c>
       <c r="P15" t="n">
-        <v>0.06050453840204764</v>
+        <v>2.74900247035337</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.339604902380339e-05</v>
+        <v>5.379982887070306e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.03552019345491834</v>
+        <v>0.08693335561387526</v>
       </c>
       <c r="S15" t="n">
-        <v>0.000592003224248639</v>
+        <v>0.001448889260231254</v>
       </c>
       <c r="T15" t="n">
-        <v>16.52768579697415</v>
+        <v>0.3637683162472587</v>
       </c>
       <c r="U15" t="n">
-        <v>13641.86919237547</v>
+        <v>26931.11280545826</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (none)</t>
+          <t>Opus 4.8 (high)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.1909870904304247</v>
+        <v>0.5757636668124306</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0648967551622419</v>
+        <v>0.516224188790561</v>
       </c>
       <c r="G16" t="n">
-        <v>0.333333333333333</v>
+        <v>0.823970037453183</v>
       </c>
       <c r="H16" t="n">
-        <v>0.174731182795699</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="I16" t="n">
-        <v>0.06947505231083852</v>
+        <v>3.7823013803681</v>
       </c>
       <c r="J16" t="n">
-        <v>131.816209611452</v>
+        <v>761.0308312883442</v>
       </c>
       <c r="K16" t="n">
-        <v>54.28629856850716</v>
+        <v>104.7627811860941</v>
       </c>
       <c r="L16" t="n">
-        <v>3549957.210633946</v>
+        <v>9188690.866053157</v>
       </c>
       <c r="M16" t="n">
-        <v>1835572.532719836</v>
+        <v>4574601.889570553</v>
       </c>
       <c r="N16" t="n">
-        <v>7934.628834355828</v>
+        <v>40682.70756646217</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8748960056789888</v>
+        <v>0.9682475638703767</v>
       </c>
       <c r="P16" t="n">
-        <v>2.74900247035337</v>
+        <v>0.152225750650361</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.379982887070306e-05</v>
+        <v>6.266003233818007e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>0.08693335561387526</v>
+        <v>0.04539345659657893</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001448889260231254</v>
+        <v>0.0007565576099429822</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3637683162472587</v>
+        <v>6.569190795431485</v>
       </c>
       <c r="U16" t="n">
-        <v>26931.11280545826</v>
+        <v>12074.00605636132</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin CLI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Opus 4.8 (high)</t>
+          <t>SWE-1.7 Lightning Max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Cognition</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5757636668124306</v>
+        <v>0.5221389513465003</v>
       </c>
       <c r="F17" t="n">
-        <v>0.516224188790561</v>
+        <v>0.404129793510324</v>
       </c>
       <c r="G17" t="n">
-        <v>0.823970037453183</v>
+        <v>0.7940074906367039</v>
       </c>
       <c r="H17" t="n">
-        <v>0.387096774193548</v>
+        <v>0.368279569892473</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7823013803681</v>
+        <v>8.521259638036815</v>
       </c>
       <c r="J17" t="n">
-        <v>761.030831288344</v>
+        <v>637.3248271983654</v>
       </c>
       <c r="K17" t="n">
-        <v>104.7627811860941</v>
+        <v>86.57157464212679</v>
       </c>
       <c r="L17" t="n">
-        <v>9188690.866053157</v>
+        <v>15573672.60122699</v>
       </c>
       <c r="M17" t="n">
-        <v>4574601.889570553</v>
+        <v>7834231.955010225</v>
       </c>
       <c r="N17" t="n">
-        <v>40682.70756646217</v>
+        <v>38917.19427402863</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9682475638703767</v>
+        <v>0.9746033359706329</v>
       </c>
       <c r="P17" t="n">
-        <v>0.152225750650361</v>
+        <v>0.06127485530610991</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.266003233818007e-05</v>
+        <v>3.352702761359984e-05</v>
       </c>
       <c r="R17" t="n">
-        <v>0.04539345659657895</v>
+        <v>0.04915599666579311</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0007565576099429824</v>
+        <v>0.0008192666110965519</v>
       </c>
       <c r="T17" t="n">
-        <v>6.569190795431485</v>
+        <v>16.31990797863682</v>
       </c>
       <c r="U17" t="n">
-        <v>12074.00605636132</v>
+        <v>24436.00490143738</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Devin CLI</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SWE-1.7 Lightning Max</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cognition</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5221389513465007</v>
+        <v>0.466554082589455</v>
       </c>
       <c r="F18" t="n">
-        <v>0.404129793510325</v>
+        <v>0.315634218289085</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7940074906367039</v>
+        <v>0.745318352059925</v>
       </c>
       <c r="H18" t="n">
-        <v>0.368279569892473</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="I18" t="n">
-        <v>8.521259638036815</v>
+        <v>2.724905711017384</v>
       </c>
       <c r="J18" t="n">
-        <v>637.3248271983654</v>
+        <v>826.6777535787319</v>
       </c>
       <c r="K18" t="n">
-        <v>86.57157464212679</v>
+        <v>86.42229038854805</v>
       </c>
       <c r="L18" t="n">
-        <v>15573672.60122699</v>
+        <v>5728865.180470356</v>
       </c>
       <c r="M18" t="n">
-        <v>7834231.955010225</v>
+        <v>2855520.426380368</v>
       </c>
       <c r="N18" t="n">
-        <v>38917.19427402863</v>
+        <v>17872.17893660532</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9746033359706325</v>
+        <v>0.9538631453697446</v>
       </c>
       <c r="P18" t="n">
-        <v>0.06127485530610995</v>
+        <v>0.1712184317802542</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.352702761359986e-05</v>
+        <v>8.14391799932617e-05</v>
       </c>
       <c r="R18" t="n">
-        <v>0.04915599666579314</v>
+        <v>0.0338623421692226</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0008192666110965524</v>
+        <v>0.0005643723694870433</v>
       </c>
       <c r="T18" t="n">
-        <v>16.31990797863681</v>
+        <v>5.840492694638295</v>
       </c>
       <c r="U18" t="n">
-        <v>24436.00490143738</v>
+        <v>6929.985905233078</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>Gemini 3.6 Flash (high)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.4665540825894554</v>
+        <v>0.4724127134829677</v>
       </c>
       <c r="F19" t="n">
-        <v>0.315634218289086</v>
+        <v>0.412979351032448</v>
       </c>
       <c r="G19" t="n">
-        <v>0.745318352059925</v>
+        <v>0.786516853932584</v>
       </c>
       <c r="H19" t="n">
-        <v>0.338709677419355</v>
+        <v>0.217741935483871</v>
       </c>
       <c r="I19" t="n">
-        <v>2.72490571101738</v>
+        <v>2.083890154754598</v>
       </c>
       <c r="J19" t="n">
-        <v>826.6777535787322</v>
+        <v>626.0057290388545</v>
       </c>
       <c r="K19" t="n">
-        <v>86.42229038854805</v>
+        <v>65.01533742331287</v>
       </c>
       <c r="L19" t="n">
-        <v>5728865.180470352</v>
+        <v>13020159.54294479</v>
       </c>
       <c r="M19" t="n">
-        <v>2855520.426380368</v>
+        <v>6765842.061349694</v>
       </c>
       <c r="N19" t="n">
-        <v>17872.17893660532</v>
+        <v>42763.3517382413</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9538631453697446</v>
+        <v>0.8377770485520734</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1712184317802546</v>
+        <v>0.2266975120570113</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.143917999326182e-05</v>
+        <v>3.628317394458911e-05</v>
       </c>
       <c r="R19" t="n">
-        <v>0.03386234216922261</v>
+        <v>0.0452787594332364</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0005643723694870434</v>
+        <v>0.0007546459905539399</v>
       </c>
       <c r="T19" t="n">
-        <v>5.840492694638283</v>
+        <v>4.411164423138944</v>
       </c>
       <c r="U19" t="n">
-        <v>6929.985905233071</v>
+        <v>20798.78655892726</v>
       </c>
     </row>
     <row r="20">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gemini 3.6 Flash (high)</t>
+          <t>Muse Spark 1.2 (xhigh)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1855,132 +1855,132 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4724127134829677</v>
+        <v>0.5888788742875287</v>
       </c>
       <c r="F20" t="n">
-        <v>0.412979351032448</v>
+        <v>0.528023598820059</v>
       </c>
       <c r="G20" t="n">
-        <v>0.786516853932584</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="H20" t="n">
-        <v>0.217741935483871</v>
+        <v>0.440860215053763</v>
       </c>
       <c r="I20" t="n">
-        <v>2.083890154754598</v>
+        <v>1.914379785695299</v>
       </c>
       <c r="J20" t="n">
-        <v>626.0057290388548</v>
+        <v>1064.740692229039</v>
       </c>
       <c r="K20" t="n">
-        <v>65.01533742331287</v>
+        <v>65.87116564417177</v>
       </c>
       <c r="L20" t="n">
-        <v>13020159.54294479</v>
+        <v>16350688.07453988</v>
       </c>
       <c r="M20" t="n">
-        <v>6765842.061349694</v>
+        <v>8360784.971370144</v>
       </c>
       <c r="N20" t="n">
-        <v>42763.3517382413</v>
+        <v>47157.38036809816</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8377770485520737</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2266975120570113</v>
+        <v>0.3076081761245976</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.628317394458911e-05</v>
+        <v>3.601554085081526e-05</v>
       </c>
       <c r="R20" t="n">
-        <v>0.04527875943323637</v>
+        <v>0.03318435438330295</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0007546459905539396</v>
+        <v>0.0005530725730550492</v>
       </c>
       <c r="T20" t="n">
-        <v>4.411164423138944</v>
+        <v>3.250888882729005</v>
       </c>
       <c r="U20" t="n">
-        <v>20798.78655892725</v>
+        <v>15356.49777816761</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fable 5 (low) (with fallback)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.58556576973616</v>
+        <v>0.590851412183529</v>
       </c>
       <c r="F21" t="n">
-        <v>0.59882005899705</v>
+        <v>0.6076696165191739</v>
       </c>
       <c r="G21" t="n">
-        <v>0.816479400749064</v>
+        <v>0.812734082397004</v>
       </c>
       <c r="H21" t="n">
-        <v>0.341397849462366</v>
+        <v>0.352150537634409</v>
       </c>
       <c r="I21" t="n">
-        <v>3.166078810327201</v>
+        <v>2.008975153911046</v>
       </c>
       <c r="J21" t="n">
-        <v>490.7785531697341</v>
+        <v>457.9304969325152</v>
       </c>
       <c r="K21" t="n">
-        <v>54.85276073619632</v>
+        <v>147.3926380368098</v>
       </c>
       <c r="L21" t="n">
-        <v>3748013.195296523</v>
+        <v>19759750.71472392</v>
       </c>
       <c r="M21" t="n">
-        <v>1864095.536809816</v>
+        <v>10510296.86707566</v>
       </c>
       <c r="N21" t="n">
-        <v>20218.93047034765</v>
+        <v>83533.0736196319</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9618678651037137</v>
+        <v>0.8589224031432205</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1849498401069948</v>
+        <v>0.2941058833073508</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0001562336467947875</v>
+        <v>2.990176448649516e-05</v>
       </c>
       <c r="R21" t="n">
-        <v>0.07158818566388871</v>
+        <v>0.0774158632554148</v>
       </c>
       <c r="S21" t="n">
-        <v>0.001193136427731479</v>
+        <v>0.001290264387590247</v>
       </c>
       <c r="T21" t="n">
-        <v>5.406871395084705</v>
+        <v>3.40013599440636</v>
       </c>
       <c r="U21" t="n">
-        <v>7636.872416469033</v>
+        <v>43150.10868917057</v>
       </c>
     </row>
     <row r="22">
@@ -1991,158 +1991,158 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Muse Spark 1.2 (xhigh)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5888788742875287</v>
+        <v>0.5127556084440553</v>
       </c>
       <c r="F22" t="n">
-        <v>0.528023598820059</v>
+        <v>0.395280235988201</v>
       </c>
       <c r="G22" t="n">
-        <v>0.797752808988764</v>
+        <v>0.782771535580524</v>
       </c>
       <c r="H22" t="n">
-        <v>0.440860215053763</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I22" t="n">
-        <v>1.914379785695299</v>
+        <v>2.942840985557261</v>
       </c>
       <c r="J22" t="n">
-        <v>1064.740692229039</v>
+        <v>752.2755521472382</v>
       </c>
       <c r="K22" t="n">
-        <v>65.87116564417177</v>
+        <v>54.41308793456033</v>
       </c>
       <c r="L22" t="n">
-        <v>16350688.07453988</v>
+        <v>7582747.093047047</v>
       </c>
       <c r="M22" t="n">
-        <v>8360784.971370144</v>
+        <v>3744700.533231084</v>
       </c>
       <c r="N22" t="n">
-        <v>47157.38036809816</v>
+        <v>25943.59151329243</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.9584168731547833</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3076081761245976</v>
+        <v>0.1742382993034736</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.601554085081526e-05</v>
+        <v>6.762135175446157e-05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.03318435438330295</v>
+        <v>0.04089636625679125</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0005530725730550492</v>
+        <v>0.0006816061042798542</v>
       </c>
       <c r="T22" t="n">
-        <v>3.250888882729005</v>
+        <v>5.739266303663147</v>
       </c>
       <c r="U22" t="n">
-        <v>15356.49777816761</v>
+        <v>10079.74680474918</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>Opus 4.8 (low)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.590851412183529</v>
+        <v>0.4904379267565557</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6076696165191739</v>
+        <v>0.410029498525074</v>
       </c>
       <c r="G23" t="n">
-        <v>0.812734082397004</v>
+        <v>0.779026217228464</v>
       </c>
       <c r="H23" t="n">
-        <v>0.352150537634409</v>
+        <v>0.282258064516129</v>
       </c>
       <c r="I23" t="n">
-        <v>2.008975153911043</v>
+        <v>2.182594679703477</v>
       </c>
       <c r="J23" t="n">
-        <v>457.9304969325156</v>
+        <v>516.6536431492842</v>
       </c>
       <c r="K23" t="n">
-        <v>147.3926380368098</v>
+        <v>68.16359918200409</v>
       </c>
       <c r="L23" t="n">
-        <v>19759750.71472392</v>
+        <v>5214050.029652352</v>
       </c>
       <c r="M23" t="n">
-        <v>10510296.86707566</v>
+        <v>2595804.632924335</v>
       </c>
       <c r="N23" t="n">
-        <v>83533.0736196319</v>
+        <v>23270.04396728017</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8589224031432205</v>
+        <v>0.9661582176104914</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2941058833073512</v>
+        <v>0.2247040787358583</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.990176448649516e-05</v>
+        <v>9.406084022351733e-05</v>
       </c>
       <c r="R23" t="n">
-        <v>0.07741586325541473</v>
+        <v>0.0569555174836748</v>
       </c>
       <c r="S23" t="n">
-        <v>0.001290264387590245</v>
+        <v>0.0009492586247279134</v>
       </c>
       <c r="T23" t="n">
-        <v>3.400135994406355</v>
+        <v>4.450297500720978</v>
       </c>
       <c r="U23" t="n">
-        <v>43150.10868917053</v>
+        <v>10091.9641210113</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>Fable 5 (xhigh) (with fallback)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2151,274 +2151,274 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5127556084440553</v>
+        <v>0.6601695603875117</v>
       </c>
       <c r="F24" t="n">
-        <v>0.395280235988201</v>
+        <v>0.651917404129794</v>
       </c>
       <c r="G24" t="n">
-        <v>0.782771535580524</v>
+        <v>0.868913857677902</v>
       </c>
       <c r="H24" t="n">
-        <v>0.360215053763441</v>
+        <v>0.459677419354839</v>
       </c>
       <c r="I24" t="n">
-        <v>2.942840985557257</v>
+        <v>8.525764661042949</v>
       </c>
       <c r="J24" t="n">
-        <v>752.2755521472382</v>
+        <v>1028.54882822086</v>
       </c>
       <c r="K24" t="n">
-        <v>54.41308793456033</v>
+        <v>108.2208588957055</v>
       </c>
       <c r="L24" t="n">
-        <v>7582747.093047047</v>
+        <v>10319338.81901841</v>
       </c>
       <c r="M24" t="n">
-        <v>3744700.533231084</v>
+        <v>5134138.567484663</v>
       </c>
       <c r="N24" t="n">
-        <v>25943.59151329243</v>
+        <v>52975.96319018405</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9584168731547833</v>
+        <v>0.9637652234526968</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1742382993034738</v>
+        <v>0.07743229922871854</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.762135175446157e-05</v>
+        <v>6.39740173247173e-05</v>
       </c>
       <c r="R24" t="n">
-        <v>0.04089636625679125</v>
+        <v>0.03851073720220624</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0006816061042798542</v>
+        <v>0.0006418456200367707</v>
       </c>
       <c r="T24" t="n">
-        <v>5.73926630366314</v>
+        <v>12.91450738207079</v>
       </c>
       <c r="U24" t="n">
-        <v>10079.74680474918</v>
+        <v>10032.91096725896</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Opus 4.8 (low)</t>
+          <t>GPT-5.6 Sol (none)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.4904379267565557</v>
+        <v>0.4336881923573268</v>
       </c>
       <c r="F25" t="n">
-        <v>0.410029498525074</v>
+        <v>0.353982300884956</v>
       </c>
       <c r="G25" t="n">
-        <v>0.779026217228464</v>
+        <v>0.602996254681648</v>
       </c>
       <c r="H25" t="n">
-        <v>0.282258064516129</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I25" t="n">
-        <v>2.182594679703477</v>
+        <v>1.086854643353786</v>
       </c>
       <c r="J25" t="n">
-        <v>516.6536431492842</v>
+        <v>197.8853650306747</v>
       </c>
       <c r="K25" t="n">
-        <v>68.16359918200409</v>
+        <v>55.10736196319019</v>
       </c>
       <c r="L25" t="n">
-        <v>5214050.029652352</v>
+        <v>3404912.347648262</v>
       </c>
       <c r="M25" t="n">
-        <v>2595804.632924335</v>
+        <v>1731981.235173824</v>
       </c>
       <c r="N25" t="n">
-        <v>23270.04396728017</v>
+        <v>7689.902862985686</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9661582176104914</v>
+        <v>0.891939654668184</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2247040787358583</v>
+        <v>0.3990305373486411</v>
       </c>
       <c r="Q25" t="n">
-        <v>9.406084022351733e-05</v>
+        <v>0.0001273713235692751</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0569555174836748</v>
+        <v>0.1314967963265297</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0009492586247279134</v>
+        <v>0.002191613272108827</v>
       </c>
       <c r="T25" t="n">
-        <v>4.450297500720978</v>
+        <v>2.50607386252817</v>
       </c>
       <c r="U25" t="n">
-        <v>10091.9641210113</v>
+        <v>17206.48895445329</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fable 5 (xhigh) (with fallback)</t>
+          <t>GPT-5.6 Sol (xhigh)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.6601695603875121</v>
+        <v>0.633388342362512</v>
       </c>
       <c r="F26" t="n">
-        <v>0.651917404129794</v>
+        <v>0.669616519174041</v>
       </c>
       <c r="G26" t="n">
-        <v>0.868913857677903</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="H26" t="n">
-        <v>0.459677419354839</v>
+        <v>0.432795698924731</v>
       </c>
       <c r="I26" t="n">
-        <v>8.525764661042945</v>
+        <v>3.736677527198365</v>
       </c>
       <c r="J26" t="n">
-        <v>1028.54882822086</v>
+        <v>440.5130695296522</v>
       </c>
       <c r="K26" t="n">
-        <v>108.2208588957055</v>
+        <v>93.87525562372188</v>
       </c>
       <c r="L26" t="n">
-        <v>10319338.81901841</v>
+        <v>9886595.803681007</v>
       </c>
       <c r="M26" t="n">
-        <v>5134138.567484663</v>
+        <v>5095034.968302658</v>
       </c>
       <c r="N26" t="n">
-        <v>52975.96319018405</v>
+        <v>25684.60429447853</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9637652234526964</v>
+        <v>0.9080963249335339</v>
       </c>
       <c r="P26" t="n">
-        <v>0.07743229922871861</v>
+        <v>0.1695057541766001</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.397401732471733e-05</v>
+        <v>6.406536232893095e-05</v>
       </c>
       <c r="R26" t="n">
-        <v>0.03851073720220626</v>
+        <v>0.08627054035497261</v>
       </c>
       <c r="S26" t="n">
-        <v>0.000641845620036771</v>
+        <v>0.001437842339249544</v>
       </c>
       <c r="T26" t="n">
-        <v>12.91450738207078</v>
+        <v>5.89950473868956</v>
       </c>
       <c r="U26" t="n">
-        <v>10032.91096725896</v>
+        <v>22443.36544710738</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (none)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.4336881923573268</v>
+        <v>0.6131027159527611</v>
       </c>
       <c r="F27" t="n">
-        <v>0.353982300884956</v>
+        <v>0.519174041297935</v>
       </c>
       <c r="G27" t="n">
-        <v>0.602996254681648</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H27" t="n">
-        <v>0.344086021505376</v>
+        <v>0.481182795698925</v>
       </c>
       <c r="I27" t="n">
-        <v>1.086854643353786</v>
+        <v>3.230610966002048</v>
       </c>
       <c r="J27" t="n">
-        <v>197.8853650306747</v>
+        <v>1792.147180981595</v>
       </c>
       <c r="K27" t="n">
-        <v>55.10736196319019</v>
+        <v>159.5848670756646</v>
       </c>
       <c r="L27" t="n">
-        <v>3404912.347648262</v>
+        <v>12503741.56441719</v>
       </c>
       <c r="M27" t="n">
-        <v>1731981.235173824</v>
+        <v>6469207.32413088</v>
       </c>
       <c r="N27" t="n">
-        <v>7689.902862985686</v>
+        <v>63117.84253578731</v>
       </c>
       <c r="O27" t="n">
-        <v>0.891939654668184</v>
+        <v>0.8998815214008218</v>
       </c>
       <c r="P27" t="n">
-        <v>0.3990305373486411</v>
+        <v>0.189779184929682</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.0001273713235692751</v>
+        <v>4.90335403042488e-05</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1314967963265297</v>
+        <v>0.02052630684998603</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002191613272108827</v>
+        <v>0.0003421051141664338</v>
       </c>
       <c r="T27" t="n">
-        <v>2.50607386252817</v>
+        <v>5.269281772764097</v>
       </c>
       <c r="U27" t="n">
-        <v>17206.48895445329</v>
+        <v>6976.96132165252</v>
       </c>
     </row>
     <row r="28">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (xhigh)</t>
+          <t>GPT-5.6 Luna (low)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2443,201 +2443,201 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.633388342362512</v>
+        <v>0.250636604330228</v>
       </c>
       <c r="F28" t="n">
-        <v>0.669616519174041</v>
+        <v>0.103244837758112</v>
       </c>
       <c r="G28" t="n">
-        <v>0.797752808988764</v>
+        <v>0.49812734082397</v>
       </c>
       <c r="H28" t="n">
-        <v>0.432795698924731</v>
+        <v>0.150537634408602</v>
       </c>
       <c r="I28" t="n">
-        <v>3.736677527198365</v>
+        <v>0.03893760139059304</v>
       </c>
       <c r="J28" t="n">
-        <v>440.5130695296522</v>
+        <v>100.0260337423312</v>
       </c>
       <c r="K28" t="n">
-        <v>93.87525562372188</v>
+        <v>34.30674846625767</v>
       </c>
       <c r="L28" t="n">
-        <v>9886595.803681007</v>
+        <v>1435665.844580776</v>
       </c>
       <c r="M28" t="n">
-        <v>5095034.968302658</v>
+        <v>762148.6063394684</v>
       </c>
       <c r="N28" t="n">
-        <v>25684.60429447853</v>
+        <v>5609.407975460122</v>
       </c>
       <c r="O28" t="n">
-        <v>0.9080963249335335</v>
+        <v>0.8430087375482057</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1695057541766001</v>
+        <v>6.436878374094698</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.406536232893095e-05</v>
+        <v>0.0001745786495348544</v>
       </c>
       <c r="R28" t="n">
-        <v>0.08627054035497261</v>
+        <v>0.1503428227350525</v>
       </c>
       <c r="S28" t="n">
-        <v>0.001437842339249544</v>
+        <v>0.002505713712250875</v>
       </c>
       <c r="T28" t="n">
-        <v>5.89950473868956</v>
+        <v>0.1553548073899474</v>
       </c>
       <c r="U28" t="n">
-        <v>22443.36544710738</v>
+        <v>14352.92184311812</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>GPT-5.6 Terra (medium)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.6131027159527611</v>
+        <v>0.4804969202427884</v>
       </c>
       <c r="F29" t="n">
-        <v>0.519174041297935</v>
+        <v>0.457227138643068</v>
       </c>
       <c r="G29" t="n">
-        <v>0.838951310861423</v>
+        <v>0.696629213483146</v>
       </c>
       <c r="H29" t="n">
-        <v>0.481182795698925</v>
+        <v>0.287634408602151</v>
       </c>
       <c r="I29" t="n">
-        <v>3.230610966002044</v>
+        <v>0.6699985707566464</v>
       </c>
       <c r="J29" t="n">
-        <v>1792.147180981595</v>
+        <v>240.094656441718</v>
       </c>
       <c r="K29" t="n">
-        <v>159.5848670756646</v>
+        <v>50.95501022494887</v>
       </c>
       <c r="L29" t="n">
-        <v>12503741.56441719</v>
+        <v>3164606.548057258</v>
       </c>
       <c r="M29" t="n">
-        <v>6469207.32413088</v>
+        <v>1632285.212678937</v>
       </c>
       <c r="N29" t="n">
-        <v>63117.84253578731</v>
+        <v>11855.54703476483</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8998815214008218</v>
+        <v>0.8944384528371324</v>
       </c>
       <c r="P29" t="n">
-        <v>0.1897791849296822</v>
+        <v>0.7171611122993159</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.90335403042488e-05</v>
+        <v>0.0001518346476713713</v>
       </c>
       <c r="R29" t="n">
-        <v>0.02052630684998603</v>
+        <v>0.1200768715215685</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0003421051141664338</v>
+        <v>0.002001281192026142</v>
       </c>
       <c r="T29" t="n">
-        <v>5.26928177276409</v>
+        <v>1.394386816086366</v>
       </c>
       <c r="U29" t="n">
-        <v>6976.96132165252</v>
+        <v>13180.66213949852</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (low)</t>
+          <t>Fable 5 (medium) (with fallback)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.250636604330228</v>
+        <v>0.6319556485024607</v>
       </c>
       <c r="F30" t="n">
-        <v>0.103244837758112</v>
+        <v>0.63716814159292</v>
       </c>
       <c r="G30" t="n">
-        <v>0.49812734082397</v>
+        <v>0.868913857677903</v>
       </c>
       <c r="H30" t="n">
-        <v>0.150537634408602</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="I30" t="n">
-        <v>0.03893760139059304</v>
+        <v>4.735521248977506</v>
       </c>
       <c r="J30" t="n">
-        <v>100.0260337423312</v>
+        <v>661.8129744376279</v>
       </c>
       <c r="K30" t="n">
-        <v>34.30674846625767</v>
+        <v>72.83793456032718</v>
       </c>
       <c r="L30" t="n">
-        <v>1435665.844580776</v>
+        <v>5651155.150306753</v>
       </c>
       <c r="M30" t="n">
-        <v>762148.6063394684</v>
+        <v>2811199.134969325</v>
       </c>
       <c r="N30" t="n">
-        <v>5609.407975460122</v>
+        <v>29358.40797546012</v>
       </c>
       <c r="O30" t="n">
-        <v>0.8430087375482054</v>
+        <v>0.9633202755012386</v>
       </c>
       <c r="P30" t="n">
-        <v>6.436878374094698</v>
+        <v>0.1334500713388019</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0001745786495348544</v>
+        <v>0.0001118276939305333</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1503428227350525</v>
+        <v>0.0572931332184409</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002505713712250876</v>
+        <v>0.0009548855536406817</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1553548073899474</v>
+        <v>7.493439231375218</v>
       </c>
       <c r="U30" t="n">
-        <v>14352.92184311813</v>
+        <v>8538.90051809394</v>
       </c>
     </row>
     <row r="31">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (medium)</t>
+          <t>GPT-5.6 Terra (xhigh)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2662,274 +2662,274 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.4804969202427884</v>
+        <v>0.5602917313962741</v>
       </c>
       <c r="F31" t="n">
-        <v>0.457227138643068</v>
+        <v>0.584070796460177</v>
       </c>
       <c r="G31" t="n">
-        <v>0.696629213483146</v>
+        <v>0.771535580524344</v>
       </c>
       <c r="H31" t="n">
-        <v>0.287634408602151</v>
+        <v>0.325268817204301</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6699985707566459</v>
+        <v>1.358856920245396</v>
       </c>
       <c r="J31" t="n">
-        <v>240.094656441718</v>
+        <v>403.2234447852761</v>
       </c>
       <c r="K31" t="n">
-        <v>50.95501022494887</v>
+        <v>74.95092024539876</v>
       </c>
       <c r="L31" t="n">
-        <v>3164606.54805726</v>
+        <v>6631652.208588957</v>
       </c>
       <c r="M31" t="n">
-        <v>1632285.212678937</v>
+        <v>3404439.702453988</v>
       </c>
       <c r="N31" t="n">
-        <v>11855.54703476483</v>
+        <v>26011.59611451943</v>
       </c>
       <c r="O31" t="n">
-        <v>0.894438452837132</v>
+        <v>0.910418152728672</v>
       </c>
       <c r="P31" t="n">
-        <v>0.7171611122993163</v>
+        <v>0.4123257740006144</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0001518346476713712</v>
+        <v>8.448750232568207e-05</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1200768715215685</v>
+        <v>0.08337189793534547</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002001281192026142</v>
+        <v>0.001389531632255758</v>
       </c>
       <c r="T31" t="n">
-        <v>1.394386816086365</v>
+        <v>2.425266774612324</v>
       </c>
       <c r="U31" t="n">
-        <v>13180.66213949853</v>
+        <v>16446.59380389063</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fable 5 (medium) (with fallback)</t>
+          <t>GPT-5.6 Sol (high)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.6319556485024607</v>
+        <v>0.6411644486641197</v>
       </c>
       <c r="F32" t="n">
-        <v>0.63716814159292</v>
+        <v>0.648967551622419</v>
       </c>
       <c r="G32" t="n">
-        <v>0.868913857677903</v>
+        <v>0.820224719101123</v>
       </c>
       <c r="H32" t="n">
-        <v>0.389784946236559</v>
+        <v>0.454301075268817</v>
       </c>
       <c r="I32" t="n">
-        <v>4.735521248977506</v>
+        <v>3.000466998773008</v>
       </c>
       <c r="J32" t="n">
-        <v>661.8129744376279</v>
+        <v>369.9402760736197</v>
       </c>
       <c r="K32" t="n">
-        <v>72.83793456032718</v>
+        <v>84.6717791411043</v>
       </c>
       <c r="L32" t="n">
-        <v>5651155.150306753</v>
+        <v>8030278.504089993</v>
       </c>
       <c r="M32" t="n">
-        <v>2811199.134969325</v>
+        <v>4136516.062372188</v>
       </c>
       <c r="N32" t="n">
-        <v>29358.40797546012</v>
+        <v>19997.77709611452</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9633202755012389</v>
+        <v>0.9060190184699437</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1334500713388019</v>
+        <v>0.2136882188427046</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.0001118276939305333</v>
+        <v>7.984336388053799e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0572931332184409</v>
+        <v>0.1039893988514825</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0009548855536406817</v>
+        <v>0.001733156647524708</v>
       </c>
       <c r="T32" t="n">
-        <v>7.493439231375218</v>
+        <v>4.679715172955312</v>
       </c>
       <c r="U32" t="n">
-        <v>8538.90051809394</v>
+        <v>21706.95926737086</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra (xhigh)</t>
+          <t>Opus 4.8 (max)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.5602917313962744</v>
+        <v>0.6214051234130329</v>
       </c>
       <c r="F33" t="n">
-        <v>0.584070796460177</v>
+        <v>0.557522123893805</v>
       </c>
       <c r="G33" t="n">
-        <v>0.771535580524345</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H33" t="n">
-        <v>0.325268817204301</v>
+        <v>0.467741935483871</v>
       </c>
       <c r="I33" t="n">
-        <v>1.358856920245396</v>
+        <v>7.724725797009214</v>
       </c>
       <c r="J33" t="n">
-        <v>403.2234447852761</v>
+        <v>1386.687798057262</v>
       </c>
       <c r="K33" t="n">
-        <v>74.95092024539876</v>
+        <v>165.0175845341703</v>
       </c>
       <c r="L33" t="n">
-        <v>6631652.208588957</v>
+        <v>17920579.42791411</v>
       </c>
       <c r="M33" t="n">
-        <v>3404439.702453988</v>
+        <v>8919829.832822086</v>
       </c>
       <c r="N33" t="n">
-        <v>26011.59611451943</v>
+        <v>89374.98517382414</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9104181527286717</v>
+        <v>0.9657541826994763</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4123257740006146</v>
+        <v>0.08044364806497373</v>
       </c>
       <c r="Q33" t="n">
-        <v>8.448750232568211e-05</v>
+        <v>3.467550398761645e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>0.08337189793534551</v>
+        <v>0.02688731195083492</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001389531632255759</v>
+        <v>0.0004481218658472487</v>
       </c>
       <c r="T33" t="n">
-        <v>2.425266774612322</v>
+        <v>12.43106229086363</v>
       </c>
       <c r="U33" t="n">
-        <v>16446.59380389063</v>
+        <v>12923.29784182185</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (high)</t>
+          <t>Opus 4.8 (medium)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.6411644486641199</v>
+        <v>0.5576883805320427</v>
       </c>
       <c r="F34" t="n">
-        <v>0.648967551622419</v>
+        <v>0.492625368731563</v>
       </c>
       <c r="G34" t="n">
         <v>0.820224719101124</v>
       </c>
       <c r="H34" t="n">
-        <v>0.454301075268817</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I34" t="n">
-        <v>3.000466998773005</v>
+        <v>3.303841633946831</v>
       </c>
       <c r="J34" t="n">
-        <v>369.9402760736197</v>
+        <v>722.922882413088</v>
       </c>
       <c r="K34" t="n">
-        <v>84.6717791411043</v>
+        <v>92.91239658858525</v>
       </c>
       <c r="L34" t="n">
-        <v>8030278.504089991</v>
+        <v>7827354.369120649</v>
       </c>
       <c r="M34" t="n">
-        <v>4136516.062372188</v>
+        <v>3898584.399795501</v>
       </c>
       <c r="N34" t="n">
-        <v>19997.77709611452</v>
+        <v>34668.28732106339</v>
       </c>
       <c r="O34" t="n">
-        <v>0.906019018469944</v>
+        <v>0.9638401283466974</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2136882188427049</v>
+        <v>0.168799973582819</v>
       </c>
       <c r="Q34" t="n">
-        <v>7.984336388053805e-05</v>
+        <v>7.12486434410271e-05</v>
       </c>
       <c r="R34" t="n">
-        <v>0.1039893988514825</v>
+        <v>0.04628613043791069</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001733156647524709</v>
+        <v>0.0007714355072985115</v>
       </c>
       <c r="T34" t="n">
-        <v>4.679715172955305</v>
+        <v>5.924171543245923</v>
       </c>
       <c r="U34" t="n">
-        <v>21706.95926737085</v>
+        <v>10827.37116162826</v>
       </c>
     </row>
     <row r="35">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Opus 4.8 (max)</t>
+          <t>Opus 5 (none)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2954,128 +2954,128 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.6214051234130329</v>
+        <v>0.5916954363711078</v>
       </c>
       <c r="F35" t="n">
-        <v>0.557522123893805</v>
+        <v>0.442477876106194</v>
       </c>
       <c r="G35" t="n">
-        <v>0.838951310861423</v>
+        <v>0.816479400749064</v>
       </c>
       <c r="H35" t="n">
-        <v>0.467741935483871</v>
+        <v>0.5161290322580649</v>
       </c>
       <c r="I35" t="n">
-        <v>7.724725797009217</v>
+        <v>3.53093715925358</v>
       </c>
       <c r="J35" t="n">
-        <v>1386.687798057262</v>
+        <v>708.6105337423306</v>
       </c>
       <c r="K35" t="n">
-        <v>165.0175845341703</v>
+        <v>60.88548057259713</v>
       </c>
       <c r="L35" t="n">
-        <v>17920579.42791411</v>
+        <v>9164445.860940713</v>
       </c>
       <c r="M35" t="n">
-        <v>8919829.832822086</v>
+        <v>4567008.523517382</v>
       </c>
       <c r="N35" t="n">
-        <v>89374.98517382414</v>
+        <v>31222.43967280163</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9657541826994763</v>
+        <v>0.9712292805469993</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0804436480649737</v>
+        <v>0.1675746153738371</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.467550398761645e-05</v>
+        <v>6.456423501751925e-05</v>
       </c>
       <c r="R35" t="n">
-        <v>0.02688731195083492</v>
+        <v>0.05010047761324393</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0004481218658472487</v>
+        <v>0.0008350079602207322</v>
       </c>
       <c r="T35" t="n">
-        <v>12.43106229086364</v>
+        <v>5.967490945863908</v>
       </c>
       <c r="U35" t="n">
-        <v>12923.29784182185</v>
+        <v>12932.98000036949</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Opus 4.8 (medium)</t>
+          <t>GPT-5.6 Sol (low)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.5576883805320431</v>
+        <v>0.5523451808562164</v>
       </c>
       <c r="F36" t="n">
-        <v>0.492625368731564</v>
+        <v>0.533923303834809</v>
       </c>
       <c r="G36" t="n">
-        <v>0.820224719101124</v>
+        <v>0.779026217228464</v>
       </c>
       <c r="H36" t="n">
-        <v>0.360215053763441</v>
+        <v>0.344086021505376</v>
       </c>
       <c r="I36" t="n">
-        <v>3.303841633946831</v>
+        <v>1.292458844580775</v>
       </c>
       <c r="J36" t="n">
-        <v>722.9228824130877</v>
+        <v>212.899582822086</v>
       </c>
       <c r="K36" t="n">
-        <v>92.91239658858525</v>
+        <v>53.92126789366053</v>
       </c>
       <c r="L36" t="n">
-        <v>7827354.369120649</v>
+        <v>3200236.065439673</v>
       </c>
       <c r="M36" t="n">
-        <v>3898584.399795501</v>
+        <v>1658130.417177914</v>
       </c>
       <c r="N36" t="n">
-        <v>34668.28732106339</v>
+        <v>8962.606339468302</v>
       </c>
       <c r="O36" t="n">
-        <v>0.963840128346697</v>
+        <v>0.8829664546361218</v>
       </c>
       <c r="P36" t="n">
-        <v>0.1687999735828191</v>
+        <v>0.4273599760427007</v>
       </c>
       <c r="Q36" t="n">
-        <v>7.124864344102714e-05</v>
+        <v>0.0001725951365966907</v>
       </c>
       <c r="R36" t="n">
-        <v>0.04628613043791074</v>
+        <v>0.1556635781624227</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0007714355072985123</v>
+        <v>0.002594392969373712</v>
       </c>
       <c r="T36" t="n">
-        <v>5.92417154324592</v>
+        <v>2.339947716348811</v>
       </c>
       <c r="U36" t="n">
-        <v>10827.37116162827</v>
+        <v>15031.6690292156</v>
       </c>
     </row>
     <row r="37">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Opus 5 (none)</t>
+          <t>Opus 4.7 (medium)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3100,128 +3100,128 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.591695436371108</v>
+        <v>0.423892771774363</v>
       </c>
       <c r="F37" t="n">
-        <v>0.442477876106195</v>
+        <v>0.274336283185841</v>
       </c>
       <c r="G37" t="n">
-        <v>0.816479400749064</v>
+        <v>0.771535580524345</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5161290322580649</v>
+        <v>0.225806451612903</v>
       </c>
       <c r="I37" t="n">
-        <v>3.53093715925358</v>
+        <v>1.800661744734152</v>
       </c>
       <c r="J37" t="n">
-        <v>708.6105337423306</v>
+        <v>399.3926789366056</v>
       </c>
       <c r="K37" t="n">
-        <v>60.88548057259713</v>
+        <v>42.04907975460122</v>
       </c>
       <c r="L37" t="n">
-        <v>9164445.860940678</v>
+        <v>4636274.728016362</v>
       </c>
       <c r="M37" t="n">
-        <v>4567008.523517382</v>
+        <v>2310268.645194274</v>
       </c>
       <c r="N37" t="n">
-        <v>31222.43967280163</v>
+        <v>17168.18507157464</v>
       </c>
       <c r="O37" t="n">
-        <v>0.9712292805469996</v>
+        <v>0.9576237577125704</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1675746153738372</v>
+        <v>0.23540943934306</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.456423501751952e-05</v>
+        <v>9.142960601813308e-05</v>
       </c>
       <c r="R37" t="n">
-        <v>0.05010047761324395</v>
+        <v>0.06368060219375923</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0008350079602207325</v>
+        <v>0.001061343369895987</v>
       </c>
       <c r="T37" t="n">
-        <v>5.967490945863906</v>
+        <v>4.247918022279086</v>
       </c>
       <c r="U37" t="n">
-        <v>12932.98000036944</v>
+        <v>11608.31175063242</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (low)</t>
+          <t>Fable 5 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.5523451808562164</v>
+        <v>0.6717276042685724</v>
       </c>
       <c r="F38" t="n">
-        <v>0.533923303834808</v>
+        <v>0.660766961651917</v>
       </c>
       <c r="G38" t="n">
-        <v>0.779026217228465</v>
+        <v>0.865168539325843</v>
       </c>
       <c r="H38" t="n">
-        <v>0.344086021505376</v>
+        <v>0.489247311827957</v>
       </c>
       <c r="I38" t="n">
-        <v>1.292458844580775</v>
+        <v>11.68740762091003</v>
       </c>
       <c r="J38" t="n">
-        <v>212.899582822086</v>
+        <v>1407.30630163599</v>
       </c>
       <c r="K38" t="n">
-        <v>53.92126789366053</v>
+        <v>137.007744236847</v>
       </c>
       <c r="L38" t="n">
-        <v>3200236.065439673</v>
+        <v>13868659.99897749</v>
       </c>
       <c r="M38" t="n">
-        <v>1658130.417177914</v>
+        <v>6901095.023517382</v>
       </c>
       <c r="N38" t="n">
-        <v>8962.606339468302</v>
+        <v>74265.48875255625</v>
       </c>
       <c r="O38" t="n">
-        <v>0.8829664546361214</v>
+        <v>0.9619283373252913</v>
       </c>
       <c r="P38" t="n">
-        <v>0.4273599760427007</v>
+        <v>0.05747447390016411</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0001725951365966907</v>
+        <v>4.843493202069251e-05</v>
       </c>
       <c r="R38" t="n">
-        <v>0.1556635781624227</v>
+        <v>0.02863886576025522</v>
       </c>
       <c r="S38" t="n">
-        <v>0.002594392969373712</v>
+        <v>0.0004773144293375869</v>
       </c>
       <c r="T38" t="n">
-        <v>2.339947716348811</v>
+        <v>17.39902833624971</v>
       </c>
       <c r="U38" t="n">
-        <v>15031.6690292156</v>
+        <v>9854.75584302807</v>
       </c>
     </row>
     <row r="39">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Opus 4.7 (medium)</t>
+          <t>GLM-5.1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3242,132 +3242,132 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>friendliai</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.4238927717743627</v>
+        <v>0.3691032797641257</v>
       </c>
       <c r="F39" t="n">
-        <v>0.274336283185841</v>
+        <v>0.185840707964602</v>
       </c>
       <c r="G39" t="n">
-        <v>0.771535580524344</v>
+        <v>0.6741573033707861</v>
       </c>
       <c r="H39" t="n">
-        <v>0.225806451612903</v>
+        <v>0.247311827956989</v>
       </c>
       <c r="I39" t="n">
-        <v>1.800661744734149</v>
+        <v>4.282000252842536</v>
       </c>
       <c r="J39" t="n">
-        <v>399.3926789366056</v>
+        <v>1140.250613496931</v>
       </c>
       <c r="K39" t="n">
-        <v>42.04907975460122</v>
+        <v>174.2367075664622</v>
       </c>
       <c r="L39" t="n">
-        <v>4636274.728016362</v>
+        <v>25761884.92944783</v>
       </c>
       <c r="M39" t="n">
-        <v>2310268.645194274</v>
+        <v>13139446.7402863</v>
       </c>
       <c r="N39" t="n">
-        <v>17168.18507157464</v>
+        <v>49883.45705521473</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9576237577125707</v>
+        <v>0.888922540999181</v>
       </c>
       <c r="P39" t="n">
-        <v>0.2354094393430603</v>
+        <v>0.08619879915212579</v>
       </c>
       <c r="Q39" t="n">
-        <v>9.142960601813301e-05</v>
+        <v>1.432749508721747e-05</v>
       </c>
       <c r="R39" t="n">
-        <v>0.06368060219375918</v>
+        <v>0.01942221869798375</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001061343369895986</v>
+        <v>0.0003237036449663959</v>
       </c>
       <c r="T39" t="n">
-        <v>4.247918022279082</v>
+        <v>11.60108968844421</v>
       </c>
       <c r="U39" t="n">
-        <v>11608.31175063242</v>
+        <v>22593.17787204784</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fable 5 (max) (with fallback)</t>
+          <t>Gemini 3.7 Flash (high)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.6717276042685724</v>
+        <v>0.5657152973570364</v>
       </c>
       <c r="F40" t="n">
-        <v>0.660766961651917</v>
+        <v>0.56047197640118</v>
       </c>
       <c r="G40" t="n">
         <v>0.865168539325843</v>
       </c>
       <c r="H40" t="n">
-        <v>0.489247311827957</v>
+        <v>0.271505376344086</v>
       </c>
       <c r="I40" t="n">
-        <v>11.68740762091003</v>
+        <v>1.396316917192255</v>
       </c>
       <c r="J40" t="n">
-        <v>1407.30630163599</v>
+        <v>384.9621257668713</v>
       </c>
       <c r="K40" t="n">
-        <v>137.007744236847</v>
+        <v>110.7985685071575</v>
       </c>
       <c r="L40" t="n">
-        <v>13868659.99897749</v>
+        <v>15113684.86595342</v>
       </c>
       <c r="M40" t="n">
-        <v>6901095.023517382</v>
+        <v>7938344.274012004</v>
       </c>
       <c r="N40" t="n">
-        <v>74265.48875255625</v>
+        <v>64430.0844098625</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9619283373252908</v>
+        <v>0.8677594149804605</v>
       </c>
       <c r="P40" t="n">
-        <v>0.05747447390016411</v>
+        <v>0.4051482083985556</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.843493202069251e-05</v>
+        <v>3.743066647045306e-05</v>
       </c>
       <c r="R40" t="n">
-        <v>0.02863886576025522</v>
+        <v>0.08817209686227062</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0004773144293375869</v>
+        <v>0.00146953494770451</v>
       </c>
       <c r="T40" t="n">
-        <v>17.39902833624971</v>
+        <v>2.468232560999683</v>
       </c>
       <c r="U40" t="n">
-        <v>9854.75584302807</v>
+        <v>39260.1865335347</v>
       </c>
     </row>
     <row r="41">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GLM-5.1</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3388,424 +3388,424 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>friendliai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.3691032797641257</v>
+        <v>0.6702814566291138</v>
       </c>
       <c r="F41" t="n">
-        <v>0.185840707964602</v>
+        <v>0.631268436578171</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6741573033707861</v>
+        <v>0.887640449438202</v>
       </c>
       <c r="H41" t="n">
-        <v>0.247311827956989</v>
+        <v>0.491935483870968</v>
       </c>
       <c r="I41" t="n">
-        <v>4.282000252842536</v>
+        <v>8.943547018021484</v>
       </c>
       <c r="J41" t="n">
-        <v>1140.250613496931</v>
+        <v>1451.329194274025</v>
       </c>
       <c r="K41" t="n">
-        <v>174.2367075664622</v>
+        <v>165.7202546941811</v>
       </c>
       <c r="L41" t="n">
-        <v>25761884.92944783</v>
+        <v>23699428.05214722</v>
       </c>
       <c r="M41" t="n">
-        <v>13139446.7402863</v>
+        <v>11810977.87014315</v>
       </c>
       <c r="N41" t="n">
-        <v>49883.45705521473</v>
+        <v>81385.06339468302</v>
       </c>
       <c r="O41" t="n">
-        <v>0.8889225409991813</v>
+        <v>0.974703359327879</v>
       </c>
       <c r="P41" t="n">
-        <v>0.08619879915212579</v>
+        <v>0.07494581906691818</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.432749508721747e-05</v>
+        <v>2.828260054015881e-05</v>
       </c>
       <c r="R41" t="n">
-        <v>0.01942221869798375</v>
+        <v>0.02771038270050364</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0003237036449663959</v>
+        <v>0.0004618397116750606</v>
       </c>
       <c r="T41" t="n">
-        <v>11.60108968844421</v>
+        <v>13.34297246264148</v>
       </c>
       <c r="U41" t="n">
-        <v>22593.17787204784</v>
+        <v>16329.46415303249</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.8</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash (high)</t>
+          <t>GPT-5.6 Luna (medium)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.5657152973570364</v>
+        <v>0.4196699779001627</v>
       </c>
       <c r="F42" t="n">
-        <v>0.56047197640118</v>
+        <v>0.365781710914454</v>
       </c>
       <c r="G42" t="n">
-        <v>0.865168539325843</v>
+        <v>0.621722846441948</v>
       </c>
       <c r="H42" t="n">
         <v>0.271505376344086</v>
       </c>
       <c r="I42" t="n">
-        <v>1.396316917192255</v>
+        <v>0.08841796668711666</v>
       </c>
       <c r="J42" t="n">
-        <v>384.9621257668713</v>
+        <v>191.3819171779141</v>
       </c>
       <c r="K42" t="n">
-        <v>110.7985685071575</v>
+        <v>57.08588957055215</v>
       </c>
       <c r="L42" t="n">
-        <v>15113684.86595342</v>
+        <v>4287327.734151328</v>
       </c>
       <c r="M42" t="n">
-        <v>7938344.274012004</v>
+        <v>2221162.702453987</v>
       </c>
       <c r="N42" t="n">
-        <v>64430.0844098625</v>
+        <v>11663.1390593047</v>
       </c>
       <c r="O42" t="n">
-        <v>0.8677594149804605</v>
+        <v>0.8832984632099318</v>
       </c>
       <c r="P42" t="n">
-        <v>0.4051482083985556</v>
+        <v>4.746433260394266</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.743066647045306e-05</v>
+        <v>9.788614351947506e-05</v>
       </c>
       <c r="R42" t="n">
-        <v>0.08817209686227062</v>
+        <v>0.1315704171288112</v>
       </c>
       <c r="S42" t="n">
-        <v>0.00146953494770451</v>
+        <v>0.002192840285480187</v>
       </c>
       <c r="T42" t="n">
-        <v>2.468232560999683</v>
+        <v>0.2106845172235571</v>
       </c>
       <c r="U42" t="n">
-        <v>39260.1865335347</v>
+        <v>22401.94788186653</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.6702814566291138</v>
+        <v>0.6505240024334411</v>
       </c>
       <c r="F43" t="n">
-        <v>0.631268436578171</v>
+        <v>0.687315634218289</v>
       </c>
       <c r="G43" t="n">
-        <v>0.887640449438202</v>
+        <v>0.831460674157303</v>
       </c>
       <c r="H43" t="n">
-        <v>0.491935483870968</v>
+        <v>0.432795698924731</v>
       </c>
       <c r="I43" t="n">
-        <v>8.943547018021487</v>
+        <v>4.995463274846626</v>
       </c>
       <c r="J43" t="n">
-        <v>1451.329194274025</v>
+        <v>613.70177198364</v>
       </c>
       <c r="K43" t="n">
-        <v>165.7202546941811</v>
+        <v>112.2689161554192</v>
       </c>
       <c r="L43" t="n">
-        <v>23699428.05214722</v>
+        <v>13169248.79601226</v>
       </c>
       <c r="M43" t="n">
-        <v>11810977.87014315</v>
+        <v>6786107.398261759</v>
       </c>
       <c r="N43" t="n">
-        <v>81385.06339468302</v>
+        <v>35184.01329243354</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9747033593278783</v>
+        <v>0.902597320865973</v>
       </c>
       <c r="P43" t="n">
-        <v>0.07494581906691815</v>
+        <v>0.1302229576401828</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.82826005401588e-05</v>
+        <v>4.939719892226686e-05</v>
       </c>
       <c r="R43" t="n">
-        <v>0.02771038270050364</v>
+        <v>0.06360001213593849</v>
       </c>
       <c r="S43" t="n">
-        <v>0.0004618397116750606</v>
+        <v>0.001060000202265642</v>
       </c>
       <c r="T43" t="n">
-        <v>13.34297246264148</v>
+        <v>7.679137520152826</v>
       </c>
       <c r="U43" t="n">
-        <v>16329.4641530325</v>
+        <v>21458.71072434076</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (medium)</t>
+          <t>Kimi K2.6</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.4196699779001627</v>
+        <v>0.3388925953605663</v>
       </c>
       <c r="F44" t="n">
-        <v>0.365781710914454</v>
+        <v>0.165191740412979</v>
       </c>
       <c r="G44" t="n">
-        <v>0.621722846441948</v>
+        <v>0.6928838951310859</v>
       </c>
       <c r="H44" t="n">
-        <v>0.271505376344086</v>
+        <v>0.158602150537634</v>
       </c>
       <c r="I44" t="n">
-        <v>0.08841796668711666</v>
+        <v>1.21710007411043</v>
       </c>
       <c r="J44" t="n">
-        <v>191.3819171779141</v>
+        <v>2443.385067484662</v>
       </c>
       <c r="K44" t="n">
-        <v>57.08588957055215</v>
+        <v>133.7675410760877</v>
       </c>
       <c r="L44" t="n">
-        <v>4287327.734151328</v>
+        <v>11660527.81595092</v>
       </c>
       <c r="M44" t="n">
-        <v>2221162.702453987</v>
+        <v>5891966.377300614</v>
       </c>
       <c r="N44" t="n">
-        <v>11663.1390593047</v>
+        <v>36930.17791411043</v>
       </c>
       <c r="O44" t="n">
-        <v>0.8832984632099318</v>
+        <v>0.9554328157869916</v>
       </c>
       <c r="P44" t="n">
-        <v>4.746433260394266</v>
+        <v>0.2784426708775453</v>
       </c>
       <c r="Q44" t="n">
-        <v>9.788614351947506e-05</v>
+        <v>2.906322944463811e-05</v>
       </c>
       <c r="R44" t="n">
-        <v>0.1315704171288112</v>
+        <v>0.008321879343629747</v>
       </c>
       <c r="S44" t="n">
-        <v>0.002192840285480187</v>
+        <v>0.0001386979890604958</v>
       </c>
       <c r="T44" t="n">
-        <v>0.2106845172235571</v>
+        <v>3.591403561991346</v>
       </c>
       <c r="U44" t="n">
-        <v>22401.94788186653</v>
+        <v>4772.284144289555</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Opus 4.8 (xhigh)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.6505240024334414</v>
+        <v>0.590718121759733</v>
       </c>
       <c r="F45" t="n">
-        <v>0.687315634218289</v>
+        <v>0.513274336283186</v>
       </c>
       <c r="G45" t="n">
-        <v>0.831460674157304</v>
+        <v>0.831460674157303</v>
       </c>
       <c r="H45" t="n">
-        <v>0.432795698924731</v>
+        <v>0.42741935483871</v>
       </c>
       <c r="I45" t="n">
-        <v>4.995463274846626</v>
+        <v>5.665366469580767</v>
       </c>
       <c r="J45" t="n">
-        <v>613.70177198364</v>
+        <v>1065.615385480574</v>
       </c>
       <c r="K45" t="n">
-        <v>112.2689161554192</v>
+        <v>136.1303390500093</v>
       </c>
       <c r="L45" t="n">
-        <v>13169248.79601226</v>
+        <v>13628306.24233129</v>
       </c>
       <c r="M45" t="n">
-        <v>6786107.398261759</v>
+        <v>6783846.309815951</v>
       </c>
       <c r="N45" t="n">
-        <v>35184.01329243354</v>
+        <v>62541.86503067485</v>
       </c>
       <c r="O45" t="n">
-        <v>0.902597320865973</v>
+        <v>0.9687226730983397</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1302229576401829</v>
+        <v>0.104268298428971</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.939719892226689e-05</v>
+        <v>4.3344940395079e-05</v>
       </c>
       <c r="R45" t="n">
-        <v>0.06360001213593852</v>
+        <v>0.03326067527600474</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001060000202265642</v>
+        <v>0.0005543445879334123</v>
       </c>
       <c r="T45" t="n">
-        <v>7.679137520152823</v>
+        <v>9.590642746330172</v>
       </c>
       <c r="U45" t="n">
-        <v>21458.71072434076</v>
+        <v>12789.14177481134</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kimi K2.6</t>
+          <t>GPT-5.6 Luna (xhigh)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.3388925953605663</v>
+        <v>0.529584326329171</v>
       </c>
       <c r="F46" t="n">
-        <v>0.165191740412979</v>
+        <v>0.566371681415929</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6928838951310859</v>
+        <v>0.707865168539326</v>
       </c>
       <c r="H46" t="n">
-        <v>0.158602150537634</v>
+        <v>0.314516129032258</v>
       </c>
       <c r="I46" t="n">
-        <v>1.21710007411043</v>
+        <v>0.235909783783231</v>
       </c>
       <c r="J46" t="n">
-        <v>2443.385067484662</v>
+        <v>413.8987709611452</v>
       </c>
       <c r="K46" t="n">
-        <v>133.7675410760877</v>
+        <v>96.1922290388548</v>
       </c>
       <c r="L46" t="n">
-        <v>11660527.81595092</v>
+        <v>12806609.00511247</v>
       </c>
       <c r="M46" t="n">
-        <v>5891966.377300614</v>
+        <v>6575104.906952964</v>
       </c>
       <c r="N46" t="n">
-        <v>36930.17791411043</v>
+        <v>30840.24642126789</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9554328157869918</v>
+        <v>0.910023539336985</v>
       </c>
       <c r="P46" t="n">
-        <v>0.2784426708775453</v>
+        <v>2.244859529928555</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.906322944463811e-05</v>
+        <v>4.135242405837159e-05</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008321879343629747</v>
+        <v>0.07677012305681175</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0001386979890604958</v>
+        <v>0.001279502050946862</v>
       </c>
       <c r="T46" t="n">
-        <v>3.591403561991346</v>
+        <v>0.4454621710926501</v>
       </c>
       <c r="U46" t="n">
-        <v>4772.284144289555</v>
+        <v>30941.40380115961</v>
       </c>
     </row>
     <row r="47">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>GPT-5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3830,55 +3830,55 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.5716614223656344</v>
+        <v>0.6103327520587847</v>
       </c>
       <c r="F47" t="n">
-        <v>0.634218289085546</v>
+        <v>0.64306784660767</v>
       </c>
       <c r="G47" t="n">
-        <v>0.752808988764045</v>
+        <v>0.827715355805243</v>
       </c>
       <c r="H47" t="n">
-        <v>0.327956989247312</v>
+        <v>0.360215053763441</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2882767483844579</v>
+        <v>4.75237007157464</v>
       </c>
       <c r="J47" t="n">
-        <v>482.0907147239265</v>
+        <v>614.9898987730064</v>
       </c>
       <c r="K47" t="n">
-        <v>114.6288343558282</v>
+        <v>107.1319018404908</v>
       </c>
       <c r="L47" t="n">
-        <v>15963259.28016359</v>
+        <v>12150851.17995912</v>
       </c>
       <c r="M47" t="n">
-        <v>8170928.992842535</v>
+        <v>6164087.486707566</v>
       </c>
       <c r="N47" t="n">
-        <v>41094.49386503067</v>
+        <v>25286.0654396728</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9181831202060824</v>
+        <v>0.9341674523911521</v>
       </c>
       <c r="P47" t="n">
-        <v>1.983029937618288</v>
+        <v>0.1284270254350285</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.58110716823348e-05</v>
+        <v>5.022962943249859e-05</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0711477825528751</v>
+        <v>0.0595456367601959</v>
       </c>
       <c r="S47" t="n">
-        <v>0.001185796375881252</v>
+        <v>0.0009924272793365983</v>
       </c>
       <c r="T47" t="n">
-        <v>0.5042788215295665</v>
+        <v>7.786523098332615</v>
       </c>
       <c r="U47" t="n">
-        <v>33112.56324300934</v>
+        <v>19757.8061106399</v>
       </c>
     </row>
     <row r="48">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (xhigh)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3903,55 +3903,55 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.529584326329171</v>
+        <v>0.5716614223656344</v>
       </c>
       <c r="F48" t="n">
-        <v>0.566371681415929</v>
+        <v>0.634218289085546</v>
       </c>
       <c r="G48" t="n">
-        <v>0.707865168539326</v>
+        <v>0.752808988764045</v>
       </c>
       <c r="H48" t="n">
-        <v>0.314516129032258</v>
+        <v>0.327956989247312</v>
       </c>
       <c r="I48" t="n">
-        <v>0.235909783783231</v>
+        <v>0.2882767483844579</v>
       </c>
       <c r="J48" t="n">
-        <v>413.8987709611455</v>
+        <v>482.0907147239265</v>
       </c>
       <c r="K48" t="n">
-        <v>96.1922290388548</v>
+        <v>114.6288343558282</v>
       </c>
       <c r="L48" t="n">
-        <v>12806609.00511247</v>
+        <v>15963259.28016359</v>
       </c>
       <c r="M48" t="n">
-        <v>6575104.906952964</v>
+        <v>8170928.992842535</v>
       </c>
       <c r="N48" t="n">
-        <v>30840.24642126789</v>
+        <v>41094.49386503067</v>
       </c>
       <c r="O48" t="n">
-        <v>0.9100235393369858</v>
+        <v>0.9181831202060824</v>
       </c>
       <c r="P48" t="n">
-        <v>2.244859529928555</v>
+        <v>1.983029937618288</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.135242405837159e-05</v>
+        <v>3.58110716823348e-05</v>
       </c>
       <c r="R48" t="n">
-        <v>0.07677012305681169</v>
+        <v>0.0711477825528751</v>
       </c>
       <c r="S48" t="n">
-        <v>0.001279502050946862</v>
+        <v>0.001185796375881252</v>
       </c>
       <c r="T48" t="n">
-        <v>0.4454621710926501</v>
+        <v>0.5042788215295665</v>
       </c>
       <c r="U48" t="n">
-        <v>30941.40380115958</v>
+        <v>33112.56324300934</v>
       </c>
     </row>
     <row r="49">
@@ -4070,7 +4070,7 @@
         <v>128.1457055214724</v>
       </c>
       <c r="L50" t="n">
-        <v>9942165.528629858</v>
+        <v>9942165.52862986</v>
       </c>
       <c r="M50" t="n">
         <v>5181244.880368099</v>
@@ -4097,7 +4097,7 @@
         <v>0.77593622002864</v>
       </c>
       <c r="U50" t="n">
-        <v>9269.809250112252</v>
+        <v>9269.809250112254</v>
       </c>
     </row>
     <row r="51">
@@ -4152,7 +4152,7 @@
         <v>37331.49386503067</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9702723303233399</v>
+        <v>0.9702723303233403</v>
       </c>
       <c r="P51" t="n">
         <v>0.1674507672197952</v>
@@ -4362,7 +4362,7 @@
         <v>85.64621676891616</v>
       </c>
       <c r="L54" t="n">
-        <v>7097848.362985685</v>
+        <v>7097848.362985681</v>
       </c>
       <c r="M54" t="n">
         <v>3530817.211656442</v>
@@ -4371,13 +4371,13 @@
         <v>37468.96625766872</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9637766239989285</v>
+        <v>0.9637766239989286</v>
       </c>
       <c r="P54" t="n">
         <v>0.1090722005384973</v>
       </c>
       <c r="Q54" t="n">
-        <v>9.175590278393167e-05</v>
+        <v>9.175590278393172e-05</v>
       </c>
       <c r="R54" t="n">
         <v>0.05342818151634792</v>
@@ -4389,7 +4389,7 @@
         <v>9.168238974394281</v>
       </c>
       <c r="U54" t="n">
-        <v>9704.767376503558</v>
+        <v>9704.767376503551</v>
       </c>
     </row>
     <row r="55">
@@ -4429,13 +4429,13 @@
         <v>0.09081146755368105</v>
       </c>
       <c r="J55" t="n">
-        <v>743.5829417177918</v>
+        <v>743.5829417177914</v>
       </c>
       <c r="K55" t="n">
         <v>66.08691206543966</v>
       </c>
       <c r="L55" t="n">
-        <v>12713750.95194277</v>
+        <v>12713750.95194274</v>
       </c>
       <c r="M55" t="n">
         <v>6378205.537321064</v>
@@ -4450,19 +4450,19 @@
         <v>4.710825220261948</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.364836650158773e-05</v>
+        <v>3.364836650158783e-05</v>
       </c>
       <c r="R55" t="n">
-        <v>0.03451910426986959</v>
+        <v>0.03451910426986961</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0005753184044978266</v>
+        <v>0.0005753184044978268</v>
       </c>
       <c r="T55" t="n">
         <v>0.2122770328431744</v>
       </c>
       <c r="U55" t="n">
-        <v>17097.95940527097</v>
+        <v>17097.95940527093</v>
       </c>
     </row>
     <row r="56">
@@ -4502,7 +4502,7 @@
         <v>1.140926299999998</v>
       </c>
       <c r="J56" t="n">
-        <v>358.7396482617588</v>
+        <v>358.7396482617585</v>
       </c>
       <c r="K56" t="n">
         <v>67.06952965235175</v>
@@ -4517,7 +4517,7 @@
         <v>20902.66564417178</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9049339862289006</v>
+        <v>0.9049339862289004</v>
       </c>
       <c r="P56" t="n">
         <v>0.478965837655659</v>
@@ -4526,16 +4526,16 @@
         <v>9.757818061694565e-05</v>
       </c>
       <c r="R56" t="n">
-        <v>0.09139743381542303</v>
+        <v>0.09139743381542312</v>
       </c>
       <c r="S56" t="n">
-        <v>0.001523290563590384</v>
+        <v>0.001523290563590385</v>
       </c>
       <c r="T56" t="n">
         <v>2.087831576662313</v>
       </c>
       <c r="U56" t="n">
-        <v>15610.97526065008</v>
+        <v>15610.9752606501</v>
       </c>
     </row>
     <row r="57">
@@ -4572,7 +4572,7 @@
         <v>0.370967741935484</v>
       </c>
       <c r="I57" t="n">
-        <v>5.915424259100206</v>
+        <v>5.915424259100202</v>
       </c>
       <c r="J57" t="n">
         <v>950.312358895707</v>
@@ -4590,10 +4590,10 @@
         <v>47224.16462167689</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9665216325317721</v>
+        <v>0.9665216325317719</v>
       </c>
       <c r="P57" t="n">
-        <v>0.08719738512044993</v>
+        <v>0.08719738512044999</v>
       </c>
       <c r="Q57" t="n">
         <v>3.197882093879829e-05</v>
@@ -4605,7 +4605,7 @@
         <v>0.0005427789320460904</v>
       </c>
       <c r="T57" t="n">
-        <v>11.46823380791353</v>
+        <v>11.46823380791352</v>
       </c>
       <c r="U57" t="n">
         <v>16973.07518263015</v>
@@ -4648,13 +4648,13 @@
         <v>3.171867192484664</v>
       </c>
       <c r="J58" t="n">
-        <v>730.9243895705519</v>
+        <v>730.924389570552</v>
       </c>
       <c r="K58" t="n">
         <v>83.47801635991821</v>
       </c>
       <c r="L58" t="n">
-        <v>7999358.108384448</v>
+        <v>7999358.108384455</v>
       </c>
       <c r="M58" t="n">
         <v>3984815.59611452</v>
@@ -4663,25 +4663,25 @@
         <v>30206.12781186094</v>
       </c>
       <c r="O58" t="n">
-        <v>0.9695331242878965</v>
+        <v>0.9695331242878967</v>
       </c>
       <c r="P58" t="n">
         <v>0.2019897766252884</v>
       </c>
       <c r="Q58" t="n">
-        <v>8.009201951135686e-05</v>
+        <v>8.00920195113568e-05</v>
       </c>
       <c r="R58" t="n">
         <v>0.05259242308809697</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0008765403848016162</v>
+        <v>0.0008765403848016161</v>
       </c>
       <c r="T58" t="n">
         <v>4.950745610532072</v>
       </c>
       <c r="U58" t="n">
-        <v>10944.16634952406</v>
+        <v>10944.16634952407</v>
       </c>
     </row>
     <row r="59">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.616404415975891</v>
+        <v>0.6164044159758908</v>
       </c>
       <c r="F59" t="n">
-        <v>0.581120943952803</v>
+        <v>0.581120943952802</v>
       </c>
       <c r="G59" t="n">
         <v>0.816479400749064</v>
@@ -4739,19 +4739,19 @@
         <v>0.9538301727874866</v>
       </c>
       <c r="P59" t="n">
-        <v>0.297374353974967</v>
+        <v>0.2973743539749669</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.087712875993297e-05</v>
+        <v>3.087712875993296e-05</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01510398217189027</v>
+        <v>0.01510398217189026</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0002517330361981712</v>
+        <v>0.0002517330361981711</v>
       </c>
       <c r="T59" t="n">
-        <v>3.362764766474045</v>
+        <v>3.362764766474046</v>
       </c>
       <c r="U59" t="n">
         <v>8152.734606749675</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>GLM-5.2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4775,132 +4775,132 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>novita</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.7043078467074591</v>
+        <v>0.433101571936022</v>
       </c>
       <c r="F60" t="n">
-        <v>0.660766961651917</v>
+        <v>0.286135693215339</v>
       </c>
       <c r="G60" t="n">
-        <v>0.887640449438202</v>
+        <v>0.722846441947566</v>
       </c>
       <c r="H60" t="n">
-        <v>0.564516129032258</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="I60" t="n">
-        <v>9.183238026073614</v>
+        <v>1.909399563940522</v>
       </c>
       <c r="J60" t="n">
-        <v>1438.866784253578</v>
+        <v>1507.044470347651</v>
       </c>
       <c r="K60" t="n">
-        <v>25.38548057259714</v>
+        <v>127.4036879531512</v>
       </c>
       <c r="L60" t="n">
-        <v>7135668.150306755</v>
+        <v>10784557.42954308</v>
       </c>
       <c r="M60" t="n">
-        <v>3522976.932515338</v>
+        <v>5529735.922290388</v>
       </c>
       <c r="N60" t="n">
-        <v>101478.4161554192</v>
+        <v>28567.83231083845</v>
       </c>
       <c r="O60" t="n">
-        <v>0.9015196331153521</v>
+        <v>0.9451181301216958</v>
       </c>
       <c r="P60" t="n">
-        <v>0.07669493534935552</v>
+        <v>0.2268260557482317</v>
       </c>
       <c r="Q60" t="n">
-        <v>9.8702438492348e-05</v>
+        <v>4.01594200564586e-05</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02936927258653026</v>
+        <v>0.01724308394838989</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0004894878764421709</v>
+        <v>0.0002873847324731648</v>
       </c>
       <c r="T60" t="n">
-        <v>13.03867061683889</v>
+        <v>4.408664589706405</v>
       </c>
       <c r="U60" t="n">
-        <v>4959.227795371226</v>
+        <v>7156.097674447029</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.6263880112748013</v>
+        <v>0.4975760031619054</v>
       </c>
       <c r="F61" t="n">
-        <v>0.63716814159292</v>
+        <v>0.427728613569322</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8764044943820219</v>
+        <v>0.677902621722846</v>
       </c>
       <c r="H61" t="n">
-        <v>0.365591397849462</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="I61" t="n">
-        <v>3.081635541610432</v>
+        <v>0.05949917044417178</v>
       </c>
       <c r="J61" t="n">
-        <v>1447.373053169734</v>
+        <v>868.3750143149272</v>
       </c>
       <c r="K61" t="n">
-        <v>122.9498977505112</v>
+        <v>105.9314928425358</v>
       </c>
       <c r="L61" t="n">
-        <v>10383196.73788345</v>
+        <v>20844227.99386501</v>
       </c>
       <c r="M61" t="n">
-        <v>5296768.575664621</v>
+        <v>10443571.69734151</v>
       </c>
       <c r="N61" t="n">
-        <v>54498.01533742331</v>
+        <v>58411.25766871166</v>
       </c>
       <c r="O61" t="n">
-        <v>0.9500000000000018</v>
+        <v>0.9807621661364226</v>
       </c>
       <c r="P61" t="n">
-        <v>0.2032647932621705</v>
+        <v>8.362738496140583</v>
       </c>
       <c r="Q61" t="n">
-        <v>6.032708683920077e-05</v>
+        <v>2.387116487635592e-05</v>
       </c>
       <c r="R61" t="n">
-        <v>0.02596654718296781</v>
+        <v>0.03437980100483083</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0004327757863827968</v>
+        <v>0.0005729966834138472</v>
       </c>
       <c r="T61" t="n">
-        <v>4.919691127770474</v>
+        <v>0.1195780545405672</v>
       </c>
       <c r="U61" t="n">
-        <v>7173.822060003357</v>
+        <v>24003.71688527831</v>
       </c>
     </row>
     <row r="62">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GLM-5.2</t>
+          <t>Opus 5 (xhigh)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4921,497 +4921,497 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>novita</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.433101571936022</v>
+        <v>0.6814975428587517</v>
       </c>
       <c r="F62" t="n">
-        <v>0.286135693215339</v>
+        <v>0.6047197640117991</v>
       </c>
       <c r="G62" t="n">
-        <v>0.722846441947566</v>
+        <v>0.891385767790262</v>
       </c>
       <c r="H62" t="n">
-        <v>0.290322580645161</v>
+        <v>0.5483870967741939</v>
       </c>
       <c r="I62" t="n">
-        <v>1.909399563940518</v>
+        <v>8.170783921523505</v>
       </c>
       <c r="J62" t="n">
-        <v>1507.044470347651</v>
+        <v>1421.879982617589</v>
       </c>
       <c r="K62" t="n">
-        <v>127.4036879531512</v>
+        <v>152.0771983640082</v>
       </c>
       <c r="L62" t="n">
-        <v>10784557.42954308</v>
+        <v>21565879.13803684</v>
       </c>
       <c r="M62" t="n">
-        <v>5529735.922290388</v>
+        <v>10747525.6196319</v>
       </c>
       <c r="N62" t="n">
-        <v>28567.83231083845</v>
+        <v>73273.02862985685</v>
       </c>
       <c r="O62" t="n">
-        <v>0.9451181301216958</v>
+        <v>0.9740249879523308</v>
       </c>
       <c r="P62" t="n">
-        <v>0.2268260557482321</v>
+        <v>0.08340662896047817</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.015942005645859e-05</v>
+        <v>3.160073088125398e-05</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01724308394838989</v>
+        <v>0.02875759773778482</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0002873847324731648</v>
+        <v>0.000479293295629747</v>
       </c>
       <c r="T62" t="n">
-        <v>4.408664589706397</v>
+        <v>11.98945470477946</v>
       </c>
       <c r="U62" t="n">
-        <v>7156.097674447032</v>
+        <v>15167.15855183182</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.4975760031619054</v>
+        <v>0.6115009143224124</v>
       </c>
       <c r="F63" t="n">
-        <v>0.427728613569322</v>
+        <v>0.616519174041298</v>
       </c>
       <c r="G63" t="n">
-        <v>0.677902621722846</v>
+        <v>0.838951310861423</v>
       </c>
       <c r="H63" t="n">
-        <v>0.387096774193548</v>
+        <v>0.379032258064516</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05949917044417178</v>
+        <v>2.037777941104297</v>
       </c>
       <c r="J63" t="n">
-        <v>868.3750143149272</v>
+        <v>711.0750562372191</v>
       </c>
       <c r="K63" t="n">
-        <v>105.9314928425358</v>
+        <v>119.5439672801636</v>
       </c>
       <c r="L63" t="n">
-        <v>20844227.99386501</v>
+        <v>27777783.86094069</v>
       </c>
       <c r="M63" t="n">
-        <v>10443571.69734151</v>
+        <v>14366013.18404908</v>
       </c>
       <c r="N63" t="n">
-        <v>58411.25766871166</v>
+        <v>71460.62372188139</v>
       </c>
       <c r="O63" t="n">
-        <v>0.9807621661364226</v>
+        <v>0.883209569217322</v>
       </c>
       <c r="P63" t="n">
-        <v>8.362738496140583</v>
+        <v>0.3000822130752051</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.387116487635592e-05</v>
+        <v>2.201402809466975e-05</v>
       </c>
       <c r="R63" t="n">
-        <v>0.03437980100483083</v>
+        <v>0.05159800577662889</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005729966834138472</v>
+        <v>0.0008599667629438148</v>
       </c>
       <c r="T63" t="n">
-        <v>0.1195780545405672</v>
+        <v>3.332420104984313</v>
       </c>
       <c r="U63" t="n">
-        <v>24003.71688527831</v>
+        <v>39064.48920868046</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Opus 5 (xhigh)</t>
+          <t>Grok 4.5 (high)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.6814975428587517</v>
+        <v>0.6408998279698193</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6047197640117991</v>
+        <v>0.59882005899705</v>
       </c>
       <c r="G64" t="n">
-        <v>0.891385767790262</v>
+        <v>0.842696629213483</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5483870967741939</v>
+        <v>0.481182795698925</v>
       </c>
       <c r="I64" t="n">
-        <v>8.170783921523503</v>
+        <v>2.438982443762777</v>
       </c>
       <c r="J64" t="n">
-        <v>1421.879982617589</v>
+        <v>929.185109406954</v>
       </c>
       <c r="K64" t="n">
-        <v>152.0771983640082</v>
+        <v>60.74437627811862</v>
       </c>
       <c r="L64" t="n">
-        <v>21565879.13803681</v>
+        <v>3598867.582822087</v>
       </c>
       <c r="M64" t="n">
-        <v>10747525.6196319</v>
+        <v>1837535.160531697</v>
       </c>
       <c r="N64" t="n">
-        <v>73273.02862985685</v>
+        <v>25699.40797546012</v>
       </c>
       <c r="O64" t="n">
-        <v>0.9740249879523305</v>
+        <v>0.9238990226060748</v>
       </c>
       <c r="P64" t="n">
-        <v>0.08340662896047819</v>
+        <v>0.2627734486604427</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.160073088125403e-05</v>
+        <v>0.0001780837480736792</v>
       </c>
       <c r="R64" t="n">
-        <v>0.02875759773778482</v>
+        <v>0.04138463831252327</v>
       </c>
       <c r="S64" t="n">
-        <v>0.000479293295629747</v>
+        <v>0.0006897439718753878</v>
       </c>
       <c r="T64" t="n">
-        <v>11.98945470477946</v>
+        <v>3.805559523223389</v>
       </c>
       <c r="U64" t="n">
-        <v>15167.15855183179</v>
+        <v>3873.143840110653</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.6115009143224124</v>
+        <v>0.669713903153459</v>
       </c>
       <c r="F65" t="n">
-        <v>0.616519174041298</v>
+        <v>0.669616519174041</v>
       </c>
       <c r="G65" t="n">
-        <v>0.838951310861423</v>
+        <v>0.831460674157304</v>
       </c>
       <c r="H65" t="n">
-        <v>0.379032258064516</v>
+        <v>0.508064516129032</v>
       </c>
       <c r="I65" t="n">
-        <v>2.037777941104297</v>
+        <v>4.717329430604448</v>
       </c>
       <c r="J65" t="n">
-        <v>711.0750562372191</v>
+        <v>1609.089816462168</v>
       </c>
       <c r="K65" t="n">
-        <v>119.5439672801636</v>
+        <v>29.18660531697342</v>
       </c>
       <c r="L65" t="n">
-        <v>27777783.86094069</v>
+        <v>4035764.689496798</v>
       </c>
       <c r="M65" t="n">
-        <v>14366013.18404908</v>
+        <v>2061908.266988501</v>
       </c>
       <c r="N65" t="n">
-        <v>71460.62372188139</v>
+        <v>31575.50107278152</v>
       </c>
       <c r="O65" t="n">
-        <v>0.8832095692173221</v>
+        <v>0.9133755788574925</v>
       </c>
       <c r="P65" t="n">
-        <v>0.3000822130752051</v>
+        <v>0.1419688645886336</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.201402809466975e-05</v>
+        <v>0.0001659447353054082</v>
       </c>
       <c r="R65" t="n">
-        <v>0.05159800577662889</v>
+        <v>0.02497239978657978</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0008599667629438148</v>
+        <v>0.0004162066631096631</v>
       </c>
       <c r="T65" t="n">
-        <v>3.332420104984313</v>
+        <v>7.043797968643206</v>
       </c>
       <c r="U65" t="n">
-        <v>39064.48920868046</v>
+        <v>2508.104052494751</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Grok 4.5 (high)</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.6408998279698193</v>
+        <v>0.641775036414302</v>
       </c>
       <c r="F66" t="n">
-        <v>0.59882005899705</v>
+        <v>0.669616519174041</v>
       </c>
       <c r="G66" t="n">
-        <v>0.842696629213483</v>
+        <v>0.820224719101123</v>
       </c>
       <c r="H66" t="n">
-        <v>0.481182795698925</v>
+        <v>0.435483870967742</v>
       </c>
       <c r="I66" t="n">
-        <v>2.438982443762777</v>
+        <v>1.615020825613495</v>
       </c>
       <c r="J66" t="n">
-        <v>929.1851094069543</v>
+        <v>769.975962167688</v>
       </c>
       <c r="K66" t="n">
-        <v>60.74437627811862</v>
+        <v>130.7924335378323</v>
       </c>
       <c r="L66" t="n">
-        <v>3598867.582822083</v>
+        <v>14753563.55112474</v>
       </c>
       <c r="M66" t="n">
-        <v>1837535.160531697</v>
+        <v>7495698.047034764</v>
       </c>
       <c r="N66" t="n">
-        <v>25699.40797546012</v>
+        <v>42813.14417177914</v>
       </c>
       <c r="O66" t="n">
-        <v>0.9238990226060743</v>
+        <v>0.9474470984376897</v>
       </c>
       <c r="P66" t="n">
-        <v>0.2627734486604427</v>
+        <v>0.3973787992303517</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.0001780837480736794</v>
+        <v>4.349966258595037e-05</v>
       </c>
       <c r="R66" t="n">
-        <v>0.04138463831252326</v>
+        <v>0.05001000560647638</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0006897439718753876</v>
+        <v>0.000833500093441273</v>
       </c>
       <c r="T66" t="n">
-        <v>3.805559523223388</v>
+        <v>2.516490567531063</v>
       </c>
       <c r="U66" t="n">
-        <v>3873.143840110648</v>
+        <v>19161.07031392191</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.6697139031534587</v>
+        <v>0.6263880112748013</v>
       </c>
       <c r="F67" t="n">
-        <v>0.669616519174041</v>
+        <v>0.63716814159292</v>
       </c>
       <c r="G67" t="n">
-        <v>0.831460674157303</v>
+        <v>0.8764044943820219</v>
       </c>
       <c r="H67" t="n">
-        <v>0.508064516129032</v>
+        <v>0.365591397849462</v>
       </c>
       <c r="I67" t="n">
-        <v>4.717329430604444</v>
+        <v>3.081635541610432</v>
       </c>
       <c r="J67" t="n">
-        <v>1609.089816462168</v>
+        <v>1447.373053169734</v>
       </c>
       <c r="K67" t="n">
-        <v>29.18660531697342</v>
+        <v>122.9498977505112</v>
       </c>
       <c r="L67" t="n">
-        <v>4035764.689496797</v>
+        <v>10383196.73788345</v>
       </c>
       <c r="M67" t="n">
-        <v>2061908.266988501</v>
+        <v>5296768.575664621</v>
       </c>
       <c r="N67" t="n">
-        <v>31575.50107278152</v>
+        <v>54498.01533742331</v>
       </c>
       <c r="O67" t="n">
-        <v>0.9133755788574922</v>
+        <v>0.9500000000000018</v>
       </c>
       <c r="P67" t="n">
-        <v>0.1419688645886337</v>
+        <v>0.2032647932621705</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.0001659447353054082</v>
+        <v>6.032708683920077e-05</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02497239978657977</v>
+        <v>0.02596654718296781</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004162066631096628</v>
+        <v>0.0004327757863827968</v>
       </c>
       <c r="T67" t="n">
-        <v>7.043797968643204</v>
+        <v>4.919691127770474</v>
       </c>
       <c r="U67" t="n">
-        <v>2508.10405249475</v>
+        <v>7173.822060003357</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.6417750364143022</v>
+        <v>0.7043078467074591</v>
       </c>
       <c r="F68" t="n">
-        <v>0.669616519174041</v>
+        <v>0.660766961651917</v>
       </c>
       <c r="G68" t="n">
-        <v>0.820224719101124</v>
+        <v>0.887640449438202</v>
       </c>
       <c r="H68" t="n">
-        <v>0.435483870967742</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="I68" t="n">
-        <v>1.615020825613495</v>
+        <v>9.183238026073614</v>
       </c>
       <c r="J68" t="n">
-        <v>769.975962167688</v>
+        <v>1438.866784253578</v>
       </c>
       <c r="K68" t="n">
-        <v>130.7924335378323</v>
+        <v>25.38548057259714</v>
       </c>
       <c r="L68" t="n">
-        <v>14753563.55112475</v>
+        <v>7135668.150306755</v>
       </c>
       <c r="M68" t="n">
-        <v>7495698.047034764</v>
+        <v>3522976.932515338</v>
       </c>
       <c r="N68" t="n">
-        <v>42813.14417177914</v>
+        <v>101478.4161554192</v>
       </c>
       <c r="O68" t="n">
-        <v>0.9474470984376897</v>
+        <v>0.9015196331153518</v>
       </c>
       <c r="P68" t="n">
-        <v>0.3973787992303519</v>
+        <v>0.07669493534935552</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.349966258595037e-05</v>
+        <v>9.8702438492348e-05</v>
       </c>
       <c r="R68" t="n">
-        <v>0.05001000560647639</v>
+        <v>0.02936927258653026</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0008335000934412733</v>
+        <v>0.0004894878764421709</v>
       </c>
       <c r="T68" t="n">
-        <v>2.516490567531062</v>
+        <v>13.03867061683889</v>
       </c>
       <c r="U68" t="n">
-        <v>19161.07031392191</v>
+        <v>4959.227795371226</v>
       </c>
     </row>
     <row r="69">
@@ -5448,7 +5448,7 @@
         <v>0.3118279569892475</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5573437730061347</v>
+        <v>0.5573437730061354</v>
       </c>
       <c r="J69" t="n">
         <v>472.3722024539875</v>
@@ -5457,7 +5457,7 @@
         <v>116.8680981595092</v>
       </c>
       <c r="L69" t="n">
-        <v>4259887.413087938</v>
+        <v>4259887.413087934</v>
       </c>
       <c r="M69" t="n">
         <v>2153033.982617587</v>
@@ -5469,10 +5469,10 @@
         <v>0.9355410155352533</v>
       </c>
       <c r="P69" t="n">
-        <v>0.6872016098268293</v>
+        <v>0.6872016098268284</v>
       </c>
       <c r="Q69" t="n">
-        <v>8.991024900330346e-05</v>
+        <v>8.991024900330353e-05</v>
       </c>
       <c r="R69" t="n">
         <v>0.04864903599920222</v>
@@ -5481,10 +5481,10 @@
         <v>0.0008108172666533704</v>
       </c>
       <c r="T69" t="n">
-        <v>1.455177033493845</v>
+        <v>1.455177033493847</v>
       </c>
       <c r="U69" t="n">
-        <v>9018.073864121761</v>
+        <v>9018.073864121752</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coding Agents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coding Agents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
